--- a/atlas_max_plus_to_poly_mapping_template.xlsx
+++ b/atlas_max_plus_to_poly_mapping_template.xlsx
@@ -8,37 +8,39 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raeltonhonorio/Documents/KDAM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF40927-4600-5740-B9F5-8B8208C257D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E165D97-2723-EF49-8ADA-96FC3A6EBB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Plus_to_Poly_Mapping" sheetId="2" r:id="rId2"/>
     <sheet name="Poly_to_Plus_Mapping" sheetId="11" r:id="rId3"/>
-    <sheet name="AVHD6_to_Plus" sheetId="15" r:id="rId4"/>
-    <sheet name="Poly_Setups" sheetId="5" r:id="rId5"/>
-    <sheet name="Poly_Media" sheetId="6" r:id="rId6"/>
-    <sheet name="Poly_Output_ICCs" sheetId="7" r:id="rId7"/>
-    <sheet name="Plus_Setups" sheetId="8" r:id="rId8"/>
-    <sheet name="Plus Media" sheetId="9" r:id="rId9"/>
-    <sheet name="Plus_Output_ICCs" sheetId="10" r:id="rId10"/>
-    <sheet name="AVHD6 MEDIA" sheetId="12" r:id="rId11"/>
+    <sheet name="AVHD6_TO_PLUS" sheetId="15" r:id="rId4"/>
+    <sheet name="MAX_TO_POLY" sheetId="16" r:id="rId5"/>
+    <sheet name="Poly_Setups" sheetId="5" r:id="rId6"/>
+    <sheet name="Poly_Media" sheetId="6" r:id="rId7"/>
+    <sheet name="Poly_Output_ICCs" sheetId="7" r:id="rId8"/>
+    <sheet name="Plus_Setups" sheetId="8" r:id="rId9"/>
+    <sheet name="Plus Media" sheetId="9" r:id="rId10"/>
+    <sheet name="Plus_Output_ICCs" sheetId="10" r:id="rId11"/>
     <sheet name="AVHD6 SETUPS" sheetId="13" r:id="rId12"/>
-    <sheet name="AVHD6_OUTPUT_ICC" sheetId="14" r:id="rId13"/>
+    <sheet name="AVHD6 MEDIA" sheetId="12" r:id="rId13"/>
+    <sheet name="AVHD6_OUTPUT_ICC" sheetId="14" r:id="rId14"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'AVHD6 MEDIA'!$A$1:$A$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'AVHD6 MEDIA'!$A$1:$A$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'AVHD6 SETUPS'!$A$1:$A$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">AVHD6_OUTPUT_ICC!$A$1:$B$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">AVHD6_to_Plus!$A$1:$J$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Plus Media'!$A$1:$A$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">Plus_Output_ICCs!$A$1:$A$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Plus_Setups!$A$1:$A$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">AVHD6_OUTPUT_ICC!$A$1:$B$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">AVHD6_TO_PLUS!$A$1:$J$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">MAX_TO_POLY!$A$1:$J$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Plus Media'!$A$1:$A$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">Plus_Output_ICCs!$A$1:$A$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Plus_Setups!$A$1:$A$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Plus_to_Poly_Mapping!$A$1:$J$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Poly_Media!$A$1:$C$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Poly_Output_ICCs!$A$1:$A$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Poly_Setups!$A$1:$B$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Poly_Media!$A$1:$C$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Poly_Output_ICCs!$A$1:$A$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Poly_Setups!$A$1:$B$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Poly_to_Plus_Mapping!$A$1:$J$44</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -46,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="330">
   <si>
     <t>Atlas Max Plus → Atlas Max Poly Mapping Workbook</t>
   </si>
@@ -1024,6 +1026,18 @@
   </si>
   <si>
     <t>ATL Poly UltraHQ icm</t>
+  </si>
+  <si>
+    <t>MAX_BASE_SETUP</t>
+  </si>
+  <si>
+    <t>MAX_MEDIA</t>
+  </si>
+  <si>
+    <t>MAX_OUTPUT_ICC</t>
+  </si>
+  <si>
+    <t>MAX_INPUT_RGB</t>
   </si>
 </sst>
 </file>
@@ -1388,7 +1402,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="157">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1591,12 +1605,6 @@
     <xf numFmtId="0" fontId="14" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1619,17 +1627,20 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1804,10 +1815,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="68.25" customHeight="1">
-      <c r="A1" s="128" t="s">
+      <c r="A1" s="152" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="129"/>
+      <c r="B1" s="153"/>
     </row>
     <row r="2" spans="1:2" ht="45.5" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -1866,6 +1877,125 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2EAD9B5-EDDD-BA49-A0DC-91F6C002BCB0}">
+  <sheetPr filterMode="1">
+    <tabColor theme="9" tint="0.39997558519241921"/>
+  </sheetPr>
+  <dimension ref="A1:A19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="33.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="18">
+      <c r="A1" s="5" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="16" hidden="1">
+      <c r="A2" s="4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="16" hidden="1">
+      <c r="A3" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="16" hidden="1">
+      <c r="A4" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="16" hidden="1">
+      <c r="A5" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="16" hidden="1">
+      <c r="A6" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="16" hidden="1">
+      <c r="A7" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="16" hidden="1">
+      <c r="A8" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="16" hidden="1">
+      <c r="A9" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="16" hidden="1">
+      <c r="A10" s="4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="16" hidden="1">
+      <c r="A11" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="16" hidden="1">
+      <c r="A12" s="4" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="16" hidden="1">
+      <c r="A13" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="16" hidden="1">
+      <c r="A14" s="4" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="16" hidden="1">
+      <c r="A15" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="16">
+      <c r="A16" s="4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="16">
+      <c r="A17" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="16" hidden="1">
+      <c r="A18" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="16" hidden="1">
+      <c r="A19" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:A19" xr:uid="{D2EAD9B5-EDDD-BA49-A0DC-91F6C002BCB0}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Atlas MAX+ XDi Extra High Density"/>
+        <filter val="Atlas MAX+ XDi High Density"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{869A1179-B4DD-1849-B576-03864D6D4F7F}">
   <sheetPr>
     <tabColor theme="9" tint="0.39997558519241921"/>
@@ -2098,103 +2228,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:A44" xr:uid="{869A1179-B4DD-1849-B576-03864D6D4F7F}"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6649CACF-ACCD-FB40-AE6B-8E1F74CC0FEA}">
-  <sheetPr>
-    <tabColor rgb="FFFFFF00"/>
-  </sheetPr>
-  <dimension ref="A1:A16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
-  <cols>
-    <col min="1" max="1" width="44" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" ht="18">
-      <c r="A1" s="5" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>295</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:A16" xr:uid="{6649CACF-ACCD-FB40-AE6B-8E1F74CC0FEA}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2267,6 +2300,103 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6649CACF-ACCD-FB40-AE6B-8E1F74CC0FEA}">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+  </sheetPr>
+  <dimension ref="A1:A16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="44" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="18">
+      <c r="A1" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>295</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:A16" xr:uid="{6649CACF-ACCD-FB40-AE6B-8E1F74CC0FEA}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13E8489B-0C4E-0C4F-874E-AE2C83D835E4}">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
@@ -3251,7 +3381,7 @@
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
-  <dimension ref="A1:J92"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="38.83203125" style="97" bestFit="1" customWidth="1"/>
@@ -3570,16 +3700,16 @@
         <v>200</v>
       </c>
       <c r="E12" s="102"/>
-      <c r="G12" s="130" t="s">
+      <c r="G12" s="128" t="s">
         <v>182</v>
       </c>
-      <c r="H12" s="131" t="s">
+      <c r="H12" s="129" t="s">
         <v>182</v>
       </c>
-      <c r="I12" s="132" t="s">
+      <c r="I12" s="130" t="s">
         <v>232</v>
       </c>
-      <c r="J12" s="133" t="s">
+      <c r="J12" s="131" t="s">
         <v>200</v>
       </c>
     </row>
@@ -3597,16 +3727,16 @@
         <v>200</v>
       </c>
       <c r="E13" s="104"/>
-      <c r="G13" s="135" t="s">
+      <c r="G13" s="133" t="s">
         <v>191</v>
       </c>
-      <c r="H13" s="136" t="s">
+      <c r="H13" s="134" t="s">
         <v>191</v>
       </c>
-      <c r="I13" s="137" t="s">
+      <c r="I13" s="135" t="s">
         <v>245</v>
       </c>
-      <c r="J13" s="138" t="s">
+      <c r="J13" s="136" t="s">
         <v>201</v>
       </c>
     </row>
@@ -3678,16 +3808,16 @@
         <v>200</v>
       </c>
       <c r="E16" s="103"/>
-      <c r="G16" s="130" t="s">
+      <c r="G16" s="128" t="s">
         <v>182</v>
       </c>
-      <c r="H16" s="131" t="s">
+      <c r="H16" s="129" t="s">
         <v>182</v>
       </c>
-      <c r="I16" s="132" t="s">
+      <c r="I16" s="130" t="s">
         <v>232</v>
       </c>
-      <c r="J16" s="133" t="s">
+      <c r="J16" s="131" t="s">
         <v>200</v>
       </c>
     </row>
@@ -3714,7 +3844,7 @@
       <c r="I17" s="49" t="s">
         <v>210</v>
       </c>
-      <c r="J17" s="139" t="s">
+      <c r="J17" s="137" t="s">
         <v>201</v>
       </c>
     </row>
@@ -3759,16 +3889,16 @@
         <v>201</v>
       </c>
       <c r="E19" s="103"/>
-      <c r="G19" s="140" t="s">
+      <c r="G19" s="138" t="s">
         <v>182</v>
       </c>
-      <c r="H19" s="141" t="s">
+      <c r="H19" s="139" t="s">
         <v>182</v>
       </c>
-      <c r="I19" s="141" t="s">
+      <c r="I19" s="139" t="s">
         <v>211</v>
       </c>
-      <c r="J19" s="142" t="s">
+      <c r="J19" s="140" t="s">
         <v>201</v>
       </c>
     </row>
@@ -3786,16 +3916,16 @@
         <v>201</v>
       </c>
       <c r="E20" s="103"/>
-      <c r="G20" s="140" t="s">
+      <c r="G20" s="138" t="s">
         <v>182</v>
       </c>
-      <c r="H20" s="141" t="s">
+      <c r="H20" s="139" t="s">
         <v>182</v>
       </c>
-      <c r="I20" s="141" t="s">
+      <c r="I20" s="139" t="s">
         <v>211</v>
       </c>
-      <c r="J20" s="142" t="s">
+      <c r="J20" s="140" t="s">
         <v>201</v>
       </c>
     </row>
@@ -3840,16 +3970,16 @@
         <v>201</v>
       </c>
       <c r="E22" s="102"/>
-      <c r="G22" s="146" t="s">
+      <c r="G22" s="144" t="s">
         <v>195</v>
       </c>
-      <c r="H22" s="147" t="s">
+      <c r="H22" s="145" t="s">
         <v>195</v>
       </c>
-      <c r="I22" s="148" t="s">
+      <c r="I22" s="146" t="s">
         <v>232</v>
       </c>
-      <c r="J22" s="149" t="s">
+      <c r="J22" s="147" t="s">
         <v>200</v>
       </c>
     </row>
@@ -3894,16 +4024,16 @@
         <v>24</v>
       </c>
       <c r="E24" s="103"/>
-      <c r="G24" s="130" t="s">
+      <c r="G24" s="128" t="s">
         <v>182</v>
       </c>
-      <c r="H24" s="131" t="s">
+      <c r="H24" s="129" t="s">
         <v>182</v>
       </c>
-      <c r="I24" s="132" t="s">
+      <c r="I24" s="130" t="s">
         <v>232</v>
       </c>
-      <c r="J24" s="133" t="s">
+      <c r="J24" s="131" t="s">
         <v>200</v>
       </c>
     </row>
@@ -3921,16 +4051,16 @@
         <v>24</v>
       </c>
       <c r="E25" s="103"/>
-      <c r="G25" s="130" t="s">
+      <c r="G25" s="128" t="s">
         <v>182</v>
       </c>
-      <c r="H25" s="131" t="s">
+      <c r="H25" s="129" t="s">
         <v>182</v>
       </c>
-      <c r="I25" s="132" t="s">
+      <c r="I25" s="130" t="s">
         <v>232</v>
       </c>
-      <c r="J25" s="133" t="s">
+      <c r="J25" s="131" t="s">
         <v>200</v>
       </c>
     </row>
@@ -4021,16 +4151,16 @@
         <v>24</v>
       </c>
       <c r="E29" s="102"/>
-      <c r="G29" s="143" t="s">
+      <c r="G29" s="141" t="s">
         <v>182</v>
       </c>
-      <c r="H29" s="144" t="s">
+      <c r="H29" s="142" t="s">
         <v>182</v>
       </c>
-      <c r="I29" s="134" t="s">
+      <c r="I29" s="132" t="s">
         <v>232</v>
       </c>
-      <c r="J29" s="145" t="s">
+      <c r="J29" s="143" t="s">
         <v>200</v>
       </c>
     </row>
@@ -4048,16 +4178,16 @@
         <v>24</v>
       </c>
       <c r="E30" s="103"/>
-      <c r="G30" s="143" t="s">
+      <c r="G30" s="141" t="s">
         <v>182</v>
       </c>
-      <c r="H30" s="144" t="s">
+      <c r="H30" s="142" t="s">
         <v>182</v>
       </c>
-      <c r="I30" s="134" t="s">
+      <c r="I30" s="132" t="s">
         <v>232</v>
       </c>
-      <c r="J30" s="145" t="s">
+      <c r="J30" s="143" t="s">
         <v>200</v>
       </c>
     </row>
@@ -4129,16 +4259,16 @@
         <v>201</v>
       </c>
       <c r="E33" s="104"/>
-      <c r="G33" s="140" t="s">
+      <c r="G33" s="138" t="s">
         <v>182</v>
       </c>
-      <c r="H33" s="141" t="s">
+      <c r="H33" s="139" t="s">
         <v>182</v>
       </c>
-      <c r="I33" s="141" t="s">
+      <c r="I33" s="139" t="s">
         <v>211</v>
       </c>
-      <c r="J33" s="142" t="s">
+      <c r="J33" s="140" t="s">
         <v>201</v>
       </c>
     </row>
@@ -4156,16 +4286,16 @@
         <v>201</v>
       </c>
       <c r="E34" s="104"/>
-      <c r="G34" s="140" t="s">
+      <c r="G34" s="138" t="s">
         <v>182</v>
       </c>
-      <c r="H34" s="141" t="s">
+      <c r="H34" s="139" t="s">
         <v>182</v>
       </c>
-      <c r="I34" s="141" t="s">
+      <c r="I34" s="139" t="s">
         <v>211</v>
       </c>
-      <c r="J34" s="142" t="s">
+      <c r="J34" s="140" t="s">
         <v>201</v>
       </c>
     </row>
@@ -4200,16 +4330,16 @@
         <v>201</v>
       </c>
       <c r="E36" s="104"/>
-      <c r="G36" s="146" t="s">
+      <c r="G36" s="144" t="s">
         <v>195</v>
       </c>
-      <c r="H36" s="147" t="s">
+      <c r="H36" s="145" t="s">
         <v>195</v>
       </c>
-      <c r="I36" s="148" t="s">
+      <c r="I36" s="146" t="s">
         <v>232</v>
       </c>
-      <c r="J36" s="149" t="s">
+      <c r="J36" s="147" t="s">
         <v>200</v>
       </c>
     </row>
@@ -4227,16 +4357,16 @@
         <v>201</v>
       </c>
       <c r="E37" s="104"/>
-      <c r="G37" s="143" t="s">
+      <c r="G37" s="141" t="s">
         <v>182</v>
       </c>
-      <c r="H37" s="144" t="s">
+      <c r="H37" s="142" t="s">
         <v>182</v>
       </c>
-      <c r="I37" s="134" t="s">
+      <c r="I37" s="132" t="s">
         <v>232</v>
       </c>
-      <c r="J37" s="145" t="s">
+      <c r="J37" s="143" t="s">
         <v>200</v>
       </c>
     </row>
@@ -4308,16 +4438,16 @@
         <v>201</v>
       </c>
       <c r="E40" s="104"/>
-      <c r="G40" s="143" t="s">
+      <c r="G40" s="141" t="s">
         <v>182</v>
       </c>
-      <c r="H40" s="144" t="s">
+      <c r="H40" s="142" t="s">
         <v>182</v>
       </c>
-      <c r="I40" s="134" t="s">
+      <c r="I40" s="132" t="s">
         <v>232</v>
       </c>
-      <c r="J40" s="145" t="s">
+      <c r="J40" s="143" t="s">
         <v>200</v>
       </c>
     </row>
@@ -4335,16 +4465,16 @@
         <v>201</v>
       </c>
       <c r="E41" s="104"/>
-      <c r="G41" s="143" t="s">
+      <c r="G41" s="141" t="s">
         <v>182</v>
       </c>
-      <c r="H41" s="144" t="s">
+      <c r="H41" s="142" t="s">
         <v>182</v>
       </c>
-      <c r="I41" s="134" t="s">
+      <c r="I41" s="132" t="s">
         <v>232</v>
       </c>
-      <c r="J41" s="145" t="s">
+      <c r="J41" s="143" t="s">
         <v>200</v>
       </c>
     </row>
@@ -4389,16 +4519,16 @@
         <v>201</v>
       </c>
       <c r="E43" s="104"/>
-      <c r="G43" s="143" t="s">
+      <c r="G43" s="141" t="s">
         <v>182</v>
       </c>
-      <c r="H43" s="144" t="s">
+      <c r="H43" s="142" t="s">
         <v>182</v>
       </c>
-      <c r="I43" s="134" t="s">
+      <c r="I43" s="132" t="s">
         <v>232</v>
       </c>
-      <c r="J43" s="145" t="s">
+      <c r="J43" s="143" t="s">
         <v>200</v>
       </c>
     </row>
@@ -4432,10 +4562,10 @@
     <row r="45" spans="1:10" ht="16">
       <c r="A45" s="98"/>
       <c r="E45" s="93"/>
-      <c r="G45" s="150"/>
-      <c r="H45" s="151"/>
-      <c r="I45" s="151"/>
-      <c r="J45" s="152"/>
+      <c r="G45" s="148"/>
+      <c r="H45" s="149"/>
+      <c r="I45" s="149"/>
+      <c r="J45" s="150"/>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="98"/>
@@ -4479,334 +4609,165 @@
       <c r="J51" s="101"/>
     </row>
     <row r="53" spans="1:10" ht="16">
-      <c r="G53" s="153"/>
-      <c r="H53" s="153"/>
-      <c r="I53" s="153"/>
-      <c r="J53" s="153"/>
+      <c r="G53" s="149"/>
+      <c r="H53" s="149"/>
+      <c r="I53" s="149"/>
+      <c r="J53" s="149"/>
     </row>
     <row r="54" spans="1:10" ht="16">
-      <c r="G54" s="153"/>
-      <c r="H54" s="153"/>
-      <c r="I54" s="154"/>
-      <c r="J54" s="153"/>
+      <c r="G54" s="149"/>
+      <c r="H54" s="149"/>
+      <c r="J54" s="149"/>
     </row>
     <row r="55" spans="1:10" ht="16">
-      <c r="G55" s="153"/>
-      <c r="H55" s="153"/>
-      <c r="I55" s="154"/>
-      <c r="J55" s="153"/>
+      <c r="G55" s="149"/>
+      <c r="H55" s="149"/>
+      <c r="J55" s="149"/>
     </row>
     <row r="56" spans="1:10" ht="16">
-      <c r="G56" s="153"/>
-      <c r="H56" s="153"/>
-      <c r="I56" s="154"/>
-      <c r="J56" s="153"/>
+      <c r="G56" s="149"/>
+      <c r="H56" s="149"/>
+      <c r="J56" s="149"/>
     </row>
     <row r="57" spans="1:10" ht="16">
-      <c r="G57" s="153"/>
-      <c r="H57" s="153"/>
-      <c r="I57" s="154"/>
-      <c r="J57" s="153"/>
+      <c r="G57" s="149"/>
+      <c r="H57" s="149"/>
+      <c r="J57" s="149"/>
     </row>
     <row r="58" spans="1:10" ht="16">
-      <c r="G58" s="153"/>
-      <c r="H58" s="153"/>
-      <c r="I58" s="153"/>
-      <c r="J58" s="153"/>
+      <c r="G58" s="149"/>
+      <c r="H58" s="149"/>
+      <c r="I58" s="149"/>
+      <c r="J58" s="149"/>
     </row>
     <row r="59" spans="1:10" ht="16">
-      <c r="G59" s="153"/>
-      <c r="H59" s="153"/>
-      <c r="I59" s="153"/>
-      <c r="J59" s="153"/>
+      <c r="G59" s="149"/>
+      <c r="H59" s="149"/>
+      <c r="I59" s="149"/>
+      <c r="J59" s="149"/>
     </row>
     <row r="60" spans="1:10" ht="16">
-      <c r="G60" s="153"/>
-      <c r="H60" s="153"/>
-      <c r="I60" s="153"/>
-      <c r="J60" s="153"/>
+      <c r="G60" s="149"/>
+      <c r="H60" s="149"/>
+      <c r="I60" s="149"/>
+      <c r="J60" s="149"/>
     </row>
     <row r="61" spans="1:10" ht="16">
-      <c r="G61" s="153"/>
-      <c r="H61" s="153"/>
-      <c r="I61" s="153"/>
-      <c r="J61" s="153"/>
+      <c r="G61" s="149"/>
+      <c r="H61" s="149"/>
+      <c r="I61" s="149"/>
+      <c r="J61" s="149"/>
     </row>
     <row r="62" spans="1:10" ht="16">
-      <c r="G62" s="153"/>
-      <c r="H62" s="153"/>
-      <c r="I62" s="153"/>
-      <c r="J62" s="153"/>
+      <c r="G62" s="149"/>
+      <c r="H62" s="149"/>
+      <c r="I62" s="149"/>
+      <c r="J62" s="149"/>
     </row>
     <row r="63" spans="1:10" ht="16">
-      <c r="G63" s="153"/>
-      <c r="H63" s="153"/>
-      <c r="I63" s="153"/>
-      <c r="J63" s="153"/>
+      <c r="G63" s="149"/>
+      <c r="H63" s="149"/>
+      <c r="I63" s="149"/>
+      <c r="J63" s="149"/>
     </row>
     <row r="64" spans="1:10" ht="16">
-      <c r="G64" s="153"/>
-      <c r="H64" s="153"/>
-      <c r="I64" s="153"/>
-      <c r="J64" s="153"/>
-    </row>
-    <row r="65" spans="1:10" ht="16">
-      <c r="G65" s="153"/>
-      <c r="H65" s="153"/>
-      <c r="I65" s="154"/>
-      <c r="J65" s="155"/>
-    </row>
-    <row r="66" spans="1:10" ht="16">
-      <c r="G66" s="153"/>
-      <c r="H66" s="153"/>
-      <c r="I66" s="154"/>
-      <c r="J66" s="155"/>
-    </row>
-    <row r="67" spans="1:10" ht="16">
-      <c r="G67" s="153"/>
-      <c r="H67" s="153"/>
-      <c r="I67" s="154"/>
-      <c r="J67" s="155"/>
-    </row>
-    <row r="68" spans="1:10" ht="16">
-      <c r="G68" s="153"/>
-      <c r="H68" s="153"/>
-      <c r="I68" s="154"/>
-      <c r="J68" s="153"/>
-    </row>
-    <row r="69" spans="1:10" ht="16">
-      <c r="G69" s="153"/>
-      <c r="H69" s="153"/>
-      <c r="I69" s="154"/>
-      <c r="J69" s="153"/>
-    </row>
-    <row r="70" spans="1:10" ht="16">
-      <c r="G70" s="153"/>
-      <c r="H70" s="153"/>
-      <c r="I70" s="154"/>
-      <c r="J70" s="154"/>
-    </row>
-    <row r="71" spans="1:10" ht="16">
-      <c r="G71" s="153"/>
-      <c r="H71" s="153"/>
-      <c r="I71" s="154"/>
-      <c r="J71" s="154"/>
-    </row>
-    <row r="72" spans="1:10" ht="16">
-      <c r="G72" s="153"/>
-      <c r="H72" s="153"/>
-      <c r="I72" s="153"/>
-      <c r="J72" s="153"/>
-    </row>
-    <row r="73" spans="1:10" ht="16">
-      <c r="G73" s="153"/>
-      <c r="H73" s="153"/>
-      <c r="I73" s="153"/>
-      <c r="J73" s="153"/>
-    </row>
-    <row r="74" spans="1:10" ht="16">
-      <c r="G74" s="153"/>
-      <c r="H74" s="153"/>
-      <c r="I74" s="153"/>
-      <c r="J74" s="153"/>
-    </row>
-    <row r="75" spans="1:10" ht="16">
-      <c r="G75" s="153"/>
-      <c r="H75" s="153"/>
-      <c r="I75" s="153"/>
-      <c r="J75" s="153"/>
-    </row>
-    <row r="76" spans="1:10" ht="16">
-      <c r="G76" s="153"/>
-      <c r="H76" s="153"/>
-      <c r="I76" s="154"/>
-      <c r="J76" s="154"/>
-    </row>
-    <row r="77" spans="1:10" ht="16">
-      <c r="G77" s="153"/>
-      <c r="H77" s="153"/>
-      <c r="I77" s="154"/>
-      <c r="J77" s="154"/>
-    </row>
-    <row r="78" spans="1:10" s="156" customFormat="1" ht="16">
-      <c r="A78" s="154"/>
-      <c r="B78" s="154"/>
-      <c r="C78" s="154"/>
-      <c r="D78" s="154"/>
-      <c r="E78" s="154"/>
-      <c r="F78" s="154"/>
-      <c r="G78" s="153"/>
-      <c r="H78" s="153"/>
-      <c r="I78" s="154"/>
-      <c r="J78" s="153"/>
-    </row>
-    <row r="79" spans="1:10" s="156" customFormat="1" ht="16">
-      <c r="A79" s="154"/>
-      <c r="B79" s="154"/>
-      <c r="C79" s="154"/>
-      <c r="D79" s="154"/>
-      <c r="E79" s="154"/>
-      <c r="F79" s="154"/>
-      <c r="G79" s="153"/>
-      <c r="H79" s="153"/>
-      <c r="I79" s="154"/>
-      <c r="J79" s="154"/>
-    </row>
-    <row r="80" spans="1:10" s="156" customFormat="1" ht="16">
-      <c r="A80" s="154"/>
-      <c r="B80" s="154"/>
-      <c r="C80" s="154"/>
-      <c r="D80" s="154"/>
-      <c r="E80" s="154"/>
-      <c r="F80" s="154"/>
-      <c r="G80" s="153"/>
-      <c r="H80" s="153"/>
-      <c r="I80" s="153"/>
-      <c r="J80" s="153"/>
-    </row>
-    <row r="81" spans="1:10" s="156" customFormat="1" ht="16">
-      <c r="A81" s="154"/>
-      <c r="B81" s="154"/>
-      <c r="C81" s="154"/>
-      <c r="D81" s="154"/>
-      <c r="E81" s="154"/>
-      <c r="F81" s="154"/>
-      <c r="G81" s="153"/>
-      <c r="H81" s="153"/>
-      <c r="I81" s="154"/>
-      <c r="J81" s="153"/>
-    </row>
-    <row r="82" spans="1:10" s="156" customFormat="1" ht="16">
-      <c r="A82" s="154"/>
-      <c r="B82" s="154"/>
-      <c r="C82" s="154"/>
-      <c r="D82" s="154"/>
-      <c r="E82" s="154"/>
-      <c r="F82" s="154"/>
-      <c r="G82" s="153"/>
-      <c r="H82" s="153"/>
-      <c r="I82" s="154"/>
-      <c r="J82" s="154"/>
-    </row>
-    <row r="83" spans="1:10" s="156" customFormat="1" ht="16">
-      <c r="A83" s="154"/>
-      <c r="B83" s="154"/>
-      <c r="C83" s="154"/>
-      <c r="D83" s="154"/>
-      <c r="E83" s="154"/>
-      <c r="F83" s="154"/>
-      <c r="G83" s="153"/>
-      <c r="H83" s="153"/>
-      <c r="I83" s="154"/>
-      <c r="J83" s="154"/>
-    </row>
-    <row r="84" spans="1:10" s="156" customFormat="1">
-      <c r="A84" s="154"/>
-      <c r="B84" s="154"/>
-      <c r="C84" s="154"/>
-      <c r="D84" s="154"/>
-      <c r="E84" s="154"/>
-      <c r="F84" s="154"/>
-      <c r="G84" s="154"/>
-      <c r="H84" s="154"/>
-      <c r="I84" s="154"/>
-      <c r="J84" s="154"/>
-    </row>
-    <row r="85" spans="1:10" s="156" customFormat="1">
-      <c r="A85" s="154"/>
-      <c r="B85" s="154"/>
-      <c r="C85" s="154"/>
-      <c r="D85" s="154"/>
-      <c r="E85" s="154"/>
-      <c r="F85" s="154"/>
-      <c r="G85" s="154"/>
-      <c r="H85" s="154"/>
-      <c r="I85" s="154"/>
-      <c r="J85" s="154"/>
-    </row>
-    <row r="86" spans="1:10" s="156" customFormat="1">
-      <c r="A86" s="154"/>
-      <c r="B86" s="154"/>
-      <c r="C86" s="154"/>
-      <c r="D86" s="154"/>
-      <c r="E86" s="154"/>
-      <c r="F86" s="154"/>
-      <c r="G86" s="154"/>
-      <c r="H86" s="154"/>
-      <c r="I86" s="154"/>
-      <c r="J86" s="154"/>
-    </row>
-    <row r="87" spans="1:10" s="156" customFormat="1">
-      <c r="A87" s="154"/>
-      <c r="B87" s="154"/>
-      <c r="C87" s="154"/>
-      <c r="D87" s="154"/>
-      <c r="E87" s="154"/>
-      <c r="F87" s="154"/>
-      <c r="G87" s="154"/>
-      <c r="H87" s="154"/>
-      <c r="I87" s="154"/>
-      <c r="J87" s="154"/>
-    </row>
-    <row r="88" spans="1:10" s="156" customFormat="1">
-      <c r="A88" s="154"/>
-      <c r="B88" s="154"/>
-      <c r="C88" s="154"/>
-      <c r="D88" s="154"/>
-      <c r="E88" s="154"/>
-      <c r="F88" s="154"/>
-      <c r="G88" s="154"/>
-      <c r="H88" s="154"/>
-      <c r="I88" s="154"/>
-      <c r="J88" s="154"/>
-    </row>
-    <row r="89" spans="1:10" s="156" customFormat="1">
-      <c r="A89" s="154"/>
-      <c r="B89" s="154"/>
-      <c r="C89" s="154"/>
-      <c r="D89" s="154"/>
-      <c r="E89" s="154"/>
-      <c r="F89" s="154"/>
-      <c r="G89" s="154"/>
-      <c r="H89" s="154"/>
-      <c r="I89" s="154"/>
-      <c r="J89" s="154"/>
-    </row>
-    <row r="90" spans="1:10" s="156" customFormat="1">
-      <c r="A90" s="154"/>
-      <c r="B90" s="154"/>
-      <c r="C90" s="154"/>
-      <c r="D90" s="154"/>
-      <c r="E90" s="154"/>
-      <c r="F90" s="154"/>
-      <c r="G90" s="154"/>
-      <c r="H90" s="154"/>
-      <c r="I90" s="154"/>
-      <c r="J90" s="154"/>
-    </row>
-    <row r="91" spans="1:10" s="156" customFormat="1">
-      <c r="A91" s="154"/>
-      <c r="B91" s="154"/>
-      <c r="C91" s="154"/>
-      <c r="D91" s="154"/>
-      <c r="E91" s="154"/>
-      <c r="F91" s="154"/>
-      <c r="G91" s="154"/>
-      <c r="H91" s="154"/>
-      <c r="I91" s="154"/>
-      <c r="J91" s="154"/>
-    </row>
-    <row r="92" spans="1:10" s="156" customFormat="1">
-      <c r="A92" s="154"/>
-      <c r="B92" s="154"/>
-      <c r="C92" s="154"/>
-      <c r="D92" s="154"/>
-      <c r="E92" s="154"/>
-      <c r="F92" s="154"/>
-      <c r="G92" s="154"/>
-      <c r="H92" s="154"/>
-      <c r="I92" s="154"/>
-      <c r="J92" s="154"/>
+      <c r="G64" s="149"/>
+      <c r="H64" s="149"/>
+      <c r="I64" s="149"/>
+      <c r="J64" s="149"/>
+    </row>
+    <row r="65" spans="7:10" ht="16">
+      <c r="G65" s="149"/>
+      <c r="H65" s="149"/>
+      <c r="J65" s="151"/>
+    </row>
+    <row r="66" spans="7:10" ht="16">
+      <c r="G66" s="149"/>
+      <c r="H66" s="149"/>
+      <c r="J66" s="151"/>
+    </row>
+    <row r="67" spans="7:10" ht="16">
+      <c r="G67" s="149"/>
+      <c r="H67" s="149"/>
+      <c r="J67" s="151"/>
+    </row>
+    <row r="68" spans="7:10" ht="16">
+      <c r="G68" s="149"/>
+      <c r="H68" s="149"/>
+      <c r="J68" s="149"/>
+    </row>
+    <row r="69" spans="7:10" ht="16">
+      <c r="G69" s="149"/>
+      <c r="H69" s="149"/>
+      <c r="J69" s="149"/>
+    </row>
+    <row r="70" spans="7:10" ht="16">
+      <c r="G70" s="149"/>
+      <c r="H70" s="149"/>
+    </row>
+    <row r="71" spans="7:10" ht="16">
+      <c r="G71" s="149"/>
+      <c r="H71" s="149"/>
+    </row>
+    <row r="72" spans="7:10" ht="16">
+      <c r="G72" s="149"/>
+      <c r="H72" s="149"/>
+      <c r="I72" s="149"/>
+      <c r="J72" s="149"/>
+    </row>
+    <row r="73" spans="7:10" ht="16">
+      <c r="G73" s="149"/>
+      <c r="H73" s="149"/>
+      <c r="I73" s="149"/>
+      <c r="J73" s="149"/>
+    </row>
+    <row r="74" spans="7:10" ht="16">
+      <c r="G74" s="149"/>
+      <c r="H74" s="149"/>
+      <c r="I74" s="149"/>
+      <c r="J74" s="149"/>
+    </row>
+    <row r="75" spans="7:10" ht="16">
+      <c r="G75" s="149"/>
+      <c r="H75" s="149"/>
+      <c r="I75" s="149"/>
+      <c r="J75" s="149"/>
+    </row>
+    <row r="76" spans="7:10" ht="16">
+      <c r="G76" s="149"/>
+      <c r="H76" s="149"/>
+    </row>
+    <row r="77" spans="7:10" ht="16">
+      <c r="G77" s="149"/>
+      <c r="H77" s="149"/>
+    </row>
+    <row r="78" spans="7:10" ht="16">
+      <c r="G78" s="149"/>
+      <c r="H78" s="149"/>
+      <c r="J78" s="149"/>
+    </row>
+    <row r="79" spans="7:10" ht="16">
+      <c r="G79" s="149"/>
+      <c r="H79" s="149"/>
+    </row>
+    <row r="80" spans="7:10" ht="16">
+      <c r="G80" s="149"/>
+      <c r="H80" s="149"/>
+      <c r="I80" s="149"/>
+      <c r="J80" s="149"/>
+    </row>
+    <row r="81" spans="7:10" ht="16">
+      <c r="G81" s="149"/>
+      <c r="H81" s="149"/>
+      <c r="J81" s="149"/>
+    </row>
+    <row r="82" spans="7:10" ht="16">
+      <c r="G82" s="149"/>
+      <c r="H82" s="149"/>
+    </row>
+    <row r="83" spans="7:10" ht="16">
+      <c r="G83" s="149"/>
+      <c r="H83" s="149"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J44" xr:uid="{10D28488-2FC5-CC48-B811-68259D205C19}"/>
@@ -5130,6 +5091,867 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED162C4F-E21B-764F-B660-862D16C0693D}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:J45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="37.33203125" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.1640625" customWidth="1"/>
+    <col min="4" max="4" width="33.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="1.6640625" customWidth="1"/>
+    <col min="6" max="6" width="38.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="39" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="35.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="2.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="17" thickBot="1">
+      <c r="A1" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="E1" s="3"/>
+      <c r="F1" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="16">
+      <c r="A2" s="71" t="s">
+        <v>181</v>
+      </c>
+      <c r="B2" s="72" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2" s="72" t="s">
+        <v>230</v>
+      </c>
+      <c r="D2" s="73" t="s">
+        <v>201</v>
+      </c>
+      <c r="E2" s="55"/>
+      <c r="F2" s="71" t="s">
+        <v>60</v>
+      </c>
+      <c r="G2" s="72" t="s">
+        <v>156</v>
+      </c>
+      <c r="H2" s="72" t="s">
+        <v>106</v>
+      </c>
+      <c r="I2" s="72" t="s">
+        <v>321</v>
+      </c>
+      <c r="J2" s="73" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="16">
+      <c r="A3" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="E3" s="55"/>
+      <c r="F3" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="I3" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" s="54" customFormat="1" ht="16">
+      <c r="A4" s="79" t="s">
+        <v>184</v>
+      </c>
+      <c r="B4" s="80" t="s">
+        <v>184</v>
+      </c>
+      <c r="C4" s="80" t="s">
+        <v>203</v>
+      </c>
+      <c r="D4" s="81" t="s">
+        <v>201</v>
+      </c>
+      <c r="E4" s="55"/>
+      <c r="F4" s="74" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="64" t="s">
+        <v>156</v>
+      </c>
+      <c r="H4" s="64" t="s">
+        <v>106</v>
+      </c>
+      <c r="I4" s="64" t="s">
+        <v>321</v>
+      </c>
+      <c r="J4" s="75" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="54" customFormat="1" ht="16">
+      <c r="A5" s="79" t="s">
+        <v>183</v>
+      </c>
+      <c r="B5" s="80" t="s">
+        <v>183</v>
+      </c>
+      <c r="C5" s="80" t="s">
+        <v>203</v>
+      </c>
+      <c r="D5" s="81" t="s">
+        <v>201</v>
+      </c>
+      <c r="E5" s="55"/>
+      <c r="F5" s="74" t="s">
+        <v>60</v>
+      </c>
+      <c r="G5" s="64" t="s">
+        <v>156</v>
+      </c>
+      <c r="H5" s="64" t="s">
+        <v>106</v>
+      </c>
+      <c r="I5" s="64" t="s">
+        <v>321</v>
+      </c>
+      <c r="J5" s="75" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="54" customFormat="1" ht="16">
+      <c r="A6" s="79" t="s">
+        <v>185</v>
+      </c>
+      <c r="B6" s="80" t="s">
+        <v>185</v>
+      </c>
+      <c r="C6" s="80" t="s">
+        <v>185</v>
+      </c>
+      <c r="D6" s="81" t="s">
+        <v>201</v>
+      </c>
+      <c r="E6" s="55"/>
+      <c r="F6" s="74" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" s="64" t="s">
+        <v>156</v>
+      </c>
+      <c r="H6" s="64" t="s">
+        <v>106</v>
+      </c>
+      <c r="I6" s="64" t="s">
+        <v>321</v>
+      </c>
+      <c r="J6" s="75" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="16">
+      <c r="A7" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>318</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="E7" s="55"/>
+      <c r="F7" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="H7" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="I7" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="16">
+      <c r="A8" s="79" t="s">
+        <v>188</v>
+      </c>
+      <c r="B8" s="80" t="s">
+        <v>188</v>
+      </c>
+      <c r="C8" s="80" t="s">
+        <v>204</v>
+      </c>
+      <c r="D8" s="81" t="s">
+        <v>201</v>
+      </c>
+      <c r="E8" s="55"/>
+      <c r="F8" s="74" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8" s="64" t="s">
+        <v>156</v>
+      </c>
+      <c r="H8" s="64" t="s">
+        <v>106</v>
+      </c>
+      <c r="I8" s="64" t="s">
+        <v>200</v>
+      </c>
+      <c r="J8" s="75" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="16">
+      <c r="A9" s="79" t="s">
+        <v>187</v>
+      </c>
+      <c r="B9" s="80" t="s">
+        <v>187</v>
+      </c>
+      <c r="C9" s="80" t="s">
+        <v>204</v>
+      </c>
+      <c r="D9" s="81" t="s">
+        <v>201</v>
+      </c>
+      <c r="E9" s="55"/>
+      <c r="F9" s="74" t="s">
+        <v>60</v>
+      </c>
+      <c r="G9" s="64" t="s">
+        <v>156</v>
+      </c>
+      <c r="H9" s="64" t="s">
+        <v>106</v>
+      </c>
+      <c r="I9" s="64" t="s">
+        <v>200</v>
+      </c>
+      <c r="J9" s="75" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="16">
+      <c r="A10" s="60" t="s">
+        <v>189</v>
+      </c>
+      <c r="B10" s="59" t="s">
+        <v>205</v>
+      </c>
+      <c r="C10" s="59" t="s">
+        <v>206</v>
+      </c>
+      <c r="D10" s="61" t="s">
+        <v>201</v>
+      </c>
+      <c r="E10" s="55"/>
+      <c r="F10" s="7"/>
+      <c r="J10" s="93"/>
+    </row>
+    <row r="11" spans="1:10" ht="16">
+      <c r="A11" s="56" t="s">
+        <v>190</v>
+      </c>
+      <c r="B11" s="65" t="s">
+        <v>190</v>
+      </c>
+      <c r="C11" s="65" t="s">
+        <v>213</v>
+      </c>
+      <c r="D11" s="57" t="s">
+        <v>201</v>
+      </c>
+      <c r="E11" s="55"/>
+      <c r="F11" s="56" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" s="65" t="s">
+        <v>169</v>
+      </c>
+      <c r="H11" s="65" t="s">
+        <v>110</v>
+      </c>
+      <c r="I11" s="65" t="s">
+        <v>201</v>
+      </c>
+      <c r="J11" s="57" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="16">
+      <c r="A12" s="90" t="s">
+        <v>191</v>
+      </c>
+      <c r="B12" s="91" t="s">
+        <v>191</v>
+      </c>
+      <c r="C12" s="91" t="s">
+        <v>319</v>
+      </c>
+      <c r="D12" s="92" t="s">
+        <v>201</v>
+      </c>
+      <c r="E12" s="55"/>
+      <c r="F12" s="87" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" s="88" t="s">
+        <v>127</v>
+      </c>
+      <c r="H12" s="88" t="s">
+        <v>128</v>
+      </c>
+      <c r="I12" s="88" t="s">
+        <v>200</v>
+      </c>
+      <c r="J12" s="89" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="16">
+      <c r="A13" s="56" t="s">
+        <v>192</v>
+      </c>
+      <c r="B13" s="65" t="s">
+        <v>192</v>
+      </c>
+      <c r="C13" s="65" t="s">
+        <v>207</v>
+      </c>
+      <c r="D13" s="57" t="s">
+        <v>201</v>
+      </c>
+      <c r="E13" s="55"/>
+      <c r="F13" s="56" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13" s="65" t="s">
+        <v>169</v>
+      </c>
+      <c r="H13" s="65" t="s">
+        <v>110</v>
+      </c>
+      <c r="I13" s="65" t="s">
+        <v>201</v>
+      </c>
+      <c r="J13" s="57" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="16">
+      <c r="A14" s="76" t="s">
+        <v>193</v>
+      </c>
+      <c r="B14" s="66" t="s">
+        <v>193</v>
+      </c>
+      <c r="C14" s="66" t="s">
+        <v>208</v>
+      </c>
+      <c r="D14" s="85" t="s">
+        <v>201</v>
+      </c>
+      <c r="E14" s="55"/>
+      <c r="F14" s="76" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" s="67" t="s">
+        <v>130</v>
+      </c>
+      <c r="H14" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I14" s="68" t="s">
+        <v>200</v>
+      </c>
+      <c r="J14" s="58" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="16">
+      <c r="A15" s="77" t="s">
+        <v>194</v>
+      </c>
+      <c r="B15" s="62" t="s">
+        <v>194</v>
+      </c>
+      <c r="C15" s="62" t="s">
+        <v>209</v>
+      </c>
+      <c r="D15" s="86" t="s">
+        <v>201</v>
+      </c>
+      <c r="E15" s="55"/>
+      <c r="F15" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="G15" s="63" t="s">
+        <v>156</v>
+      </c>
+      <c r="H15" s="63" t="s">
+        <v>106</v>
+      </c>
+      <c r="I15" s="63" t="s">
+        <v>200</v>
+      </c>
+      <c r="J15" s="78" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="16">
+      <c r="A16" s="83" t="s">
+        <v>195</v>
+      </c>
+      <c r="B16" s="49" t="s">
+        <v>195</v>
+      </c>
+      <c r="C16" s="49" t="s">
+        <v>320</v>
+      </c>
+      <c r="D16" s="84" t="s">
+        <v>201</v>
+      </c>
+      <c r="E16" s="55"/>
+      <c r="F16" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="G16" s="69" t="s">
+        <v>166</v>
+      </c>
+      <c r="H16" s="69" t="s">
+        <v>106</v>
+      </c>
+      <c r="I16" s="69" t="s">
+        <v>201</v>
+      </c>
+      <c r="J16" s="16" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="16">
+      <c r="A17" s="83" t="s">
+        <v>196</v>
+      </c>
+      <c r="B17" s="49" t="s">
+        <v>196</v>
+      </c>
+      <c r="C17" s="49" t="s">
+        <v>210</v>
+      </c>
+      <c r="D17" s="84" t="s">
+        <v>201</v>
+      </c>
+      <c r="E17" s="55"/>
+      <c r="F17" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="69" t="s">
+        <v>166</v>
+      </c>
+      <c r="H17" s="69" t="s">
+        <v>106</v>
+      </c>
+      <c r="I17" s="69" t="s">
+        <v>201</v>
+      </c>
+      <c r="J17" s="16" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="16">
+      <c r="A18" s="79" t="s">
+        <v>197</v>
+      </c>
+      <c r="B18" s="80" t="s">
+        <v>188</v>
+      </c>
+      <c r="C18" s="80" t="s">
+        <v>204</v>
+      </c>
+      <c r="D18" s="81" t="s">
+        <v>201</v>
+      </c>
+      <c r="E18" s="55"/>
+      <c r="F18" s="74" t="s">
+        <v>60</v>
+      </c>
+      <c r="G18" s="64" t="s">
+        <v>156</v>
+      </c>
+      <c r="H18" s="64" t="s">
+        <v>106</v>
+      </c>
+      <c r="I18" s="70" t="s">
+        <v>321</v>
+      </c>
+      <c r="J18" s="75" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="16">
+      <c r="A19" s="79" t="s">
+        <v>198</v>
+      </c>
+      <c r="B19" s="80" t="s">
+        <v>188</v>
+      </c>
+      <c r="C19" s="80" t="s">
+        <v>204</v>
+      </c>
+      <c r="D19" s="82" t="s">
+        <v>200</v>
+      </c>
+      <c r="E19" s="55"/>
+      <c r="F19" s="74" t="s">
+        <v>60</v>
+      </c>
+      <c r="G19" s="64" t="s">
+        <v>156</v>
+      </c>
+      <c r="H19" s="64" t="s">
+        <v>106</v>
+      </c>
+      <c r="I19" s="70" t="s">
+        <v>321</v>
+      </c>
+      <c r="J19" s="75" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="16">
+      <c r="A20" s="79" t="s">
+        <v>184</v>
+      </c>
+      <c r="B20" s="80" t="s">
+        <v>184</v>
+      </c>
+      <c r="C20" s="80" t="s">
+        <v>212</v>
+      </c>
+      <c r="D20" s="82" t="s">
+        <v>200</v>
+      </c>
+      <c r="E20" s="55"/>
+      <c r="F20" s="74" t="s">
+        <v>60</v>
+      </c>
+      <c r="G20" s="64" t="s">
+        <v>156</v>
+      </c>
+      <c r="H20" s="64" t="s">
+        <v>106</v>
+      </c>
+      <c r="I20" s="64" t="s">
+        <v>24</v>
+      </c>
+      <c r="J20" s="75" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="16">
+      <c r="A21" s="76" t="s">
+        <v>193</v>
+      </c>
+      <c r="B21" s="66" t="s">
+        <v>193</v>
+      </c>
+      <c r="C21" s="66" t="s">
+        <v>248</v>
+      </c>
+      <c r="D21" s="85" t="s">
+        <v>200</v>
+      </c>
+      <c r="E21" s="55"/>
+      <c r="F21" s="76" t="s">
+        <v>59</v>
+      </c>
+      <c r="G21" s="67" t="s">
+        <v>130</v>
+      </c>
+      <c r="H21" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="I21" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="J21" s="58" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="16">
+      <c r="A22" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="G22" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="H22" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="I22" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="J22" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="16">
+      <c r="A23" s="22"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="55"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="52"/>
+      <c r="I23" s="52"/>
+      <c r="J23" s="53"/>
+    </row>
+    <row r="24" spans="1:10" ht="16">
+      <c r="A24" s="22"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="55"/>
+      <c r="F24" s="51"/>
+      <c r="G24" s="52"/>
+      <c r="H24" s="52"/>
+      <c r="I24" s="52"/>
+      <c r="J24" s="53"/>
+    </row>
+    <row r="25" spans="1:10" ht="16">
+      <c r="A25" s="22"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="23"/>
+      <c r="F25" s="7"/>
+      <c r="J25" s="19"/>
+    </row>
+    <row r="26" spans="1:10" ht="16">
+      <c r="A26" s="22"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="23"/>
+      <c r="F26" s="7"/>
+      <c r="J26" s="19"/>
+    </row>
+    <row r="27" spans="1:10" ht="16">
+      <c r="A27" s="22"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="23"/>
+      <c r="F27" s="7"/>
+      <c r="J27" s="19"/>
+    </row>
+    <row r="28" spans="1:10" ht="16">
+      <c r="A28" s="22"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="23"/>
+      <c r="F28" s="7"/>
+      <c r="J28" s="19"/>
+    </row>
+    <row r="29" spans="1:10" ht="16">
+      <c r="A29" s="22"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="23"/>
+      <c r="F29" s="7"/>
+      <c r="J29" s="19"/>
+    </row>
+    <row r="30" spans="1:10" ht="16">
+      <c r="A30" s="22"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="23"/>
+      <c r="F30" s="7"/>
+      <c r="J30" s="19"/>
+    </row>
+    <row r="31" spans="1:10" ht="16">
+      <c r="A31" s="22"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="23"/>
+      <c r="F31" s="7"/>
+      <c r="J31" s="19"/>
+    </row>
+    <row r="32" spans="1:10" ht="16">
+      <c r="A32" s="22"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="23"/>
+      <c r="F32" s="7"/>
+      <c r="J32" s="19"/>
+    </row>
+    <row r="33" spans="1:10" ht="16">
+      <c r="A33" s="22"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="23"/>
+      <c r="F33" s="7"/>
+      <c r="J33" s="19"/>
+    </row>
+    <row r="34" spans="1:10" ht="16">
+      <c r="A34" s="22"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="23"/>
+      <c r="F34" s="7"/>
+      <c r="J34" s="19"/>
+    </row>
+    <row r="35" spans="1:10" ht="16">
+      <c r="A35" s="22"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="23"/>
+      <c r="F35" s="7"/>
+      <c r="J35" s="19"/>
+    </row>
+    <row r="36" spans="1:10" ht="16">
+      <c r="A36" s="22"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="23"/>
+      <c r="F36" s="7"/>
+      <c r="J36" s="19"/>
+    </row>
+    <row r="37" spans="1:10" ht="16">
+      <c r="A37" s="22"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="23"/>
+      <c r="F37" s="7"/>
+      <c r="J37" s="19"/>
+    </row>
+    <row r="38" spans="1:10" ht="16">
+      <c r="A38" s="22"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="23"/>
+      <c r="F38" s="7"/>
+      <c r="J38" s="19"/>
+    </row>
+    <row r="39" spans="1:10" ht="16">
+      <c r="A39" s="22"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="23"/>
+      <c r="F39" s="7"/>
+      <c r="J39" s="19"/>
+    </row>
+    <row r="40" spans="1:10" ht="16">
+      <c r="A40" s="22"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="23"/>
+      <c r="F40" s="7"/>
+      <c r="J40" s="19"/>
+    </row>
+    <row r="41" spans="1:10" ht="16">
+      <c r="A41" s="22"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="23"/>
+      <c r="F41" s="7"/>
+      <c r="J41" s="19"/>
+    </row>
+    <row r="42" spans="1:10" ht="16">
+      <c r="A42" s="22"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="23"/>
+      <c r="F42" s="7"/>
+      <c r="J42" s="19"/>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="7"/>
+      <c r="D43" s="19"/>
+      <c r="F43" s="7"/>
+      <c r="J43" s="19"/>
+    </row>
+    <row r="44" spans="1:10" ht="15" thickBot="1">
+      <c r="A44" s="24"/>
+      <c r="B44" s="25"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="26"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="25"/>
+      <c r="H44" s="25"/>
+      <c r="I44" s="25"/>
+      <c r="J44" s="26"/>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="7"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J45" xr:uid="{ED162C4F-E21B-764F-B660-862D16C0693D}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1">
     <tabColor theme="8" tint="0.39997558519241921"/>
@@ -5705,7 +6527,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr filterMode="1">
     <tabColor theme="8" tint="0.39997558519241921"/>
@@ -6232,7 +7054,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="0.39997558519241921"/>
@@ -6409,7 +7231,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41D029F1-3F90-764F-9191-4F62BF9F0215}">
   <sheetPr filterMode="1">
     <tabColor theme="9" tint="0.39997558519241921"/>
@@ -6526,123 +7348,4 @@
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2EAD9B5-EDDD-BA49-A0DC-91F6C002BCB0}">
-  <sheetPr filterMode="1">
-    <tabColor theme="9" tint="0.39997558519241921"/>
-  </sheetPr>
-  <dimension ref="A1:A19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
-  <cols>
-    <col min="1" max="1" width="33.5" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" ht="18">
-      <c r="A1" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="16" hidden="1">
-      <c r="A2" s="4" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="16" hidden="1">
-      <c r="A3" s="4" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="16" hidden="1">
-      <c r="A4" s="4" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="16" hidden="1">
-      <c r="A5" s="4" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="16" hidden="1">
-      <c r="A6" s="4" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" ht="16" hidden="1">
-      <c r="A7" s="4" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" ht="16" hidden="1">
-      <c r="A8" s="4" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" ht="16" hidden="1">
-      <c r="A9" s="4" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" ht="16" hidden="1">
-      <c r="A10" s="4" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" ht="16" hidden="1">
-      <c r="A11" s="4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" ht="16" hidden="1">
-      <c r="A12" s="4" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" ht="16" hidden="1">
-      <c r="A13" s="4" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" ht="16" hidden="1">
-      <c r="A14" s="4" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" ht="16" hidden="1">
-      <c r="A15" s="4" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" ht="16">
-      <c r="A16" s="4" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="16">
-      <c r="A17" s="4" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" ht="16" hidden="1">
-      <c r="A18" s="4" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" ht="16" hidden="1">
-      <c r="A19" s="4" t="s">
-        <v>188</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:A19" xr:uid="{D2EAD9B5-EDDD-BA49-A0DC-91F6C002BCB0}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Atlas MAX+ XDi Extra High Density"/>
-        <filter val="Atlas MAX+ XDi High Density"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/atlas_max_plus_to_poly_mapping_template.xlsx
+++ b/atlas_max_plus_to_poly_mapping_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raeltonhonorio/Documents/KDAM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E165D97-2723-EF49-8ADA-96FC3A6EBB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC52F8B5-59CC-2846-B5D8-FC30C03D55F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Plus Media'!$A$1:$A$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">Plus_Output_ICCs!$A$1:$A$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Plus_Setups!$A$1:$A$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Plus_to_Poly_Mapping!$A$1:$J$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Plus_to_Poly_Mapping!$A$1:$L$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Poly_Media!$A$1:$C$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Poly_Output_ICCs!$A$1:$A$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Poly_Setups!$A$1:$B$69</definedName>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1362" uniqueCount="328">
   <si>
     <t>Atlas Max Plus → Atlas Max Poly Mapping Workbook</t>
   </si>
@@ -1013,9 +1013,6 @@
     <t>Atlas MAX Black HQ icm</t>
   </si>
   <si>
-    <t>sRGB Color Space Profile.icc</t>
-  </si>
-  <si>
     <t>ATL Poly Neon icm</t>
   </si>
   <si>
@@ -1028,16 +1025,13 @@
     <t>ATL Poly UltraHQ icm</t>
   </si>
   <si>
-    <t>MAX_BASE_SETUP</t>
-  </si>
-  <si>
-    <t>MAX_MEDIA</t>
-  </si>
-  <si>
-    <t>MAX_OUTPUT_ICC</t>
-  </si>
-  <si>
-    <t>MAX_INPUT_RGB</t>
+    <t>POLY_INPUT_CMYK</t>
+  </si>
+  <si>
+    <t>POLY_PALLET</t>
+  </si>
+  <si>
+    <t>Standard pallet</t>
   </si>
 </sst>
 </file>
@@ -1161,7 +1155,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1309,6 +1303,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -1402,7 +1402,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1635,12 +1635,39 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1815,10 +1842,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="68.25" customHeight="1">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="161" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="153"/>
+      <c r="B1" s="162"/>
     </row>
     <row r="2" spans="1:2" ht="45.5" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -2520,23 +2547,23 @@
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <dimension ref="A1:L45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="18.1640625" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="37.33203125" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.1640625" customWidth="1"/>
-    <col min="4" max="4" width="33.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="1.6640625" customWidth="1"/>
-    <col min="6" max="6" width="38.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="39" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="35.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="33.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="1.1640625" customWidth="1"/>
+    <col min="6" max="6" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.1640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="28.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="2.6640625" customWidth="1"/>
+    <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17" thickBot="1">
+    <row r="1" spans="1:12" ht="17" thickBot="1">
       <c r="A1" s="8" t="s">
         <v>13</v>
       </c>
@@ -2565,8 +2592,14 @@
       <c r="J1" s="10" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="16">
+      <c r="K1" s="164" t="s">
+        <v>325</v>
+      </c>
+      <c r="L1" s="164" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="16">
       <c r="A2" s="71" t="s">
         <v>181</v>
       </c>
@@ -2589,14 +2622,20 @@
       <c r="H2" s="72" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="72" t="s">
-        <v>321</v>
+      <c r="I2" s="64" t="s">
+        <v>200</v>
       </c>
       <c r="J2" s="73" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="16">
+      <c r="K2" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L2" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="16">
       <c r="A3" s="13" t="s">
         <v>182</v>
       </c>
@@ -2625,8 +2664,14 @@
       <c r="J3" s="14" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" s="54" customFormat="1" ht="16">
+      <c r="K3" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L3" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="54" customFormat="1" ht="31">
       <c r="A4" s="79" t="s">
         <v>184</v>
       </c>
@@ -2650,13 +2695,19 @@
         <v>106</v>
       </c>
       <c r="I4" s="64" t="s">
-        <v>321</v>
+        <v>200</v>
       </c>
       <c r="J4" s="75" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" s="54" customFormat="1" ht="16">
+      <c r="K4" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L4" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" s="54" customFormat="1" ht="31">
       <c r="A5" s="79" t="s">
         <v>183</v>
       </c>
@@ -2680,13 +2731,19 @@
         <v>106</v>
       </c>
       <c r="I5" s="64" t="s">
-        <v>321</v>
+        <v>200</v>
       </c>
       <c r="J5" s="75" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" s="54" customFormat="1" ht="16">
+      <c r="K5" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L5" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" s="54" customFormat="1" ht="31">
       <c r="A6" s="79" t="s">
         <v>185</v>
       </c>
@@ -2710,13 +2767,19 @@
         <v>106</v>
       </c>
       <c r="I6" s="64" t="s">
-        <v>321</v>
+        <v>200</v>
       </c>
       <c r="J6" s="75" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="16">
+      <c r="K6" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L6" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="16">
       <c r="A7" s="13" t="s">
         <v>186</v>
       </c>
@@ -2745,8 +2808,14 @@
       <c r="J7" s="14" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="16">
+      <c r="K7" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L7" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="16">
       <c r="A8" s="79" t="s">
         <v>188</v>
       </c>
@@ -2775,8 +2844,14 @@
       <c r="J8" s="75" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="16">
+      <c r="K8" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L8" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="16">
       <c r="A9" s="79" t="s">
         <v>187</v>
       </c>
@@ -2805,8 +2880,14 @@
       <c r="J9" s="75" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="16">
+      <c r="K9" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L9" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="16">
       <c r="A10" s="60" t="s">
         <v>189</v>
       </c>
@@ -2822,8 +2903,10 @@
       <c r="E10" s="55"/>
       <c r="F10" s="7"/>
       <c r="J10" s="93"/>
-    </row>
-    <row r="11" spans="1:10" ht="16">
+      <c r="K10" s="163"/>
+      <c r="L10" s="163"/>
+    </row>
+    <row r="11" spans="1:12" ht="16">
       <c r="A11" s="56" t="s">
         <v>190</v>
       </c>
@@ -2852,8 +2935,14 @@
       <c r="J11" s="57" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="16">
+      <c r="K11" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L11" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="16">
       <c r="A12" s="90" t="s">
         <v>191</v>
       </c>
@@ -2882,8 +2971,14 @@
       <c r="J12" s="89" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="16">
+      <c r="K12" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L12" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="16">
       <c r="A13" s="56" t="s">
         <v>192</v>
       </c>
@@ -2912,8 +3007,14 @@
       <c r="J13" s="57" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="16">
+      <c r="K13" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L13" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="16">
       <c r="A14" s="76" t="s">
         <v>193</v>
       </c>
@@ -2942,8 +3043,14 @@
       <c r="J14" s="58" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" ht="16">
+      <c r="K14" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L14" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="16">
       <c r="A15" s="77" t="s">
         <v>194</v>
       </c>
@@ -2966,14 +3073,20 @@
       <c r="H15" s="63" t="s">
         <v>106</v>
       </c>
-      <c r="I15" s="63" t="s">
+      <c r="I15" s="70" t="s">
         <v>200</v>
       </c>
       <c r="J15" s="78" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="16">
+      <c r="K15" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L15" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="16">
       <c r="A16" s="83" t="s">
         <v>195</v>
       </c>
@@ -3002,8 +3115,14 @@
       <c r="J16" s="16" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" ht="16">
+      <c r="K16" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L16" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="16">
       <c r="A17" s="83" t="s">
         <v>196</v>
       </c>
@@ -3032,8 +3151,14 @@
       <c r="J17" s="16" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" ht="16">
+      <c r="K17" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L17" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="16">
       <c r="A18" s="79" t="s">
         <v>197</v>
       </c>
@@ -3057,13 +3182,19 @@
         <v>106</v>
       </c>
       <c r="I18" s="70" t="s">
-        <v>321</v>
+        <v>200</v>
       </c>
       <c r="J18" s="75" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" ht="16">
+      <c r="K18" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L18" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="16">
       <c r="A19" s="79" t="s">
         <v>198</v>
       </c>
@@ -3087,13 +3218,19 @@
         <v>106</v>
       </c>
       <c r="I19" s="70" t="s">
-        <v>321</v>
+        <v>200</v>
       </c>
       <c r="J19" s="75" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" ht="16">
+      <c r="K19" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L19" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="16">
       <c r="A20" s="79" t="s">
         <v>184</v>
       </c>
@@ -3122,8 +3259,14 @@
       <c r="J20" s="75" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" ht="16">
+      <c r="K20" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L20" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="16">
       <c r="A21" s="76" t="s">
         <v>193</v>
       </c>
@@ -3152,8 +3295,14 @@
       <c r="J21" s="58" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" ht="16">
+      <c r="K21" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L21" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="16">
       <c r="A22" s="13" t="s">
         <v>182</v>
       </c>
@@ -3181,8 +3330,14 @@
       <c r="J22" s="14" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" ht="16">
+      <c r="K22" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L22" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="16">
       <c r="A23" s="22"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -3194,7 +3349,7 @@
       <c r="I23" s="52"/>
       <c r="J23" s="53"/>
     </row>
-    <row r="24" spans="1:10" ht="16">
+    <row r="24" spans="1:12" ht="16">
       <c r="A24" s="22"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -3206,7 +3361,7 @@
       <c r="I24" s="52"/>
       <c r="J24" s="53"/>
     </row>
-    <row r="25" spans="1:10" ht="16">
+    <row r="25" spans="1:12" ht="16">
       <c r="A25" s="22"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -3214,7 +3369,7 @@
       <c r="F25" s="7"/>
       <c r="J25" s="19"/>
     </row>
-    <row r="26" spans="1:10" ht="16">
+    <row r="26" spans="1:12" ht="16">
       <c r="A26" s="22"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -3222,7 +3377,7 @@
       <c r="F26" s="7"/>
       <c r="J26" s="19"/>
     </row>
-    <row r="27" spans="1:10" ht="16">
+    <row r="27" spans="1:12" ht="16">
       <c r="A27" s="22"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -3230,7 +3385,7 @@
       <c r="F27" s="7"/>
       <c r="J27" s="19"/>
     </row>
-    <row r="28" spans="1:10" ht="16">
+    <row r="28" spans="1:12" ht="16">
       <c r="A28" s="22"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -3238,7 +3393,7 @@
       <c r="F28" s="7"/>
       <c r="J28" s="19"/>
     </row>
-    <row r="29" spans="1:10" ht="16">
+    <row r="29" spans="1:12" ht="16">
       <c r="A29" s="22"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -3246,7 +3401,7 @@
       <c r="F29" s="7"/>
       <c r="J29" s="19"/>
     </row>
-    <row r="30" spans="1:10" ht="16">
+    <row r="30" spans="1:12" ht="16">
       <c r="A30" s="22"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -3254,7 +3409,7 @@
       <c r="F30" s="7"/>
       <c r="J30" s="19"/>
     </row>
-    <row r="31" spans="1:10" ht="16">
+    <row r="31" spans="1:12" ht="16">
       <c r="A31" s="22"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -3262,7 +3417,7 @@
       <c r="F31" s="7"/>
       <c r="J31" s="19"/>
     </row>
-    <row r="32" spans="1:10" ht="16">
+    <row r="32" spans="1:12" ht="16">
       <c r="A32" s="22"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -3371,7 +3526,7 @@
       <c r="A45" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J24" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:L45" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3596,7 +3751,7 @@
         <v>99</v>
       </c>
       <c r="C8" s="110" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D8" s="110" t="s">
         <v>201</v>
@@ -3829,7 +3984,7 @@
         <v>166</v>
       </c>
       <c r="C17" s="110" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D17" s="113" t="s">
         <v>201</v>
@@ -3910,7 +4065,7 @@
         <v>142</v>
       </c>
       <c r="C20" s="110" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D20" s="112" t="s">
         <v>201</v>
@@ -4226,7 +4381,7 @@
         <v>156</v>
       </c>
       <c r="C32" s="110" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D32" s="110" t="s">
         <v>201</v>
@@ -4280,7 +4435,7 @@
         <v>163</v>
       </c>
       <c r="C34" s="110" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D34" s="113" t="s">
         <v>201</v>
@@ -4351,7 +4506,7 @@
         <v>143</v>
       </c>
       <c r="C37" s="110" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D37" s="113" t="s">
         <v>201</v>
@@ -5095,7 +5250,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="37.33203125" customWidth="1"/>
@@ -5108,21 +5263,22 @@
     <col min="8" max="8" width="35.1640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="28.83203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="2.6640625" customWidth="1"/>
+    <col min="11" max="11" width="19.1640625" style="163" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14" style="163" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17" thickBot="1">
+    <row r="1" spans="1:12" ht="17" thickBot="1">
       <c r="A1" s="8" t="s">
-        <v>326</v>
+        <v>13</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>327</v>
+        <v>14</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>328</v>
+        <v>15</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>329</v>
+        <v>16</v>
       </c>
       <c r="E1" s="3"/>
       <c r="F1" s="8" t="s">
@@ -5140,8 +5296,14 @@
       <c r="J1" s="10" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="16">
+      <c r="K1" s="163" t="s">
+        <v>325</v>
+      </c>
+      <c r="L1" s="163" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="16">
       <c r="A2" s="71" t="s">
         <v>181</v>
       </c>
@@ -5164,14 +5326,20 @@
       <c r="H2" s="72" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="72" t="s">
-        <v>321</v>
+      <c r="I2" s="64" t="s">
+        <v>200</v>
       </c>
       <c r="J2" s="73" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="16">
+      <c r="K2" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L2" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="16">
       <c r="A3" s="13" t="s">
         <v>182</v>
       </c>
@@ -5200,8 +5368,14 @@
       <c r="J3" s="14" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" s="54" customFormat="1" ht="16">
+      <c r="K3" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L3" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="54" customFormat="1" ht="16">
       <c r="A4" s="79" t="s">
         <v>184</v>
       </c>
@@ -5225,13 +5399,19 @@
         <v>106</v>
       </c>
       <c r="I4" s="64" t="s">
-        <v>321</v>
+        <v>200</v>
       </c>
       <c r="J4" s="75" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" s="54" customFormat="1" ht="16">
+      <c r="K4" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L4" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" s="54" customFormat="1" ht="16">
       <c r="A5" s="79" t="s">
         <v>183</v>
       </c>
@@ -5255,13 +5435,19 @@
         <v>106</v>
       </c>
       <c r="I5" s="64" t="s">
-        <v>321</v>
+        <v>200</v>
       </c>
       <c r="J5" s="75" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" s="54" customFormat="1" ht="16">
+      <c r="K5" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L5" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" s="54" customFormat="1" ht="16">
       <c r="A6" s="79" t="s">
         <v>185</v>
       </c>
@@ -5285,13 +5471,19 @@
         <v>106</v>
       </c>
       <c r="I6" s="64" t="s">
-        <v>321</v>
+        <v>200</v>
       </c>
       <c r="J6" s="75" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="16">
+      <c r="K6" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L6" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="16">
       <c r="A7" s="13" t="s">
         <v>186</v>
       </c>
@@ -5320,8 +5512,14 @@
       <c r="J7" s="14" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="16">
+      <c r="K7" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L7" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="16">
       <c r="A8" s="79" t="s">
         <v>188</v>
       </c>
@@ -5350,8 +5548,14 @@
       <c r="J8" s="75" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="16">
+      <c r="K8" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L8" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="16">
       <c r="A9" s="79" t="s">
         <v>187</v>
       </c>
@@ -5380,8 +5584,14 @@
       <c r="J9" s="75" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="16">
+      <c r="K9" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L9" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="16">
       <c r="A10" s="60" t="s">
         <v>189</v>
       </c>
@@ -5398,7 +5608,7 @@
       <c r="F10" s="7"/>
       <c r="J10" s="93"/>
     </row>
-    <row r="11" spans="1:10" ht="16">
+    <row r="11" spans="1:12" ht="16">
       <c r="A11" s="56" t="s">
         <v>190</v>
       </c>
@@ -5427,8 +5637,14 @@
       <c r="J11" s="57" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="16">
+      <c r="K11" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L11" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="16">
       <c r="A12" s="90" t="s">
         <v>191</v>
       </c>
@@ -5457,8 +5673,14 @@
       <c r="J12" s="89" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="16">
+      <c r="K12" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L12" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="16">
       <c r="A13" s="56" t="s">
         <v>192</v>
       </c>
@@ -5487,8 +5709,14 @@
       <c r="J13" s="57" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="16">
+      <c r="K13" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L13" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="16">
       <c r="A14" s="76" t="s">
         <v>193</v>
       </c>
@@ -5517,8 +5745,14 @@
       <c r="J14" s="58" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" ht="16">
+      <c r="K14" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L14" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="16">
       <c r="A15" s="77" t="s">
         <v>194</v>
       </c>
@@ -5541,14 +5775,20 @@
       <c r="H15" s="63" t="s">
         <v>106</v>
       </c>
-      <c r="I15" s="63" t="s">
+      <c r="I15" s="70" t="s">
         <v>200</v>
       </c>
       <c r="J15" s="78" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="16">
+      <c r="K15" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L15" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="16">
       <c r="A16" s="83" t="s">
         <v>195</v>
       </c>
@@ -5577,8 +5817,14 @@
       <c r="J16" s="16" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" ht="16">
+      <c r="K16" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L16" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="16">
       <c r="A17" s="83" t="s">
         <v>196</v>
       </c>
@@ -5607,8 +5853,14 @@
       <c r="J17" s="16" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" ht="16">
+      <c r="K17" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L17" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="16">
       <c r="A18" s="79" t="s">
         <v>197</v>
       </c>
@@ -5632,13 +5884,19 @@
         <v>106</v>
       </c>
       <c r="I18" s="70" t="s">
-        <v>321</v>
+        <v>200</v>
       </c>
       <c r="J18" s="75" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" ht="16">
+      <c r="K18" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L18" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="16">
       <c r="A19" s="79" t="s">
         <v>198</v>
       </c>
@@ -5662,13 +5920,19 @@
         <v>106</v>
       </c>
       <c r="I19" s="70" t="s">
-        <v>321</v>
+        <v>200</v>
       </c>
       <c r="J19" s="75" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" ht="16">
+      <c r="K19" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L19" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="16">
       <c r="A20" s="79" t="s">
         <v>184</v>
       </c>
@@ -5697,8 +5961,14 @@
       <c r="J20" s="75" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" ht="16">
+      <c r="K20" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L20" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="16">
       <c r="A21" s="76" t="s">
         <v>193</v>
       </c>
@@ -5727,8 +5997,14 @@
       <c r="J21" s="58" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" ht="16">
+      <c r="K21" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L21" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="16">
       <c r="A22" s="13" t="s">
         <v>182</v>
       </c>
@@ -5756,8 +6032,14 @@
       <c r="J22" s="14" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" ht="16">
+      <c r="K22" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="L22" s="163" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="16">
       <c r="A23" s="22"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -5769,7 +6051,7 @@
       <c r="I23" s="52"/>
       <c r="J23" s="53"/>
     </row>
-    <row r="24" spans="1:10" ht="16">
+    <row r="24" spans="1:12" ht="16">
       <c r="A24" s="22"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -5781,7 +6063,7 @@
       <c r="I24" s="52"/>
       <c r="J24" s="53"/>
     </row>
-    <row r="25" spans="1:10" ht="16">
+    <row r="25" spans="1:12" ht="16">
       <c r="A25" s="22"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -5789,7 +6071,7 @@
       <c r="F25" s="7"/>
       <c r="J25" s="19"/>
     </row>
-    <row r="26" spans="1:10" ht="16">
+    <row r="26" spans="1:12" ht="16">
       <c r="A26" s="22"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -5797,7 +6079,7 @@
       <c r="F26" s="7"/>
       <c r="J26" s="19"/>
     </row>
-    <row r="27" spans="1:10" ht="16">
+    <row r="27" spans="1:12" ht="16">
       <c r="A27" s="22"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -5805,7 +6087,7 @@
       <c r="F27" s="7"/>
       <c r="J27" s="19"/>
     </row>
-    <row r="28" spans="1:10" ht="16">
+    <row r="28" spans="1:12" ht="16">
       <c r="A28" s="22"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -5813,7 +6095,7 @@
       <c r="F28" s="7"/>
       <c r="J28" s="19"/>
     </row>
-    <row r="29" spans="1:10" ht="16">
+    <row r="29" spans="1:12" ht="16">
       <c r="A29" s="22"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -5821,7 +6103,7 @@
       <c r="F29" s="7"/>
       <c r="J29" s="19"/>
     </row>
-    <row r="30" spans="1:10" ht="16">
+    <row r="30" spans="1:12" ht="16">
       <c r="A30" s="22"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -5829,7 +6111,7 @@
       <c r="F30" s="7"/>
       <c r="J30" s="19"/>
     </row>
-    <row r="31" spans="1:10" ht="16">
+    <row r="31" spans="1:12" ht="16">
       <c r="A31" s="22"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -5837,7 +6119,7 @@
       <c r="F31" s="7"/>
       <c r="J31" s="19"/>
     </row>
-    <row r="32" spans="1:10" ht="16">
+    <row r="32" spans="1:12" ht="16">
       <c r="A32" s="22"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -5953,7 +6235,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <tabColor theme="8" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:B69"/>
@@ -5963,565 +6245,559 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="22.75" customHeight="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="10" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A3" t="s">
+    <row r="3" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A4" t="s">
+    <row r="4" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A5" t="s">
+    <row r="5" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A6" t="s">
+    <row r="6" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A7" t="s">
+    <row r="7" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A7" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A8" t="s">
+    <row r="8" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A8" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A9" t="s">
+    <row r="9" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A9" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A10" t="s">
+    <row r="10" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A10" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A11" t="s">
+    <row r="11" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A11" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A12" t="s">
+    <row r="12" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A12" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A13" t="s">
+    <row r="13" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A13" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A14" t="s">
+    <row r="14" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A14" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A15" t="s">
+    <row r="15" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A15" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A16" t="s">
+    <row r="16" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A16" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A17" t="s">
+    <row r="17" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A17" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A18" t="s">
+    <row r="18" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A18" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A19" t="s">
+    <row r="19" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A19" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A20" t="s">
+    <row r="20" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A20" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A21" t="s">
+    <row r="21" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A21" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A22" t="s">
+    <row r="22" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A22" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A23" t="s">
+    <row r="23" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A23" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A24" t="s">
+    <row r="24" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A24" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A25" t="s">
+    <row r="25" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A25" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A26" t="s">
+    <row r="26" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A26" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A27" t="s">
+    <row r="27" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A27" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A28" t="s">
+    <row r="28" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A28" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A29" t="s">
+    <row r="29" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A29" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A30" t="s">
+    <row r="30" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A30" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A31" t="s">
+    <row r="31" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A31" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A32" t="s">
+    <row r="32" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A32" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A33" t="s">
+    <row r="33" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A33" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A34" t="s">
+    <row r="34" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A34" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A35" t="s">
+    <row r="35" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A35" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A36" t="s">
+    <row r="36" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A36" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A37" t="s">
+    <row r="37" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A37" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A38" t="s">
+    <row r="38" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A38" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A39" t="s">
+    <row r="39" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A39" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A40" t="s">
+    <row r="40" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A40" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A41" t="s">
+    <row r="41" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A41" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A42" t="s">
+    <row r="42" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A42" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A43" t="s">
+    <row r="43" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A43" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A44" t="s">
+    <row r="44" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A44" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A45" t="s">
+    <row r="45" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A45" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A46" t="s">
+    <row r="46" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A46" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A47" t="s">
+    <row r="47" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A47" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A48" t="s">
+    <row r="48" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A48" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A49" t="s">
+    <row r="49" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A49" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="19" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="22.75" customHeight="1">
-      <c r="A50" t="s">
+      <c r="A50" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A51" t="s">
+    <row r="51" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A51" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A52" t="s">
+    <row r="52" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A52" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A53" t="s">
+    <row r="53" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A53" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A54" t="s">
+    <row r="54" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A54" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A55" t="s">
+    <row r="55" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A55" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A56" t="s">
+    <row r="56" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A56" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A57" t="s">
+    <row r="57" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A57" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A58" t="s">
+    <row r="58" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A58" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A59" t="s">
+    <row r="59" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A59" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A60" t="s">
+    <row r="60" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A60" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A61" t="s">
+    <row r="61" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A61" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A62" t="s">
+    <row r="62" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A62" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A63" t="s">
+    <row r="63" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A63" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A64" t="s">
+    <row r="64" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A64" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A65" t="s">
+    <row r="65" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A65" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A66" t="s">
+    <row r="66" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A66" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A67" t="s">
+    <row r="67" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A67" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A68" t="s">
+    <row r="68" spans="1:2" ht="22.75" customHeight="1">
+      <c r="A68" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="22.75" hidden="1" customHeight="1">
-      <c r="A69" t="s">
+    <row r="69" spans="1:2" ht="22.75" customHeight="1" thickBot="1">
+      <c r="A69" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="26" t="s">
         <v>28</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B69" xr:uid="{00000000-0001-0000-0400-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="MaxPoly Neon Look UHQ DM Guard"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:B69" xr:uid="{00000000-0001-0000-0400-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -6529,13 +6805,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <tabColor theme="8" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="39.5" defaultRowHeight="14"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="45.5" customHeight="1">
+    <row r="1" spans="1:3" ht="45.5" customHeight="1" thickBot="1">
       <c r="A1" s="3" t="s">
         <v>96</v>
       </c>
@@ -6546,509 +6822,503 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A2" s="152" t="s">
         <v>99</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="153" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="154" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A3" s="155" t="s">
         <v>101</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="156" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A4" s="155" t="s">
         <v>102</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="156" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A5" s="155" t="s">
         <v>105</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="156" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="155" t="s">
         <v>108</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="156" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="22.75" hidden="1" customHeight="1">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:3" ht="22.75" customHeight="1">
+      <c r="A7" s="155" t="s">
         <v>109</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="156" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A8" s="155" t="s">
         <v>112</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="156" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A9" s="155" t="s">
         <v>115</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="156" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A10" s="155" t="s">
         <v>118</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="156" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A11" s="155" t="s">
         <v>121</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="156" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A12" s="1" t="s">
+    <row r="12" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A12" s="155" t="s">
         <v>124</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="156" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A13" s="1" t="s">
+    <row r="13" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A13" s="155" t="s">
         <v>127</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="156" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A14" s="1" t="s">
+    <row r="14" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A14" s="155" t="s">
         <v>130</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="156" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A15" s="155" t="s">
         <v>133</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="156" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A16" s="1" t="s">
+    <row r="16" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A16" s="155" t="s">
         <v>136</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="156" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A17" s="1" t="s">
+    <row r="17" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A17" s="155" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="156" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A18" s="1" t="s">
+    <row r="18" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A18" s="155" t="s">
         <v>142</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="156" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A19" s="1" t="s">
+    <row r="19" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A19" s="155" t="s">
         <v>143</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="156" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A20" s="155" t="s">
         <v>145</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="156" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A21" s="1" t="s">
+    <row r="21" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A21" s="155" t="s">
         <v>146</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="156" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A22" s="1" t="s">
+    <row r="22" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A22" s="155" t="s">
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="156" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A23" s="1" t="s">
+    <row r="23" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A23" s="155" t="s">
         <v>147</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="156" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A24" s="1" t="s">
+    <row r="24" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A24" s="155" t="s">
         <v>148</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="156" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A25" s="1" t="s">
+    <row r="25" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A25" s="155" t="s">
         <v>150</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="156" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A26" s="1" t="s">
+    <row r="26" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A26" s="155" t="s">
         <v>152</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="156" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A27" s="1" t="s">
+    <row r="27" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A27" s="155" t="s">
         <v>153</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="156" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A28" s="1" t="s">
+    <row r="28" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A28" s="155" t="s">
         <v>155</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="156" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A29" s="1" t="s">
+    <row r="29" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A29" s="155" t="s">
         <v>156</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="156" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A30" s="1" t="s">
+    <row r="30" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A30" s="155" t="s">
         <v>157</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="156" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A31" s="1" t="s">
+    <row r="31" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A31" s="155" t="s">
         <v>158</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="156" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A32" s="1" t="s">
+    <row r="32" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A32" s="155" t="s">
         <v>160</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="156" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A33" s="1" t="s">
+    <row r="33" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A33" s="155" t="s">
         <v>163</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="156" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A34" s="1" t="s">
+    <row r="34" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A34" s="155" t="s">
         <v>164</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="156" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="68.25" hidden="1" customHeight="1">
-      <c r="A35" s="1" t="s">
+    <row r="35" spans="1:3" ht="68.25" customHeight="1">
+      <c r="A35" s="155" t="s">
         <v>166</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="156" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="68.25" hidden="1" customHeight="1">
-      <c r="A36" s="1" t="s">
+    <row r="36" spans="1:3" ht="68.25" customHeight="1">
+      <c r="A36" s="155" t="s">
         <v>168</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="156" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="22.75" hidden="1" customHeight="1">
-      <c r="A37" s="1" t="s">
+    <row r="37" spans="1:3" ht="22.75" customHeight="1">
+      <c r="A37" s="155" t="s">
         <v>169</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="156" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A38" s="1" t="s">
+    <row r="38" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A38" s="155" t="s">
         <v>41</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="156" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A39" s="1" t="s">
+    <row r="39" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A39" s="155" t="s">
         <v>170</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="156" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A40" s="1" t="s">
+    <row r="40" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A40" s="155" t="s">
         <v>171</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="156" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A41" s="1" t="s">
+    <row r="41" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A41" s="155" t="s">
         <v>173</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="156" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A42" s="1" t="s">
+    <row r="42" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A42" s="155" t="s">
         <v>174</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="156" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A43" s="1" t="s">
+    <row r="43" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A43" s="155" t="s">
         <v>176</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="156" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A44" s="1" t="s">
+    <row r="44" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A44" s="155" t="s">
         <v>177</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="156" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A45" s="1" t="s">
+    <row r="45" spans="1:3" ht="45.5" customHeight="1">
+      <c r="A45" s="155" t="s">
         <v>178</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="156" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="45.5" hidden="1" customHeight="1">
-      <c r="A46" s="1" t="s">
+    <row r="46" spans="1:3" ht="45.5" customHeight="1" thickBot="1">
+      <c r="A46" s="157" t="s">
         <v>179</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="158" t="s">
         <v>175</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="159" t="s">
         <v>107</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C46" xr:uid="{00000000-0001-0000-0500-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Atlas MAX Poly Brushed STD DM Guard"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:C46" xr:uid="{00000000-0001-0000-0500-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -7067,163 +7337,168 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="16">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="160"/>
+      <c r="C1" s="10" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" t="s">
+      <c r="A2" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="19" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" t="s">
+      <c r="A3" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="19" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" t="s">
+      <c r="A4" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="19" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" t="s">
+      <c r="A5" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="19" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" t="s">
+      <c r="A6" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="19" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" t="s">
+      <c r="A7" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="19" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" t="s">
+      <c r="A8" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="19" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" t="s">
+      <c r="A9" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="19" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" t="s">
+      <c r="A10" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="19" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" t="s">
+      <c r="A11" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="19" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" t="s">
+      <c r="A12" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="19" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" t="s">
+      <c r="A13" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="19" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" t="s">
+      <c r="A14" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="19" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" t="s">
+      <c r="A15" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="19" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" t="s">
+      <c r="A16" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="19" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" t="s">
+      <c r="A17" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="19" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" t="s">
+      <c r="A18" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="19" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" t="s">
+      <c r="A19" s="7" t="s">
         <v>161</v>
       </c>
+      <c r="C19" s="19"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" t="s">
+      <c r="A20" s="7" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
+      <c r="C20" s="19"/>
+    </row>
+    <row r="21" spans="1:3" ht="15" thickBot="1">
+      <c r="A21" s="24" t="s">
         <v>252</v>
       </c>
+      <c r="B21" s="25"/>
+      <c r="C21" s="26"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:A21" xr:uid="{00000000-0001-0000-0600-000000000000}"/>

--- a/atlas_max_plus_to_poly_mapping_template.xlsx
+++ b/atlas_max_plus_to_poly_mapping_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raeltonhonorio/Documents/KDAM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC52F8B5-59CC-2846-B5D8-FC30C03D55F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF21DA24-0DC1-AB48-B5B1-A33DB0BE5039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -1402,7 +1402,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="165">
+  <cellXfs count="164">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1660,14 +1660,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1842,10 +1841,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="68.25" customHeight="1">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="162" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="162"/>
+      <c r="B1" s="163"/>
     </row>
     <row r="2" spans="1:2" ht="45.5" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -2592,10 +2591,10 @@
       <c r="J1" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="164" t="s">
+      <c r="K1" s="161" t="s">
         <v>325</v>
       </c>
-      <c r="L1" s="164" t="s">
+      <c r="L1" s="161" t="s">
         <v>326</v>
       </c>
     </row>
@@ -2628,10 +2627,10 @@
       <c r="J2" s="73" t="s">
         <v>199</v>
       </c>
-      <c r="K2" s="163" t="s">
+      <c r="K2" t="s">
         <v>261</v>
       </c>
-      <c r="L2" s="163" t="s">
+      <c r="L2" t="s">
         <v>327</v>
       </c>
     </row>
@@ -2664,14 +2663,14 @@
       <c r="J3" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="K3" s="163" t="s">
+      <c r="K3" t="s">
         <v>261</v>
       </c>
-      <c r="L3" s="163" t="s">
+      <c r="L3" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="54" customFormat="1" ht="31">
+    <row r="4" spans="1:12" s="54" customFormat="1" ht="16">
       <c r="A4" s="79" t="s">
         <v>184</v>
       </c>
@@ -2700,14 +2699,14 @@
       <c r="J4" s="75" t="s">
         <v>199</v>
       </c>
-      <c r="K4" s="163" t="s">
+      <c r="K4" t="s">
         <v>261</v>
       </c>
-      <c r="L4" s="163" t="s">
+      <c r="L4" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="54" customFormat="1" ht="31">
+    <row r="5" spans="1:12" s="54" customFormat="1" ht="16">
       <c r="A5" s="79" t="s">
         <v>183</v>
       </c>
@@ -2736,14 +2735,14 @@
       <c r="J5" s="75" t="s">
         <v>199</v>
       </c>
-      <c r="K5" s="163" t="s">
+      <c r="K5" t="s">
         <v>261</v>
       </c>
-      <c r="L5" s="163" t="s">
+      <c r="L5" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="54" customFormat="1" ht="31">
+    <row r="6" spans="1:12" s="54" customFormat="1" ht="16">
       <c r="A6" s="79" t="s">
         <v>185</v>
       </c>
@@ -2772,10 +2771,10 @@
       <c r="J6" s="75" t="s">
         <v>199</v>
       </c>
-      <c r="K6" s="163" t="s">
+      <c r="K6" t="s">
         <v>261</v>
       </c>
-      <c r="L6" s="163" t="s">
+      <c r="L6" t="s">
         <v>327</v>
       </c>
     </row>
@@ -2808,10 +2807,10 @@
       <c r="J7" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="K7" s="163" t="s">
+      <c r="K7" t="s">
         <v>261</v>
       </c>
-      <c r="L7" s="163" t="s">
+      <c r="L7" t="s">
         <v>327</v>
       </c>
     </row>
@@ -2844,10 +2843,10 @@
       <c r="J8" s="75" t="s">
         <v>199</v>
       </c>
-      <c r="K8" s="163" t="s">
+      <c r="K8" t="s">
         <v>261</v>
       </c>
-      <c r="L8" s="163" t="s">
+      <c r="L8" t="s">
         <v>327</v>
       </c>
     </row>
@@ -2880,10 +2879,10 @@
       <c r="J9" s="75" t="s">
         <v>199</v>
       </c>
-      <c r="K9" s="163" t="s">
+      <c r="K9" t="s">
         <v>261</v>
       </c>
-      <c r="L9" s="163" t="s">
+      <c r="L9" t="s">
         <v>327</v>
       </c>
     </row>
@@ -2903,8 +2902,6 @@
       <c r="E10" s="55"/>
       <c r="F10" s="7"/>
       <c r="J10" s="93"/>
-      <c r="K10" s="163"/>
-      <c r="L10" s="163"/>
     </row>
     <row r="11" spans="1:12" ht="16">
       <c r="A11" s="56" t="s">
@@ -2935,10 +2932,10 @@
       <c r="J11" s="57" t="s">
         <v>199</v>
       </c>
-      <c r="K11" s="163" t="s">
+      <c r="K11" t="s">
         <v>261</v>
       </c>
-      <c r="L11" s="163" t="s">
+      <c r="L11" t="s">
         <v>327</v>
       </c>
     </row>
@@ -2971,10 +2968,10 @@
       <c r="J12" s="89" t="s">
         <v>199</v>
       </c>
-      <c r="K12" s="163" t="s">
+      <c r="K12" t="s">
         <v>261</v>
       </c>
-      <c r="L12" s="163" t="s">
+      <c r="L12" t="s">
         <v>327</v>
       </c>
     </row>
@@ -3007,10 +3004,10 @@
       <c r="J13" s="57" t="s">
         <v>199</v>
       </c>
-      <c r="K13" s="163" t="s">
+      <c r="K13" t="s">
         <v>261</v>
       </c>
-      <c r="L13" s="163" t="s">
+      <c r="L13" t="s">
         <v>327</v>
       </c>
     </row>
@@ -3043,10 +3040,10 @@
       <c r="J14" s="58" t="s">
         <v>199</v>
       </c>
-      <c r="K14" s="163" t="s">
+      <c r="K14" t="s">
         <v>261</v>
       </c>
-      <c r="L14" s="163" t="s">
+      <c r="L14" t="s">
         <v>327</v>
       </c>
     </row>
@@ -3079,10 +3076,10 @@
       <c r="J15" s="78" t="s">
         <v>199</v>
       </c>
-      <c r="K15" s="163" t="s">
+      <c r="K15" t="s">
         <v>261</v>
       </c>
-      <c r="L15" s="163" t="s">
+      <c r="L15" t="s">
         <v>327</v>
       </c>
     </row>
@@ -3115,10 +3112,10 @@
       <c r="J16" s="16" t="s">
         <v>199</v>
       </c>
-      <c r="K16" s="163" t="s">
+      <c r="K16" t="s">
         <v>261</v>
       </c>
-      <c r="L16" s="163" t="s">
+      <c r="L16" t="s">
         <v>327</v>
       </c>
     </row>
@@ -3151,10 +3148,10 @@
       <c r="J17" s="16" t="s">
         <v>199</v>
       </c>
-      <c r="K17" s="163" t="s">
+      <c r="K17" t="s">
         <v>261</v>
       </c>
-      <c r="L17" s="163" t="s">
+      <c r="L17" t="s">
         <v>327</v>
       </c>
     </row>
@@ -3187,10 +3184,10 @@
       <c r="J18" s="75" t="s">
         <v>199</v>
       </c>
-      <c r="K18" s="163" t="s">
+      <c r="K18" t="s">
         <v>261</v>
       </c>
-      <c r="L18" s="163" t="s">
+      <c r="L18" t="s">
         <v>327</v>
       </c>
     </row>
@@ -3223,10 +3220,10 @@
       <c r="J19" s="75" t="s">
         <v>199</v>
       </c>
-      <c r="K19" s="163" t="s">
+      <c r="K19" t="s">
         <v>261</v>
       </c>
-      <c r="L19" s="163" t="s">
+      <c r="L19" t="s">
         <v>327</v>
       </c>
     </row>
@@ -3259,10 +3256,10 @@
       <c r="J20" s="75" t="s">
         <v>199</v>
       </c>
-      <c r="K20" s="163" t="s">
+      <c r="K20" t="s">
         <v>261</v>
       </c>
-      <c r="L20" s="163" t="s">
+      <c r="L20" t="s">
         <v>327</v>
       </c>
     </row>
@@ -3295,10 +3292,10 @@
       <c r="J21" s="58" t="s">
         <v>199</v>
       </c>
-      <c r="K21" s="163" t="s">
+      <c r="K21" t="s">
         <v>261</v>
       </c>
-      <c r="L21" s="163" t="s">
+      <c r="L21" t="s">
         <v>327</v>
       </c>
     </row>
@@ -3330,10 +3327,10 @@
       <c r="J22" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="K22" s="163" t="s">
+      <c r="K22" t="s">
         <v>261</v>
       </c>
-      <c r="L22" s="163" t="s">
+      <c r="L22" t="s">
         <v>327</v>
       </c>
     </row>
@@ -5263,8 +5260,8 @@
     <col min="8" max="8" width="35.1640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="28.83203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="19.1640625" style="163" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14" style="163" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17" thickBot="1">
@@ -5296,10 +5293,10 @@
       <c r="J1" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="163" t="s">
+      <c r="K1" t="s">
         <v>325</v>
       </c>
-      <c r="L1" s="163" t="s">
+      <c r="L1" t="s">
         <v>326</v>
       </c>
     </row>
@@ -5332,10 +5329,10 @@
       <c r="J2" s="73" t="s">
         <v>199</v>
       </c>
-      <c r="K2" s="163" t="s">
+      <c r="K2" t="s">
         <v>261</v>
       </c>
-      <c r="L2" s="163" t="s">
+      <c r="L2" t="s">
         <v>327</v>
       </c>
     </row>
@@ -5368,10 +5365,10 @@
       <c r="J3" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="K3" s="163" t="s">
+      <c r="K3" t="s">
         <v>261</v>
       </c>
-      <c r="L3" s="163" t="s">
+      <c r="L3" t="s">
         <v>327</v>
       </c>
     </row>
@@ -5404,10 +5401,10 @@
       <c r="J4" s="75" t="s">
         <v>199</v>
       </c>
-      <c r="K4" s="163" t="s">
+      <c r="K4" t="s">
         <v>261</v>
       </c>
-      <c r="L4" s="163" t="s">
+      <c r="L4" t="s">
         <v>327</v>
       </c>
     </row>
@@ -5440,10 +5437,10 @@
       <c r="J5" s="75" t="s">
         <v>199</v>
       </c>
-      <c r="K5" s="163" t="s">
+      <c r="K5" t="s">
         <v>261</v>
       </c>
-      <c r="L5" s="163" t="s">
+      <c r="L5" t="s">
         <v>327</v>
       </c>
     </row>
@@ -5476,10 +5473,10 @@
       <c r="J6" s="75" t="s">
         <v>199</v>
       </c>
-      <c r="K6" s="163" t="s">
+      <c r="K6" t="s">
         <v>261</v>
       </c>
-      <c r="L6" s="163" t="s">
+      <c r="L6" t="s">
         <v>327</v>
       </c>
     </row>
@@ -5512,10 +5509,10 @@
       <c r="J7" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="K7" s="163" t="s">
+      <c r="K7" t="s">
         <v>261</v>
       </c>
-      <c r="L7" s="163" t="s">
+      <c r="L7" t="s">
         <v>327</v>
       </c>
     </row>
@@ -5548,10 +5545,10 @@
       <c r="J8" s="75" t="s">
         <v>199</v>
       </c>
-      <c r="K8" s="163" t="s">
+      <c r="K8" t="s">
         <v>261</v>
       </c>
-      <c r="L8" s="163" t="s">
+      <c r="L8" t="s">
         <v>327</v>
       </c>
     </row>
@@ -5584,10 +5581,10 @@
       <c r="J9" s="75" t="s">
         <v>199</v>
       </c>
-      <c r="K9" s="163" t="s">
+      <c r="K9" t="s">
         <v>261</v>
       </c>
-      <c r="L9" s="163" t="s">
+      <c r="L9" t="s">
         <v>327</v>
       </c>
     </row>
@@ -5637,10 +5634,10 @@
       <c r="J11" s="57" t="s">
         <v>199</v>
       </c>
-      <c r="K11" s="163" t="s">
+      <c r="K11" t="s">
         <v>261</v>
       </c>
-      <c r="L11" s="163" t="s">
+      <c r="L11" t="s">
         <v>327</v>
       </c>
     </row>
@@ -5673,10 +5670,10 @@
       <c r="J12" s="89" t="s">
         <v>199</v>
       </c>
-      <c r="K12" s="163" t="s">
+      <c r="K12" t="s">
         <v>261</v>
       </c>
-      <c r="L12" s="163" t="s">
+      <c r="L12" t="s">
         <v>327</v>
       </c>
     </row>
@@ -5709,10 +5706,10 @@
       <c r="J13" s="57" t="s">
         <v>199</v>
       </c>
-      <c r="K13" s="163" t="s">
+      <c r="K13" t="s">
         <v>261</v>
       </c>
-      <c r="L13" s="163" t="s">
+      <c r="L13" t="s">
         <v>327</v>
       </c>
     </row>
@@ -5745,10 +5742,10 @@
       <c r="J14" s="58" t="s">
         <v>199</v>
       </c>
-      <c r="K14" s="163" t="s">
+      <c r="K14" t="s">
         <v>261</v>
       </c>
-      <c r="L14" s="163" t="s">
+      <c r="L14" t="s">
         <v>327</v>
       </c>
     </row>
@@ -5781,10 +5778,10 @@
       <c r="J15" s="78" t="s">
         <v>199</v>
       </c>
-      <c r="K15" s="163" t="s">
+      <c r="K15" t="s">
         <v>261</v>
       </c>
-      <c r="L15" s="163" t="s">
+      <c r="L15" t="s">
         <v>327</v>
       </c>
     </row>
@@ -5817,10 +5814,10 @@
       <c r="J16" s="16" t="s">
         <v>199</v>
       </c>
-      <c r="K16" s="163" t="s">
+      <c r="K16" t="s">
         <v>261</v>
       </c>
-      <c r="L16" s="163" t="s">
+      <c r="L16" t="s">
         <v>327</v>
       </c>
     </row>
@@ -5853,10 +5850,10 @@
       <c r="J17" s="16" t="s">
         <v>199</v>
       </c>
-      <c r="K17" s="163" t="s">
+      <c r="K17" t="s">
         <v>261</v>
       </c>
-      <c r="L17" s="163" t="s">
+      <c r="L17" t="s">
         <v>327</v>
       </c>
     </row>
@@ -5889,10 +5886,10 @@
       <c r="J18" s="75" t="s">
         <v>199</v>
       </c>
-      <c r="K18" s="163" t="s">
+      <c r="K18" t="s">
         <v>261</v>
       </c>
-      <c r="L18" s="163" t="s">
+      <c r="L18" t="s">
         <v>327</v>
       </c>
     </row>
@@ -5925,10 +5922,10 @@
       <c r="J19" s="75" t="s">
         <v>199</v>
       </c>
-      <c r="K19" s="163" t="s">
+      <c r="K19" t="s">
         <v>261</v>
       </c>
-      <c r="L19" s="163" t="s">
+      <c r="L19" t="s">
         <v>327</v>
       </c>
     </row>
@@ -5961,10 +5958,10 @@
       <c r="J20" s="75" t="s">
         <v>199</v>
       </c>
-      <c r="K20" s="163" t="s">
+      <c r="K20" t="s">
         <v>261</v>
       </c>
-      <c r="L20" s="163" t="s">
+      <c r="L20" t="s">
         <v>327</v>
       </c>
     </row>
@@ -5997,10 +5994,10 @@
       <c r="J21" s="58" t="s">
         <v>199</v>
       </c>
-      <c r="K21" s="163" t="s">
+      <c r="K21" t="s">
         <v>261</v>
       </c>
-      <c r="L21" s="163" t="s">
+      <c r="L21" t="s">
         <v>327</v>
       </c>
     </row>
@@ -6032,10 +6029,10 @@
       <c r="J22" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="K22" s="163" t="s">
+      <c r="K22" t="s">
         <v>261</v>
       </c>
-      <c r="L22" s="163" t="s">
+      <c r="L22" t="s">
         <v>327</v>
       </c>
     </row>

--- a/atlas_max_plus_to_poly_mapping_template.xlsx
+++ b/atlas_max_plus_to_poly_mapping_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raeltonhonorio/Documents/KDAM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF21DA24-0DC1-AB48-B5B1-A33DB0BE5039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2FE0A67-87A6-D841-B08E-A2C33735C9F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" firstSheet="9" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -27,6 +27,10 @@
     <sheet name="AVHD6 SETUPS" sheetId="13" r:id="rId12"/>
     <sheet name="AVHD6 MEDIA" sheetId="12" r:id="rId13"/>
     <sheet name="AVHD6_OUTPUT_ICC" sheetId="14" r:id="rId14"/>
+    <sheet name="AV100 SETUPS" sheetId="17" r:id="rId15"/>
+    <sheet name="AV1000 MEDIA" sheetId="18" r:id="rId16"/>
+    <sheet name="AV100_OUTPUT_ICC" sheetId="19" r:id="rId17"/>
+    <sheet name="AV1000 TO PLUS" sheetId="20" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'AVHD6 MEDIA'!$A$1:$A$16</definedName>
@@ -48,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1362" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1548" uniqueCount="390">
   <si>
     <t>Atlas Max Plus → Atlas Max Poly Mapping Workbook</t>
   </si>
@@ -1032,13 +1036,199 @@
   </si>
   <si>
     <t>Standard pallet</t>
+  </si>
+  <si>
+    <t>AV1000 SETUPS</t>
+  </si>
+  <si>
+    <t>AV HD6 Black v1.icm</t>
+  </si>
+  <si>
+    <t>AV HD6 Color v1.icm</t>
+  </si>
+  <si>
+    <t>AV HD6 Light v1.icm</t>
+  </si>
+  <si>
+    <t>OUTPUT Profile</t>
+  </si>
+  <si>
+    <t>AC BlackT HQ.kst</t>
+  </si>
+  <si>
+    <t>AC BlackT STD.kst</t>
+  </si>
+  <si>
+    <t>AC ColorT Black Ink Only.kst</t>
+  </si>
+  <si>
+    <t>AC ColorT HQ.kst</t>
+  </si>
+  <si>
+    <t>AC ColorT STD.kst</t>
+  </si>
+  <si>
+    <t>AC ColorT White Ink.kst</t>
+  </si>
+  <si>
+    <t>AC WhiteT HQ.kst</t>
+  </si>
+  <si>
+    <t>AC WhiteT STD.kst</t>
+  </si>
+  <si>
+    <t>BIG SIZES.kst</t>
+  </si>
+  <si>
+    <t>BLACK BIG SIZE.kst</t>
+  </si>
+  <si>
+    <t>BLACK GILDAN.kst</t>
+  </si>
+  <si>
+    <t>BLACK HEATHER TALLS.kst</t>
+  </si>
+  <si>
+    <t>BLACK HEATHER.kst</t>
+  </si>
+  <si>
+    <t>C.kst</t>
+  </si>
+  <si>
+    <t>CW.kst</t>
+  </si>
+  <si>
+    <t>DARK GILDAN.kst</t>
+  </si>
+  <si>
+    <t>DARK TALL.kst</t>
+  </si>
+  <si>
+    <t>HEATHER BIG SIZE.kst</t>
+  </si>
+  <si>
+    <t>HEATHER WHITE.kst</t>
+  </si>
+  <si>
+    <t>HEATHERS NO WHITE.kst</t>
+  </si>
+  <si>
+    <t>LIGHT NO WHITE.kst</t>
+  </si>
+  <si>
+    <t>MID TONE NO WHITE.kst</t>
+  </si>
+  <si>
+    <t>SMOKE.kst</t>
+  </si>
+  <si>
+    <t>W.kst</t>
+  </si>
+  <si>
+    <t>Media AV1000</t>
+  </si>
+  <si>
+    <t>linear45.lut</t>
+  </si>
+  <si>
+    <t>linear45RG.lut</t>
+  </si>
+  <si>
+    <t>MediaDB.xml</t>
+  </si>
+  <si>
+    <t>version.txt</t>
+  </si>
+  <si>
+    <t>AC BlackT HQ</t>
+  </si>
+  <si>
+    <t>AC ColorT Black Ink Only</t>
+  </si>
+  <si>
+    <t>AC BlackT STD</t>
+  </si>
+  <si>
+    <t>AC ColorT HQ</t>
+  </si>
+  <si>
+    <t>AC ColorT STD</t>
+  </si>
+  <si>
+    <t>AC ColorT White Ink</t>
+  </si>
+  <si>
+    <t>AC WhiteT HQ</t>
+  </si>
+  <si>
+    <t>AC WhiteT STD</t>
+  </si>
+  <si>
+    <t>AV HD6 Black High Production 64038</t>
+  </si>
+  <si>
+    <t>AV HD6 Color High Production 64038</t>
+  </si>
+  <si>
+    <t>AV HD6 Light High Production 64038</t>
+  </si>
+  <si>
+    <t>BIG SIZES</t>
+  </si>
+  <si>
+    <t>BLACK BIG SIZE</t>
+  </si>
+  <si>
+    <t>BLACK GILDAN</t>
+  </si>
+  <si>
+    <t>BLACK HEATHER TALLS</t>
+  </si>
+  <si>
+    <t>BLACK HEATHER</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>CW</t>
+  </si>
+  <si>
+    <t>DARK GILDAN</t>
+  </si>
+  <si>
+    <t>DARK TALL</t>
+  </si>
+  <si>
+    <t>HEATHER BIG SIZE</t>
+  </si>
+  <si>
+    <t>HEATHER WHITE</t>
+  </si>
+  <si>
+    <t>HEATHERS NO WHITE</t>
+  </si>
+  <si>
+    <t>LIGHT NO WHITE</t>
+  </si>
+  <si>
+    <t>MID TONE NO WHITE</t>
+  </si>
+  <si>
+    <t>SMOKE</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>Fixa</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1154,8 +1344,14 @@
       <name val="Helvetica"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="27">
+  <fills count="28">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1309,6 +1505,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -1402,7 +1604,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="164">
+  <cellXfs count="170">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1426,13 +1628,10 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1445,8 +1644,6 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1661,6 +1858,17 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1841,10 +2049,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="68.25" customHeight="1">
-      <c r="A1" s="162" t="s">
+      <c r="A1" s="168" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="163"/>
+      <c r="B1" s="169"/>
     </row>
     <row r="2" spans="1:2" ht="45.5" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -2541,6 +2749,997 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C79466E2-B626-384A-80AE-38283B2719E9}">
+  <dimension ref="A1:A34"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="35" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="18">
+      <c r="A1" s="5" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>356</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5400D9C-18EA-F34A-AF9F-98FEF126EAE6}">
+  <dimension ref="A1:A17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="44" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>295</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{489560A0-066C-D242-A978-32CDD53942A5}">
+  <dimension ref="A1:A7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="22.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>331</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C35120B4-BDCF-CB4C-BC62-FC29CBC3A109}">
+  <dimension ref="A1:L35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="20" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="2" width="36.6640625" customWidth="1"/>
+    <col min="3" max="3" width="31.5" customWidth="1"/>
+    <col min="4" max="4" width="25.5" customWidth="1"/>
+    <col min="5" max="5" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="1.6640625" customWidth="1"/>
+    <col min="8" max="9" width="33" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="28.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="16">
+      <c r="A1" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="16">
+      <c r="A2" s="92" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2" s="92"/>
+      <c r="C2" s="92" t="s">
+        <v>312</v>
+      </c>
+      <c r="D2" s="163" t="s">
+        <v>299</v>
+      </c>
+      <c r="E2" s="164"/>
+      <c r="F2" s="164"/>
+      <c r="H2" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="J2" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="K2" s="166"/>
+    </row>
+    <row r="3" spans="1:12" ht="16">
+      <c r="A3" s="92" t="s">
+        <v>364</v>
+      </c>
+      <c r="B3" s="92"/>
+      <c r="C3" s="163" t="s">
+        <v>313</v>
+      </c>
+      <c r="D3" s="163" t="s">
+        <v>299</v>
+      </c>
+      <c r="E3" s="164"/>
+      <c r="F3" s="164"/>
+      <c r="H3" s="165" t="s">
+        <v>187</v>
+      </c>
+      <c r="I3" s="165" t="s">
+        <v>187</v>
+      </c>
+      <c r="J3" s="165" t="s">
+        <v>204</v>
+      </c>
+      <c r="K3" s="166"/>
+    </row>
+    <row r="4" spans="1:12" ht="16">
+      <c r="A4" s="92" t="s">
+        <v>363</v>
+      </c>
+      <c r="B4" s="92"/>
+      <c r="C4" s="163" t="s">
+        <v>315</v>
+      </c>
+      <c r="D4" s="163" t="s">
+        <v>300</v>
+      </c>
+      <c r="E4" s="164"/>
+      <c r="F4" s="164"/>
+      <c r="H4" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="I4" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="J4" s="45" t="s">
+        <v>215</v>
+      </c>
+      <c r="K4" s="166"/>
+    </row>
+    <row r="5" spans="1:12" ht="16">
+      <c r="A5" s="92" t="s">
+        <v>365</v>
+      </c>
+      <c r="B5" s="92"/>
+      <c r="C5" s="163" t="s">
+        <v>312</v>
+      </c>
+      <c r="D5" s="163" t="s">
+        <v>299</v>
+      </c>
+      <c r="E5" s="164"/>
+      <c r="F5" s="164"/>
+      <c r="H5" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="I5" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="J5" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="K5" s="166"/>
+    </row>
+    <row r="6" spans="1:12" ht="16">
+      <c r="A6" s="92" t="s">
+        <v>366</v>
+      </c>
+      <c r="B6" s="92"/>
+      <c r="C6" s="144" t="s">
+        <v>313</v>
+      </c>
+      <c r="D6" s="144" t="s">
+        <v>299</v>
+      </c>
+      <c r="E6" s="144"/>
+      <c r="F6" s="144"/>
+      <c r="H6" s="165" t="s">
+        <v>187</v>
+      </c>
+      <c r="I6" s="165" t="s">
+        <v>187</v>
+      </c>
+      <c r="J6" s="165" t="s">
+        <v>204</v>
+      </c>
+      <c r="K6" s="166"/>
+    </row>
+    <row r="7" spans="1:12" ht="16">
+      <c r="A7" s="92" t="s">
+        <v>367</v>
+      </c>
+      <c r="B7" s="92"/>
+      <c r="C7" s="163" t="s">
+        <v>312</v>
+      </c>
+      <c r="D7" s="144" t="s">
+        <v>299</v>
+      </c>
+      <c r="E7" s="164"/>
+      <c r="F7" s="164"/>
+      <c r="H7" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="I7" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="J7" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="K7" s="166"/>
+    </row>
+    <row r="8" spans="1:12" ht="16">
+      <c r="A8" s="92" t="s">
+        <v>368</v>
+      </c>
+      <c r="B8" s="92"/>
+      <c r="C8" s="163" t="s">
+        <v>315</v>
+      </c>
+      <c r="D8" s="163" t="s">
+        <v>300</v>
+      </c>
+      <c r="E8" s="164"/>
+      <c r="F8" s="164"/>
+      <c r="H8" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="I8" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="J8" s="45" t="s">
+        <v>215</v>
+      </c>
+      <c r="K8" s="166"/>
+      <c r="L8" s="41"/>
+    </row>
+    <row r="9" spans="1:12" ht="16">
+      <c r="A9" s="92" t="s">
+        <v>369</v>
+      </c>
+      <c r="B9" s="92"/>
+      <c r="C9" s="163" t="s">
+        <v>316</v>
+      </c>
+      <c r="D9" s="163" t="s">
+        <v>300</v>
+      </c>
+      <c r="E9" s="164"/>
+      <c r="F9" s="164"/>
+      <c r="H9" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="K9" s="166"/>
+    </row>
+    <row r="10" spans="1:12" ht="16">
+      <c r="A10" s="92" t="s">
+        <v>370</v>
+      </c>
+      <c r="B10" s="92"/>
+      <c r="C10" s="144" t="s">
+        <v>308</v>
+      </c>
+      <c r="D10" s="144" t="s">
+        <v>298</v>
+      </c>
+      <c r="E10" s="144"/>
+      <c r="F10" s="144"/>
+      <c r="H10" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="I10" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="J10" s="33" t="s">
+        <v>214</v>
+      </c>
+      <c r="K10" s="166"/>
+    </row>
+    <row r="11" spans="1:12" ht="16">
+      <c r="A11" s="92" t="s">
+        <v>309</v>
+      </c>
+      <c r="B11" s="92"/>
+      <c r="C11" s="92" t="s">
+        <v>309</v>
+      </c>
+      <c r="D11" s="144" t="s">
+        <v>298</v>
+      </c>
+      <c r="E11" s="92"/>
+      <c r="F11" s="92"/>
+      <c r="H11" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="I11" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="J11" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="K11" s="166"/>
+    </row>
+    <row r="12" spans="1:12" ht="16">
+      <c r="A12" s="92" t="s">
+        <v>310</v>
+      </c>
+      <c r="B12" s="92"/>
+      <c r="C12" s="92" t="s">
+        <v>310</v>
+      </c>
+      <c r="D12" s="144" t="s">
+        <v>298</v>
+      </c>
+      <c r="E12" s="92"/>
+      <c r="F12" s="92"/>
+      <c r="H12" s="165" t="s">
+        <v>187</v>
+      </c>
+      <c r="I12" s="165" t="s">
+        <v>187</v>
+      </c>
+      <c r="J12" s="165" t="s">
+        <v>204</v>
+      </c>
+      <c r="K12" s="166"/>
+    </row>
+    <row r="13" spans="1:12" ht="16">
+      <c r="A13" s="92" t="s">
+        <v>371</v>
+      </c>
+      <c r="B13" s="92"/>
+      <c r="C13" s="92" t="s">
+        <v>311</v>
+      </c>
+      <c r="D13" s="163" t="s">
+        <v>299</v>
+      </c>
+      <c r="E13" s="92"/>
+      <c r="F13" s="92"/>
+      <c r="H13" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="I13" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="J13" s="33" t="s">
+        <v>214</v>
+      </c>
+      <c r="K13" s="166"/>
+    </row>
+    <row r="14" spans="1:12" ht="16">
+      <c r="A14" s="92" t="s">
+        <v>312</v>
+      </c>
+      <c r="B14" s="92"/>
+      <c r="C14" s="92" t="s">
+        <v>312</v>
+      </c>
+      <c r="D14" s="163" t="s">
+        <v>299</v>
+      </c>
+      <c r="E14" s="92"/>
+      <c r="F14" s="92"/>
+      <c r="H14" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="I14" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="J14" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="K14" s="166"/>
+    </row>
+    <row r="15" spans="1:12" ht="16">
+      <c r="A15" s="92" t="s">
+        <v>313</v>
+      </c>
+      <c r="B15" s="92"/>
+      <c r="C15" s="92" t="s">
+        <v>313</v>
+      </c>
+      <c r="D15" s="163" t="s">
+        <v>299</v>
+      </c>
+      <c r="E15" s="92"/>
+      <c r="F15" s="92"/>
+      <c r="H15" s="165" t="s">
+        <v>187</v>
+      </c>
+      <c r="I15" s="165" t="s">
+        <v>187</v>
+      </c>
+      <c r="J15" s="165" t="s">
+        <v>204</v>
+      </c>
+      <c r="K15" s="166"/>
+    </row>
+    <row r="16" spans="1:12" ht="16">
+      <c r="A16" s="92" t="s">
+        <v>372</v>
+      </c>
+      <c r="B16" s="92"/>
+      <c r="C16" s="92" t="s">
+        <v>314</v>
+      </c>
+      <c r="D16" s="163" t="s">
+        <v>300</v>
+      </c>
+      <c r="E16" s="92"/>
+      <c r="F16" s="92"/>
+      <c r="H16" s="41" t="s">
+        <v>190</v>
+      </c>
+      <c r="I16" s="42" t="s">
+        <v>190</v>
+      </c>
+      <c r="J16" s="42" t="s">
+        <v>213</v>
+      </c>
+      <c r="K16" s="166"/>
+    </row>
+    <row r="17" spans="1:11" ht="16">
+      <c r="A17" s="92" t="s">
+        <v>315</v>
+      </c>
+      <c r="B17" s="92"/>
+      <c r="C17" s="92" t="s">
+        <v>315</v>
+      </c>
+      <c r="D17" s="163" t="s">
+        <v>300</v>
+      </c>
+      <c r="E17" s="92"/>
+      <c r="F17" s="92"/>
+      <c r="H17" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="I17" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="J17" s="45" t="s">
+        <v>215</v>
+      </c>
+      <c r="K17" s="166"/>
+    </row>
+    <row r="18" spans="1:11" ht="16">
+      <c r="A18" s="92" t="s">
+        <v>316</v>
+      </c>
+      <c r="B18" s="92"/>
+      <c r="C18" s="92" t="s">
+        <v>316</v>
+      </c>
+      <c r="D18" s="163" t="s">
+        <v>300</v>
+      </c>
+      <c r="E18" s="92"/>
+      <c r="F18" s="92"/>
+      <c r="H18" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="I18" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="J18" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="K18" s="166"/>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="92" t="s">
+        <v>373</v>
+      </c>
+      <c r="B19" s="92"/>
+      <c r="C19" s="92"/>
+      <c r="D19" s="92"/>
+      <c r="E19" s="92"/>
+      <c r="F19" s="92"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="92" t="s">
+        <v>374</v>
+      </c>
+      <c r="B20" s="92"/>
+      <c r="C20" s="92"/>
+      <c r="D20" s="92"/>
+      <c r="E20" s="92"/>
+      <c r="F20" s="92"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="92" t="s">
+        <v>375</v>
+      </c>
+      <c r="B21" s="92"/>
+      <c r="C21" s="92"/>
+      <c r="D21" s="92"/>
+      <c r="E21" s="92"/>
+      <c r="F21" s="92"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="92" t="s">
+        <v>376</v>
+      </c>
+      <c r="B22" s="92"/>
+      <c r="C22" s="92"/>
+      <c r="D22" s="92"/>
+      <c r="E22" s="92"/>
+      <c r="F22" s="92"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="92" t="s">
+        <v>377</v>
+      </c>
+      <c r="B23" s="92"/>
+      <c r="C23" s="92"/>
+      <c r="D23" s="92"/>
+      <c r="E23" s="92"/>
+      <c r="F23" s="92"/>
+    </row>
+    <row r="24" spans="1:11" ht="16">
+      <c r="A24" s="92" t="s">
+        <v>378</v>
+      </c>
+      <c r="B24" s="92"/>
+      <c r="C24" s="92"/>
+      <c r="D24" s="163"/>
+      <c r="E24" s="92"/>
+      <c r="F24" s="92"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="K24" s="160"/>
+    </row>
+    <row r="25" spans="1:11" ht="16">
+      <c r="A25" s="92" t="s">
+        <v>379</v>
+      </c>
+      <c r="B25" s="92"/>
+      <c r="D25" s="92"/>
+      <c r="E25" s="92"/>
+      <c r="F25" s="92"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="47"/>
+      <c r="J25" s="47"/>
+      <c r="K25" s="48"/>
+    </row>
+    <row r="26" spans="1:11" ht="16">
+      <c r="A26" s="92" t="s">
+        <v>380</v>
+      </c>
+      <c r="B26" s="92"/>
+      <c r="C26" s="92"/>
+      <c r="D26" s="92"/>
+      <c r="E26" s="92"/>
+      <c r="F26" s="92"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="20"/>
+    </row>
+    <row r="27" spans="1:11" ht="16">
+      <c r="A27" s="92" t="s">
+        <v>381</v>
+      </c>
+      <c r="B27" s="92"/>
+      <c r="C27" s="92"/>
+      <c r="D27" s="92"/>
+      <c r="E27" s="92"/>
+      <c r="F27" s="92"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+    </row>
+    <row r="28" spans="1:11" ht="16">
+      <c r="A28" s="92" t="s">
+        <v>382</v>
+      </c>
+      <c r="B28" s="92"/>
+      <c r="C28" s="92"/>
+      <c r="D28" s="92"/>
+      <c r="E28" s="92"/>
+      <c r="F28" s="92"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+    </row>
+    <row r="29" spans="1:11" ht="16">
+      <c r="A29" s="92" t="s">
+        <v>383</v>
+      </c>
+      <c r="B29" s="92"/>
+      <c r="C29" s="92"/>
+      <c r="D29" s="92"/>
+      <c r="E29" s="92"/>
+      <c r="F29" s="92"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+    </row>
+    <row r="30" spans="1:11" ht="16">
+      <c r="A30" s="92" t="s">
+        <v>384</v>
+      </c>
+      <c r="B30" s="92"/>
+      <c r="C30" s="92"/>
+      <c r="D30" s="92"/>
+      <c r="E30" s="92"/>
+      <c r="F30" s="92"/>
+      <c r="H30" s="162"/>
+      <c r="I30" s="161"/>
+      <c r="J30" s="161"/>
+      <c r="K30" s="162"/>
+    </row>
+    <row r="31" spans="1:11" ht="16">
+      <c r="A31" s="92" t="s">
+        <v>385</v>
+      </c>
+      <c r="B31" s="92"/>
+      <c r="C31" s="92"/>
+      <c r="D31" s="92"/>
+      <c r="E31" s="92"/>
+      <c r="F31" s="92"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="47"/>
+      <c r="J31" s="49"/>
+      <c r="K31" s="49"/>
+    </row>
+    <row r="32" spans="1:11" ht="16">
+      <c r="A32" s="92" t="s">
+        <v>386</v>
+      </c>
+      <c r="B32" s="92"/>
+      <c r="C32" s="92"/>
+      <c r="D32" s="92"/>
+      <c r="E32" s="92"/>
+      <c r="F32" s="92"/>
+      <c r="H32" s="46"/>
+      <c r="I32" s="47"/>
+      <c r="J32" s="47"/>
+      <c r="K32" s="48"/>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="92" t="s">
+        <v>387</v>
+      </c>
+      <c r="B33" s="92"/>
+      <c r="C33" s="92"/>
+      <c r="D33" s="92"/>
+      <c r="E33" s="92"/>
+      <c r="F33" s="92"/>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="92" t="s">
+        <v>388</v>
+      </c>
+      <c r="B34" s="92"/>
+      <c r="C34" s="92"/>
+      <c r="D34" s="92"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="92"/>
+    </row>
+    <row r="35" spans="1:10" ht="16">
+      <c r="C35" s="92"/>
+      <c r="D35" s="167"/>
+      <c r="E35" s="92"/>
+      <c r="F35" s="92"/>
+      <c r="H35" s="47"/>
+      <c r="I35" s="47"/>
+      <c r="J35" s="49"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
@@ -2591,40 +3790,40 @@
       <c r="J1" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="161" t="s">
+      <c r="K1" s="156" t="s">
         <v>325</v>
       </c>
-      <c r="L1" s="161" t="s">
+      <c r="L1" s="156" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="16">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="66" t="s">
         <v>181</v>
       </c>
-      <c r="B2" s="72" t="s">
+      <c r="B2" s="67" t="s">
         <v>181</v>
       </c>
-      <c r="C2" s="72" t="s">
+      <c r="C2" s="67" t="s">
         <v>230</v>
       </c>
-      <c r="D2" s="73" t="s">
-        <v>201</v>
-      </c>
-      <c r="E2" s="55"/>
-      <c r="F2" s="71" t="s">
+      <c r="D2" s="68" t="s">
+        <v>201</v>
+      </c>
+      <c r="E2" s="50"/>
+      <c r="F2" s="66" t="s">
         <v>60</v>
       </c>
-      <c r="G2" s="72" t="s">
+      <c r="G2" s="67" t="s">
         <v>156</v>
       </c>
-      <c r="H2" s="72" t="s">
+      <c r="H2" s="67" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="64" t="s">
+      <c r="I2" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="J2" s="73" t="s">
+      <c r="J2" s="68" t="s">
         <v>199</v>
       </c>
       <c r="K2" t="s">
@@ -2635,32 +3834,32 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="16">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="15" t="s">
         <v>317</v>
       </c>
-      <c r="D3" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="E3" s="55"/>
-      <c r="F3" s="13" t="s">
+      <c r="D3" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="E3" s="50"/>
+      <c r="F3" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="I3" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="J3" s="14" t="s">
+      <c r="I3" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="J3" s="12" t="s">
         <v>199</v>
       </c>
       <c r="K3" t="s">
@@ -2670,33 +3869,33 @@
         <v>327</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="54" customFormat="1" ht="16">
-      <c r="A4" s="79" t="s">
+    <row r="4" spans="1:12" s="49" customFormat="1" ht="16">
+      <c r="A4" s="74" t="s">
         <v>184</v>
       </c>
-      <c r="B4" s="80" t="s">
+      <c r="B4" s="75" t="s">
         <v>184</v>
       </c>
-      <c r="C4" s="80" t="s">
+      <c r="C4" s="75" t="s">
         <v>203</v>
       </c>
-      <c r="D4" s="81" t="s">
-        <v>201</v>
-      </c>
-      <c r="E4" s="55"/>
-      <c r="F4" s="74" t="s">
+      <c r="D4" s="76" t="s">
+        <v>201</v>
+      </c>
+      <c r="E4" s="50"/>
+      <c r="F4" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="G4" s="64" t="s">
+      <c r="G4" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="H4" s="64" t="s">
+      <c r="H4" s="59" t="s">
         <v>106</v>
       </c>
-      <c r="I4" s="64" t="s">
+      <c r="I4" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="J4" s="75" t="s">
+      <c r="J4" s="70" t="s">
         <v>199</v>
       </c>
       <c r="K4" t="s">
@@ -2706,33 +3905,33 @@
         <v>327</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="54" customFormat="1" ht="16">
-      <c r="A5" s="79" t="s">
+    <row r="5" spans="1:12" s="49" customFormat="1" ht="16">
+      <c r="A5" s="74" t="s">
         <v>183</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="75" t="s">
         <v>183</v>
       </c>
-      <c r="C5" s="80" t="s">
+      <c r="C5" s="75" t="s">
         <v>203</v>
       </c>
-      <c r="D5" s="81" t="s">
-        <v>201</v>
-      </c>
-      <c r="E5" s="55"/>
-      <c r="F5" s="74" t="s">
+      <c r="D5" s="76" t="s">
+        <v>201</v>
+      </c>
+      <c r="E5" s="50"/>
+      <c r="F5" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="G5" s="64" t="s">
+      <c r="G5" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="H5" s="64" t="s">
+      <c r="H5" s="59" t="s">
         <v>106</v>
       </c>
-      <c r="I5" s="64" t="s">
+      <c r="I5" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="J5" s="75" t="s">
+      <c r="J5" s="70" t="s">
         <v>199</v>
       </c>
       <c r="K5" t="s">
@@ -2742,33 +3941,33 @@
         <v>327</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="54" customFormat="1" ht="16">
-      <c r="A6" s="79" t="s">
+    <row r="6" spans="1:12" s="49" customFormat="1" ht="16">
+      <c r="A6" s="74" t="s">
         <v>185</v>
       </c>
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="75" t="s">
         <v>185</v>
       </c>
-      <c r="C6" s="80" t="s">
+      <c r="C6" s="75" t="s">
         <v>185</v>
       </c>
-      <c r="D6" s="81" t="s">
-        <v>201</v>
-      </c>
-      <c r="E6" s="55"/>
-      <c r="F6" s="74" t="s">
+      <c r="D6" s="76" t="s">
+        <v>201</v>
+      </c>
+      <c r="E6" s="50"/>
+      <c r="F6" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="G6" s="64" t="s">
+      <c r="G6" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="H6" s="64" t="s">
+      <c r="H6" s="59" t="s">
         <v>106</v>
       </c>
-      <c r="I6" s="64" t="s">
+      <c r="I6" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="J6" s="75" t="s">
+      <c r="J6" s="70" t="s">
         <v>199</v>
       </c>
       <c r="K6" t="s">
@@ -2779,32 +3978,32 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="15" t="s">
         <v>318</v>
       </c>
-      <c r="D7" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="E7" s="55"/>
-      <c r="F7" s="13" t="s">
+      <c r="D7" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="E7" s="50"/>
+      <c r="F7" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="H7" s="18" t="s">
+      <c r="H7" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="I7" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="J7" s="14" t="s">
+      <c r="I7" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="J7" s="12" t="s">
         <v>199</v>
       </c>
       <c r="K7" t="s">
@@ -2815,32 +4014,32 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16">
-      <c r="A8" s="79" t="s">
+      <c r="A8" s="74" t="s">
         <v>188</v>
       </c>
-      <c r="B8" s="80" t="s">
+      <c r="B8" s="75" t="s">
         <v>188</v>
       </c>
-      <c r="C8" s="80" t="s">
+      <c r="C8" s="75" t="s">
         <v>204</v>
       </c>
-      <c r="D8" s="81" t="s">
-        <v>201</v>
-      </c>
-      <c r="E8" s="55"/>
-      <c r="F8" s="74" t="s">
+      <c r="D8" s="76" t="s">
+        <v>201</v>
+      </c>
+      <c r="E8" s="50"/>
+      <c r="F8" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="G8" s="64" t="s">
+      <c r="G8" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="H8" s="64" t="s">
+      <c r="H8" s="59" t="s">
         <v>106</v>
       </c>
-      <c r="I8" s="64" t="s">
+      <c r="I8" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="J8" s="75" t="s">
+      <c r="J8" s="70" t="s">
         <v>199</v>
       </c>
       <c r="K8" t="s">
@@ -2851,32 +4050,32 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16">
-      <c r="A9" s="79" t="s">
+      <c r="A9" s="74" t="s">
         <v>187</v>
       </c>
-      <c r="B9" s="80" t="s">
+      <c r="B9" s="75" t="s">
         <v>187</v>
       </c>
-      <c r="C9" s="80" t="s">
+      <c r="C9" s="75" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="81" t="s">
-        <v>201</v>
-      </c>
-      <c r="E9" s="55"/>
-      <c r="F9" s="74" t="s">
+      <c r="D9" s="76" t="s">
+        <v>201</v>
+      </c>
+      <c r="E9" s="50"/>
+      <c r="F9" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="G9" s="64" t="s">
+      <c r="G9" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="H9" s="64" t="s">
+      <c r="H9" s="59" t="s">
         <v>106</v>
       </c>
-      <c r="I9" s="64" t="s">
+      <c r="I9" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="J9" s="75" t="s">
+      <c r="J9" s="70" t="s">
         <v>199</v>
       </c>
       <c r="K9" t="s">
@@ -2887,49 +4086,49 @@
       </c>
     </row>
     <row r="10" spans="1:12" ht="16">
-      <c r="A10" s="60" t="s">
+      <c r="A10" s="55" t="s">
         <v>189</v>
       </c>
-      <c r="B10" s="59" t="s">
+      <c r="B10" s="54" t="s">
         <v>205</v>
       </c>
-      <c r="C10" s="59" t="s">
+      <c r="C10" s="54" t="s">
         <v>206</v>
       </c>
-      <c r="D10" s="61" t="s">
-        <v>201</v>
-      </c>
-      <c r="E10" s="55"/>
+      <c r="D10" s="56" t="s">
+        <v>201</v>
+      </c>
+      <c r="E10" s="50"/>
       <c r="F10" s="7"/>
-      <c r="J10" s="93"/>
+      <c r="J10" s="88"/>
     </row>
     <row r="11" spans="1:12" ht="16">
-      <c r="A11" s="56" t="s">
+      <c r="A11" s="51" t="s">
         <v>190</v>
       </c>
-      <c r="B11" s="65" t="s">
+      <c r="B11" s="60" t="s">
         <v>190</v>
       </c>
-      <c r="C11" s="65" t="s">
+      <c r="C11" s="60" t="s">
         <v>213</v>
       </c>
-      <c r="D11" s="57" t="s">
-        <v>201</v>
-      </c>
-      <c r="E11" s="55"/>
-      <c r="F11" s="56" t="s">
+      <c r="D11" s="52" t="s">
+        <v>201</v>
+      </c>
+      <c r="E11" s="50"/>
+      <c r="F11" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="65" t="s">
+      <c r="G11" s="60" t="s">
         <v>169</v>
       </c>
-      <c r="H11" s="65" t="s">
+      <c r="H11" s="60" t="s">
         <v>110</v>
       </c>
-      <c r="I11" s="65" t="s">
-        <v>201</v>
-      </c>
-      <c r="J11" s="57" t="s">
+      <c r="I11" s="60" t="s">
+        <v>201</v>
+      </c>
+      <c r="J11" s="52" t="s">
         <v>199</v>
       </c>
       <c r="K11" t="s">
@@ -2940,32 +4139,32 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16">
-      <c r="A12" s="90" t="s">
+      <c r="A12" s="85" t="s">
         <v>191</v>
       </c>
-      <c r="B12" s="91" t="s">
+      <c r="B12" s="86" t="s">
         <v>191</v>
       </c>
-      <c r="C12" s="91" t="s">
+      <c r="C12" s="86" t="s">
         <v>319</v>
       </c>
-      <c r="D12" s="92" t="s">
-        <v>201</v>
-      </c>
-      <c r="E12" s="55"/>
-      <c r="F12" s="87" t="s">
+      <c r="D12" s="87" t="s">
+        <v>201</v>
+      </c>
+      <c r="E12" s="50"/>
+      <c r="F12" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="G12" s="88" t="s">
+      <c r="G12" s="83" t="s">
         <v>127</v>
       </c>
-      <c r="H12" s="88" t="s">
+      <c r="H12" s="83" t="s">
         <v>128</v>
       </c>
-      <c r="I12" s="88" t="s">
+      <c r="I12" s="83" t="s">
         <v>200</v>
       </c>
-      <c r="J12" s="89" t="s">
+      <c r="J12" s="84" t="s">
         <v>199</v>
       </c>
       <c r="K12" t="s">
@@ -2976,32 +4175,32 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16">
-      <c r="A13" s="56" t="s">
+      <c r="A13" s="51" t="s">
         <v>192</v>
       </c>
-      <c r="B13" s="65" t="s">
+      <c r="B13" s="60" t="s">
         <v>192</v>
       </c>
-      <c r="C13" s="65" t="s">
+      <c r="C13" s="60" t="s">
         <v>207</v>
       </c>
-      <c r="D13" s="57" t="s">
-        <v>201</v>
-      </c>
-      <c r="E13" s="55"/>
-      <c r="F13" s="56" t="s">
+      <c r="D13" s="52" t="s">
+        <v>201</v>
+      </c>
+      <c r="E13" s="50"/>
+      <c r="F13" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="G13" s="65" t="s">
+      <c r="G13" s="60" t="s">
         <v>169</v>
       </c>
-      <c r="H13" s="65" t="s">
+      <c r="H13" s="60" t="s">
         <v>110</v>
       </c>
-      <c r="I13" s="65" t="s">
-        <v>201</v>
-      </c>
-      <c r="J13" s="57" t="s">
+      <c r="I13" s="60" t="s">
+        <v>201</v>
+      </c>
+      <c r="J13" s="52" t="s">
         <v>199</v>
       </c>
       <c r="K13" t="s">
@@ -3012,32 +4211,32 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16">
-      <c r="A14" s="76" t="s">
+      <c r="A14" s="71" t="s">
         <v>193</v>
       </c>
-      <c r="B14" s="66" t="s">
+      <c r="B14" s="61" t="s">
         <v>193</v>
       </c>
-      <c r="C14" s="66" t="s">
+      <c r="C14" s="61" t="s">
         <v>208</v>
       </c>
-      <c r="D14" s="85" t="s">
-        <v>201</v>
-      </c>
-      <c r="E14" s="55"/>
-      <c r="F14" s="76" t="s">
+      <c r="D14" s="80" t="s">
+        <v>201</v>
+      </c>
+      <c r="E14" s="50"/>
+      <c r="F14" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="G14" s="67" t="s">
+      <c r="G14" s="62" t="s">
         <v>130</v>
       </c>
-      <c r="H14" s="66" t="s">
+      <c r="H14" s="61" t="s">
         <v>131</v>
       </c>
-      <c r="I14" s="68" t="s">
+      <c r="I14" s="63" t="s">
         <v>200</v>
       </c>
-      <c r="J14" s="58" t="s">
+      <c r="J14" s="53" t="s">
         <v>199</v>
       </c>
       <c r="K14" t="s">
@@ -3048,32 +4247,32 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16">
-      <c r="A15" s="77" t="s">
+      <c r="A15" s="72" t="s">
         <v>194</v>
       </c>
-      <c r="B15" s="62" t="s">
+      <c r="B15" s="57" t="s">
         <v>194</v>
       </c>
-      <c r="C15" s="62" t="s">
+      <c r="C15" s="57" t="s">
         <v>209</v>
       </c>
-      <c r="D15" s="86" t="s">
-        <v>201</v>
-      </c>
-      <c r="E15" s="55"/>
-      <c r="F15" s="77" t="s">
+      <c r="D15" s="81" t="s">
+        <v>201</v>
+      </c>
+      <c r="E15" s="50"/>
+      <c r="F15" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="G15" s="63" t="s">
+      <c r="G15" s="58" t="s">
         <v>156</v>
       </c>
-      <c r="H15" s="63" t="s">
+      <c r="H15" s="58" t="s">
         <v>106</v>
       </c>
-      <c r="I15" s="70" t="s">
+      <c r="I15" s="65" t="s">
         <v>200</v>
       </c>
-      <c r="J15" s="78" t="s">
+      <c r="J15" s="73" t="s">
         <v>199</v>
       </c>
       <c r="K15" t="s">
@@ -3084,32 +4283,32 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16">
-      <c r="A16" s="83" t="s">
+      <c r="A16" s="78" t="s">
         <v>195</v>
       </c>
-      <c r="B16" s="49" t="s">
+      <c r="B16" s="44" t="s">
         <v>195</v>
       </c>
-      <c r="C16" s="49" t="s">
+      <c r="C16" s="44" t="s">
         <v>320</v>
       </c>
-      <c r="D16" s="84" t="s">
-        <v>201</v>
-      </c>
-      <c r="E16" s="55"/>
-      <c r="F16" s="15" t="s">
+      <c r="D16" s="79" t="s">
+        <v>201</v>
+      </c>
+      <c r="E16" s="50"/>
+      <c r="F16" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="G16" s="69" t="s">
+      <c r="G16" s="64" t="s">
         <v>166</v>
       </c>
-      <c r="H16" s="69" t="s">
+      <c r="H16" s="64" t="s">
         <v>106</v>
       </c>
-      <c r="I16" s="69" t="s">
-        <v>201</v>
-      </c>
-      <c r="J16" s="16" t="s">
+      <c r="I16" s="64" t="s">
+        <v>201</v>
+      </c>
+      <c r="J16" s="14" t="s">
         <v>199</v>
       </c>
       <c r="K16" t="s">
@@ -3120,32 +4319,32 @@
       </c>
     </row>
     <row r="17" spans="1:12" ht="16">
-      <c r="A17" s="83" t="s">
+      <c r="A17" s="78" t="s">
         <v>196</v>
       </c>
-      <c r="B17" s="49" t="s">
+      <c r="B17" s="44" t="s">
         <v>196</v>
       </c>
-      <c r="C17" s="49" t="s">
+      <c r="C17" s="44" t="s">
         <v>210</v>
       </c>
-      <c r="D17" s="84" t="s">
-        <v>201</v>
-      </c>
-      <c r="E17" s="55"/>
-      <c r="F17" s="15" t="s">
+      <c r="D17" s="79" t="s">
+        <v>201</v>
+      </c>
+      <c r="E17" s="50"/>
+      <c r="F17" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="G17" s="69" t="s">
+      <c r="G17" s="64" t="s">
         <v>166</v>
       </c>
-      <c r="H17" s="69" t="s">
+      <c r="H17" s="64" t="s">
         <v>106</v>
       </c>
-      <c r="I17" s="69" t="s">
-        <v>201</v>
-      </c>
-      <c r="J17" s="16" t="s">
+      <c r="I17" s="64" t="s">
+        <v>201</v>
+      </c>
+      <c r="J17" s="14" t="s">
         <v>199</v>
       </c>
       <c r="K17" t="s">
@@ -3156,32 +4355,32 @@
       </c>
     </row>
     <row r="18" spans="1:12" ht="16">
-      <c r="A18" s="79" t="s">
+      <c r="A18" s="74" t="s">
         <v>197</v>
       </c>
-      <c r="B18" s="80" t="s">
+      <c r="B18" s="75" t="s">
         <v>188</v>
       </c>
-      <c r="C18" s="80" t="s">
+      <c r="C18" s="75" t="s">
         <v>204</v>
       </c>
-      <c r="D18" s="81" t="s">
-        <v>201</v>
-      </c>
-      <c r="E18" s="55"/>
-      <c r="F18" s="74" t="s">
+      <c r="D18" s="76" t="s">
+        <v>201</v>
+      </c>
+      <c r="E18" s="50"/>
+      <c r="F18" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="G18" s="64" t="s">
+      <c r="G18" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="H18" s="64" t="s">
+      <c r="H18" s="59" t="s">
         <v>106</v>
       </c>
-      <c r="I18" s="70" t="s">
+      <c r="I18" s="65" t="s">
         <v>200</v>
       </c>
-      <c r="J18" s="75" t="s">
+      <c r="J18" s="70" t="s">
         <v>199</v>
       </c>
       <c r="K18" t="s">
@@ -3192,32 +4391,32 @@
       </c>
     </row>
     <row r="19" spans="1:12" ht="16">
-      <c r="A19" s="79" t="s">
+      <c r="A19" s="74" t="s">
         <v>198</v>
       </c>
-      <c r="B19" s="80" t="s">
+      <c r="B19" s="75" t="s">
         <v>188</v>
       </c>
-      <c r="C19" s="80" t="s">
+      <c r="C19" s="75" t="s">
         <v>204</v>
       </c>
-      <c r="D19" s="82" t="s">
+      <c r="D19" s="77" t="s">
         <v>200</v>
       </c>
-      <c r="E19" s="55"/>
-      <c r="F19" s="74" t="s">
+      <c r="E19" s="50"/>
+      <c r="F19" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="G19" s="64" t="s">
+      <c r="G19" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="H19" s="64" t="s">
+      <c r="H19" s="59" t="s">
         <v>106</v>
       </c>
-      <c r="I19" s="70" t="s">
+      <c r="I19" s="65" t="s">
         <v>200</v>
       </c>
-      <c r="J19" s="75" t="s">
+      <c r="J19" s="70" t="s">
         <v>199</v>
       </c>
       <c r="K19" t="s">
@@ -3228,32 +4427,32 @@
       </c>
     </row>
     <row r="20" spans="1:12" ht="16">
-      <c r="A20" s="79" t="s">
+      <c r="A20" s="74" t="s">
         <v>184</v>
       </c>
-      <c r="B20" s="80" t="s">
+      <c r="B20" s="75" t="s">
         <v>184</v>
       </c>
-      <c r="C20" s="80" t="s">
+      <c r="C20" s="75" t="s">
         <v>212</v>
       </c>
-      <c r="D20" s="82" t="s">
+      <c r="D20" s="77" t="s">
         <v>200</v>
       </c>
-      <c r="E20" s="55"/>
-      <c r="F20" s="74" t="s">
+      <c r="E20" s="50"/>
+      <c r="F20" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="G20" s="64" t="s">
+      <c r="G20" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="H20" s="64" t="s">
+      <c r="H20" s="59" t="s">
         <v>106</v>
       </c>
-      <c r="I20" s="64" t="s">
+      <c r="I20" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="J20" s="75" t="s">
+      <c r="J20" s="70" t="s">
         <v>199</v>
       </c>
       <c r="K20" t="s">
@@ -3264,32 +4463,32 @@
       </c>
     </row>
     <row r="21" spans="1:12" ht="16">
-      <c r="A21" s="76" t="s">
+      <c r="A21" s="71" t="s">
         <v>193</v>
       </c>
-      <c r="B21" s="66" t="s">
+      <c r="B21" s="61" t="s">
         <v>193</v>
       </c>
-      <c r="C21" s="66" t="s">
+      <c r="C21" s="61" t="s">
         <v>248</v>
       </c>
-      <c r="D21" s="85" t="s">
+      <c r="D21" s="80" t="s">
         <v>200</v>
       </c>
-      <c r="E21" s="55"/>
-      <c r="F21" s="76" t="s">
+      <c r="E21" s="50"/>
+      <c r="F21" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="G21" s="67" t="s">
+      <c r="G21" s="62" t="s">
         <v>130</v>
       </c>
-      <c r="H21" s="66" t="s">
+      <c r="H21" s="61" t="s">
         <v>131</v>
       </c>
-      <c r="I21" s="68" t="s">
+      <c r="I21" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="J21" s="58" t="s">
+      <c r="J21" s="53" t="s">
         <v>199</v>
       </c>
       <c r="K21" t="s">
@@ -3300,31 +4499,31 @@
       </c>
     </row>
     <row r="22" spans="1:12" ht="16">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="F22" s="13" t="s">
+      <c r="F22" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="G22" s="18" t="s">
+      <c r="G22" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="H22" s="18" t="s">
+      <c r="H22" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="I22" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="J22" s="14" t="s">
+      <c r="I22" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="J22" s="12" t="s">
         <v>199</v>
       </c>
       <c r="K22" t="s">
@@ -3335,189 +4534,189 @@
       </c>
     </row>
     <row r="23" spans="1:12" ht="16">
-      <c r="A23" s="22"/>
+      <c r="A23" s="19"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="55"/>
-      <c r="F23" s="51"/>
-      <c r="G23" s="52"/>
-      <c r="H23" s="52"/>
-      <c r="I23" s="52"/>
-      <c r="J23" s="53"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="47"/>
+      <c r="I23" s="47"/>
+      <c r="J23" s="48"/>
     </row>
     <row r="24" spans="1:12" ht="16">
-      <c r="A24" s="22"/>
+      <c r="A24" s="19"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="55"/>
-      <c r="F24" s="51"/>
-      <c r="G24" s="52"/>
-      <c r="H24" s="52"/>
-      <c r="I24" s="52"/>
-      <c r="J24" s="53"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="47"/>
+      <c r="H24" s="47"/>
+      <c r="I24" s="47"/>
+      <c r="J24" s="48"/>
     </row>
     <row r="25" spans="1:12" ht="16">
-      <c r="A25" s="22"/>
+      <c r="A25" s="19"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
-      <c r="D25" s="23"/>
+      <c r="D25" s="20"/>
       <c r="F25" s="7"/>
-      <c r="J25" s="19"/>
+      <c r="J25" s="16"/>
     </row>
     <row r="26" spans="1:12" ht="16">
-      <c r="A26" s="22"/>
+      <c r="A26" s="19"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
-      <c r="D26" s="23"/>
+      <c r="D26" s="20"/>
       <c r="F26" s="7"/>
-      <c r="J26" s="19"/>
+      <c r="J26" s="16"/>
     </row>
     <row r="27" spans="1:12" ht="16">
-      <c r="A27" s="22"/>
+      <c r="A27" s="19"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
-      <c r="D27" s="23"/>
+      <c r="D27" s="20"/>
       <c r="F27" s="7"/>
-      <c r="J27" s="19"/>
+      <c r="J27" s="16"/>
     </row>
     <row r="28" spans="1:12" ht="16">
-      <c r="A28" s="22"/>
+      <c r="A28" s="19"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
-      <c r="D28" s="23"/>
+      <c r="D28" s="20"/>
       <c r="F28" s="7"/>
-      <c r="J28" s="19"/>
+      <c r="J28" s="16"/>
     </row>
     <row r="29" spans="1:12" ht="16">
-      <c r="A29" s="22"/>
+      <c r="A29" s="19"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
-      <c r="D29" s="23"/>
+      <c r="D29" s="20"/>
       <c r="F29" s="7"/>
-      <c r="J29" s="19"/>
+      <c r="J29" s="16"/>
     </row>
     <row r="30" spans="1:12" ht="16">
-      <c r="A30" s="22"/>
+      <c r="A30" s="19"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
-      <c r="D30" s="23"/>
+      <c r="D30" s="20"/>
       <c r="F30" s="7"/>
-      <c r="J30" s="19"/>
+      <c r="J30" s="16"/>
     </row>
     <row r="31" spans="1:12" ht="16">
-      <c r="A31" s="22"/>
+      <c r="A31" s="19"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
-      <c r="D31" s="23"/>
+      <c r="D31" s="20"/>
       <c r="F31" s="7"/>
-      <c r="J31" s="19"/>
+      <c r="J31" s="16"/>
     </row>
     <row r="32" spans="1:12" ht="16">
-      <c r="A32" s="22"/>
+      <c r="A32" s="19"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
-      <c r="D32" s="23"/>
+      <c r="D32" s="20"/>
       <c r="F32" s="7"/>
-      <c r="J32" s="19"/>
+      <c r="J32" s="16"/>
     </row>
     <row r="33" spans="1:10" ht="16">
-      <c r="A33" s="22"/>
+      <c r="A33" s="19"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="23"/>
+      <c r="D33" s="20"/>
       <c r="F33" s="7"/>
-      <c r="J33" s="19"/>
+      <c r="J33" s="16"/>
     </row>
     <row r="34" spans="1:10" ht="16">
-      <c r="A34" s="22"/>
+      <c r="A34" s="19"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
-      <c r="D34" s="23"/>
+      <c r="D34" s="20"/>
       <c r="F34" s="7"/>
-      <c r="J34" s="19"/>
+      <c r="J34" s="16"/>
     </row>
     <row r="35" spans="1:10" ht="16">
-      <c r="A35" s="22"/>
+      <c r="A35" s="19"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
-      <c r="D35" s="23"/>
+      <c r="D35" s="20"/>
       <c r="F35" s="7"/>
-      <c r="J35" s="19"/>
+      <c r="J35" s="16"/>
     </row>
     <row r="36" spans="1:10" ht="16">
-      <c r="A36" s="22"/>
+      <c r="A36" s="19"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
-      <c r="D36" s="23"/>
+      <c r="D36" s="20"/>
       <c r="F36" s="7"/>
-      <c r="J36" s="19"/>
+      <c r="J36" s="16"/>
     </row>
     <row r="37" spans="1:10" ht="16">
-      <c r="A37" s="22"/>
+      <c r="A37" s="19"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
-      <c r="D37" s="23"/>
+      <c r="D37" s="20"/>
       <c r="F37" s="7"/>
-      <c r="J37" s="19"/>
+      <c r="J37" s="16"/>
     </row>
     <row r="38" spans="1:10" ht="16">
-      <c r="A38" s="22"/>
+      <c r="A38" s="19"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
-      <c r="D38" s="23"/>
+      <c r="D38" s="20"/>
       <c r="F38" s="7"/>
-      <c r="J38" s="19"/>
+      <c r="J38" s="16"/>
     </row>
     <row r="39" spans="1:10" ht="16">
-      <c r="A39" s="22"/>
+      <c r="A39" s="19"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
-      <c r="D39" s="23"/>
+      <c r="D39" s="20"/>
       <c r="F39" s="7"/>
-      <c r="J39" s="19"/>
+      <c r="J39" s="16"/>
     </row>
     <row r="40" spans="1:10" ht="16">
-      <c r="A40" s="22"/>
+      <c r="A40" s="19"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
-      <c r="D40" s="23"/>
+      <c r="D40" s="20"/>
       <c r="F40" s="7"/>
-      <c r="J40" s="19"/>
+      <c r="J40" s="16"/>
     </row>
     <row r="41" spans="1:10" ht="16">
-      <c r="A41" s="22"/>
+      <c r="A41" s="19"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
-      <c r="D41" s="23"/>
+      <c r="D41" s="20"/>
       <c r="F41" s="7"/>
-      <c r="J41" s="19"/>
+      <c r="J41" s="16"/>
     </row>
     <row r="42" spans="1:10" ht="16">
-      <c r="A42" s="22"/>
+      <c r="A42" s="19"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
-      <c r="D42" s="23"/>
+      <c r="D42" s="20"/>
       <c r="F42" s="7"/>
-      <c r="J42" s="19"/>
+      <c r="J42" s="16"/>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="7"/>
-      <c r="D43" s="19"/>
+      <c r="D43" s="16"/>
       <c r="F43" s="7"/>
-      <c r="J43" s="19"/>
+      <c r="J43" s="16"/>
     </row>
     <row r="44" spans="1:10" ht="15" thickBot="1">
-      <c r="A44" s="24"/>
-      <c r="B44" s="25"/>
-      <c r="C44" s="25"/>
-      <c r="D44" s="26"/>
-      <c r="F44" s="24"/>
-      <c r="G44" s="25"/>
-      <c r="H44" s="25"/>
-      <c r="I44" s="25"/>
-      <c r="J44" s="26"/>
+      <c r="A44" s="21"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="23"/>
+      <c r="F44" s="21"/>
+      <c r="G44" s="22"/>
+      <c r="H44" s="22"/>
+      <c r="I44" s="22"/>
+      <c r="J44" s="23"/>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="7"/>
@@ -3536,1390 +4735,1390 @@
   <dimension ref="A1:J83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="38.83203125" style="97" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39" style="97" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.1640625" style="97" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.83203125" style="97" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.1640625" style="97" customWidth="1"/>
-    <col min="6" max="6" width="2.1640625" style="97" customWidth="1"/>
-    <col min="7" max="8" width="33.5" style="97" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="33.83203125" style="97" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.83203125" style="97" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.83203125" style="92" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39" style="92" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.1640625" style="92" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.83203125" style="92" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1640625" style="92" customWidth="1"/>
+    <col min="6" max="6" width="2.1640625" style="92" customWidth="1"/>
+    <col min="7" max="8" width="33.5" style="92" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="33.83203125" style="92" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.83203125" style="92" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8.5" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="7.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17" thickBot="1">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="89" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="95" t="s">
+      <c r="B1" s="90" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="95" t="s">
+      <c r="C1" s="90" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="95" t="s">
+      <c r="D1" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="96" t="s">
+      <c r="E1" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="94" t="s">
+      <c r="G1" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="95" t="s">
+      <c r="H1" s="90" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="95" t="s">
+      <c r="I1" s="90" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="96" t="s">
+      <c r="J1" s="91" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="22.75" customHeight="1">
-      <c r="A2" s="105" t="s">
+      <c r="A2" s="100" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="106" t="s">
+      <c r="B2" s="101" t="s">
         <v>108</v>
       </c>
-      <c r="C2" s="107" t="s">
+      <c r="C2" s="102" t="s">
         <v>106</v>
       </c>
-      <c r="D2" s="107" t="s">
-        <v>201</v>
-      </c>
-      <c r="E2" s="108"/>
-      <c r="G2" s="117" t="s">
+      <c r="D2" s="102" t="s">
+        <v>201</v>
+      </c>
+      <c r="E2" s="103"/>
+      <c r="G2" s="112" t="s">
         <v>184</v>
       </c>
-      <c r="H2" s="118" t="s">
+      <c r="H2" s="113" t="s">
         <v>184</v>
       </c>
-      <c r="I2" s="118" t="s">
+      <c r="I2" s="113" t="s">
         <v>203</v>
       </c>
-      <c r="J2" s="119" t="s">
+      <c r="J2" s="114" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="22.75" customHeight="1">
-      <c r="A3" s="109" t="s">
+      <c r="A3" s="104" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="110" t="s">
+      <c r="B3" s="105" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="110" t="s">
+      <c r="C3" s="105" t="s">
         <v>106</v>
       </c>
-      <c r="D3" s="110" t="s">
-        <v>201</v>
-      </c>
-      <c r="E3" s="103"/>
-      <c r="G3" s="117" t="s">
+      <c r="D3" s="105" t="s">
+        <v>201</v>
+      </c>
+      <c r="E3" s="98"/>
+      <c r="G3" s="112" t="s">
         <v>184</v>
       </c>
-      <c r="H3" s="118" t="s">
+      <c r="H3" s="113" t="s">
         <v>184</v>
       </c>
-      <c r="I3" s="118" t="s">
+      <c r="I3" s="113" t="s">
         <v>203</v>
       </c>
-      <c r="J3" s="119" t="s">
+      <c r="J3" s="114" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="22.75" customHeight="1">
-      <c r="A4" s="109" t="s">
+      <c r="A4" s="104" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="110" t="s">
+      <c r="B4" s="105" t="s">
         <v>109</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="105" t="s">
         <v>110</v>
       </c>
-      <c r="D4" s="110" t="s">
-        <v>201</v>
-      </c>
-      <c r="E4" s="103"/>
-      <c r="G4" s="114" t="s">
+      <c r="D4" s="105" t="s">
+        <v>201</v>
+      </c>
+      <c r="E4" s="98"/>
+      <c r="G4" s="109" t="s">
         <v>193</v>
       </c>
-      <c r="H4" s="115" t="s">
+      <c r="H4" s="110" t="s">
         <v>193</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="I4" s="110" t="s">
         <v>208</v>
       </c>
-      <c r="J4" s="116" t="s">
+      <c r="J4" s="111" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="22.75" customHeight="1">
-      <c r="A5" s="111" t="s">
+      <c r="A5" s="106" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="112" t="s">
+      <c r="B5" s="107" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="110" t="s">
+      <c r="C5" s="105" t="s">
         <v>103</v>
       </c>
-      <c r="D5" s="110" t="s">
+      <c r="D5" s="105" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="104"/>
-      <c r="G5" s="124" t="s">
+      <c r="E5" s="99"/>
+      <c r="G5" s="119" t="s">
         <v>193</v>
       </c>
-      <c r="H5" s="125" t="s">
+      <c r="H5" s="120" t="s">
         <v>193</v>
       </c>
-      <c r="I5" s="126" t="s">
+      <c r="I5" s="121" t="s">
         <v>248</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="122" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="22.75" customHeight="1">
-      <c r="A6" s="111" t="s">
+      <c r="A6" s="106" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="110" t="s">
+      <c r="B6" s="105" t="s">
         <v>99</v>
       </c>
-      <c r="C6" s="110" t="s">
+      <c r="C6" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="110" t="s">
+      <c r="D6" s="105" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="103"/>
-      <c r="G6" s="120" t="s">
+      <c r="E6" s="98"/>
+      <c r="G6" s="115" t="s">
         <v>184</v>
       </c>
-      <c r="H6" s="121" t="s">
+      <c r="H6" s="116" t="s">
         <v>184</v>
       </c>
-      <c r="I6" s="122" t="s">
+      <c r="I6" s="117" t="s">
         <v>212</v>
       </c>
-      <c r="J6" s="123" t="s">
+      <c r="J6" s="118" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="22.75" customHeight="1">
-      <c r="A7" s="109" t="s">
+      <c r="A7" s="104" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="110" t="s">
+      <c r="B7" s="105" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="110" t="s">
+      <c r="C7" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="110" t="s">
+      <c r="D7" s="105" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="103"/>
-      <c r="G7" s="120" t="s">
+      <c r="E7" s="98"/>
+      <c r="G7" s="115" t="s">
         <v>184</v>
       </c>
-      <c r="H7" s="121" t="s">
+      <c r="H7" s="116" t="s">
         <v>184</v>
       </c>
-      <c r="I7" s="122" t="s">
+      <c r="I7" s="117" t="s">
         <v>212</v>
       </c>
-      <c r="J7" s="123" t="s">
+      <c r="J7" s="118" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="22.75" customHeight="1">
-      <c r="A8" s="109" t="s">
+      <c r="A8" s="104" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="110" t="s">
+      <c r="B8" s="105" t="s">
         <v>99</v>
       </c>
-      <c r="C8" s="110" t="s">
+      <c r="C8" s="105" t="s">
         <v>321</v>
       </c>
-      <c r="D8" s="110" t="s">
-        <v>201</v>
-      </c>
-      <c r="E8" s="103"/>
-      <c r="G8" s="120" t="s">
+      <c r="D8" s="105" t="s">
+        <v>201</v>
+      </c>
+      <c r="E8" s="98"/>
+      <c r="G8" s="115" t="s">
         <v>184</v>
       </c>
-      <c r="H8" s="121" t="s">
+      <c r="H8" s="116" t="s">
         <v>184</v>
       </c>
-      <c r="I8" s="122" t="s">
+      <c r="I8" s="117" t="s">
         <v>212</v>
       </c>
-      <c r="J8" s="123" t="s">
+      <c r="J8" s="118" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="22.75" customHeight="1">
-      <c r="A9" s="109" t="s">
+      <c r="A9" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="110" t="s">
+      <c r="B9" s="105" t="s">
         <v>99</v>
       </c>
-      <c r="C9" s="110" t="s">
+      <c r="C9" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="110" t="s">
-        <v>201</v>
-      </c>
-      <c r="E9" s="102"/>
-      <c r="G9" s="120" t="s">
+      <c r="D9" s="105" t="s">
+        <v>201</v>
+      </c>
+      <c r="E9" s="97"/>
+      <c r="G9" s="115" t="s">
         <v>184</v>
       </c>
-      <c r="H9" s="121" t="s">
+      <c r="H9" s="116" t="s">
         <v>184</v>
       </c>
-      <c r="I9" s="122" t="s">
+      <c r="I9" s="117" t="s">
         <v>212</v>
       </c>
-      <c r="J9" s="123" t="s">
+      <c r="J9" s="118" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="22.75" customHeight="1">
-      <c r="A10" s="109" t="s">
+      <c r="A10" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="112" t="s">
+      <c r="B10" s="107" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="110" t="s">
+      <c r="C10" s="105" t="s">
         <v>103</v>
       </c>
-      <c r="D10" s="110" t="s">
-        <v>201</v>
-      </c>
-      <c r="E10" s="102"/>
-      <c r="G10" s="124" t="s">
+      <c r="D10" s="105" t="s">
+        <v>201</v>
+      </c>
+      <c r="E10" s="97"/>
+      <c r="G10" s="119" t="s">
         <v>193</v>
       </c>
-      <c r="H10" s="125" t="s">
+      <c r="H10" s="120" t="s">
         <v>193</v>
       </c>
-      <c r="I10" s="126" t="s">
+      <c r="I10" s="121" t="s">
         <v>248</v>
       </c>
-      <c r="J10" s="127" t="s">
+      <c r="J10" s="122" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="22.75" customHeight="1">
-      <c r="A11" s="109" t="s">
+      <c r="A11" s="104" t="s">
         <v>57</v>
       </c>
-      <c r="B11" s="110" t="s">
+      <c r="B11" s="105" t="s">
         <v>124</v>
       </c>
-      <c r="C11" s="110" t="s">
+      <c r="C11" s="105" t="s">
         <v>125</v>
       </c>
-      <c r="D11" s="110" t="s">
+      <c r="D11" s="105" t="s">
         <v>200</v>
       </c>
-      <c r="E11" s="103"/>
-      <c r="G11" s="98"/>
-      <c r="J11" s="93"/>
+      <c r="E11" s="98"/>
+      <c r="G11" s="93"/>
+      <c r="J11" s="88"/>
     </row>
     <row r="12" spans="1:10" ht="22.75" customHeight="1">
-      <c r="A12" s="109" t="s">
+      <c r="A12" s="104" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="110" t="s">
+      <c r="B12" s="105" t="s">
         <v>121</v>
       </c>
-      <c r="C12" s="110" t="s">
+      <c r="C12" s="105" t="s">
         <v>122</v>
       </c>
-      <c r="D12" s="110" t="s">
+      <c r="D12" s="105" t="s">
         <v>200</v>
       </c>
-      <c r="E12" s="102"/>
-      <c r="G12" s="128" t="s">
+      <c r="E12" s="97"/>
+      <c r="G12" s="123" t="s">
         <v>182</v>
       </c>
-      <c r="H12" s="129" t="s">
+      <c r="H12" s="124" t="s">
         <v>182</v>
       </c>
-      <c r="I12" s="130" t="s">
+      <c r="I12" s="125" t="s">
         <v>232</v>
       </c>
-      <c r="J12" s="131" t="s">
+      <c r="J12" s="126" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="22.75" customHeight="1">
-      <c r="A13" s="109" t="s">
+      <c r="A13" s="104" t="s">
         <v>58</v>
       </c>
-      <c r="B13" s="112" t="s">
+      <c r="B13" s="107" t="s">
         <v>127</v>
       </c>
-      <c r="C13" s="113" t="s">
+      <c r="C13" s="108" t="s">
         <v>128</v>
       </c>
-      <c r="D13" s="110" t="s">
+      <c r="D13" s="105" t="s">
         <v>200</v>
       </c>
-      <c r="E13" s="104"/>
-      <c r="G13" s="133" t="s">
+      <c r="E13" s="99"/>
+      <c r="G13" s="128" t="s">
         <v>191</v>
       </c>
-      <c r="H13" s="134" t="s">
+      <c r="H13" s="129" t="s">
         <v>191</v>
       </c>
-      <c r="I13" s="135" t="s">
+      <c r="I13" s="130" t="s">
         <v>245</v>
       </c>
-      <c r="J13" s="136" t="s">
+      <c r="J13" s="131" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="22.75" customHeight="1">
-      <c r="A14" s="109" t="s">
+      <c r="A14" s="104" t="s">
         <v>60</v>
       </c>
-      <c r="B14" s="110" t="s">
+      <c r="B14" s="105" t="s">
         <v>133</v>
       </c>
-      <c r="C14" s="110" t="s">
+      <c r="C14" s="105" t="s">
         <v>134</v>
       </c>
-      <c r="D14" s="110" t="s">
+      <c r="D14" s="105" t="s">
         <v>200</v>
       </c>
-      <c r="E14" s="103"/>
-      <c r="G14" s="120" t="s">
+      <c r="E14" s="98"/>
+      <c r="G14" s="115" t="s">
         <v>184</v>
       </c>
-      <c r="H14" s="121" t="s">
+      <c r="H14" s="116" t="s">
         <v>184</v>
       </c>
-      <c r="I14" s="122" t="s">
+      <c r="I14" s="117" t="s">
         <v>212</v>
       </c>
-      <c r="J14" s="123" t="s">
+      <c r="J14" s="118" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="22.75" customHeight="1">
-      <c r="A15" s="109" t="s">
+      <c r="A15" s="104" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="112" t="s">
+      <c r="B15" s="107" t="s">
         <v>130</v>
       </c>
-      <c r="C15" s="113" t="s">
+      <c r="C15" s="108" t="s">
         <v>131</v>
       </c>
-      <c r="D15" s="112" t="s">
+      <c r="D15" s="107" t="s">
         <v>200</v>
       </c>
-      <c r="E15" s="103"/>
-      <c r="G15" s="114" t="s">
+      <c r="E15" s="98"/>
+      <c r="G15" s="109" t="s">
         <v>193</v>
       </c>
-      <c r="H15" s="115" t="s">
+      <c r="H15" s="110" t="s">
         <v>193</v>
       </c>
-      <c r="I15" s="115" t="s">
+      <c r="I15" s="110" t="s">
         <v>208</v>
       </c>
-      <c r="J15" s="116" t="s">
+      <c r="J15" s="111" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="22.75" customHeight="1">
-      <c r="A16" s="109" t="s">
+      <c r="A16" s="104" t="s">
         <v>61</v>
       </c>
-      <c r="B16" s="110" t="s">
+      <c r="B16" s="105" t="s">
         <v>136</v>
       </c>
-      <c r="C16" s="110" t="s">
+      <c r="C16" s="105" t="s">
         <v>137</v>
       </c>
-      <c r="D16" s="113" t="s">
+      <c r="D16" s="108" t="s">
         <v>200</v>
       </c>
-      <c r="E16" s="103"/>
-      <c r="G16" s="128" t="s">
+      <c r="E16" s="98"/>
+      <c r="G16" s="123" t="s">
         <v>182</v>
       </c>
-      <c r="H16" s="129" t="s">
+      <c r="H16" s="124" t="s">
         <v>182</v>
       </c>
-      <c r="I16" s="130" t="s">
+      <c r="I16" s="125" t="s">
         <v>232</v>
       </c>
-      <c r="J16" s="131" t="s">
+      <c r="J16" s="126" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="22.75" customHeight="1">
-      <c r="A17" s="109" t="s">
+      <c r="A17" s="104" t="s">
         <v>62</v>
       </c>
-      <c r="B17" s="110" t="s">
+      <c r="B17" s="105" t="s">
         <v>166</v>
       </c>
-      <c r="C17" s="110" t="s">
+      <c r="C17" s="105" t="s">
         <v>322</v>
       </c>
-      <c r="D17" s="113" t="s">
-        <v>201</v>
-      </c>
-      <c r="E17" s="103"/>
-      <c r="G17" s="32" t="s">
+      <c r="D17" s="108" t="s">
+        <v>201</v>
+      </c>
+      <c r="E17" s="98"/>
+      <c r="G17" s="27" t="s">
         <v>196</v>
       </c>
-      <c r="H17" s="32" t="s">
+      <c r="H17" s="27" t="s">
         <v>196</v>
       </c>
-      <c r="I17" s="49" t="s">
+      <c r="I17" s="44" t="s">
         <v>210</v>
       </c>
-      <c r="J17" s="137" t="s">
+      <c r="J17" s="132" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="22.75" customHeight="1">
-      <c r="A18" s="109" t="s">
+      <c r="A18" s="104" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="112" t="s">
+      <c r="B18" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="C18" s="112" t="s">
+      <c r="C18" s="107" t="s">
         <v>106</v>
       </c>
-      <c r="D18" s="112" t="s">
-        <v>201</v>
-      </c>
-      <c r="E18" s="103"/>
-      <c r="G18" s="117" t="s">
+      <c r="D18" s="107" t="s">
+        <v>201</v>
+      </c>
+      <c r="E18" s="98"/>
+      <c r="G18" s="112" t="s">
         <v>184</v>
       </c>
-      <c r="H18" s="118" t="s">
+      <c r="H18" s="113" t="s">
         <v>184</v>
       </c>
-      <c r="I18" s="118" t="s">
+      <c r="I18" s="113" t="s">
         <v>203</v>
       </c>
-      <c r="J18" s="119" t="s">
+      <c r="J18" s="114" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="16">
-      <c r="A19" s="109" t="s">
+      <c r="A19" s="104" t="s">
         <v>64</v>
       </c>
-      <c r="B19" s="110" t="s">
+      <c r="B19" s="105" t="s">
         <v>139</v>
       </c>
-      <c r="C19" s="110" t="s">
+      <c r="C19" s="105" t="s">
         <v>140</v>
       </c>
-      <c r="D19" s="112" t="s">
-        <v>201</v>
-      </c>
-      <c r="E19" s="103"/>
-      <c r="G19" s="138" t="s">
+      <c r="D19" s="107" t="s">
+        <v>201</v>
+      </c>
+      <c r="E19" s="98"/>
+      <c r="G19" s="133" t="s">
         <v>182</v>
       </c>
-      <c r="H19" s="139" t="s">
+      <c r="H19" s="134" t="s">
         <v>182</v>
       </c>
-      <c r="I19" s="139" t="s">
+      <c r="I19" s="134" t="s">
         <v>211</v>
       </c>
-      <c r="J19" s="140" t="s">
+      <c r="J19" s="135" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="16">
-      <c r="A20" s="109" t="s">
+      <c r="A20" s="104" t="s">
         <v>65</v>
       </c>
-      <c r="B20" s="110" t="s">
+      <c r="B20" s="105" t="s">
         <v>142</v>
       </c>
-      <c r="C20" s="110" t="s">
+      <c r="C20" s="105" t="s">
         <v>323</v>
       </c>
-      <c r="D20" s="112" t="s">
-        <v>201</v>
-      </c>
-      <c r="E20" s="103"/>
-      <c r="G20" s="138" t="s">
+      <c r="D20" s="107" t="s">
+        <v>201</v>
+      </c>
+      <c r="E20" s="98"/>
+      <c r="G20" s="133" t="s">
         <v>182</v>
       </c>
-      <c r="H20" s="139" t="s">
+      <c r="H20" s="134" t="s">
         <v>182</v>
       </c>
-      <c r="I20" s="139" t="s">
+      <c r="I20" s="134" t="s">
         <v>211</v>
       </c>
-      <c r="J20" s="140" t="s">
+      <c r="J20" s="135" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="16">
-      <c r="A21" s="109" t="s">
+      <c r="A21" s="104" t="s">
         <v>66</v>
       </c>
-      <c r="B21" s="110" t="s">
+      <c r="B21" s="105" t="s">
         <v>169</v>
       </c>
-      <c r="C21" s="110" t="s">
+      <c r="C21" s="105" t="s">
         <v>110</v>
       </c>
-      <c r="D21" s="110" t="s">
-        <v>201</v>
-      </c>
-      <c r="E21" s="102"/>
-      <c r="G21" s="114" t="s">
+      <c r="D21" s="105" t="s">
+        <v>201</v>
+      </c>
+      <c r="E21" s="97"/>
+      <c r="G21" s="109" t="s">
         <v>193</v>
       </c>
-      <c r="H21" s="115" t="s">
+      <c r="H21" s="110" t="s">
         <v>193</v>
       </c>
-      <c r="I21" s="115" t="s">
+      <c r="I21" s="110" t="s">
         <v>208</v>
       </c>
-      <c r="J21" s="116" t="s">
+      <c r="J21" s="111" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="16">
-      <c r="A22" s="109" t="s">
+      <c r="A22" s="104" t="s">
         <v>68</v>
       </c>
-      <c r="B22" s="110" t="s">
+      <c r="B22" s="105" t="s">
         <v>153</v>
       </c>
-      <c r="C22" s="110" t="s">
+      <c r="C22" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="110" t="s">
-        <v>201</v>
-      </c>
-      <c r="E22" s="102"/>
-      <c r="G22" s="144" t="s">
+      <c r="D22" s="105" t="s">
+        <v>201</v>
+      </c>
+      <c r="E22" s="97"/>
+      <c r="G22" s="139" t="s">
         <v>195</v>
       </c>
-      <c r="H22" s="145" t="s">
+      <c r="H22" s="140" t="s">
         <v>195</v>
       </c>
-      <c r="I22" s="146" t="s">
+      <c r="I22" s="141" t="s">
         <v>232</v>
       </c>
-      <c r="J22" s="147" t="s">
+      <c r="J22" s="142" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="16">
-      <c r="A23" s="111" t="s">
+      <c r="A23" s="106" t="s">
         <v>69</v>
       </c>
-      <c r="B23" s="110" t="s">
+      <c r="B23" s="105" t="s">
         <v>202</v>
       </c>
-      <c r="C23" s="110" t="s">
+      <c r="C23" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="D23" s="110" t="s">
+      <c r="D23" s="105" t="s">
         <v>24</v>
       </c>
-      <c r="E23" s="103"/>
-      <c r="G23" s="120" t="s">
+      <c r="E23" s="98"/>
+      <c r="G23" s="115" t="s">
         <v>184</v>
       </c>
-      <c r="H23" s="121" t="s">
+      <c r="H23" s="116" t="s">
         <v>184</v>
       </c>
-      <c r="I23" s="122" t="s">
+      <c r="I23" s="117" t="s">
         <v>212</v>
       </c>
-      <c r="J23" s="123" t="s">
+      <c r="J23" s="118" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="16">
-      <c r="A24" s="109" t="s">
+      <c r="A24" s="104" t="s">
         <v>70</v>
       </c>
-      <c r="B24" s="110" t="s">
+      <c r="B24" s="105" t="s">
         <v>143</v>
       </c>
-      <c r="C24" s="110" t="s">
+      <c r="C24" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="112" t="s">
+      <c r="D24" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="E24" s="103"/>
-      <c r="G24" s="128" t="s">
+      <c r="E24" s="98"/>
+      <c r="G24" s="123" t="s">
         <v>182</v>
       </c>
-      <c r="H24" s="129" t="s">
+      <c r="H24" s="124" t="s">
         <v>182</v>
       </c>
-      <c r="I24" s="130" t="s">
+      <c r="I24" s="125" t="s">
         <v>232</v>
       </c>
-      <c r="J24" s="131" t="s">
+      <c r="J24" s="126" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="16">
-      <c r="A25" s="109" t="s">
+      <c r="A25" s="104" t="s">
         <v>71</v>
       </c>
-      <c r="B25" s="112" t="s">
+      <c r="B25" s="107" t="s">
         <v>145</v>
       </c>
-      <c r="C25" s="112" t="s">
+      <c r="C25" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="112" t="s">
+      <c r="D25" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="E25" s="103"/>
-      <c r="G25" s="128" t="s">
+      <c r="E25" s="98"/>
+      <c r="G25" s="123" t="s">
         <v>182</v>
       </c>
-      <c r="H25" s="129" t="s">
+      <c r="H25" s="124" t="s">
         <v>182</v>
       </c>
-      <c r="I25" s="130" t="s">
+      <c r="I25" s="125" t="s">
         <v>232</v>
       </c>
-      <c r="J25" s="131" t="s">
+      <c r="J25" s="126" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="16">
-      <c r="A26" s="109" t="s">
+      <c r="A26" s="104" t="s">
         <v>72</v>
       </c>
-      <c r="B26" s="110" t="s">
+      <c r="B26" s="105" t="s">
         <v>146</v>
       </c>
-      <c r="C26" s="110" t="s">
+      <c r="C26" s="105" t="s">
         <v>103</v>
       </c>
-      <c r="D26" s="113" t="s">
+      <c r="D26" s="108" t="s">
         <v>24</v>
       </c>
-      <c r="E26" s="104"/>
-      <c r="G26" s="120"/>
-      <c r="H26" s="121"/>
-      <c r="I26" s="122"/>
-      <c r="J26" s="123"/>
+      <c r="E26" s="99"/>
+      <c r="G26" s="115"/>
+      <c r="H26" s="116"/>
+      <c r="I26" s="117"/>
+      <c r="J26" s="118"/>
     </row>
     <row r="27" spans="1:10" ht="16">
-      <c r="A27" s="109" t="s">
+      <c r="A27" s="104" t="s">
         <v>73</v>
       </c>
-      <c r="B27" s="110" t="s">
+      <c r="B27" s="105" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="110" t="s">
+      <c r="C27" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="D27" s="112" t="s">
+      <c r="D27" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="E27" s="103"/>
-      <c r="G27" s="120" t="s">
+      <c r="E27" s="98"/>
+      <c r="G27" s="115" t="s">
         <v>184</v>
       </c>
-      <c r="H27" s="121" t="s">
+      <c r="H27" s="116" t="s">
         <v>184</v>
       </c>
-      <c r="I27" s="122" t="s">
+      <c r="I27" s="117" t="s">
         <v>212</v>
       </c>
-      <c r="J27" s="123" t="s">
+      <c r="J27" s="118" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="16">
-      <c r="A28" s="111" t="s">
+      <c r="A28" s="106" t="s">
         <v>74</v>
       </c>
-      <c r="B28" s="112" t="s">
+      <c r="B28" s="107" t="s">
         <v>147</v>
       </c>
-      <c r="C28" s="112" t="s">
+      <c r="C28" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="D28" s="113" t="s">
+      <c r="D28" s="108" t="s">
         <v>24</v>
       </c>
-      <c r="E28" s="104"/>
-      <c r="G28" s="120" t="s">
+      <c r="E28" s="99"/>
+      <c r="G28" s="115" t="s">
         <v>184</v>
       </c>
-      <c r="H28" s="121" t="s">
+      <c r="H28" s="116" t="s">
         <v>184</v>
       </c>
-      <c r="I28" s="122" t="s">
+      <c r="I28" s="117" t="s">
         <v>212</v>
       </c>
-      <c r="J28" s="123" t="s">
+      <c r="J28" s="118" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="16">
-      <c r="A29" s="109" t="s">
+      <c r="A29" s="104" t="s">
         <v>75</v>
       </c>
-      <c r="B29" s="110" t="s">
+      <c r="B29" s="105" t="s">
         <v>150</v>
       </c>
-      <c r="C29" s="110" t="s">
+      <c r="C29" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="110" t="s">
+      <c r="D29" s="105" t="s">
         <v>24</v>
       </c>
-      <c r="E29" s="102"/>
-      <c r="G29" s="141" t="s">
+      <c r="E29" s="97"/>
+      <c r="G29" s="136" t="s">
         <v>182</v>
       </c>
-      <c r="H29" s="142" t="s">
+      <c r="H29" s="137" t="s">
         <v>182</v>
       </c>
-      <c r="I29" s="132" t="s">
+      <c r="I29" s="127" t="s">
         <v>232</v>
       </c>
-      <c r="J29" s="143" t="s">
+      <c r="J29" s="138" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="16">
-      <c r="A30" s="111" t="s">
+      <c r="A30" s="106" t="s">
         <v>76</v>
       </c>
-      <c r="B30" s="112" t="s">
+      <c r="B30" s="107" t="s">
         <v>152</v>
       </c>
-      <c r="C30" s="110" t="s">
+      <c r="C30" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="D30" s="112" t="s">
+      <c r="D30" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="E30" s="103"/>
-      <c r="G30" s="141" t="s">
+      <c r="E30" s="98"/>
+      <c r="G30" s="136" t="s">
         <v>182</v>
       </c>
-      <c r="H30" s="142" t="s">
+      <c r="H30" s="137" t="s">
         <v>182</v>
       </c>
-      <c r="I30" s="132" t="s">
+      <c r="I30" s="127" t="s">
         <v>232</v>
       </c>
-      <c r="J30" s="143" t="s">
+      <c r="J30" s="138" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="16">
-      <c r="A31" s="109" t="s">
+      <c r="A31" s="104" t="s">
         <v>78</v>
       </c>
-      <c r="B31" s="110" t="s">
+      <c r="B31" s="105" t="s">
         <v>157</v>
       </c>
-      <c r="C31" s="110" t="s">
+      <c r="C31" s="105" t="s">
         <v>106</v>
       </c>
-      <c r="D31" s="113" t="s">
-        <v>201</v>
-      </c>
-      <c r="E31" s="104"/>
-      <c r="G31" s="117" t="s">
+      <c r="D31" s="108" t="s">
+        <v>201</v>
+      </c>
+      <c r="E31" s="99"/>
+      <c r="G31" s="112" t="s">
         <v>184</v>
       </c>
-      <c r="H31" s="118" t="s">
+      <c r="H31" s="113" t="s">
         <v>184</v>
       </c>
-      <c r="I31" s="118" t="s">
+      <c r="I31" s="113" t="s">
         <v>203</v>
       </c>
-      <c r="J31" s="119" t="s">
+      <c r="J31" s="114" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="16">
-      <c r="A32" s="109" t="s">
+      <c r="A32" s="104" t="s">
         <v>77</v>
       </c>
-      <c r="B32" s="110" t="s">
+      <c r="B32" s="105" t="s">
         <v>156</v>
       </c>
-      <c r="C32" s="110" t="s">
+      <c r="C32" s="105" t="s">
         <v>322</v>
       </c>
-      <c r="D32" s="110" t="s">
-        <v>201</v>
-      </c>
-      <c r="E32" s="102"/>
-      <c r="G32" s="117" t="s">
+      <c r="D32" s="105" t="s">
+        <v>201</v>
+      </c>
+      <c r="E32" s="97"/>
+      <c r="G32" s="112" t="s">
         <v>184</v>
       </c>
-      <c r="H32" s="118" t="s">
+      <c r="H32" s="113" t="s">
         <v>184</v>
       </c>
-      <c r="I32" s="118" t="s">
+      <c r="I32" s="113" t="s">
         <v>203</v>
       </c>
-      <c r="J32" s="119" t="s">
+      <c r="J32" s="114" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="16">
-      <c r="A33" s="109" t="s">
+      <c r="A33" s="104" t="s">
         <v>80</v>
       </c>
-      <c r="B33" s="110" t="s">
+      <c r="B33" s="105" t="s">
         <v>160</v>
       </c>
-      <c r="C33" s="110" t="s">
+      <c r="C33" s="105" t="s">
         <v>161</v>
       </c>
-      <c r="D33" s="113" t="s">
-        <v>201</v>
-      </c>
-      <c r="E33" s="104"/>
-      <c r="G33" s="138" t="s">
+      <c r="D33" s="108" t="s">
+        <v>201</v>
+      </c>
+      <c r="E33" s="99"/>
+      <c r="G33" s="133" t="s">
         <v>182</v>
       </c>
-      <c r="H33" s="139" t="s">
+      <c r="H33" s="134" t="s">
         <v>182</v>
       </c>
-      <c r="I33" s="139" t="s">
+      <c r="I33" s="134" t="s">
         <v>211</v>
       </c>
-      <c r="J33" s="140" t="s">
+      <c r="J33" s="135" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="16">
-      <c r="A34" s="109" t="s">
+      <c r="A34" s="104" t="s">
         <v>81</v>
       </c>
-      <c r="B34" s="112" t="s">
+      <c r="B34" s="107" t="s">
         <v>163</v>
       </c>
-      <c r="C34" s="110" t="s">
+      <c r="C34" s="105" t="s">
         <v>324</v>
       </c>
-      <c r="D34" s="113" t="s">
-        <v>201</v>
-      </c>
-      <c r="E34" s="104"/>
-      <c r="G34" s="138" t="s">
+      <c r="D34" s="108" t="s">
+        <v>201</v>
+      </c>
+      <c r="E34" s="99"/>
+      <c r="G34" s="133" t="s">
         <v>182</v>
       </c>
-      <c r="H34" s="139" t="s">
+      <c r="H34" s="134" t="s">
         <v>182</v>
       </c>
-      <c r="I34" s="139" t="s">
+      <c r="I34" s="134" t="s">
         <v>211</v>
       </c>
-      <c r="J34" s="140" t="s">
+      <c r="J34" s="135" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="16">
-      <c r="A35" s="109" t="s">
+      <c r="A35" s="104" t="s">
         <v>82</v>
       </c>
-      <c r="B35" s="110" t="s">
+      <c r="B35" s="105" t="s">
         <v>164</v>
       </c>
-      <c r="C35" s="110" t="s">
+      <c r="C35" s="105" t="s">
         <v>106</v>
       </c>
-      <c r="D35" s="113" t="s">
-        <v>201</v>
-      </c>
-      <c r="E35" s="104"/>
-      <c r="G35" s="98"/>
-      <c r="J35" s="93"/>
+      <c r="D35" s="108" t="s">
+        <v>201</v>
+      </c>
+      <c r="E35" s="99"/>
+      <c r="G35" s="93"/>
+      <c r="J35" s="88"/>
     </row>
     <row r="36" spans="1:10" ht="16">
-      <c r="A36" s="109" t="s">
+      <c r="A36" s="104" t="s">
         <v>83</v>
       </c>
-      <c r="B36" s="110" t="s">
+      <c r="B36" s="105" t="s">
         <v>153</v>
       </c>
-      <c r="C36" s="110" t="s">
+      <c r="C36" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="D36" s="113" t="s">
-        <v>201</v>
-      </c>
-      <c r="E36" s="104"/>
-      <c r="G36" s="144" t="s">
+      <c r="D36" s="108" t="s">
+        <v>201</v>
+      </c>
+      <c r="E36" s="99"/>
+      <c r="G36" s="139" t="s">
         <v>195</v>
       </c>
-      <c r="H36" s="145" t="s">
+      <c r="H36" s="140" t="s">
         <v>195</v>
       </c>
-      <c r="I36" s="146" t="s">
+      <c r="I36" s="141" t="s">
         <v>232</v>
       </c>
-      <c r="J36" s="147" t="s">
+      <c r="J36" s="142" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="16">
-      <c r="A37" s="109" t="s">
+      <c r="A37" s="104" t="s">
         <v>85</v>
       </c>
-      <c r="B37" s="110" t="s">
+      <c r="B37" s="105" t="s">
         <v>143</v>
       </c>
-      <c r="C37" s="110" t="s">
+      <c r="C37" s="105" t="s">
         <v>321</v>
       </c>
-      <c r="D37" s="113" t="s">
-        <v>201</v>
-      </c>
-      <c r="E37" s="104"/>
-      <c r="G37" s="141" t="s">
+      <c r="D37" s="108" t="s">
+        <v>201</v>
+      </c>
+      <c r="E37" s="99"/>
+      <c r="G37" s="136" t="s">
         <v>182</v>
       </c>
-      <c r="H37" s="142" t="s">
+      <c r="H37" s="137" t="s">
         <v>182</v>
       </c>
-      <c r="I37" s="132" t="s">
+      <c r="I37" s="127" t="s">
         <v>232</v>
       </c>
-      <c r="J37" s="143" t="s">
+      <c r="J37" s="138" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="16">
-      <c r="A38" s="109" t="s">
+      <c r="A38" s="104" t="s">
         <v>84</v>
       </c>
-      <c r="B38" s="110" t="s">
+      <c r="B38" s="105" t="s">
         <v>202</v>
       </c>
-      <c r="C38" s="110" t="s">
+      <c r="C38" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="D38" s="113" t="s">
-        <v>201</v>
-      </c>
-      <c r="E38" s="104"/>
-      <c r="G38" s="120" t="s">
+      <c r="D38" s="108" t="s">
+        <v>201</v>
+      </c>
+      <c r="E38" s="99"/>
+      <c r="G38" s="115" t="s">
         <v>184</v>
       </c>
-      <c r="H38" s="121" t="s">
+      <c r="H38" s="116" t="s">
         <v>184</v>
       </c>
-      <c r="I38" s="122" t="s">
+      <c r="I38" s="117" t="s">
         <v>212</v>
       </c>
-      <c r="J38" s="123" t="s">
+      <c r="J38" s="118" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="16">
-      <c r="A39" s="109" t="s">
+      <c r="A39" s="104" t="s">
         <v>89</v>
       </c>
-      <c r="B39" s="112" t="s">
+      <c r="B39" s="107" t="s">
         <v>147</v>
       </c>
-      <c r="C39" s="112" t="s">
+      <c r="C39" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="D39" s="113" t="s">
-        <v>201</v>
-      </c>
-      <c r="E39" s="104"/>
-      <c r="G39" s="120" t="s">
+      <c r="D39" s="108" t="s">
+        <v>201</v>
+      </c>
+      <c r="E39" s="99"/>
+      <c r="G39" s="115" t="s">
         <v>184</v>
       </c>
-      <c r="H39" s="121" t="s">
+      <c r="H39" s="116" t="s">
         <v>184</v>
       </c>
-      <c r="I39" s="122" t="s">
+      <c r="I39" s="117" t="s">
         <v>212</v>
       </c>
-      <c r="J39" s="123" t="s">
+      <c r="J39" s="118" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="16">
-      <c r="A40" s="109" t="s">
+      <c r="A40" s="104" t="s">
         <v>86</v>
       </c>
-      <c r="B40" s="112" t="s">
+      <c r="B40" s="107" t="s">
         <v>145</v>
       </c>
-      <c r="C40" s="110" t="s">
+      <c r="C40" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="D40" s="113" t="s">
-        <v>201</v>
-      </c>
-      <c r="E40" s="104"/>
-      <c r="G40" s="141" t="s">
+      <c r="D40" s="108" t="s">
+        <v>201</v>
+      </c>
+      <c r="E40" s="99"/>
+      <c r="G40" s="136" t="s">
         <v>182</v>
       </c>
-      <c r="H40" s="142" t="s">
+      <c r="H40" s="137" t="s">
         <v>182</v>
       </c>
-      <c r="I40" s="132" t="s">
+      <c r="I40" s="127" t="s">
         <v>232</v>
       </c>
-      <c r="J40" s="143" t="s">
+      <c r="J40" s="138" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="16">
-      <c r="A41" s="109" t="s">
+      <c r="A41" s="104" t="s">
         <v>90</v>
       </c>
-      <c r="B41" s="110" t="s">
+      <c r="B41" s="105" t="s">
         <v>150</v>
       </c>
-      <c r="C41" s="110" t="s">
+      <c r="C41" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="D41" s="113" t="s">
-        <v>201</v>
-      </c>
-      <c r="E41" s="104"/>
-      <c r="G41" s="141" t="s">
+      <c r="D41" s="108" t="s">
+        <v>201</v>
+      </c>
+      <c r="E41" s="99"/>
+      <c r="G41" s="136" t="s">
         <v>182</v>
       </c>
-      <c r="H41" s="142" t="s">
+      <c r="H41" s="137" t="s">
         <v>182</v>
       </c>
-      <c r="I41" s="132" t="s">
+      <c r="I41" s="127" t="s">
         <v>232</v>
       </c>
-      <c r="J41" s="143" t="s">
+      <c r="J41" s="138" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="16">
-      <c r="A42" s="109" t="s">
+      <c r="A42" s="104" t="s">
         <v>87</v>
       </c>
-      <c r="B42" s="110" t="s">
+      <c r="B42" s="105" t="s">
         <v>146</v>
       </c>
-      <c r="C42" s="110" t="s">
+      <c r="C42" s="105" t="s">
         <v>103</v>
       </c>
-      <c r="D42" s="113" t="s">
-        <v>201</v>
-      </c>
-      <c r="E42" s="104"/>
-      <c r="G42" s="124" t="s">
+      <c r="D42" s="108" t="s">
+        <v>201</v>
+      </c>
+      <c r="E42" s="99"/>
+      <c r="G42" s="119" t="s">
         <v>193</v>
       </c>
-      <c r="H42" s="125" t="s">
+      <c r="H42" s="120" t="s">
         <v>193</v>
       </c>
-      <c r="I42" s="126" t="s">
+      <c r="I42" s="121" t="s">
         <v>248</v>
       </c>
-      <c r="J42" s="127" t="s">
+      <c r="J42" s="122" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="16">
-      <c r="A43" s="109" t="s">
+      <c r="A43" s="104" t="s">
         <v>91</v>
       </c>
-      <c r="B43" s="112" t="s">
+      <c r="B43" s="107" t="s">
         <v>152</v>
       </c>
-      <c r="C43" s="110" t="s">
+      <c r="C43" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="D43" s="113" t="s">
-        <v>201</v>
-      </c>
-      <c r="E43" s="104"/>
-      <c r="G43" s="141" t="s">
+      <c r="D43" s="108" t="s">
+        <v>201</v>
+      </c>
+      <c r="E43" s="99"/>
+      <c r="G43" s="136" t="s">
         <v>182</v>
       </c>
-      <c r="H43" s="142" t="s">
+      <c r="H43" s="137" t="s">
         <v>182</v>
       </c>
-      <c r="I43" s="132" t="s">
+      <c r="I43" s="127" t="s">
         <v>232</v>
       </c>
-      <c r="J43" s="143" t="s">
+      <c r="J43" s="138" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="16">
-      <c r="A44" s="109" t="s">
+      <c r="A44" s="104" t="s">
         <v>88</v>
       </c>
-      <c r="B44" s="110" t="s">
+      <c r="B44" s="105" t="s">
         <v>22</v>
       </c>
-      <c r="C44" s="110" t="s">
+      <c r="C44" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="D44" s="113" t="s">
-        <v>201</v>
-      </c>
-      <c r="E44" s="104"/>
-      <c r="G44" s="120" t="s">
+      <c r="D44" s="108" t="s">
+        <v>201</v>
+      </c>
+      <c r="E44" s="99"/>
+      <c r="G44" s="115" t="s">
         <v>184</v>
       </c>
-      <c r="H44" s="121" t="s">
+      <c r="H44" s="116" t="s">
         <v>184</v>
       </c>
-      <c r="I44" s="122" t="s">
+      <c r="I44" s="117" t="s">
         <v>212</v>
       </c>
-      <c r="J44" s="123" t="s">
+      <c r="J44" s="118" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="16">
-      <c r="A45" s="98"/>
-      <c r="E45" s="93"/>
-      <c r="G45" s="148"/>
-      <c r="H45" s="149"/>
-      <c r="I45" s="149"/>
-      <c r="J45" s="150"/>
+      <c r="A45" s="93"/>
+      <c r="E45" s="88"/>
+      <c r="G45" s="143"/>
+      <c r="H45" s="144"/>
+      <c r="I45" s="144"/>
+      <c r="J45" s="145"/>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="98"/>
-      <c r="E46" s="93"/>
-      <c r="G46" s="98"/>
-      <c r="J46" s="93"/>
+      <c r="A46" s="93"/>
+      <c r="E46" s="88"/>
+      <c r="G46" s="93"/>
+      <c r="J46" s="88"/>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="98"/>
-      <c r="E47" s="93"/>
-      <c r="G47" s="98"/>
-      <c r="J47" s="93"/>
+      <c r="A47" s="93"/>
+      <c r="E47" s="88"/>
+      <c r="G47" s="93"/>
+      <c r="J47" s="88"/>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="98"/>
-      <c r="E48" s="93"/>
-      <c r="G48" s="98"/>
-      <c r="J48" s="93"/>
+      <c r="A48" s="93"/>
+      <c r="E48" s="88"/>
+      <c r="G48" s="93"/>
+      <c r="J48" s="88"/>
     </row>
     <row r="49" spans="1:10">
-      <c r="A49" s="98"/>
-      <c r="E49" s="93"/>
-      <c r="G49" s="98"/>
-      <c r="J49" s="93"/>
+      <c r="A49" s="93"/>
+      <c r="E49" s="88"/>
+      <c r="G49" s="93"/>
+      <c r="J49" s="88"/>
     </row>
     <row r="50" spans="1:10">
-      <c r="A50" s="98"/>
-      <c r="E50" s="93"/>
-      <c r="G50" s="98"/>
-      <c r="J50" s="93"/>
+      <c r="A50" s="93"/>
+      <c r="E50" s="88"/>
+      <c r="G50" s="93"/>
+      <c r="J50" s="88"/>
     </row>
     <row r="51" spans="1:10" ht="15" thickBot="1">
-      <c r="A51" s="99"/>
-      <c r="B51" s="100"/>
-      <c r="C51" s="100"/>
-      <c r="D51" s="100"/>
-      <c r="E51" s="101"/>
-      <c r="G51" s="99"/>
-      <c r="H51" s="100"/>
-      <c r="I51" s="100"/>
-      <c r="J51" s="101"/>
+      <c r="A51" s="94"/>
+      <c r="B51" s="95"/>
+      <c r="C51" s="95"/>
+      <c r="D51" s="95"/>
+      <c r="E51" s="96"/>
+      <c r="G51" s="94"/>
+      <c r="H51" s="95"/>
+      <c r="I51" s="95"/>
+      <c r="J51" s="96"/>
     </row>
     <row r="53" spans="1:10" ht="16">
-      <c r="G53" s="149"/>
-      <c r="H53" s="149"/>
-      <c r="I53" s="149"/>
-      <c r="J53" s="149"/>
+      <c r="G53" s="144"/>
+      <c r="H53" s="144"/>
+      <c r="I53" s="144"/>
+      <c r="J53" s="144"/>
     </row>
     <row r="54" spans="1:10" ht="16">
-      <c r="G54" s="149"/>
-      <c r="H54" s="149"/>
-      <c r="J54" s="149"/>
+      <c r="G54" s="144"/>
+      <c r="H54" s="144"/>
+      <c r="J54" s="144"/>
     </row>
     <row r="55" spans="1:10" ht="16">
-      <c r="G55" s="149"/>
-      <c r="H55" s="149"/>
-      <c r="J55" s="149"/>
+      <c r="G55" s="144"/>
+      <c r="H55" s="144"/>
+      <c r="J55" s="144"/>
     </row>
     <row r="56" spans="1:10" ht="16">
-      <c r="G56" s="149"/>
-      <c r="H56" s="149"/>
-      <c r="J56" s="149"/>
+      <c r="G56" s="144"/>
+      <c r="H56" s="144"/>
+      <c r="J56" s="144"/>
     </row>
     <row r="57" spans="1:10" ht="16">
-      <c r="G57" s="149"/>
-      <c r="H57" s="149"/>
-      <c r="J57" s="149"/>
+      <c r="G57" s="144"/>
+      <c r="H57" s="144"/>
+      <c r="J57" s="144"/>
     </row>
     <row r="58" spans="1:10" ht="16">
-      <c r="G58" s="149"/>
-      <c r="H58" s="149"/>
-      <c r="I58" s="149"/>
-      <c r="J58" s="149"/>
+      <c r="G58" s="144"/>
+      <c r="H58" s="144"/>
+      <c r="I58" s="144"/>
+      <c r="J58" s="144"/>
     </row>
     <row r="59" spans="1:10" ht="16">
-      <c r="G59" s="149"/>
-      <c r="H59" s="149"/>
-      <c r="I59" s="149"/>
-      <c r="J59" s="149"/>
+      <c r="G59" s="144"/>
+      <c r="H59" s="144"/>
+      <c r="I59" s="144"/>
+      <c r="J59" s="144"/>
     </row>
     <row r="60" spans="1:10" ht="16">
-      <c r="G60" s="149"/>
-      <c r="H60" s="149"/>
-      <c r="I60" s="149"/>
-      <c r="J60" s="149"/>
+      <c r="G60" s="144"/>
+      <c r="H60" s="144"/>
+      <c r="I60" s="144"/>
+      <c r="J60" s="144"/>
     </row>
     <row r="61" spans="1:10" ht="16">
-      <c r="G61" s="149"/>
-      <c r="H61" s="149"/>
-      <c r="I61" s="149"/>
-      <c r="J61" s="149"/>
+      <c r="G61" s="144"/>
+      <c r="H61" s="144"/>
+      <c r="I61" s="144"/>
+      <c r="J61" s="144"/>
     </row>
     <row r="62" spans="1:10" ht="16">
-      <c r="G62" s="149"/>
-      <c r="H62" s="149"/>
-      <c r="I62" s="149"/>
-      <c r="J62" s="149"/>
+      <c r="G62" s="144"/>
+      <c r="H62" s="144"/>
+      <c r="I62" s="144"/>
+      <c r="J62" s="144"/>
     </row>
     <row r="63" spans="1:10" ht="16">
-      <c r="G63" s="149"/>
-      <c r="H63" s="149"/>
-      <c r="I63" s="149"/>
-      <c r="J63" s="149"/>
+      <c r="G63" s="144"/>
+      <c r="H63" s="144"/>
+      <c r="I63" s="144"/>
+      <c r="J63" s="144"/>
     </row>
     <row r="64" spans="1:10" ht="16">
-      <c r="G64" s="149"/>
-      <c r="H64" s="149"/>
-      <c r="I64" s="149"/>
-      <c r="J64" s="149"/>
+      <c r="G64" s="144"/>
+      <c r="H64" s="144"/>
+      <c r="I64" s="144"/>
+      <c r="J64" s="144"/>
     </row>
     <row r="65" spans="7:10" ht="16">
-      <c r="G65" s="149"/>
-      <c r="H65" s="149"/>
-      <c r="J65" s="151"/>
+      <c r="G65" s="144"/>
+      <c r="H65" s="144"/>
+      <c r="J65" s="146"/>
     </row>
     <row r="66" spans="7:10" ht="16">
-      <c r="G66" s="149"/>
-      <c r="H66" s="149"/>
-      <c r="J66" s="151"/>
+      <c r="G66" s="144"/>
+      <c r="H66" s="144"/>
+      <c r="J66" s="146"/>
     </row>
     <row r="67" spans="7:10" ht="16">
-      <c r="G67" s="149"/>
-      <c r="H67" s="149"/>
-      <c r="J67" s="151"/>
+      <c r="G67" s="144"/>
+      <c r="H67" s="144"/>
+      <c r="J67" s="146"/>
     </row>
     <row r="68" spans="7:10" ht="16">
-      <c r="G68" s="149"/>
-      <c r="H68" s="149"/>
-      <c r="J68" s="149"/>
+      <c r="G68" s="144"/>
+      <c r="H68" s="144"/>
+      <c r="J68" s="144"/>
     </row>
     <row r="69" spans="7:10" ht="16">
-      <c r="G69" s="149"/>
-      <c r="H69" s="149"/>
-      <c r="J69" s="149"/>
+      <c r="G69" s="144"/>
+      <c r="H69" s="144"/>
+      <c r="J69" s="144"/>
     </row>
     <row r="70" spans="7:10" ht="16">
-      <c r="G70" s="149"/>
-      <c r="H70" s="149"/>
+      <c r="G70" s="144"/>
+      <c r="H70" s="144"/>
     </row>
     <row r="71" spans="7:10" ht="16">
-      <c r="G71" s="149"/>
-      <c r="H71" s="149"/>
+      <c r="G71" s="144"/>
+      <c r="H71" s="144"/>
     </row>
     <row r="72" spans="7:10" ht="16">
-      <c r="G72" s="149"/>
-      <c r="H72" s="149"/>
-      <c r="I72" s="149"/>
-      <c r="J72" s="149"/>
+      <c r="G72" s="144"/>
+      <c r="H72" s="144"/>
+      <c r="I72" s="144"/>
+      <c r="J72" s="144"/>
     </row>
     <row r="73" spans="7:10" ht="16">
-      <c r="G73" s="149"/>
-      <c r="H73" s="149"/>
-      <c r="I73" s="149"/>
-      <c r="J73" s="149"/>
+      <c r="G73" s="144"/>
+      <c r="H73" s="144"/>
+      <c r="I73" s="144"/>
+      <c r="J73" s="144"/>
     </row>
     <row r="74" spans="7:10" ht="16">
-      <c r="G74" s="149"/>
-      <c r="H74" s="149"/>
-      <c r="I74" s="149"/>
-      <c r="J74" s="149"/>
+      <c r="G74" s="144"/>
+      <c r="H74" s="144"/>
+      <c r="I74" s="144"/>
+      <c r="J74" s="144"/>
     </row>
     <row r="75" spans="7:10" ht="16">
-      <c r="G75" s="149"/>
-      <c r="H75" s="149"/>
-      <c r="I75" s="149"/>
-      <c r="J75" s="149"/>
+      <c r="G75" s="144"/>
+      <c r="H75" s="144"/>
+      <c r="I75" s="144"/>
+      <c r="J75" s="144"/>
     </row>
     <row r="76" spans="7:10" ht="16">
-      <c r="G76" s="149"/>
-      <c r="H76" s="149"/>
+      <c r="G76" s="144"/>
+      <c r="H76" s="144"/>
     </row>
     <row r="77" spans="7:10" ht="16">
-      <c r="G77" s="149"/>
-      <c r="H77" s="149"/>
+      <c r="G77" s="144"/>
+      <c r="H77" s="144"/>
     </row>
     <row r="78" spans="7:10" ht="16">
-      <c r="G78" s="149"/>
-      <c r="H78" s="149"/>
-      <c r="J78" s="149"/>
+      <c r="G78" s="144"/>
+      <c r="H78" s="144"/>
+      <c r="J78" s="144"/>
     </row>
     <row r="79" spans="7:10" ht="16">
-      <c r="G79" s="149"/>
-      <c r="H79" s="149"/>
+      <c r="G79" s="144"/>
+      <c r="H79" s="144"/>
     </row>
     <row r="80" spans="7:10" ht="16">
-      <c r="G80" s="149"/>
-      <c r="H80" s="149"/>
-      <c r="I80" s="149"/>
-      <c r="J80" s="149"/>
+      <c r="G80" s="144"/>
+      <c r="H80" s="144"/>
+      <c r="I80" s="144"/>
+      <c r="J80" s="144"/>
     </row>
     <row r="81" spans="7:10" ht="16">
-      <c r="G81" s="149"/>
-      <c r="H81" s="149"/>
-      <c r="J81" s="149"/>
+      <c r="G81" s="144"/>
+      <c r="H81" s="144"/>
+      <c r="J81" s="144"/>
     </row>
     <row r="82" spans="7:10" ht="16">
-      <c r="G82" s="149"/>
-      <c r="H82" s="149"/>
+      <c r="G82" s="144"/>
+      <c r="H82" s="144"/>
     </row>
     <row r="83" spans="7:10" ht="16">
-      <c r="G83" s="149"/>
-      <c r="H83" s="149"/>
+      <c r="G83" s="144"/>
+      <c r="H83" s="144"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J44" xr:uid="{10D28488-2FC5-CC48-B811-68259D205C19}"/>
@@ -4975,264 +6174,264 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="16">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="25" t="s">
         <v>271</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="26" t="s">
         <v>308</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="D2" s="28" t="s">
-        <v>201</v>
-      </c>
-      <c r="E2" s="28" t="s">
+      <c r="D2" s="25" t="s">
+        <v>201</v>
+      </c>
+      <c r="E2" s="25" t="s">
         <v>199</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="18" t="s">
         <v>230</v>
       </c>
-      <c r="J2" s="28" t="s">
+      <c r="J2" s="25" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="16">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="31" t="s">
         <v>272</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="32" t="s">
         <v>309</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="32" t="s">
         <v>298</v>
       </c>
-      <c r="D3" s="36" t="s">
-        <v>201</v>
-      </c>
-      <c r="E3" s="36" t="s">
+      <c r="D3" s="31" t="s">
+        <v>201</v>
+      </c>
+      <c r="E3" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="G3" s="33" t="s">
+      <c r="G3" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="H3" s="34" t="s">
+      <c r="H3" s="29" t="s">
         <v>182</v>
       </c>
-      <c r="I3" s="34" t="s">
+      <c r="I3" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="J3" s="35" t="s">
+      <c r="J3" s="30" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="16">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="158" t="s">
         <v>273</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="159" t="s">
         <v>310</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="159" t="s">
         <v>298</v>
       </c>
-      <c r="D4" s="30" t="s">
-        <v>201</v>
-      </c>
-      <c r="E4" s="30" t="s">
+      <c r="D4" s="158" t="s">
+        <v>201</v>
+      </c>
+      <c r="E4" s="158" t="s">
         <v>199</v>
       </c>
-      <c r="G4" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="H4" s="17" t="s">
-        <v>184</v>
-      </c>
-      <c r="I4" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="J4" s="12" t="s">
+      <c r="G4" s="140" t="s">
+        <v>183</v>
+      </c>
+      <c r="H4" s="140" t="s">
+        <v>187</v>
+      </c>
+      <c r="I4" s="140" t="s">
+        <v>204</v>
+      </c>
+      <c r="J4" s="157" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="16">
-      <c r="A5" s="40" t="s">
+      <c r="A5" s="35" t="s">
         <v>274</v>
       </c>
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="36" t="s">
         <v>311</v>
       </c>
-      <c r="C5" s="41" t="s">
+      <c r="C5" s="36" t="s">
         <v>299</v>
       </c>
-      <c r="D5" s="40" t="s">
-        <v>201</v>
-      </c>
-      <c r="E5" s="40" t="s">
+      <c r="D5" s="35" t="s">
+        <v>201</v>
+      </c>
+      <c r="E5" s="35" t="s">
         <v>199</v>
       </c>
-      <c r="G5" s="38" t="s">
+      <c r="G5" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="H5" s="38" t="s">
+      <c r="H5" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="I5" s="38" t="s">
+      <c r="I5" s="33" t="s">
         <v>214</v>
       </c>
-      <c r="J5" s="39" t="s">
+      <c r="J5" s="34" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="16">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="24" t="s">
         <v>275</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="24" t="s">
         <v>312</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="24" t="s">
         <v>312</v>
       </c>
-      <c r="D6" s="27" t="s">
-        <v>201</v>
-      </c>
-      <c r="E6" s="27" t="s">
+      <c r="D6" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="E6" s="24" t="s">
         <v>199</v>
       </c>
-      <c r="G6" s="27" t="s">
+      <c r="G6" s="24" t="s">
         <v>186</v>
       </c>
-      <c r="H6" s="27" t="s">
+      <c r="H6" s="24" t="s">
         <v>186</v>
       </c>
-      <c r="I6" s="27" t="s">
+      <c r="I6" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="J6" s="27" t="s">
+      <c r="J6" s="24" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="16">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="39" t="s">
         <v>276</v>
       </c>
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="40" t="s">
         <v>313</v>
       </c>
-      <c r="C7" s="45" t="s">
+      <c r="C7" s="40" t="s">
         <v>299</v>
       </c>
-      <c r="D7" s="44" t="s">
-        <v>201</v>
-      </c>
-      <c r="E7" s="44" t="s">
+      <c r="D7" s="39" t="s">
+        <v>201</v>
+      </c>
+      <c r="E7" s="39" t="s">
         <v>199</v>
       </c>
-      <c r="G7" s="42" t="s">
+      <c r="G7" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="H7" s="42" t="s">
+      <c r="H7" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="I7" s="43" t="s">
+      <c r="I7" s="38" t="s">
         <v>204</v>
       </c>
-      <c r="J7" s="43" t="s">
+      <c r="J7" s="38" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="16">
-      <c r="A8" s="46" t="s">
+      <c r="A8" s="41" t="s">
         <v>277</v>
       </c>
-      <c r="B8" s="47" t="s">
+      <c r="B8" s="42" t="s">
         <v>314</v>
       </c>
-      <c r="C8" s="47" t="s">
+      <c r="C8" s="42" t="s">
         <v>300</v>
       </c>
-      <c r="D8" s="46" t="s">
-        <v>201</v>
-      </c>
-      <c r="E8" s="46" t="s">
+      <c r="D8" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="E8" s="41" t="s">
         <v>199</v>
       </c>
-      <c r="G8" s="46" t="s">
+      <c r="G8" s="41" t="s">
         <v>190</v>
       </c>
-      <c r="H8" s="47" t="s">
+      <c r="H8" s="42" t="s">
         <v>190</v>
       </c>
-      <c r="I8" s="47" t="s">
+      <c r="I8" s="42" t="s">
         <v>213</v>
       </c>
-      <c r="J8" s="46" t="s">
-        <v>201</v>
-      </c>
-      <c r="K8" s="46"/>
+      <c r="J8" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="K8" s="41"/>
     </row>
     <row r="9" spans="1:11" ht="16">
-      <c r="A9" s="48" t="s">
+      <c r="A9" s="43" t="s">
         <v>278</v>
       </c>
-      <c r="B9" s="49" t="s">
+      <c r="B9" s="44" t="s">
         <v>315</v>
       </c>
-      <c r="C9" s="49" t="s">
+      <c r="C9" s="44" t="s">
         <v>300</v>
       </c>
-      <c r="D9" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="E9" s="48" t="s">
+      <c r="D9" s="43" t="s">
+        <v>201</v>
+      </c>
+      <c r="E9" s="43" t="s">
         <v>199</v>
       </c>
-      <c r="G9" s="32" t="s">
+      <c r="G9" s="27" t="s">
         <v>191</v>
       </c>
-      <c r="H9" s="32" t="s">
+      <c r="H9" s="27" t="s">
         <v>191</v>
       </c>
-      <c r="I9" s="50" t="s">
+      <c r="I9" s="45" t="s">
         <v>215</v>
       </c>
-      <c r="J9" s="50" t="s">
+      <c r="J9" s="45" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="16">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="15" t="s">
         <v>279</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="15" t="s">
         <v>316</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="D10" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="E10" s="18" t="s">
+      <c r="D10" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="E10" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="H10" s="18" t="s">
+      <c r="H10" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="I10" s="18" t="s">
+      <c r="I10" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="J10" s="14" t="s">
+      <c r="J10" s="12" t="s">
         <v>201</v>
       </c>
     </row>
@@ -5301,32 +6500,32 @@
       </c>
     </row>
     <row r="2" spans="1:12" ht="16">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="66" t="s">
         <v>181</v>
       </c>
-      <c r="B2" s="72" t="s">
+      <c r="B2" s="67" t="s">
         <v>181</v>
       </c>
-      <c r="C2" s="72" t="s">
+      <c r="C2" s="67" t="s">
         <v>230</v>
       </c>
-      <c r="D2" s="73" t="s">
-        <v>201</v>
-      </c>
-      <c r="E2" s="55"/>
-      <c r="F2" s="71" t="s">
+      <c r="D2" s="68" t="s">
+        <v>201</v>
+      </c>
+      <c r="E2" s="50"/>
+      <c r="F2" s="66" t="s">
         <v>60</v>
       </c>
-      <c r="G2" s="72" t="s">
+      <c r="G2" s="67" t="s">
         <v>156</v>
       </c>
-      <c r="H2" s="72" t="s">
+      <c r="H2" s="67" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="64" t="s">
+      <c r="I2" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="J2" s="73" t="s">
+      <c r="J2" s="68" t="s">
         <v>199</v>
       </c>
       <c r="K2" t="s">
@@ -5337,32 +6536,32 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="16">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="15" t="s">
         <v>317</v>
       </c>
-      <c r="D3" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="E3" s="55"/>
-      <c r="F3" s="13" t="s">
+      <c r="D3" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="E3" s="50"/>
+      <c r="F3" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="I3" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="J3" s="14" t="s">
+      <c r="I3" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="J3" s="12" t="s">
         <v>199</v>
       </c>
       <c r="K3" t="s">
@@ -5372,33 +6571,33 @@
         <v>327</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="54" customFormat="1" ht="16">
-      <c r="A4" s="79" t="s">
+    <row r="4" spans="1:12" s="49" customFormat="1" ht="16">
+      <c r="A4" s="74" t="s">
         <v>184</v>
       </c>
-      <c r="B4" s="80" t="s">
+      <c r="B4" s="75" t="s">
         <v>184</v>
       </c>
-      <c r="C4" s="80" t="s">
+      <c r="C4" s="75" t="s">
         <v>203</v>
       </c>
-      <c r="D4" s="81" t="s">
-        <v>201</v>
-      </c>
-      <c r="E4" s="55"/>
-      <c r="F4" s="74" t="s">
+      <c r="D4" s="76" t="s">
+        <v>201</v>
+      </c>
+      <c r="E4" s="50"/>
+      <c r="F4" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="G4" s="64" t="s">
+      <c r="G4" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="H4" s="64" t="s">
+      <c r="H4" s="59" t="s">
         <v>106</v>
       </c>
-      <c r="I4" s="64" t="s">
+      <c r="I4" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="J4" s="75" t="s">
+      <c r="J4" s="70" t="s">
         <v>199</v>
       </c>
       <c r="K4" t="s">
@@ -5408,33 +6607,33 @@
         <v>327</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="54" customFormat="1" ht="16">
-      <c r="A5" s="79" t="s">
+    <row r="5" spans="1:12" s="49" customFormat="1" ht="16">
+      <c r="A5" s="74" t="s">
         <v>183</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="75" t="s">
         <v>183</v>
       </c>
-      <c r="C5" s="80" t="s">
+      <c r="C5" s="75" t="s">
         <v>203</v>
       </c>
-      <c r="D5" s="81" t="s">
-        <v>201</v>
-      </c>
-      <c r="E5" s="55"/>
-      <c r="F5" s="74" t="s">
+      <c r="D5" s="76" t="s">
+        <v>201</v>
+      </c>
+      <c r="E5" s="50"/>
+      <c r="F5" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="G5" s="64" t="s">
+      <c r="G5" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="H5" s="64" t="s">
+      <c r="H5" s="59" t="s">
         <v>106</v>
       </c>
-      <c r="I5" s="64" t="s">
+      <c r="I5" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="J5" s="75" t="s">
+      <c r="J5" s="70" t="s">
         <v>199</v>
       </c>
       <c r="K5" t="s">
@@ -5444,33 +6643,33 @@
         <v>327</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="54" customFormat="1" ht="16">
-      <c r="A6" s="79" t="s">
+    <row r="6" spans="1:12" s="49" customFormat="1" ht="16">
+      <c r="A6" s="74" t="s">
         <v>185</v>
       </c>
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="75" t="s">
         <v>185</v>
       </c>
-      <c r="C6" s="80" t="s">
+      <c r="C6" s="75" t="s">
         <v>185</v>
       </c>
-      <c r="D6" s="81" t="s">
-        <v>201</v>
-      </c>
-      <c r="E6" s="55"/>
-      <c r="F6" s="74" t="s">
+      <c r="D6" s="76" t="s">
+        <v>201</v>
+      </c>
+      <c r="E6" s="50"/>
+      <c r="F6" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="G6" s="64" t="s">
+      <c r="G6" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="H6" s="64" t="s">
+      <c r="H6" s="59" t="s">
         <v>106</v>
       </c>
-      <c r="I6" s="64" t="s">
+      <c r="I6" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="J6" s="75" t="s">
+      <c r="J6" s="70" t="s">
         <v>199</v>
       </c>
       <c r="K6" t="s">
@@ -5481,32 +6680,32 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="15" t="s">
         <v>318</v>
       </c>
-      <c r="D7" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="E7" s="55"/>
-      <c r="F7" s="13" t="s">
+      <c r="D7" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="E7" s="50"/>
+      <c r="F7" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="H7" s="18" t="s">
+      <c r="H7" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="I7" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="J7" s="14" t="s">
+      <c r="I7" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="J7" s="12" t="s">
         <v>199</v>
       </c>
       <c r="K7" t="s">
@@ -5517,32 +6716,32 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16">
-      <c r="A8" s="79" t="s">
+      <c r="A8" s="74" t="s">
         <v>188</v>
       </c>
-      <c r="B8" s="80" t="s">
+      <c r="B8" s="75" t="s">
         <v>188</v>
       </c>
-      <c r="C8" s="80" t="s">
+      <c r="C8" s="75" t="s">
         <v>204</v>
       </c>
-      <c r="D8" s="81" t="s">
-        <v>201</v>
-      </c>
-      <c r="E8" s="55"/>
-      <c r="F8" s="74" t="s">
+      <c r="D8" s="76" t="s">
+        <v>201</v>
+      </c>
+      <c r="E8" s="50"/>
+      <c r="F8" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="G8" s="64" t="s">
+      <c r="G8" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="H8" s="64" t="s">
+      <c r="H8" s="59" t="s">
         <v>106</v>
       </c>
-      <c r="I8" s="64" t="s">
+      <c r="I8" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="J8" s="75" t="s">
+      <c r="J8" s="70" t="s">
         <v>199</v>
       </c>
       <c r="K8" t="s">
@@ -5553,32 +6752,32 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16">
-      <c r="A9" s="79" t="s">
+      <c r="A9" s="74" t="s">
         <v>187</v>
       </c>
-      <c r="B9" s="80" t="s">
+      <c r="B9" s="75" t="s">
         <v>187</v>
       </c>
-      <c r="C9" s="80" t="s">
+      <c r="C9" s="75" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="81" t="s">
-        <v>201</v>
-      </c>
-      <c r="E9" s="55"/>
-      <c r="F9" s="74" t="s">
+      <c r="D9" s="76" t="s">
+        <v>201</v>
+      </c>
+      <c r="E9" s="50"/>
+      <c r="F9" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="G9" s="64" t="s">
+      <c r="G9" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="H9" s="64" t="s">
+      <c r="H9" s="59" t="s">
         <v>106</v>
       </c>
-      <c r="I9" s="64" t="s">
+      <c r="I9" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="J9" s="75" t="s">
+      <c r="J9" s="70" t="s">
         <v>199</v>
       </c>
       <c r="K9" t="s">
@@ -5589,49 +6788,49 @@
       </c>
     </row>
     <row r="10" spans="1:12" ht="16">
-      <c r="A10" s="60" t="s">
+      <c r="A10" s="55" t="s">
         <v>189</v>
       </c>
-      <c r="B10" s="59" t="s">
+      <c r="B10" s="54" t="s">
         <v>205</v>
       </c>
-      <c r="C10" s="59" t="s">
+      <c r="C10" s="54" t="s">
         <v>206</v>
       </c>
-      <c r="D10" s="61" t="s">
-        <v>201</v>
-      </c>
-      <c r="E10" s="55"/>
+      <c r="D10" s="56" t="s">
+        <v>201</v>
+      </c>
+      <c r="E10" s="50"/>
       <c r="F10" s="7"/>
-      <c r="J10" s="93"/>
+      <c r="J10" s="88"/>
     </row>
     <row r="11" spans="1:12" ht="16">
-      <c r="A11" s="56" t="s">
+      <c r="A11" s="51" t="s">
         <v>190</v>
       </c>
-      <c r="B11" s="65" t="s">
+      <c r="B11" s="60" t="s">
         <v>190</v>
       </c>
-      <c r="C11" s="65" t="s">
+      <c r="C11" s="60" t="s">
         <v>213</v>
       </c>
-      <c r="D11" s="57" t="s">
-        <v>201</v>
-      </c>
-      <c r="E11" s="55"/>
-      <c r="F11" s="56" t="s">
+      <c r="D11" s="52" t="s">
+        <v>201</v>
+      </c>
+      <c r="E11" s="50"/>
+      <c r="F11" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="65" t="s">
+      <c r="G11" s="60" t="s">
         <v>169</v>
       </c>
-      <c r="H11" s="65" t="s">
+      <c r="H11" s="60" t="s">
         <v>110</v>
       </c>
-      <c r="I11" s="65" t="s">
-        <v>201</v>
-      </c>
-      <c r="J11" s="57" t="s">
+      <c r="I11" s="60" t="s">
+        <v>201</v>
+      </c>
+      <c r="J11" s="52" t="s">
         <v>199</v>
       </c>
       <c r="K11" t="s">
@@ -5642,32 +6841,32 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16">
-      <c r="A12" s="90" t="s">
+      <c r="A12" s="85" t="s">
         <v>191</v>
       </c>
-      <c r="B12" s="91" t="s">
+      <c r="B12" s="86" t="s">
         <v>191</v>
       </c>
-      <c r="C12" s="91" t="s">
+      <c r="C12" s="86" t="s">
         <v>319</v>
       </c>
-      <c r="D12" s="92" t="s">
-        <v>201</v>
-      </c>
-      <c r="E12" s="55"/>
-      <c r="F12" s="87" t="s">
+      <c r="D12" s="87" t="s">
+        <v>201</v>
+      </c>
+      <c r="E12" s="50"/>
+      <c r="F12" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="G12" s="88" t="s">
+      <c r="G12" s="83" t="s">
         <v>127</v>
       </c>
-      <c r="H12" s="88" t="s">
+      <c r="H12" s="83" t="s">
         <v>128</v>
       </c>
-      <c r="I12" s="88" t="s">
+      <c r="I12" s="83" t="s">
         <v>200</v>
       </c>
-      <c r="J12" s="89" t="s">
+      <c r="J12" s="84" t="s">
         <v>199</v>
       </c>
       <c r="K12" t="s">
@@ -5678,32 +6877,32 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16">
-      <c r="A13" s="56" t="s">
+      <c r="A13" s="51" t="s">
         <v>192</v>
       </c>
-      <c r="B13" s="65" t="s">
+      <c r="B13" s="60" t="s">
         <v>192</v>
       </c>
-      <c r="C13" s="65" t="s">
+      <c r="C13" s="60" t="s">
         <v>207</v>
       </c>
-      <c r="D13" s="57" t="s">
-        <v>201</v>
-      </c>
-      <c r="E13" s="55"/>
-      <c r="F13" s="56" t="s">
+      <c r="D13" s="52" t="s">
+        <v>201</v>
+      </c>
+      <c r="E13" s="50"/>
+      <c r="F13" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="G13" s="65" t="s">
+      <c r="G13" s="60" t="s">
         <v>169</v>
       </c>
-      <c r="H13" s="65" t="s">
+      <c r="H13" s="60" t="s">
         <v>110</v>
       </c>
-      <c r="I13" s="65" t="s">
-        <v>201</v>
-      </c>
-      <c r="J13" s="57" t="s">
+      <c r="I13" s="60" t="s">
+        <v>201</v>
+      </c>
+      <c r="J13" s="52" t="s">
         <v>199</v>
       </c>
       <c r="K13" t="s">
@@ -5714,32 +6913,32 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16">
-      <c r="A14" s="76" t="s">
+      <c r="A14" s="71" t="s">
         <v>193</v>
       </c>
-      <c r="B14" s="66" t="s">
+      <c r="B14" s="61" t="s">
         <v>193</v>
       </c>
-      <c r="C14" s="66" t="s">
+      <c r="C14" s="61" t="s">
         <v>208</v>
       </c>
-      <c r="D14" s="85" t="s">
-        <v>201</v>
-      </c>
-      <c r="E14" s="55"/>
-      <c r="F14" s="76" t="s">
+      <c r="D14" s="80" t="s">
+        <v>201</v>
+      </c>
+      <c r="E14" s="50"/>
+      <c r="F14" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="G14" s="67" t="s">
+      <c r="G14" s="62" t="s">
         <v>130</v>
       </c>
-      <c r="H14" s="66" t="s">
+      <c r="H14" s="61" t="s">
         <v>131</v>
       </c>
-      <c r="I14" s="68" t="s">
+      <c r="I14" s="63" t="s">
         <v>200</v>
       </c>
-      <c r="J14" s="58" t="s">
+      <c r="J14" s="53" t="s">
         <v>199</v>
       </c>
       <c r="K14" t="s">
@@ -5750,32 +6949,32 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16">
-      <c r="A15" s="77" t="s">
+      <c r="A15" s="72" t="s">
         <v>194</v>
       </c>
-      <c r="B15" s="62" t="s">
+      <c r="B15" s="57" t="s">
         <v>194</v>
       </c>
-      <c r="C15" s="62" t="s">
+      <c r="C15" s="57" t="s">
         <v>209</v>
       </c>
-      <c r="D15" s="86" t="s">
-        <v>201</v>
-      </c>
-      <c r="E15" s="55"/>
-      <c r="F15" s="77" t="s">
+      <c r="D15" s="81" t="s">
+        <v>201</v>
+      </c>
+      <c r="E15" s="50"/>
+      <c r="F15" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="G15" s="63" t="s">
+      <c r="G15" s="58" t="s">
         <v>156</v>
       </c>
-      <c r="H15" s="63" t="s">
+      <c r="H15" s="58" t="s">
         <v>106</v>
       </c>
-      <c r="I15" s="70" t="s">
+      <c r="I15" s="65" t="s">
         <v>200</v>
       </c>
-      <c r="J15" s="78" t="s">
+      <c r="J15" s="73" t="s">
         <v>199</v>
       </c>
       <c r="K15" t="s">
@@ -5786,32 +6985,32 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16">
-      <c r="A16" s="83" t="s">
+      <c r="A16" s="78" t="s">
         <v>195</v>
       </c>
-      <c r="B16" s="49" t="s">
+      <c r="B16" s="44" t="s">
         <v>195</v>
       </c>
-      <c r="C16" s="49" t="s">
+      <c r="C16" s="44" t="s">
         <v>320</v>
       </c>
-      <c r="D16" s="84" t="s">
-        <v>201</v>
-      </c>
-      <c r="E16" s="55"/>
-      <c r="F16" s="15" t="s">
+      <c r="D16" s="79" t="s">
+        <v>201</v>
+      </c>
+      <c r="E16" s="50"/>
+      <c r="F16" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="G16" s="69" t="s">
+      <c r="G16" s="64" t="s">
         <v>166</v>
       </c>
-      <c r="H16" s="69" t="s">
+      <c r="H16" s="64" t="s">
         <v>106</v>
       </c>
-      <c r="I16" s="69" t="s">
-        <v>201</v>
-      </c>
-      <c r="J16" s="16" t="s">
+      <c r="I16" s="64" t="s">
+        <v>201</v>
+      </c>
+      <c r="J16" s="14" t="s">
         <v>199</v>
       </c>
       <c r="K16" t="s">
@@ -5822,32 +7021,32 @@
       </c>
     </row>
     <row r="17" spans="1:12" ht="16">
-      <c r="A17" s="83" t="s">
+      <c r="A17" s="78" t="s">
         <v>196</v>
       </c>
-      <c r="B17" s="49" t="s">
+      <c r="B17" s="44" t="s">
         <v>196</v>
       </c>
-      <c r="C17" s="49" t="s">
+      <c r="C17" s="44" t="s">
         <v>210</v>
       </c>
-      <c r="D17" s="84" t="s">
-        <v>201</v>
-      </c>
-      <c r="E17" s="55"/>
-      <c r="F17" s="15" t="s">
+      <c r="D17" s="79" t="s">
+        <v>201</v>
+      </c>
+      <c r="E17" s="50"/>
+      <c r="F17" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="G17" s="69" t="s">
+      <c r="G17" s="64" t="s">
         <v>166</v>
       </c>
-      <c r="H17" s="69" t="s">
+      <c r="H17" s="64" t="s">
         <v>106</v>
       </c>
-      <c r="I17" s="69" t="s">
-        <v>201</v>
-      </c>
-      <c r="J17" s="16" t="s">
+      <c r="I17" s="64" t="s">
+        <v>201</v>
+      </c>
+      <c r="J17" s="14" t="s">
         <v>199</v>
       </c>
       <c r="K17" t="s">
@@ -5858,32 +7057,32 @@
       </c>
     </row>
     <row r="18" spans="1:12" ht="16">
-      <c r="A18" s="79" t="s">
+      <c r="A18" s="74" t="s">
         <v>197</v>
       </c>
-      <c r="B18" s="80" t="s">
+      <c r="B18" s="75" t="s">
         <v>188</v>
       </c>
-      <c r="C18" s="80" t="s">
+      <c r="C18" s="75" t="s">
         <v>204</v>
       </c>
-      <c r="D18" s="81" t="s">
-        <v>201</v>
-      </c>
-      <c r="E18" s="55"/>
-      <c r="F18" s="74" t="s">
+      <c r="D18" s="76" t="s">
+        <v>201</v>
+      </c>
+      <c r="E18" s="50"/>
+      <c r="F18" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="G18" s="64" t="s">
+      <c r="G18" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="H18" s="64" t="s">
+      <c r="H18" s="59" t="s">
         <v>106</v>
       </c>
-      <c r="I18" s="70" t="s">
+      <c r="I18" s="65" t="s">
         <v>200</v>
       </c>
-      <c r="J18" s="75" t="s">
+      <c r="J18" s="70" t="s">
         <v>199</v>
       </c>
       <c r="K18" t="s">
@@ -5894,32 +7093,32 @@
       </c>
     </row>
     <row r="19" spans="1:12" ht="16">
-      <c r="A19" s="79" t="s">
+      <c r="A19" s="74" t="s">
         <v>198</v>
       </c>
-      <c r="B19" s="80" t="s">
+      <c r="B19" s="75" t="s">
         <v>188</v>
       </c>
-      <c r="C19" s="80" t="s">
+      <c r="C19" s="75" t="s">
         <v>204</v>
       </c>
-      <c r="D19" s="82" t="s">
+      <c r="D19" s="77" t="s">
         <v>200</v>
       </c>
-      <c r="E19" s="55"/>
-      <c r="F19" s="74" t="s">
+      <c r="E19" s="50"/>
+      <c r="F19" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="G19" s="64" t="s">
+      <c r="G19" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="H19" s="64" t="s">
+      <c r="H19" s="59" t="s">
         <v>106</v>
       </c>
-      <c r="I19" s="70" t="s">
+      <c r="I19" s="65" t="s">
         <v>200</v>
       </c>
-      <c r="J19" s="75" t="s">
+      <c r="J19" s="70" t="s">
         <v>199</v>
       </c>
       <c r="K19" t="s">
@@ -5930,32 +7129,32 @@
       </c>
     </row>
     <row r="20" spans="1:12" ht="16">
-      <c r="A20" s="79" t="s">
+      <c r="A20" s="74" t="s">
         <v>184</v>
       </c>
-      <c r="B20" s="80" t="s">
+      <c r="B20" s="75" t="s">
         <v>184</v>
       </c>
-      <c r="C20" s="80" t="s">
+      <c r="C20" s="75" t="s">
         <v>212</v>
       </c>
-      <c r="D20" s="82" t="s">
+      <c r="D20" s="77" t="s">
         <v>200</v>
       </c>
-      <c r="E20" s="55"/>
-      <c r="F20" s="74" t="s">
+      <c r="E20" s="50"/>
+      <c r="F20" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="G20" s="64" t="s">
+      <c r="G20" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="H20" s="64" t="s">
+      <c r="H20" s="59" t="s">
         <v>106</v>
       </c>
-      <c r="I20" s="64" t="s">
+      <c r="I20" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="J20" s="75" t="s">
+      <c r="J20" s="70" t="s">
         <v>199</v>
       </c>
       <c r="K20" t="s">
@@ -5966,32 +7165,32 @@
       </c>
     </row>
     <row r="21" spans="1:12" ht="16">
-      <c r="A21" s="76" t="s">
+      <c r="A21" s="71" t="s">
         <v>193</v>
       </c>
-      <c r="B21" s="66" t="s">
+      <c r="B21" s="61" t="s">
         <v>193</v>
       </c>
-      <c r="C21" s="66" t="s">
+      <c r="C21" s="61" t="s">
         <v>248</v>
       </c>
-      <c r="D21" s="85" t="s">
+      <c r="D21" s="80" t="s">
         <v>200</v>
       </c>
-      <c r="E21" s="55"/>
-      <c r="F21" s="76" t="s">
+      <c r="E21" s="50"/>
+      <c r="F21" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="G21" s="67" t="s">
+      <c r="G21" s="62" t="s">
         <v>130</v>
       </c>
-      <c r="H21" s="66" t="s">
+      <c r="H21" s="61" t="s">
         <v>131</v>
       </c>
-      <c r="I21" s="68" t="s">
+      <c r="I21" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="J21" s="58" t="s">
+      <c r="J21" s="53" t="s">
         <v>199</v>
       </c>
       <c r="K21" t="s">
@@ -6002,31 +7201,31 @@
       </c>
     </row>
     <row r="22" spans="1:12" ht="16">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="F22" s="13" t="s">
+      <c r="F22" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="G22" s="18" t="s">
+      <c r="G22" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="H22" s="18" t="s">
+      <c r="H22" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="I22" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="J22" s="14" t="s">
+      <c r="I22" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="J22" s="12" t="s">
         <v>199</v>
       </c>
       <c r="K22" t="s">
@@ -6037,189 +7236,189 @@
       </c>
     </row>
     <row r="23" spans="1:12" ht="16">
-      <c r="A23" s="22"/>
+      <c r="A23" s="19"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="55"/>
-      <c r="F23" s="51"/>
-      <c r="G23" s="52"/>
-      <c r="H23" s="52"/>
-      <c r="I23" s="52"/>
-      <c r="J23" s="53"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="47"/>
+      <c r="I23" s="47"/>
+      <c r="J23" s="48"/>
     </row>
     <row r="24" spans="1:12" ht="16">
-      <c r="A24" s="22"/>
+      <c r="A24" s="19"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="55"/>
-      <c r="F24" s="51"/>
-      <c r="G24" s="52"/>
-      <c r="H24" s="52"/>
-      <c r="I24" s="52"/>
-      <c r="J24" s="53"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="47"/>
+      <c r="H24" s="47"/>
+      <c r="I24" s="47"/>
+      <c r="J24" s="48"/>
     </row>
     <row r="25" spans="1:12" ht="16">
-      <c r="A25" s="22"/>
+      <c r="A25" s="19"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
-      <c r="D25" s="23"/>
+      <c r="D25" s="20"/>
       <c r="F25" s="7"/>
-      <c r="J25" s="19"/>
+      <c r="J25" s="16"/>
     </row>
     <row r="26" spans="1:12" ht="16">
-      <c r="A26" s="22"/>
+      <c r="A26" s="19"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
-      <c r="D26" s="23"/>
+      <c r="D26" s="20"/>
       <c r="F26" s="7"/>
-      <c r="J26" s="19"/>
+      <c r="J26" s="16"/>
     </row>
     <row r="27" spans="1:12" ht="16">
-      <c r="A27" s="22"/>
+      <c r="A27" s="19"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
-      <c r="D27" s="23"/>
+      <c r="D27" s="20"/>
       <c r="F27" s="7"/>
-      <c r="J27" s="19"/>
+      <c r="J27" s="16"/>
     </row>
     <row r="28" spans="1:12" ht="16">
-      <c r="A28" s="22"/>
+      <c r="A28" s="19"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
-      <c r="D28" s="23"/>
+      <c r="D28" s="20"/>
       <c r="F28" s="7"/>
-      <c r="J28" s="19"/>
+      <c r="J28" s="16"/>
     </row>
     <row r="29" spans="1:12" ht="16">
-      <c r="A29" s="22"/>
+      <c r="A29" s="19"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
-      <c r="D29" s="23"/>
+      <c r="D29" s="20"/>
       <c r="F29" s="7"/>
-      <c r="J29" s="19"/>
+      <c r="J29" s="16"/>
     </row>
     <row r="30" spans="1:12" ht="16">
-      <c r="A30" s="22"/>
+      <c r="A30" s="19"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
-      <c r="D30" s="23"/>
+      <c r="D30" s="20"/>
       <c r="F30" s="7"/>
-      <c r="J30" s="19"/>
+      <c r="J30" s="16"/>
     </row>
     <row r="31" spans="1:12" ht="16">
-      <c r="A31" s="22"/>
+      <c r="A31" s="19"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
-      <c r="D31" s="23"/>
+      <c r="D31" s="20"/>
       <c r="F31" s="7"/>
-      <c r="J31" s="19"/>
+      <c r="J31" s="16"/>
     </row>
     <row r="32" spans="1:12" ht="16">
-      <c r="A32" s="22"/>
+      <c r="A32" s="19"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
-      <c r="D32" s="23"/>
+      <c r="D32" s="20"/>
       <c r="F32" s="7"/>
-      <c r="J32" s="19"/>
+      <c r="J32" s="16"/>
     </row>
     <row r="33" spans="1:10" ht="16">
-      <c r="A33" s="22"/>
+      <c r="A33" s="19"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="23"/>
+      <c r="D33" s="20"/>
       <c r="F33" s="7"/>
-      <c r="J33" s="19"/>
+      <c r="J33" s="16"/>
     </row>
     <row r="34" spans="1:10" ht="16">
-      <c r="A34" s="22"/>
+      <c r="A34" s="19"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
-      <c r="D34" s="23"/>
+      <c r="D34" s="20"/>
       <c r="F34" s="7"/>
-      <c r="J34" s="19"/>
+      <c r="J34" s="16"/>
     </row>
     <row r="35" spans="1:10" ht="16">
-      <c r="A35" s="22"/>
+      <c r="A35" s="19"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
-      <c r="D35" s="23"/>
+      <c r="D35" s="20"/>
       <c r="F35" s="7"/>
-      <c r="J35" s="19"/>
+      <c r="J35" s="16"/>
     </row>
     <row r="36" spans="1:10" ht="16">
-      <c r="A36" s="22"/>
+      <c r="A36" s="19"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
-      <c r="D36" s="23"/>
+      <c r="D36" s="20"/>
       <c r="F36" s="7"/>
-      <c r="J36" s="19"/>
+      <c r="J36" s="16"/>
     </row>
     <row r="37" spans="1:10" ht="16">
-      <c r="A37" s="22"/>
+      <c r="A37" s="19"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
-      <c r="D37" s="23"/>
+      <c r="D37" s="20"/>
       <c r="F37" s="7"/>
-      <c r="J37" s="19"/>
+      <c r="J37" s="16"/>
     </row>
     <row r="38" spans="1:10" ht="16">
-      <c r="A38" s="22"/>
+      <c r="A38" s="19"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
-      <c r="D38" s="23"/>
+      <c r="D38" s="20"/>
       <c r="F38" s="7"/>
-      <c r="J38" s="19"/>
+      <c r="J38" s="16"/>
     </row>
     <row r="39" spans="1:10" ht="16">
-      <c r="A39" s="22"/>
+      <c r="A39" s="19"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
-      <c r="D39" s="23"/>
+      <c r="D39" s="20"/>
       <c r="F39" s="7"/>
-      <c r="J39" s="19"/>
+      <c r="J39" s="16"/>
     </row>
     <row r="40" spans="1:10" ht="16">
-      <c r="A40" s="22"/>
+      <c r="A40" s="19"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
-      <c r="D40" s="23"/>
+      <c r="D40" s="20"/>
       <c r="F40" s="7"/>
-      <c r="J40" s="19"/>
+      <c r="J40" s="16"/>
     </row>
     <row r="41" spans="1:10" ht="16">
-      <c r="A41" s="22"/>
+      <c r="A41" s="19"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
-      <c r="D41" s="23"/>
+      <c r="D41" s="20"/>
       <c r="F41" s="7"/>
-      <c r="J41" s="19"/>
+      <c r="J41" s="16"/>
     </row>
     <row r="42" spans="1:10" ht="16">
-      <c r="A42" s="22"/>
+      <c r="A42" s="19"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
-      <c r="D42" s="23"/>
+      <c r="D42" s="20"/>
       <c r="F42" s="7"/>
-      <c r="J42" s="19"/>
+      <c r="J42" s="16"/>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="7"/>
-      <c r="D43" s="19"/>
+      <c r="D43" s="16"/>
       <c r="F43" s="7"/>
-      <c r="J43" s="19"/>
+      <c r="J43" s="16"/>
     </row>
     <row r="44" spans="1:10" ht="15" thickBot="1">
-      <c r="A44" s="24"/>
-      <c r="B44" s="25"/>
-      <c r="C44" s="25"/>
-      <c r="D44" s="26"/>
-      <c r="F44" s="24"/>
-      <c r="G44" s="25"/>
-      <c r="H44" s="25"/>
-      <c r="I44" s="25"/>
-      <c r="J44" s="26"/>
+      <c r="A44" s="21"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="23"/>
+      <c r="F44" s="21"/>
+      <c r="G44" s="22"/>
+      <c r="H44" s="22"/>
+      <c r="I44" s="22"/>
+      <c r="J44" s="23"/>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="7"/>
@@ -6253,7 +7452,7 @@
       <c r="A2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6261,7 +7460,7 @@
       <c r="A3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6269,7 +7468,7 @@
       <c r="A4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6277,7 +7476,7 @@
       <c r="A5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6285,7 +7484,7 @@
       <c r="A6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6293,7 +7492,7 @@
       <c r="A7" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6301,7 +7500,7 @@
       <c r="A8" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6309,7 +7508,7 @@
       <c r="A9" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6317,7 +7516,7 @@
       <c r="A10" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6325,7 +7524,7 @@
       <c r="A11" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6333,7 +7532,7 @@
       <c r="A12" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6341,7 +7540,7 @@
       <c r="A13" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6349,7 +7548,7 @@
       <c r="A14" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6357,7 +7556,7 @@
       <c r="A15" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6365,7 +7564,7 @@
       <c r="A16" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6373,7 +7572,7 @@
       <c r="A17" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6381,7 +7580,7 @@
       <c r="A18" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6389,7 +7588,7 @@
       <c r="A19" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6397,7 +7596,7 @@
       <c r="A20" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6405,7 +7604,7 @@
       <c r="A21" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="19" t="s">
+      <c r="B21" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6413,7 +7612,7 @@
       <c r="A22" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6421,7 +7620,7 @@
       <c r="A23" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="19" t="s">
+      <c r="B23" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6429,7 +7628,7 @@
       <c r="A24" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6437,7 +7636,7 @@
       <c r="A25" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="19" t="s">
+      <c r="B25" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6445,7 +7644,7 @@
       <c r="A26" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6453,7 +7652,7 @@
       <c r="A27" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6461,7 +7660,7 @@
       <c r="A28" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6469,7 +7668,7 @@
       <c r="A29" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6477,7 +7676,7 @@
       <c r="A30" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B30" s="19" t="s">
+      <c r="B30" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6485,7 +7684,7 @@
       <c r="A31" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B31" s="19" t="s">
+      <c r="B31" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6493,7 +7692,7 @@
       <c r="A32" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B32" s="19" t="s">
+      <c r="B32" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6501,7 +7700,7 @@
       <c r="A33" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B33" s="19" t="s">
+      <c r="B33" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6509,7 +7708,7 @@
       <c r="A34" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B34" s="19" t="s">
+      <c r="B34" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6517,7 +7716,7 @@
       <c r="A35" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B35" s="19" t="s">
+      <c r="B35" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6525,7 +7724,7 @@
       <c r="A36" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B36" s="19" t="s">
+      <c r="B36" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6533,7 +7732,7 @@
       <c r="A37" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B37" s="19" t="s">
+      <c r="B37" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6541,7 +7740,7 @@
       <c r="A38" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B38" s="19" t="s">
+      <c r="B38" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6549,7 +7748,7 @@
       <c r="A39" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B39" s="19" t="s">
+      <c r="B39" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6557,7 +7756,7 @@
       <c r="A40" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B40" s="19" t="s">
+      <c r="B40" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6565,7 +7764,7 @@
       <c r="A41" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B41" s="19" t="s">
+      <c r="B41" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6573,7 +7772,7 @@
       <c r="A42" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="B42" s="19" t="s">
+      <c r="B42" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6581,7 +7780,7 @@
       <c r="A43" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B43" s="19" t="s">
+      <c r="B43" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6589,7 +7788,7 @@
       <c r="A44" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B44" s="19" t="s">
+      <c r="B44" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6597,7 +7796,7 @@
       <c r="A45" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="B45" s="19" t="s">
+      <c r="B45" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6605,7 +7804,7 @@
       <c r="A46" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B46" s="19" t="s">
+      <c r="B46" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6613,7 +7812,7 @@
       <c r="A47" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B47" s="19" t="s">
+      <c r="B47" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6621,7 +7820,7 @@
       <c r="A48" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B48" s="19" t="s">
+      <c r="B48" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6629,7 +7828,7 @@
       <c r="A49" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B49" s="19" t="s">
+      <c r="B49" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6637,7 +7836,7 @@
       <c r="A50" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B50" s="19" t="s">
+      <c r="B50" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6645,7 +7844,7 @@
       <c r="A51" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B51" s="19" t="s">
+      <c r="B51" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6653,7 +7852,7 @@
       <c r="A52" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B52" s="19" t="s">
+      <c r="B52" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6661,7 +7860,7 @@
       <c r="A53" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="B53" s="19" t="s">
+      <c r="B53" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6669,7 +7868,7 @@
       <c r="A54" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B54" s="19" t="s">
+      <c r="B54" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6677,7 +7876,7 @@
       <c r="A55" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="B55" s="19" t="s">
+      <c r="B55" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6685,7 +7884,7 @@
       <c r="A56" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B56" s="19" t="s">
+      <c r="B56" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6693,7 +7892,7 @@
       <c r="A57" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B57" s="19" t="s">
+      <c r="B57" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6701,7 +7900,7 @@
       <c r="A58" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="B58" s="19" t="s">
+      <c r="B58" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6709,7 +7908,7 @@
       <c r="A59" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B59" s="19" t="s">
+      <c r="B59" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6717,7 +7916,7 @@
       <c r="A60" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="B60" s="19" t="s">
+      <c r="B60" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6725,7 +7924,7 @@
       <c r="A61" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="B61" s="19" t="s">
+      <c r="B61" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6733,7 +7932,7 @@
       <c r="A62" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B62" s="19" t="s">
+      <c r="B62" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6741,7 +7940,7 @@
       <c r="A63" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B63" s="19" t="s">
+      <c r="B63" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6749,7 +7948,7 @@
       <c r="A64" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="B64" s="19" t="s">
+      <c r="B64" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6757,7 +7956,7 @@
       <c r="A65" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="B65" s="19" t="s">
+      <c r="B65" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6765,7 +7964,7 @@
       <c r="A66" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="B66" s="19" t="s">
+      <c r="B66" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6773,7 +7972,7 @@
       <c r="A67" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="B67" s="19" t="s">
+      <c r="B67" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6781,15 +7980,15 @@
       <c r="A68" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="B68" s="19" t="s">
+      <c r="B68" s="16" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="22.75" customHeight="1" thickBot="1">
-      <c r="A69" s="24" t="s">
+      <c r="A69" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="B69" s="26" t="s">
+      <c r="B69" s="23" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6820,497 +8019,497 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="147" t="s">
         <v>99</v>
       </c>
-      <c r="B2" s="153" t="s">
+      <c r="B2" s="148" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="154" t="s">
+      <c r="C2" s="149" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A3" s="155" t="s">
+      <c r="A3" s="150" t="s">
         <v>101</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="156" t="s">
+      <c r="C3" s="151" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A4" s="155" t="s">
+      <c r="A4" s="150" t="s">
         <v>102</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C4" s="156" t="s">
+      <c r="C4" s="151" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A5" s="155" t="s">
+      <c r="A5" s="150" t="s">
         <v>105</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="156" t="s">
+      <c r="C5" s="151" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A6" s="155" t="s">
+      <c r="A6" s="150" t="s">
         <v>108</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C6" s="156" t="s">
+      <c r="C6" s="151" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="22.75" customHeight="1">
-      <c r="A7" s="155" t="s">
+      <c r="A7" s="150" t="s">
         <v>109</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C7" s="156" t="s">
+      <c r="C7" s="151" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A8" s="155" t="s">
+      <c r="A8" s="150" t="s">
         <v>112</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C8" s="156" t="s">
+      <c r="C8" s="151" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A9" s="155" t="s">
+      <c r="A9" s="150" t="s">
         <v>115</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C9" s="156" t="s">
+      <c r="C9" s="151" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A10" s="155" t="s">
+      <c r="A10" s="150" t="s">
         <v>118</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C10" s="156" t="s">
+      <c r="C10" s="151" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A11" s="155" t="s">
+      <c r="A11" s="150" t="s">
         <v>121</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C11" s="156" t="s">
+      <c r="C11" s="151" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A12" s="155" t="s">
+      <c r="A12" s="150" t="s">
         <v>124</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C12" s="156" t="s">
+      <c r="C12" s="151" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A13" s="155" t="s">
+      <c r="A13" s="150" t="s">
         <v>127</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C13" s="156" t="s">
+      <c r="C13" s="151" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A14" s="155" t="s">
+      <c r="A14" s="150" t="s">
         <v>130</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C14" s="156" t="s">
+      <c r="C14" s="151" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A15" s="155" t="s">
+      <c r="A15" s="150" t="s">
         <v>133</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C15" s="156" t="s">
+      <c r="C15" s="151" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A16" s="155" t="s">
+      <c r="A16" s="150" t="s">
         <v>136</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C16" s="156" t="s">
+      <c r="C16" s="151" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A17" s="155" t="s">
+      <c r="A17" s="150" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C17" s="156" t="s">
+      <c r="C17" s="151" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A18" s="155" t="s">
+      <c r="A18" s="150" t="s">
         <v>142</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C18" s="156" t="s">
+      <c r="C18" s="151" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A19" s="155" t="s">
+      <c r="A19" s="150" t="s">
         <v>143</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="156" t="s">
+      <c r="C19" s="151" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A20" s="155" t="s">
+      <c r="A20" s="150" t="s">
         <v>145</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="156" t="s">
+      <c r="C20" s="151" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A21" s="155" t="s">
+      <c r="A21" s="150" t="s">
         <v>146</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C21" s="156" t="s">
+      <c r="C21" s="151" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A22" s="155" t="s">
+      <c r="A22" s="150" t="s">
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="156" t="s">
+      <c r="C22" s="151" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A23" s="155" t="s">
+      <c r="A23" s="150" t="s">
         <v>147</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="156" t="s">
+      <c r="C23" s="151" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A24" s="155" t="s">
+      <c r="A24" s="150" t="s">
         <v>148</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="156" t="s">
+      <c r="C24" s="151" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A25" s="155" t="s">
+      <c r="A25" s="150" t="s">
         <v>150</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="156" t="s">
+      <c r="C25" s="151" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A26" s="155" t="s">
+      <c r="A26" s="150" t="s">
         <v>152</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="156" t="s">
+      <c r="C26" s="151" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A27" s="155" t="s">
+      <c r="A27" s="150" t="s">
         <v>153</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C27" s="156" t="s">
+      <c r="C27" s="151" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A28" s="155" t="s">
+      <c r="A28" s="150" t="s">
         <v>155</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="156" t="s">
+      <c r="C28" s="151" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A29" s="155" t="s">
+      <c r="A29" s="150" t="s">
         <v>156</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C29" s="156" t="s">
+      <c r="C29" s="151" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A30" s="155" t="s">
+      <c r="A30" s="150" t="s">
         <v>157</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C30" s="156" t="s">
+      <c r="C30" s="151" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A31" s="155" t="s">
+      <c r="A31" s="150" t="s">
         <v>158</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C31" s="156" t="s">
+      <c r="C31" s="151" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A32" s="155" t="s">
+      <c r="A32" s="150" t="s">
         <v>160</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C32" s="156" t="s">
+      <c r="C32" s="151" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A33" s="155" t="s">
+      <c r="A33" s="150" t="s">
         <v>163</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C33" s="156" t="s">
+      <c r="C33" s="151" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A34" s="155" t="s">
+      <c r="A34" s="150" t="s">
         <v>164</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C34" s="156" t="s">
+      <c r="C34" s="151" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="68.25" customHeight="1">
-      <c r="A35" s="155" t="s">
+      <c r="A35" s="150" t="s">
         <v>166</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C35" s="156" t="s">
+      <c r="C35" s="151" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="68.25" customHeight="1">
-      <c r="A36" s="155" t="s">
+      <c r="A36" s="150" t="s">
         <v>168</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C36" s="156" t="s">
+      <c r="C36" s="151" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="22.75" customHeight="1">
-      <c r="A37" s="155" t="s">
+      <c r="A37" s="150" t="s">
         <v>169</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C37" s="156" t="s">
+      <c r="C37" s="151" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A38" s="155" t="s">
+      <c r="A38" s="150" t="s">
         <v>41</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C38" s="156" t="s">
+      <c r="C38" s="151" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A39" s="155" t="s">
+      <c r="A39" s="150" t="s">
         <v>170</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C39" s="156" t="s">
+      <c r="C39" s="151" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A40" s="155" t="s">
+      <c r="A40" s="150" t="s">
         <v>171</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C40" s="156" t="s">
+      <c r="C40" s="151" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A41" s="155" t="s">
+      <c r="A41" s="150" t="s">
         <v>173</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C41" s="156" t="s">
+      <c r="C41" s="151" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A42" s="155" t="s">
+      <c r="A42" s="150" t="s">
         <v>174</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C42" s="156" t="s">
+      <c r="C42" s="151" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A43" s="155" t="s">
+      <c r="A43" s="150" t="s">
         <v>176</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C43" s="156" t="s">
+      <c r="C43" s="151" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A44" s="155" t="s">
+      <c r="A44" s="150" t="s">
         <v>177</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C44" s="156" t="s">
+      <c r="C44" s="151" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="45.5" customHeight="1">
-      <c r="A45" s="155" t="s">
+      <c r="A45" s="150" t="s">
         <v>178</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C45" s="156" t="s">
+      <c r="C45" s="151" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="45.5" customHeight="1" thickBot="1">
-      <c r="A46" s="157" t="s">
+      <c r="A46" s="152" t="s">
         <v>179</v>
       </c>
-      <c r="B46" s="158" t="s">
+      <c r="B46" s="153" t="s">
         <v>175</v>
       </c>
-      <c r="C46" s="159" t="s">
+      <c r="C46" s="154" t="s">
         <v>107</v>
       </c>
     </row>
@@ -7337,7 +8536,7 @@
       <c r="A1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="160"/>
+      <c r="B1" s="155"/>
       <c r="C1" s="10" t="s">
         <v>180</v>
       </c>
@@ -7346,7 +8545,7 @@
       <c r="A2" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="16" t="s">
         <v>256</v>
       </c>
     </row>
@@ -7354,7 +8553,7 @@
       <c r="A3" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="16" t="s">
         <v>257</v>
       </c>
     </row>
@@ -7362,7 +8561,7 @@
       <c r="A4" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="16" t="s">
         <v>258</v>
       </c>
     </row>
@@ -7370,7 +8569,7 @@
       <c r="A5" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="16" t="s">
         <v>259</v>
       </c>
     </row>
@@ -7378,7 +8577,7 @@
       <c r="A6" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="16" t="s">
         <v>260</v>
       </c>
     </row>
@@ -7386,7 +8585,7 @@
       <c r="A7" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="16" t="s">
         <v>261</v>
       </c>
     </row>
@@ -7394,7 +8593,7 @@
       <c r="A8" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="16" t="s">
         <v>262</v>
       </c>
     </row>
@@ -7402,7 +8601,7 @@
       <c r="A9" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="16" t="s">
         <v>263</v>
       </c>
     </row>
@@ -7410,7 +8609,7 @@
       <c r="A10" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="16" t="s">
         <v>264</v>
       </c>
     </row>
@@ -7418,7 +8617,7 @@
       <c r="A11" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="16" t="s">
         <v>265</v>
       </c>
     </row>
@@ -7426,7 +8625,7 @@
       <c r="A12" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="16" t="s">
         <v>266</v>
       </c>
     </row>
@@ -7434,7 +8633,7 @@
       <c r="A13" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="16" t="s">
         <v>201</v>
       </c>
     </row>
@@ -7442,7 +8641,7 @@
       <c r="A14" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="16" t="s">
         <v>267</v>
       </c>
     </row>
@@ -7450,7 +8649,7 @@
       <c r="A15" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="16" t="s">
         <v>24</v>
       </c>
     </row>
@@ -7458,7 +8657,7 @@
       <c r="A16" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="16" t="s">
         <v>268</v>
       </c>
     </row>
@@ -7466,7 +8665,7 @@
       <c r="A17" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="16" t="s">
         <v>200</v>
       </c>
     </row>
@@ -7474,7 +8673,7 @@
       <c r="A18" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="16" t="s">
         <v>269</v>
       </c>
     </row>
@@ -7482,20 +8681,20 @@
       <c r="A19" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="C19" s="19"/>
+      <c r="C19" s="16"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="C20" s="19"/>
+      <c r="C20" s="16"/>
     </row>
     <row r="21" spans="1:3" ht="15" thickBot="1">
-      <c r="A21" s="24" t="s">
+      <c r="A21" s="21" t="s">
         <v>252</v>
       </c>
-      <c r="B21" s="25"/>
-      <c r="C21" s="26"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="23"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:A21" xr:uid="{00000000-0001-0000-0600-000000000000}"/>
@@ -7505,7 +8704,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41D029F1-3F90-764F-9191-4F62BF9F0215}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <tabColor theme="9" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:A19"/>
@@ -7519,72 +8718,72 @@
         <v>221</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="16" hidden="1">
+    <row r="2" spans="1:1" ht="16">
       <c r="A2" s="4" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="16" hidden="1">
+    <row r="3" spans="1:1" ht="16">
       <c r="A3" s="4" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="16" hidden="1">
+    <row r="4" spans="1:1" ht="16">
       <c r="A4" s="4" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="16" hidden="1">
+    <row r="5" spans="1:1" ht="16">
       <c r="A5" s="4" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="16" hidden="1">
+    <row r="6" spans="1:1" ht="16">
       <c r="A6" s="4" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="16" hidden="1">
+    <row r="7" spans="1:1" ht="16">
       <c r="A7" s="4" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="16" hidden="1">
+    <row r="8" spans="1:1" ht="16">
       <c r="A8" s="4" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="16" hidden="1">
+    <row r="9" spans="1:1" ht="16">
       <c r="A9" s="4" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="16" hidden="1">
+    <row r="10" spans="1:1" ht="16">
       <c r="A10" s="4" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="16" hidden="1">
+    <row r="11" spans="1:1" ht="16">
       <c r="A11" s="4" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="16" hidden="1">
+    <row r="12" spans="1:1" ht="16">
       <c r="A12" s="4" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="16" hidden="1">
+    <row r="13" spans="1:1" ht="16">
       <c r="A13" s="4" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="16" hidden="1">
+    <row r="14" spans="1:1" ht="16">
       <c r="A14" s="4" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="16" hidden="1">
+    <row r="15" spans="1:1" ht="16">
       <c r="A15" s="4" t="s">
         <v>194</v>
       </c>
@@ -7599,25 +8798,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="16" hidden="1">
+    <row r="18" spans="1:1" ht="16">
       <c r="A18" s="4" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="16" hidden="1">
+    <row r="19" spans="1:1" ht="16">
       <c r="A19" s="4" t="s">
         <v>198</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A19" xr:uid="{41D029F1-3F90-764F-9191-4F62BF9F0215}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Atlas MAX+ XDi Extra High Density"/>
-        <filter val="Atlas MAX+ XDi High Density"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:A19" xr:uid="{41D029F1-3F90-764F-9191-4F62BF9F0215}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/atlas_max_plus_to_poly_mapping_template.xlsx
+++ b/atlas_max_plus_to_poly_mapping_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raeltonhonorio/Documents/KDAM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2FE0A67-87A6-D841-B08E-A2C33735C9F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE4C02EC-2C6D-524C-8353-1BF9C391C5B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" firstSheet="9" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" firstSheet="13" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -18,41 +18,59 @@
     <sheet name="Poly_to_Plus_Mapping" sheetId="11" r:id="rId3"/>
     <sheet name="AVHD6_TO_PLUS" sheetId="15" r:id="rId4"/>
     <sheet name="MAX_TO_POLY" sheetId="16" r:id="rId5"/>
-    <sheet name="Poly_Setups" sheetId="5" r:id="rId6"/>
-    <sheet name="Poly_Media" sheetId="6" r:id="rId7"/>
-    <sheet name="Poly_Output_ICCs" sheetId="7" r:id="rId8"/>
-    <sheet name="Plus_Setups" sheetId="8" r:id="rId9"/>
-    <sheet name="Plus Media" sheetId="9" r:id="rId10"/>
-    <sheet name="Plus_Output_ICCs" sheetId="10" r:id="rId11"/>
-    <sheet name="AVHD6 SETUPS" sheetId="13" r:id="rId12"/>
-    <sheet name="AVHD6 MEDIA" sheetId="12" r:id="rId13"/>
-    <sheet name="AVHD6_OUTPUT_ICC" sheetId="14" r:id="rId14"/>
-    <sheet name="AV100 SETUPS" sheetId="17" r:id="rId15"/>
-    <sheet name="AV1000 MEDIA" sheetId="18" r:id="rId16"/>
-    <sheet name="AV100_OUTPUT_ICC" sheetId="19" r:id="rId17"/>
-    <sheet name="AV1000 TO PLUS" sheetId="20" r:id="rId18"/>
+    <sheet name="AV1000 TO PLUS" sheetId="20" r:id="rId6"/>
+    <sheet name="Poly_Setups" sheetId="5" r:id="rId7"/>
+    <sheet name="Poly_Media" sheetId="6" r:id="rId8"/>
+    <sheet name="Poly_Output_ICCs" sheetId="7" r:id="rId9"/>
+    <sheet name="Plus_Setups" sheetId="8" r:id="rId10"/>
+    <sheet name="Plus Media" sheetId="9" r:id="rId11"/>
+    <sheet name="Plus_Output_ICCs" sheetId="10" r:id="rId12"/>
+    <sheet name="AVHD6 SETUPS" sheetId="13" r:id="rId13"/>
+    <sheet name="AVHD6 MEDIA" sheetId="12" r:id="rId14"/>
+    <sheet name="AVHD6_OUTPUT_ICC" sheetId="14" r:id="rId15"/>
+    <sheet name="AV100 SETUPS" sheetId="17" r:id="rId16"/>
+    <sheet name="AV1000 MEDIA" sheetId="18" r:id="rId17"/>
+    <sheet name="AV100_OUTPUT_ICC" sheetId="19" r:id="rId18"/>
+    <sheet name="MATRIX SETUPS" sheetId="21" r:id="rId19"/>
+    <sheet name="MATRIX MEDIA" sheetId="22" r:id="rId20"/>
+    <sheet name="MATRIX ICC" sheetId="23" r:id="rId21"/>
+    <sheet name="PLUS TO MATRIX" sheetId="24" r:id="rId22"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'AVHD6 MEDIA'!$A$1:$A$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'AVHD6 SETUPS'!$A$1:$A$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">AVHD6_OUTPUT_ICC!$A$1:$B$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'AVHD6 MEDIA'!$A$1:$A$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'AVHD6 SETUPS'!$A$1:$A$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">AVHD6_OUTPUT_ICC!$A$1:$B$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">AVHD6_TO_PLUS!$A$1:$J$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'MATRIX SETUPS'!$A$1:$A$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">MAX_TO_POLY!$A$1:$J$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Plus Media'!$A$1:$A$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">Plus_Output_ICCs!$A$1:$A$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Plus_Setups!$A$1:$A$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Plus Media'!$A$1:$A$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">Plus_Output_ICCs!$A$1:$A$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">Plus_Setups!$A$1:$A$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Plus_to_Poly_Mapping!$A$1:$L$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Poly_Media!$A$1:$C$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Poly_Output_ICCs!$A$1:$A$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Poly_Setups!$A$1:$B$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Poly_Media!$A$1:$C$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Poly_Output_ICCs!$A$1:$A$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Poly_Setups!$A$1:$B$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Poly_to_Plus_Mapping!$A$1:$J$44</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1548" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1826" uniqueCount="465">
   <si>
     <t>Atlas Max Plus → Atlas Max Poly Mapping Workbook</t>
   </si>
@@ -1222,13 +1240,238 @@
   </si>
   <si>
     <t>Fixa</t>
+  </si>
+  <si>
+    <t>MATRIX SETUPS</t>
+  </si>
+  <si>
+    <t>MATRIX MEDIA</t>
+  </si>
+  <si>
+    <t>MATRIX ICC</t>
+  </si>
+  <si>
+    <t>KDAM BRUSHED</t>
+  </si>
+  <si>
+    <t>MATRIX Cotton Black STD</t>
+  </si>
+  <si>
+    <t>MATRIX Cotton Color HQ K standard</t>
+  </si>
+  <si>
+    <t>MATRIX Cotton Color Premium K standard</t>
+  </si>
+  <si>
+    <t>MATRIX Cotton Color Robust</t>
+  </si>
+  <si>
+    <t>MATRIX Cotton Color STD</t>
+  </si>
+  <si>
+    <t>MATRIX Cotton Light HQ K standard</t>
+  </si>
+  <si>
+    <t>MATRIX Cotton Light Premium K standard</t>
+  </si>
+  <si>
+    <t>MATRIX Cotton Light STD</t>
+  </si>
+  <si>
+    <t>MATRIX Cotton XDi HD</t>
+  </si>
+  <si>
+    <t>MATRIX Cotton Xdi</t>
+  </si>
+  <si>
+    <t>MATRIX DTFilm</t>
+  </si>
+  <si>
+    <t>MATRIX Poly Brushed</t>
+  </si>
+  <si>
+    <t>MATRIX Poly Color STD</t>
+  </si>
+  <si>
+    <t>MATRIX Poly Dye-Sub</t>
+  </si>
+  <si>
+    <t>MATRIX Poly HQ</t>
+  </si>
+  <si>
+    <t>MATRIX Poly Light STD</t>
+  </si>
+  <si>
+    <t>MATRIX Poly XDi HD</t>
+  </si>
+  <si>
+    <t>MATRIX Poly XDi Vinyl</t>
+  </si>
+  <si>
+    <t>MATRIX Poly Xdi</t>
+  </si>
+  <si>
+    <t>SOLID DyeSub</t>
+  </si>
+  <si>
+    <t>Blended Ts HQ</t>
+  </si>
+  <si>
+    <t>Blended Ts STD</t>
+  </si>
+  <si>
+    <t>MATRIX_BASE_SETUP</t>
+  </si>
+  <si>
+    <t>MATRIX_MEDIA</t>
+  </si>
+  <si>
+    <t>MATRIX_OUTPUT_ICC</t>
+  </si>
+  <si>
+    <t>MATRIX_INPUT_RGB</t>
+  </si>
+  <si>
+    <t>Atlas Matrix Cotton Black STD.icm</t>
+  </si>
+  <si>
+    <t>Atlas Matrix Cotton Color K Premium Stadndard_ColorMask60.icm</t>
+  </si>
+  <si>
+    <t>Atlas Matrix Cotton Color K Premium Stadndard_Ic20.icm</t>
+  </si>
+  <si>
+    <t>Atlas Matrix Cotton Color K Premium Standards.icm</t>
+  </si>
+  <si>
+    <t>Atlas Matrix Cotton Color STD.icm</t>
+  </si>
+  <si>
+    <t>Atlas Matrix Cotton K Color STD.icm</t>
+  </si>
+  <si>
+    <t>Atlas Matrix Cotton K Light STD.icm</t>
+  </si>
+  <si>
+    <t>Atlas Matrix Cotton Light K Premium Standard.icm</t>
+  </si>
+  <si>
+    <t>Atlas Matrix Cotton Light STD.icm</t>
+  </si>
+  <si>
+    <t>Atlas Matrix DTFilm.icm</t>
+  </si>
+  <si>
+    <t>Atlas Matrix Poly HQ.icm</t>
+  </si>
+  <si>
+    <t>Atlas Matrix Poly Light.icm</t>
+  </si>
+  <si>
+    <t>Atlas Matrix Poly Premium.icm</t>
+  </si>
+  <si>
+    <t>Atlas Matrix Poly STD.icm</t>
+  </si>
+  <si>
+    <t>INPUT / OUTPUT</t>
+  </si>
+  <si>
+    <t>HIGH White.icm</t>
+  </si>
+  <si>
+    <t>WideW_ColorT_v1.icm</t>
+  </si>
+  <si>
+    <t>Atlas MATRIX Black STD C6x7W6x8SI.lut</t>
+  </si>
+  <si>
+    <t>Atlas Matrix Cotton Black STD C6x7W6x9SI.lut</t>
+  </si>
+  <si>
+    <t>Atlas Matrix Cotton Color  K Premium Standards  W10x10.5 C10x7.lut</t>
+  </si>
+  <si>
+    <t>Atlas Matrix Cotton Color STD C6x7W6x9SI.lut</t>
+  </si>
+  <si>
+    <t>Atlas Matrix Cotton Light Premium Standards C10x7.lut</t>
+  </si>
+  <si>
+    <t>Atlas Matrix Cotton Light STD C6x9.lut</t>
+  </si>
+  <si>
+    <t>Atlas Matrix Cotton light STD K C8x9.lut</t>
+  </si>
+  <si>
+    <t>Atlas Matrix Cotton STD K W8x10.5 C8x7.lut</t>
+  </si>
+  <si>
+    <t>Atlas Matrix Cotton XDI W10x10.5_C8x9.lut</t>
+  </si>
+  <si>
+    <t>Atlas Matrix DTFilm C6x9W6x6.lut</t>
+  </si>
+  <si>
+    <t>Atlas Matrix Poly Dye Sublimated C10x7_W10x8.lut</t>
+  </si>
+  <si>
+    <t>Atlas Matrix Poly HQ W6x9 C8x7 - Copy.lut</t>
+  </si>
+  <si>
+    <t>Atlas Matrix Poly HQ W6x9 C8x7.lut</t>
+  </si>
+  <si>
+    <t>Atlas Matrix Poly Light C6x9.lut</t>
+  </si>
+  <si>
+    <t>Atlas Matrix Poly Premium C10x7_W10x8.lut</t>
+  </si>
+  <si>
+    <t>Atlas Matrix Poly Premium W10x12C8x9.lut</t>
+  </si>
+  <si>
+    <t>Atlas Matrix Poly STD C6x7_W6x9 - Copy.lut</t>
+  </si>
+  <si>
+    <t>Atlas Matrix Poly STD C6x7_W6x9.lut</t>
+  </si>
+  <si>
+    <t>Atlas Matrix XDI W12x12C8x9.lut</t>
+  </si>
+  <si>
+    <t>Atlas MAX+ Black STD C6x7W6x7SI.lut</t>
+  </si>
+  <si>
+    <t>AlphaWhite.lut</t>
+  </si>
+  <si>
+    <t>AlphaWhitePoly.lut</t>
+  </si>
+  <si>
+    <t>Chart.lut</t>
+  </si>
+  <si>
+    <t>Atlas Matrix Pro.lut</t>
+  </si>
+  <si>
+    <t>WhiteT600x600RG.lut</t>
+  </si>
+  <si>
+    <t>WhiteT600x700RG.lut</t>
+  </si>
+  <si>
+    <t>MATRIX Cotton XDi</t>
+  </si>
+  <si>
+    <t>Super grand pallet</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1350,8 +1593,21 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="28">
+  <fills count="31">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1511,6 +1767,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -1604,7 +1878,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="170">
+  <cellXfs count="216">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1875,6 +2149,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2042,7 +2390,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="95" customWidth="1"/>
@@ -2111,12 +2459,124 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41D029F1-3F90-764F-9191-4F62BF9F0215}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.39997558519241921"/>
+  </sheetPr>
+  <dimension ref="A1:A19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="33.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="21">
+      <c r="A1" s="6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="16">
+      <c r="A2" s="4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="16">
+      <c r="A3" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="16">
+      <c r="A4" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="16">
+      <c r="A5" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="16">
+      <c r="A6" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="16">
+      <c r="A7" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="16">
+      <c r="A8" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="16">
+      <c r="A9" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="16">
+      <c r="A10" s="4" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="16">
+      <c r="A11" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="16">
+      <c r="A12" s="4" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="16">
+      <c r="A13" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="16">
+      <c r="A14" s="4" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="16">
+      <c r="A15" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="16">
+      <c r="A16" s="4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="16">
+      <c r="A17" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="16">
+      <c r="A18" s="4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="16">
+      <c r="A19" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:A19" xr:uid="{41D029F1-3F90-764F-9191-4F62BF9F0215}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2EAD9B5-EDDD-BA49-A0DC-91F6C002BCB0}">
   <sheetPr filterMode="1">
     <tabColor theme="9" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:A19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="33.5" bestFit="1" customWidth="1"/>
   </cols>
@@ -2229,13 +2689,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{869A1179-B4DD-1849-B576-03864D6D4F7F}">
   <sheetPr>
     <tabColor theme="9" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:A44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="39.83203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -2466,13 +2926,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B69897BD-C765-294E-BCFB-7820395C9ED2}">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:A10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35" bestFit="1" customWidth="1"/>
   </cols>
@@ -2533,13 +2993,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6649CACF-ACCD-FB40-AE6B-8E1F74CC0FEA}">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:A16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="44" bestFit="1" customWidth="1"/>
   </cols>
@@ -2630,13 +3090,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13E8489B-0C4E-0C4F-874E-AE2C83D835E4}">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.6640625" customWidth="1"/>
@@ -2749,10 +3209,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C79466E2-B626-384A-80AE-38283B2719E9}">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
   <dimension ref="A1:A34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35" bestFit="1" customWidth="1"/>
   </cols>
@@ -2932,10 +3395,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5400D9C-18EA-F34A-AF9F-98FEF126EAE6}">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
   <dimension ref="A1:A17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="44" bestFit="1" customWidth="1"/>
   </cols>
@@ -3030,10 +3496,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{489560A0-066C-D242-A978-32CDD53942A5}">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
   <dimension ref="A1:A7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.5" bestFit="1" customWidth="1"/>
   </cols>
@@ -3078,665 +3547,140 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C35120B4-BDCF-CB4C-BC62-FC29CBC3A109}">
-  <dimension ref="A1:L35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="20" defaultRowHeight="14"/>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36271C4B-A74E-8E40-BB5B-1D9E627BC241}">
+  <sheetPr>
+    <tabColor theme="1" tint="0.499984740745262"/>
+  </sheetPr>
+  <dimension ref="A1:A24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="36.6640625" customWidth="1"/>
-    <col min="3" max="3" width="31.5" customWidth="1"/>
-    <col min="4" max="4" width="25.5" customWidth="1"/>
-    <col min="5" max="5" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="1.6640625" customWidth="1"/>
-    <col min="8" max="9" width="33" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="36.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="28.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="16">
-      <c r="A1" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>389</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="16">
-      <c r="A2" s="92" t="s">
-        <v>362</v>
-      </c>
-      <c r="B2" s="92"/>
-      <c r="C2" s="92" t="s">
-        <v>312</v>
-      </c>
-      <c r="D2" s="163" t="s">
-        <v>299</v>
-      </c>
-      <c r="E2" s="164"/>
-      <c r="F2" s="164"/>
-      <c r="H2" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="I2" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="J2" s="24" t="s">
-        <v>238</v>
-      </c>
-      <c r="K2" s="166"/>
-    </row>
-    <row r="3" spans="1:12" ht="16">
-      <c r="A3" s="92" t="s">
-        <v>364</v>
-      </c>
-      <c r="B3" s="92"/>
-      <c r="C3" s="163" t="s">
-        <v>313</v>
-      </c>
-      <c r="D3" s="163" t="s">
-        <v>299</v>
-      </c>
-      <c r="E3" s="164"/>
-      <c r="F3" s="164"/>
-      <c r="H3" s="165" t="s">
-        <v>187</v>
-      </c>
-      <c r="I3" s="165" t="s">
-        <v>187</v>
-      </c>
-      <c r="J3" s="165" t="s">
-        <v>204</v>
-      </c>
-      <c r="K3" s="166"/>
-    </row>
-    <row r="4" spans="1:12" ht="16">
-      <c r="A4" s="92" t="s">
-        <v>363</v>
-      </c>
-      <c r="B4" s="92"/>
-      <c r="C4" s="163" t="s">
-        <v>315</v>
-      </c>
-      <c r="D4" s="163" t="s">
-        <v>300</v>
-      </c>
-      <c r="E4" s="164"/>
-      <c r="F4" s="164"/>
-      <c r="H4" s="27" t="s">
-        <v>191</v>
-      </c>
-      <c r="I4" s="27" t="s">
-        <v>191</v>
-      </c>
-      <c r="J4" s="45" t="s">
-        <v>215</v>
-      </c>
-      <c r="K4" s="166"/>
-    </row>
-    <row r="5" spans="1:12" ht="16">
-      <c r="A5" s="92" t="s">
-        <v>365</v>
-      </c>
-      <c r="B5" s="92"/>
-      <c r="C5" s="163" t="s">
-        <v>312</v>
-      </c>
-      <c r="D5" s="163" t="s">
-        <v>299</v>
-      </c>
-      <c r="E5" s="164"/>
-      <c r="F5" s="164"/>
-      <c r="H5" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="I5" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="J5" s="24" t="s">
-        <v>238</v>
-      </c>
-      <c r="K5" s="166"/>
-    </row>
-    <row r="6" spans="1:12" ht="16">
-      <c r="A6" s="92" t="s">
-        <v>366</v>
-      </c>
-      <c r="B6" s="92"/>
-      <c r="C6" s="144" t="s">
-        <v>313</v>
-      </c>
-      <c r="D6" s="144" t="s">
-        <v>299</v>
-      </c>
-      <c r="E6" s="144"/>
-      <c r="F6" s="144"/>
-      <c r="H6" s="165" t="s">
-        <v>187</v>
-      </c>
-      <c r="I6" s="165" t="s">
-        <v>187</v>
-      </c>
-      <c r="J6" s="165" t="s">
-        <v>204</v>
-      </c>
-      <c r="K6" s="166"/>
-    </row>
-    <row r="7" spans="1:12" ht="16">
-      <c r="A7" s="92" t="s">
-        <v>367</v>
-      </c>
-      <c r="B7" s="92"/>
-      <c r="C7" s="163" t="s">
-        <v>312</v>
-      </c>
-      <c r="D7" s="144" t="s">
-        <v>299</v>
-      </c>
-      <c r="E7" s="164"/>
-      <c r="F7" s="164"/>
-      <c r="H7" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="I7" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="J7" s="24" t="s">
-        <v>238</v>
-      </c>
-      <c r="K7" s="166"/>
-    </row>
-    <row r="8" spans="1:12" ht="16">
-      <c r="A8" s="92" t="s">
-        <v>368</v>
-      </c>
-      <c r="B8" s="92"/>
-      <c r="C8" s="163" t="s">
-        <v>315</v>
-      </c>
-      <c r="D8" s="163" t="s">
-        <v>300</v>
-      </c>
-      <c r="E8" s="164"/>
-      <c r="F8" s="164"/>
-      <c r="H8" s="27" t="s">
-        <v>191</v>
-      </c>
-      <c r="I8" s="27" t="s">
-        <v>191</v>
-      </c>
-      <c r="J8" s="45" t="s">
-        <v>215</v>
-      </c>
-      <c r="K8" s="166"/>
-      <c r="L8" s="41"/>
-    </row>
-    <row r="9" spans="1:12" ht="16">
-      <c r="A9" s="92" t="s">
-        <v>369</v>
-      </c>
-      <c r="B9" s="92"/>
-      <c r="C9" s="163" t="s">
-        <v>316</v>
-      </c>
-      <c r="D9" s="163" t="s">
-        <v>300</v>
-      </c>
-      <c r="E9" s="164"/>
-      <c r="F9" s="164"/>
-      <c r="H9" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="I9" s="15" t="s">
-        <v>193</v>
-      </c>
-      <c r="J9" s="15" t="s">
-        <v>208</v>
-      </c>
-      <c r="K9" s="166"/>
-    </row>
-    <row r="10" spans="1:12" ht="16">
-      <c r="A10" s="92" t="s">
-        <v>370</v>
-      </c>
-      <c r="B10" s="92"/>
-      <c r="C10" s="144" t="s">
-        <v>308</v>
-      </c>
-      <c r="D10" s="144" t="s">
-        <v>298</v>
-      </c>
-      <c r="E10" s="144"/>
-      <c r="F10" s="144"/>
-      <c r="H10" s="33" t="s">
-        <v>185</v>
-      </c>
-      <c r="I10" s="33" t="s">
-        <v>185</v>
-      </c>
-      <c r="J10" s="33" t="s">
-        <v>214</v>
-      </c>
-      <c r="K10" s="166"/>
-    </row>
-    <row r="11" spans="1:12" ht="16">
-      <c r="A11" s="92" t="s">
-        <v>309</v>
-      </c>
-      <c r="B11" s="92"/>
-      <c r="C11" s="92" t="s">
-        <v>309</v>
-      </c>
-      <c r="D11" s="144" t="s">
-        <v>298</v>
-      </c>
-      <c r="E11" s="92"/>
-      <c r="F11" s="92"/>
-      <c r="H11" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="I11" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="J11" s="24" t="s">
-        <v>238</v>
-      </c>
-      <c r="K11" s="166"/>
-    </row>
-    <row r="12" spans="1:12" ht="16">
-      <c r="A12" s="92" t="s">
-        <v>310</v>
-      </c>
-      <c r="B12" s="92"/>
-      <c r="C12" s="92" t="s">
-        <v>310</v>
-      </c>
-      <c r="D12" s="144" t="s">
-        <v>298</v>
-      </c>
-      <c r="E12" s="92"/>
-      <c r="F12" s="92"/>
-      <c r="H12" s="165" t="s">
-        <v>187</v>
-      </c>
-      <c r="I12" s="165" t="s">
-        <v>187</v>
-      </c>
-      <c r="J12" s="165" t="s">
-        <v>204</v>
-      </c>
-      <c r="K12" s="166"/>
-    </row>
-    <row r="13" spans="1:12" ht="16">
-      <c r="A13" s="92" t="s">
-        <v>371</v>
-      </c>
-      <c r="B13" s="92"/>
-      <c r="C13" s="92" t="s">
-        <v>311</v>
-      </c>
-      <c r="D13" s="163" t="s">
-        <v>299</v>
-      </c>
-      <c r="E13" s="92"/>
-      <c r="F13" s="92"/>
-      <c r="H13" s="33" t="s">
-        <v>185</v>
-      </c>
-      <c r="I13" s="33" t="s">
-        <v>185</v>
-      </c>
-      <c r="J13" s="33" t="s">
-        <v>214</v>
-      </c>
-      <c r="K13" s="166"/>
-    </row>
-    <row r="14" spans="1:12" ht="16">
-      <c r="A14" s="92" t="s">
-        <v>312</v>
-      </c>
-      <c r="B14" s="92"/>
-      <c r="C14" s="92" t="s">
-        <v>312</v>
-      </c>
-      <c r="D14" s="163" t="s">
-        <v>299</v>
-      </c>
-      <c r="E14" s="92"/>
-      <c r="F14" s="92"/>
-      <c r="H14" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="I14" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="J14" s="24" t="s">
-        <v>238</v>
-      </c>
-      <c r="K14" s="166"/>
-    </row>
-    <row r="15" spans="1:12" ht="16">
-      <c r="A15" s="92" t="s">
-        <v>313</v>
-      </c>
-      <c r="B15" s="92"/>
-      <c r="C15" s="92" t="s">
-        <v>313</v>
-      </c>
-      <c r="D15" s="163" t="s">
-        <v>299</v>
-      </c>
-      <c r="E15" s="92"/>
-      <c r="F15" s="92"/>
-      <c r="H15" s="165" t="s">
-        <v>187</v>
-      </c>
-      <c r="I15" s="165" t="s">
-        <v>187</v>
-      </c>
-      <c r="J15" s="165" t="s">
-        <v>204</v>
-      </c>
-      <c r="K15" s="166"/>
-    </row>
-    <row r="16" spans="1:12" ht="16">
-      <c r="A16" s="92" t="s">
-        <v>372</v>
-      </c>
-      <c r="B16" s="92"/>
-      <c r="C16" s="92" t="s">
-        <v>314</v>
-      </c>
-      <c r="D16" s="163" t="s">
-        <v>300</v>
-      </c>
-      <c r="E16" s="92"/>
-      <c r="F16" s="92"/>
-      <c r="H16" s="41" t="s">
-        <v>190</v>
-      </c>
-      <c r="I16" s="42" t="s">
-        <v>190</v>
-      </c>
-      <c r="J16" s="42" t="s">
-        <v>213</v>
-      </c>
-      <c r="K16" s="166"/>
-    </row>
-    <row r="17" spans="1:11" ht="16">
-      <c r="A17" s="92" t="s">
-        <v>315</v>
-      </c>
-      <c r="B17" s="92"/>
-      <c r="C17" s="92" t="s">
-        <v>315</v>
-      </c>
-      <c r="D17" s="163" t="s">
-        <v>300</v>
-      </c>
-      <c r="E17" s="92"/>
-      <c r="F17" s="92"/>
-      <c r="H17" s="27" t="s">
-        <v>191</v>
-      </c>
-      <c r="I17" s="27" t="s">
-        <v>191</v>
-      </c>
-      <c r="J17" s="45" t="s">
-        <v>215</v>
-      </c>
-      <c r="K17" s="166"/>
-    </row>
-    <row r="18" spans="1:11" ht="16">
-      <c r="A18" s="92" t="s">
-        <v>316</v>
-      </c>
-      <c r="B18" s="92"/>
-      <c r="C18" s="92" t="s">
-        <v>316</v>
-      </c>
-      <c r="D18" s="163" t="s">
-        <v>300</v>
-      </c>
-      <c r="E18" s="92"/>
-      <c r="F18" s="92"/>
-      <c r="H18" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="I18" s="15" t="s">
-        <v>193</v>
-      </c>
-      <c r="J18" s="15" t="s">
-        <v>208</v>
-      </c>
-      <c r="K18" s="166"/>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" s="92" t="s">
-        <v>373</v>
-      </c>
-      <c r="B19" s="92"/>
-      <c r="C19" s="92"/>
-      <c r="D19" s="92"/>
-      <c r="E19" s="92"/>
-      <c r="F19" s="92"/>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" s="92" t="s">
-        <v>374</v>
-      </c>
-      <c r="B20" s="92"/>
-      <c r="C20" s="92"/>
-      <c r="D20" s="92"/>
-      <c r="E20" s="92"/>
-      <c r="F20" s="92"/>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" s="92" t="s">
-        <v>375</v>
-      </c>
-      <c r="B21" s="92"/>
-      <c r="C21" s="92"/>
-      <c r="D21" s="92"/>
-      <c r="E21" s="92"/>
-      <c r="F21" s="92"/>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" s="92" t="s">
-        <v>376</v>
-      </c>
-      <c r="B22" s="92"/>
-      <c r="C22" s="92"/>
-      <c r="D22" s="92"/>
-      <c r="E22" s="92"/>
-      <c r="F22" s="92"/>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" s="92" t="s">
-        <v>377</v>
-      </c>
-      <c r="B23" s="92"/>
-      <c r="C23" s="92"/>
-      <c r="D23" s="92"/>
-      <c r="E23" s="92"/>
-      <c r="F23" s="92"/>
-    </row>
-    <row r="24" spans="1:11" ht="16">
-      <c r="A24" s="92" t="s">
-        <v>378</v>
-      </c>
-      <c r="B24" s="92"/>
-      <c r="C24" s="92"/>
-      <c r="D24" s="163"/>
-      <c r="E24" s="92"/>
-      <c r="F24" s="92"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="K24" s="160"/>
-    </row>
-    <row r="25" spans="1:11" ht="16">
-      <c r="A25" s="92" t="s">
-        <v>379</v>
-      </c>
-      <c r="B25" s="92"/>
-      <c r="D25" s="92"/>
-      <c r="E25" s="92"/>
-      <c r="F25" s="92"/>
-      <c r="H25" s="46"/>
-      <c r="I25" s="47"/>
-      <c r="J25" s="47"/>
-      <c r="K25" s="48"/>
-    </row>
-    <row r="26" spans="1:11" ht="16">
-      <c r="A26" s="92" t="s">
-        <v>380</v>
-      </c>
-      <c r="B26" s="92"/>
-      <c r="C26" s="92"/>
-      <c r="D26" s="92"/>
-      <c r="E26" s="92"/>
-      <c r="F26" s="92"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="20"/>
-    </row>
-    <row r="27" spans="1:11" ht="16">
-      <c r="A27" s="92" t="s">
-        <v>381</v>
-      </c>
-      <c r="B27" s="92"/>
-      <c r="C27" s="92"/>
-      <c r="D27" s="92"/>
-      <c r="E27" s="92"/>
-      <c r="F27" s="92"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-    </row>
-    <row r="28" spans="1:11" ht="16">
-      <c r="A28" s="92" t="s">
-        <v>382</v>
-      </c>
-      <c r="B28" s="92"/>
-      <c r="C28" s="92"/>
-      <c r="D28" s="92"/>
-      <c r="E28" s="92"/>
-      <c r="F28" s="92"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
-    </row>
-    <row r="29" spans="1:11" ht="16">
-      <c r="A29" s="92" t="s">
-        <v>383</v>
-      </c>
-      <c r="B29" s="92"/>
-      <c r="C29" s="92"/>
-      <c r="D29" s="92"/>
-      <c r="E29" s="92"/>
-      <c r="F29" s="92"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-    </row>
-    <row r="30" spans="1:11" ht="16">
-      <c r="A30" s="92" t="s">
-        <v>384</v>
-      </c>
-      <c r="B30" s="92"/>
-      <c r="C30" s="92"/>
-      <c r="D30" s="92"/>
-      <c r="E30" s="92"/>
-      <c r="F30" s="92"/>
-      <c r="H30" s="162"/>
-      <c r="I30" s="161"/>
-      <c r="J30" s="161"/>
-      <c r="K30" s="162"/>
-    </row>
-    <row r="31" spans="1:11" ht="16">
-      <c r="A31" s="92" t="s">
-        <v>385</v>
-      </c>
-      <c r="B31" s="92"/>
-      <c r="C31" s="92"/>
-      <c r="D31" s="92"/>
-      <c r="E31" s="92"/>
-      <c r="F31" s="92"/>
-      <c r="H31" s="47"/>
-      <c r="I31" s="47"/>
-      <c r="J31" s="49"/>
-      <c r="K31" s="49"/>
-    </row>
-    <row r="32" spans="1:11" ht="16">
-      <c r="A32" s="92" t="s">
-        <v>386</v>
-      </c>
-      <c r="B32" s="92"/>
-      <c r="C32" s="92"/>
-      <c r="D32" s="92"/>
-      <c r="E32" s="92"/>
-      <c r="F32" s="92"/>
-      <c r="H32" s="46"/>
-      <c r="I32" s="47"/>
-      <c r="J32" s="47"/>
-      <c r="K32" s="48"/>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33" s="92" t="s">
-        <v>387</v>
-      </c>
-      <c r="B33" s="92"/>
-      <c r="C33" s="92"/>
-      <c r="D33" s="92"/>
-      <c r="E33" s="92"/>
-      <c r="F33" s="92"/>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34" s="92" t="s">
-        <v>388</v>
-      </c>
-      <c r="B34" s="92"/>
-      <c r="C34" s="92"/>
-      <c r="D34" s="92"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="92"/>
-    </row>
-    <row r="35" spans="1:10" ht="16">
-      <c r="C35" s="92"/>
-      <c r="D35" s="167"/>
-      <c r="E35" s="92"/>
-      <c r="F35" s="92"/>
-      <c r="H35" s="47"/>
-      <c r="I35" s="47"/>
-      <c r="J35" s="49"/>
+    <row r="1" spans="1:1" ht="18">
+      <c r="A1" s="5" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>415</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:A24" xr:uid="{36271C4B-A74E-8E40-BB5B-1D9E627BC241}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -3746,7 +3690,7 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:L45"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="18.1640625" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="18.1640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="33.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.1640625" bestFit="1" customWidth="1"/>
@@ -4707,7 +4651,7 @@
       <c r="F43" s="7"/>
       <c r="J43" s="16"/>
     </row>
-    <row r="44" spans="1:10" ht="15" thickBot="1">
+    <row r="44" spans="1:10" ht="16" thickBot="1">
       <c r="A44" s="21"/>
       <c r="B44" s="22"/>
       <c r="C44" s="22"/>
@@ -4723,6 +4667,1284 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:L45" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F8736C3-1C58-1646-B830-FED3997DCE44}">
+  <sheetPr>
+    <tabColor theme="1" tint="0.499984740745262"/>
+  </sheetPr>
+  <dimension ref="A1:A31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="58.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>462</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A1D7428-6F4D-D94B-B882-39478008AFA2}">
+  <sheetPr>
+    <tabColor theme="1" tint="0.499984740745262"/>
+  </sheetPr>
+  <dimension ref="A1:A34"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="56" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="18">
+      <c r="A1" s="5" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>436</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8E290EA-47B4-3E4A-96CA-2FE7529B8014}">
+  <sheetPr>
+    <tabColor theme="5" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:J44"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="18.1640625" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="2" width="33.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="1.1640625" customWidth="1"/>
+    <col min="6" max="6" width="36.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="16">
+      <c r="A1" s="194" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="195" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="195" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="196" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="197"/>
+      <c r="F1" s="194" t="s">
+        <v>416</v>
+      </c>
+      <c r="G1" s="195" t="s">
+        <v>417</v>
+      </c>
+      <c r="H1" s="195" t="s">
+        <v>418</v>
+      </c>
+      <c r="I1" s="195" t="s">
+        <v>419</v>
+      </c>
+      <c r="J1" s="195" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="16">
+      <c r="A2" s="198" t="s">
+        <v>181</v>
+      </c>
+      <c r="B2" s="199" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2" s="199" t="s">
+        <v>230</v>
+      </c>
+      <c r="D2" s="200" t="s">
+        <v>201</v>
+      </c>
+      <c r="E2" s="170"/>
+      <c r="F2" s="176" t="s">
+        <v>394</v>
+      </c>
+      <c r="G2" s="177" t="s">
+        <v>394</v>
+      </c>
+      <c r="H2" s="178" t="s">
+        <v>420</v>
+      </c>
+      <c r="I2" s="177" t="s">
+        <v>200</v>
+      </c>
+      <c r="J2" s="177" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="16">
+      <c r="A3" s="201" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3" s="202" t="s">
+        <v>182</v>
+      </c>
+      <c r="C3" s="202" t="s">
+        <v>317</v>
+      </c>
+      <c r="D3" s="203" t="s">
+        <v>201</v>
+      </c>
+      <c r="E3" s="170"/>
+      <c r="F3" s="179" t="s">
+        <v>395</v>
+      </c>
+      <c r="G3" s="180" t="s">
+        <v>395</v>
+      </c>
+      <c r="H3" s="180" t="s">
+        <v>425</v>
+      </c>
+      <c r="I3" s="180" t="s">
+        <v>200</v>
+      </c>
+      <c r="J3" s="180" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" s="49" customFormat="1" ht="16">
+      <c r="A4" s="204" t="s">
+        <v>184</v>
+      </c>
+      <c r="B4" s="205" t="s">
+        <v>184</v>
+      </c>
+      <c r="C4" s="205" t="s">
+        <v>203</v>
+      </c>
+      <c r="D4" s="206" t="s">
+        <v>201</v>
+      </c>
+      <c r="E4" s="170"/>
+      <c r="F4" s="181" t="s">
+        <v>394</v>
+      </c>
+      <c r="G4" s="178" t="s">
+        <v>394</v>
+      </c>
+      <c r="H4" s="178" t="s">
+        <v>420</v>
+      </c>
+      <c r="I4" s="178" t="s">
+        <v>200</v>
+      </c>
+      <c r="J4" s="178" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="49" customFormat="1" ht="16">
+      <c r="A5" s="204" t="s">
+        <v>183</v>
+      </c>
+      <c r="B5" s="205" t="s">
+        <v>183</v>
+      </c>
+      <c r="C5" s="205" t="s">
+        <v>203</v>
+      </c>
+      <c r="D5" s="206" t="s">
+        <v>201</v>
+      </c>
+      <c r="E5" s="170"/>
+      <c r="F5" s="181" t="s">
+        <v>394</v>
+      </c>
+      <c r="G5" s="178" t="s">
+        <v>394</v>
+      </c>
+      <c r="H5" s="178" t="s">
+        <v>420</v>
+      </c>
+      <c r="I5" s="178" t="s">
+        <v>200</v>
+      </c>
+      <c r="J5" s="178" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="49" customFormat="1" ht="16">
+      <c r="A6" s="204" t="s">
+        <v>185</v>
+      </c>
+      <c r="B6" s="205" t="s">
+        <v>185</v>
+      </c>
+      <c r="C6" s="205" t="s">
+        <v>185</v>
+      </c>
+      <c r="D6" s="206" t="s">
+        <v>201</v>
+      </c>
+      <c r="E6" s="170"/>
+      <c r="F6" s="182" t="s">
+        <v>398</v>
+      </c>
+      <c r="G6" s="183" t="s">
+        <v>398</v>
+      </c>
+      <c r="H6" s="183" t="s">
+        <v>424</v>
+      </c>
+      <c r="I6" s="183" t="s">
+        <v>200</v>
+      </c>
+      <c r="J6" s="183" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="16">
+      <c r="A7" s="201" t="s">
+        <v>186</v>
+      </c>
+      <c r="B7" s="202" t="s">
+        <v>186</v>
+      </c>
+      <c r="C7" s="202" t="s">
+        <v>318</v>
+      </c>
+      <c r="D7" s="203" t="s">
+        <v>201</v>
+      </c>
+      <c r="E7" s="170"/>
+      <c r="F7" s="179" t="s">
+        <v>395</v>
+      </c>
+      <c r="G7" s="180" t="s">
+        <v>395</v>
+      </c>
+      <c r="H7" s="180" t="s">
+        <v>425</v>
+      </c>
+      <c r="I7" s="180" t="s">
+        <v>200</v>
+      </c>
+      <c r="J7" s="180" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="16">
+      <c r="A8" s="204" t="s">
+        <v>188</v>
+      </c>
+      <c r="B8" s="205" t="s">
+        <v>188</v>
+      </c>
+      <c r="C8" s="205" t="s">
+        <v>204</v>
+      </c>
+      <c r="D8" s="206" t="s">
+        <v>201</v>
+      </c>
+      <c r="E8" s="170"/>
+      <c r="F8" s="182" t="s">
+        <v>398</v>
+      </c>
+      <c r="G8" s="183" t="s">
+        <v>398</v>
+      </c>
+      <c r="H8" s="183" t="s">
+        <v>424</v>
+      </c>
+      <c r="I8" s="183" t="s">
+        <v>200</v>
+      </c>
+      <c r="J8" s="183" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="16">
+      <c r="A9" s="204" t="s">
+        <v>187</v>
+      </c>
+      <c r="B9" s="205" t="s">
+        <v>187</v>
+      </c>
+      <c r="C9" s="205" t="s">
+        <v>204</v>
+      </c>
+      <c r="D9" s="206" t="s">
+        <v>201</v>
+      </c>
+      <c r="E9" s="170"/>
+      <c r="F9" s="182" t="s">
+        <v>398</v>
+      </c>
+      <c r="G9" s="183" t="s">
+        <v>398</v>
+      </c>
+      <c r="H9" s="183" t="s">
+        <v>424</v>
+      </c>
+      <c r="I9" s="183" t="s">
+        <v>200</v>
+      </c>
+      <c r="J9" s="183" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="16">
+      <c r="A10" s="201" t="s">
+        <v>190</v>
+      </c>
+      <c r="B10" s="202" t="s">
+        <v>190</v>
+      </c>
+      <c r="C10" s="202" t="s">
+        <v>213</v>
+      </c>
+      <c r="D10" s="203" t="s">
+        <v>201</v>
+      </c>
+      <c r="E10" s="170"/>
+      <c r="F10" s="184" t="s">
+        <v>401</v>
+      </c>
+      <c r="G10" s="185" t="s">
+        <v>401</v>
+      </c>
+      <c r="H10" s="185" t="s">
+        <v>428</v>
+      </c>
+      <c r="I10" s="185" t="s">
+        <v>200</v>
+      </c>
+      <c r="J10" s="185" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="16">
+      <c r="A11" s="204" t="s">
+        <v>191</v>
+      </c>
+      <c r="B11" s="205" t="s">
+        <v>191</v>
+      </c>
+      <c r="C11" s="205" t="s">
+        <v>319</v>
+      </c>
+      <c r="D11" s="206" t="s">
+        <v>201</v>
+      </c>
+      <c r="E11" s="170"/>
+      <c r="F11" s="186" t="s">
+        <v>399</v>
+      </c>
+      <c r="G11" s="187" t="s">
+        <v>399</v>
+      </c>
+      <c r="H11" s="187" t="s">
+        <v>426</v>
+      </c>
+      <c r="I11" s="187" t="s">
+        <v>200</v>
+      </c>
+      <c r="J11" s="187" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="16">
+      <c r="A12" s="201" t="s">
+        <v>192</v>
+      </c>
+      <c r="B12" s="202" t="s">
+        <v>192</v>
+      </c>
+      <c r="C12" s="202" t="s">
+        <v>207</v>
+      </c>
+      <c r="D12" s="203" t="s">
+        <v>201</v>
+      </c>
+      <c r="E12" s="170"/>
+      <c r="F12" s="188" t="s">
+        <v>400</v>
+      </c>
+      <c r="G12" s="189" t="s">
+        <v>400</v>
+      </c>
+      <c r="H12" s="189" t="s">
+        <v>427</v>
+      </c>
+      <c r="I12" s="189" t="s">
+        <v>201</v>
+      </c>
+      <c r="J12" s="189" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="16">
+      <c r="A13" s="207" t="s">
+        <v>193</v>
+      </c>
+      <c r="B13" s="208" t="s">
+        <v>193</v>
+      </c>
+      <c r="C13" s="208" t="s">
+        <v>208</v>
+      </c>
+      <c r="D13" s="209" t="s">
+        <v>201</v>
+      </c>
+      <c r="E13" s="170"/>
+      <c r="F13" s="184" t="s">
+        <v>401</v>
+      </c>
+      <c r="G13" s="185" t="s">
+        <v>401</v>
+      </c>
+      <c r="H13" s="185" t="s">
+        <v>428</v>
+      </c>
+      <c r="I13" s="185" t="s">
+        <v>200</v>
+      </c>
+      <c r="J13" s="185" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="198" t="s">
+        <v>194</v>
+      </c>
+      <c r="B14" s="210" t="s">
+        <v>194</v>
+      </c>
+      <c r="C14" s="210" t="s">
+        <v>209</v>
+      </c>
+      <c r="D14" s="211" t="s">
+        <v>201</v>
+      </c>
+      <c r="E14" s="170"/>
+      <c r="F14" s="190" t="s">
+        <v>396</v>
+      </c>
+      <c r="G14" s="191" t="s">
+        <v>396</v>
+      </c>
+      <c r="H14" s="191" t="s">
+        <v>423</v>
+      </c>
+      <c r="I14" s="191" t="s">
+        <v>201</v>
+      </c>
+      <c r="J14" s="191" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="16">
+      <c r="A15" s="204" t="s">
+        <v>195</v>
+      </c>
+      <c r="B15" s="205" t="s">
+        <v>195</v>
+      </c>
+      <c r="C15" s="205" t="s">
+        <v>320</v>
+      </c>
+      <c r="D15" s="206" t="s">
+        <v>201</v>
+      </c>
+      <c r="E15" s="170"/>
+      <c r="F15" s="192" t="s">
+        <v>402</v>
+      </c>
+      <c r="G15" s="193" t="s">
+        <v>402</v>
+      </c>
+      <c r="H15" s="193" t="s">
+        <v>432</v>
+      </c>
+      <c r="I15" s="193" t="s">
+        <v>200</v>
+      </c>
+      <c r="J15" s="193" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="16">
+      <c r="A16" s="204" t="s">
+        <v>196</v>
+      </c>
+      <c r="B16" s="205" t="s">
+        <v>196</v>
+      </c>
+      <c r="C16" s="205" t="s">
+        <v>210</v>
+      </c>
+      <c r="D16" s="206" t="s">
+        <v>201</v>
+      </c>
+      <c r="E16" s="170"/>
+      <c r="F16" s="192" t="s">
+        <v>463</v>
+      </c>
+      <c r="G16" s="193" t="s">
+        <v>463</v>
+      </c>
+      <c r="H16" s="193" t="s">
+        <v>432</v>
+      </c>
+      <c r="I16" s="193" t="s">
+        <v>200</v>
+      </c>
+      <c r="J16" s="193" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="16">
+      <c r="A17" s="204" t="s">
+        <v>197</v>
+      </c>
+      <c r="B17" s="205" t="s">
+        <v>188</v>
+      </c>
+      <c r="C17" s="205" t="s">
+        <v>204</v>
+      </c>
+      <c r="D17" s="206" t="s">
+        <v>201</v>
+      </c>
+      <c r="E17" s="170"/>
+      <c r="F17" s="182" t="s">
+        <v>398</v>
+      </c>
+      <c r="G17" s="183" t="s">
+        <v>398</v>
+      </c>
+      <c r="H17" s="183" t="s">
+        <v>424</v>
+      </c>
+      <c r="I17" s="183" t="s">
+        <v>200</v>
+      </c>
+      <c r="J17" s="183" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="16">
+      <c r="A18" s="204" t="s">
+        <v>198</v>
+      </c>
+      <c r="B18" s="205" t="s">
+        <v>188</v>
+      </c>
+      <c r="C18" s="205" t="s">
+        <v>204</v>
+      </c>
+      <c r="D18" s="212" t="s">
+        <v>200</v>
+      </c>
+      <c r="E18" s="170"/>
+      <c r="F18" s="182" t="s">
+        <v>398</v>
+      </c>
+      <c r="G18" s="183" t="s">
+        <v>398</v>
+      </c>
+      <c r="H18" s="183" t="s">
+        <v>424</v>
+      </c>
+      <c r="I18" s="183" t="s">
+        <v>200</v>
+      </c>
+      <c r="J18" s="183" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="16">
+      <c r="A19" s="204" t="s">
+        <v>184</v>
+      </c>
+      <c r="B19" s="205" t="s">
+        <v>184</v>
+      </c>
+      <c r="C19" s="205" t="s">
+        <v>212</v>
+      </c>
+      <c r="D19" s="212" t="s">
+        <v>200</v>
+      </c>
+      <c r="E19" s="170"/>
+      <c r="F19" s="181" t="s">
+        <v>394</v>
+      </c>
+      <c r="G19" s="178" t="s">
+        <v>394</v>
+      </c>
+      <c r="H19" s="178" t="s">
+        <v>420</v>
+      </c>
+      <c r="I19" s="178" t="s">
+        <v>200</v>
+      </c>
+      <c r="J19" s="178" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="16">
+      <c r="A20" s="207" t="s">
+        <v>193</v>
+      </c>
+      <c r="B20" s="208" t="s">
+        <v>193</v>
+      </c>
+      <c r="C20" s="208" t="s">
+        <v>248</v>
+      </c>
+      <c r="D20" s="209" t="s">
+        <v>200</v>
+      </c>
+      <c r="E20" s="170"/>
+      <c r="F20" s="184" t="s">
+        <v>401</v>
+      </c>
+      <c r="G20" s="185" t="s">
+        <v>401</v>
+      </c>
+      <c r="H20" s="185" t="s">
+        <v>428</v>
+      </c>
+      <c r="I20" s="185" t="s">
+        <v>200</v>
+      </c>
+      <c r="J20" s="185" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="16">
+      <c r="A21" s="201" t="s">
+        <v>182</v>
+      </c>
+      <c r="B21" s="202" t="s">
+        <v>182</v>
+      </c>
+      <c r="C21" s="202" t="s">
+        <v>232</v>
+      </c>
+      <c r="D21" s="203" t="s">
+        <v>200</v>
+      </c>
+      <c r="E21" s="172"/>
+      <c r="F21" s="179" t="s">
+        <v>395</v>
+      </c>
+      <c r="G21" s="180" t="s">
+        <v>395</v>
+      </c>
+      <c r="H21" s="180" t="s">
+        <v>425</v>
+      </c>
+      <c r="I21" s="180" t="s">
+        <v>200</v>
+      </c>
+      <c r="J21" s="180" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="16">
+      <c r="A22" s="201"/>
+      <c r="B22" s="202"/>
+      <c r="C22" s="202"/>
+      <c r="D22" s="203"/>
+      <c r="E22" s="170"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="173"/>
+      <c r="H22" s="173"/>
+      <c r="I22" s="173"/>
+      <c r="J22" s="16"/>
+    </row>
+    <row r="23" spans="1:10" ht="16">
+      <c r="A23" s="201"/>
+      <c r="B23" s="202"/>
+      <c r="C23" s="202"/>
+      <c r="D23" s="203"/>
+      <c r="E23" s="170"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="173"/>
+      <c r="H23" s="173"/>
+      <c r="I23" s="173"/>
+      <c r="J23" s="16"/>
+    </row>
+    <row r="24" spans="1:10" ht="16">
+      <c r="A24" s="201"/>
+      <c r="B24" s="202"/>
+      <c r="C24" s="202"/>
+      <c r="D24" s="203"/>
+      <c r="E24" s="172"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="174"/>
+      <c r="H24" s="174"/>
+      <c r="I24" s="174"/>
+      <c r="J24" s="175"/>
+    </row>
+    <row r="25" spans="1:10" ht="16">
+      <c r="A25" s="201"/>
+      <c r="B25" s="202"/>
+      <c r="C25" s="202"/>
+      <c r="D25" s="203"/>
+      <c r="E25" s="172"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="172"/>
+      <c r="H25" s="172"/>
+      <c r="I25" s="172"/>
+      <c r="J25" s="16"/>
+    </row>
+    <row r="26" spans="1:10" ht="16">
+      <c r="A26" s="201"/>
+      <c r="B26" s="202"/>
+      <c r="C26" s="202"/>
+      <c r="D26" s="203"/>
+      <c r="E26" s="172"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="172"/>
+      <c r="H26" s="172"/>
+      <c r="I26" s="172"/>
+      <c r="J26" s="16"/>
+    </row>
+    <row r="27" spans="1:10" ht="16">
+      <c r="A27" s="201"/>
+      <c r="B27" s="202"/>
+      <c r="C27" s="202"/>
+      <c r="D27" s="203"/>
+      <c r="E27" s="172"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="172"/>
+      <c r="H27" s="172"/>
+      <c r="I27" s="172"/>
+      <c r="J27" s="16"/>
+    </row>
+    <row r="28" spans="1:10" ht="16">
+      <c r="A28" s="201"/>
+      <c r="B28" s="202"/>
+      <c r="C28" s="202"/>
+      <c r="D28" s="203"/>
+      <c r="E28" s="172"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="172"/>
+      <c r="H28" s="172"/>
+      <c r="I28" s="172"/>
+      <c r="J28" s="16"/>
+    </row>
+    <row r="29" spans="1:10" ht="16">
+      <c r="A29" s="201"/>
+      <c r="B29" s="202"/>
+      <c r="C29" s="202"/>
+      <c r="D29" s="203"/>
+      <c r="E29" s="172"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="172"/>
+      <c r="H29" s="172"/>
+      <c r="I29" s="172"/>
+      <c r="J29" s="16"/>
+    </row>
+    <row r="30" spans="1:10" ht="16">
+      <c r="A30" s="201"/>
+      <c r="B30" s="202"/>
+      <c r="C30" s="202"/>
+      <c r="D30" s="203"/>
+      <c r="E30" s="172"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="172"/>
+      <c r="H30" s="172"/>
+      <c r="I30" s="172"/>
+      <c r="J30" s="16"/>
+    </row>
+    <row r="31" spans="1:10" ht="16">
+      <c r="A31" s="201"/>
+      <c r="B31" s="202"/>
+      <c r="C31" s="202"/>
+      <c r="D31" s="203"/>
+      <c r="E31" s="172"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="172"/>
+      <c r="H31" s="172"/>
+      <c r="I31" s="172"/>
+      <c r="J31" s="16"/>
+    </row>
+    <row r="32" spans="1:10" ht="16">
+      <c r="A32" s="201"/>
+      <c r="B32" s="202"/>
+      <c r="C32" s="202"/>
+      <c r="D32" s="203"/>
+      <c r="E32" s="172"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="172"/>
+      <c r="H32" s="172"/>
+      <c r="I32" s="172"/>
+      <c r="J32" s="16"/>
+    </row>
+    <row r="33" spans="1:10" ht="16">
+      <c r="A33" s="201"/>
+      <c r="B33" s="202"/>
+      <c r="C33" s="202"/>
+      <c r="D33" s="203"/>
+      <c r="E33" s="172"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="172"/>
+      <c r="H33" s="172"/>
+      <c r="I33" s="172"/>
+      <c r="J33" s="16"/>
+    </row>
+    <row r="34" spans="1:10" ht="16">
+      <c r="A34" s="201"/>
+      <c r="B34" s="202"/>
+      <c r="C34" s="202"/>
+      <c r="D34" s="203"/>
+      <c r="E34" s="172"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="172"/>
+      <c r="H34" s="172"/>
+      <c r="I34" s="172"/>
+      <c r="J34" s="16"/>
+    </row>
+    <row r="35" spans="1:10" ht="16">
+      <c r="A35" s="201"/>
+      <c r="B35" s="202"/>
+      <c r="C35" s="202"/>
+      <c r="D35" s="203"/>
+      <c r="E35" s="172"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="172"/>
+      <c r="H35" s="172"/>
+      <c r="I35" s="172"/>
+      <c r="J35" s="16"/>
+    </row>
+    <row r="36" spans="1:10" ht="16">
+      <c r="A36" s="201"/>
+      <c r="B36" s="202"/>
+      <c r="C36" s="202"/>
+      <c r="D36" s="203"/>
+      <c r="E36" s="172"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="172"/>
+      <c r="H36" s="172"/>
+      <c r="I36" s="172"/>
+      <c r="J36" s="16"/>
+    </row>
+    <row r="37" spans="1:10" ht="16">
+      <c r="A37" s="201"/>
+      <c r="B37" s="202"/>
+      <c r="C37" s="202"/>
+      <c r="D37" s="203"/>
+      <c r="E37" s="172"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="172"/>
+      <c r="H37" s="172"/>
+      <c r="I37" s="172"/>
+      <c r="J37" s="16"/>
+    </row>
+    <row r="38" spans="1:10" ht="16">
+      <c r="A38" s="201"/>
+      <c r="B38" s="202"/>
+      <c r="C38" s="202"/>
+      <c r="D38" s="203"/>
+      <c r="E38" s="172"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="172"/>
+      <c r="H38" s="172"/>
+      <c r="I38" s="172"/>
+      <c r="J38" s="16"/>
+    </row>
+    <row r="39" spans="1:10" ht="16">
+      <c r="A39" s="201"/>
+      <c r="B39" s="202"/>
+      <c r="C39" s="202"/>
+      <c r="D39" s="203"/>
+      <c r="E39" s="172"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="172"/>
+      <c r="H39" s="172"/>
+      <c r="I39" s="172"/>
+      <c r="J39" s="16"/>
+    </row>
+    <row r="40" spans="1:10" ht="17" thickBot="1">
+      <c r="A40" s="213"/>
+      <c r="B40" s="214"/>
+      <c r="C40" s="214"/>
+      <c r="D40" s="215"/>
+      <c r="E40" s="172"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="22"/>
+      <c r="I40" s="22"/>
+      <c r="J40" s="23"/>
+    </row>
+    <row r="41" spans="1:10" ht="16">
+      <c r="A41" s="171"/>
+      <c r="B41" s="171"/>
+      <c r="C41" s="171"/>
+      <c r="D41" s="171"/>
+      <c r="E41" s="172"/>
+      <c r="F41" s="172"/>
+      <c r="G41" s="172"/>
+      <c r="H41" s="172"/>
+      <c r="I41" s="172"/>
+      <c r="J41" s="172"/>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="172"/>
+      <c r="B42" s="172"/>
+      <c r="C42" s="172"/>
+      <c r="D42" s="172"/>
+      <c r="E42" s="172"/>
+      <c r="F42" s="172"/>
+      <c r="G42" s="172"/>
+      <c r="H42" s="172"/>
+      <c r="I42" s="172"/>
+      <c r="J42" s="172"/>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="172"/>
+      <c r="B43" s="172"/>
+      <c r="C43" s="172"/>
+      <c r="D43" s="172"/>
+      <c r="E43" s="172"/>
+      <c r="F43" s="172"/>
+      <c r="G43" s="172"/>
+      <c r="H43" s="172"/>
+      <c r="I43" s="172"/>
+      <c r="J43" s="172"/>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="7"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4733,7 +5955,7 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:J83"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.83203125" style="92" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="39" style="92" bestFit="1" customWidth="1"/>
@@ -5948,7 +7170,7 @@
       <c r="G50" s="93"/>
       <c r="J50" s="88"/>
     </row>
-    <row r="51" spans="1:10" ht="15" thickBot="1">
+    <row r="51" spans="1:10" ht="16" thickBot="1">
       <c r="A51" s="94"/>
       <c r="B51" s="95"/>
       <c r="C51" s="95"/>
@@ -6132,7 +7354,7 @@
     <tabColor theme="1" tint="0.34998626667073579"/>
   </sheetPr>
   <dimension ref="A1:K10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="20" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="20" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36.6640625" customWidth="1"/>
     <col min="2" max="2" width="31.5" customWidth="1"/>
@@ -6447,7 +7669,7 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:L45"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="37.33203125" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
@@ -7409,7 +8631,7 @@
       <c r="F43" s="7"/>
       <c r="J43" s="16"/>
     </row>
-    <row r="44" spans="1:10" ht="15" thickBot="1">
+    <row r="44" spans="1:10" ht="16" thickBot="1">
       <c r="A44" s="21"/>
       <c r="B44" s="22"/>
       <c r="C44" s="22"/>
@@ -7430,12 +8652,677 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C35120B4-BDCF-CB4C-BC62-FC29CBC3A109}">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
+  <dimension ref="A1:L35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="20" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="2" width="36.6640625" customWidth="1"/>
+    <col min="3" max="3" width="31.5" customWidth="1"/>
+    <col min="4" max="4" width="25.5" customWidth="1"/>
+    <col min="5" max="5" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="1.6640625" customWidth="1"/>
+    <col min="8" max="9" width="33" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="28.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="16">
+      <c r="A1" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="16">
+      <c r="A2" s="92" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2" s="92"/>
+      <c r="C2" s="92" t="s">
+        <v>312</v>
+      </c>
+      <c r="D2" s="163" t="s">
+        <v>299</v>
+      </c>
+      <c r="E2" s="164"/>
+      <c r="F2" s="164"/>
+      <c r="H2" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="J2" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="K2" s="166"/>
+    </row>
+    <row r="3" spans="1:12" ht="16">
+      <c r="A3" s="92" t="s">
+        <v>364</v>
+      </c>
+      <c r="B3" s="92"/>
+      <c r="C3" s="163" t="s">
+        <v>313</v>
+      </c>
+      <c r="D3" s="163" t="s">
+        <v>299</v>
+      </c>
+      <c r="E3" s="164"/>
+      <c r="F3" s="164"/>
+      <c r="H3" s="165" t="s">
+        <v>187</v>
+      </c>
+      <c r="I3" s="165" t="s">
+        <v>187</v>
+      </c>
+      <c r="J3" s="165" t="s">
+        <v>204</v>
+      </c>
+      <c r="K3" s="166"/>
+    </row>
+    <row r="4" spans="1:12" ht="16">
+      <c r="A4" s="92" t="s">
+        <v>363</v>
+      </c>
+      <c r="B4" s="92"/>
+      <c r="C4" s="163" t="s">
+        <v>315</v>
+      </c>
+      <c r="D4" s="163" t="s">
+        <v>300</v>
+      </c>
+      <c r="E4" s="164"/>
+      <c r="F4" s="164"/>
+      <c r="H4" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="I4" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="J4" s="45" t="s">
+        <v>215</v>
+      </c>
+      <c r="K4" s="166"/>
+    </row>
+    <row r="5" spans="1:12" ht="16">
+      <c r="A5" s="92" t="s">
+        <v>365</v>
+      </c>
+      <c r="B5" s="92"/>
+      <c r="C5" s="163" t="s">
+        <v>312</v>
+      </c>
+      <c r="D5" s="163" t="s">
+        <v>299</v>
+      </c>
+      <c r="E5" s="164"/>
+      <c r="F5" s="164"/>
+      <c r="H5" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="I5" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="J5" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="K5" s="166"/>
+    </row>
+    <row r="6" spans="1:12" ht="16">
+      <c r="A6" s="92" t="s">
+        <v>366</v>
+      </c>
+      <c r="B6" s="92"/>
+      <c r="C6" s="144" t="s">
+        <v>313</v>
+      </c>
+      <c r="D6" s="144" t="s">
+        <v>299</v>
+      </c>
+      <c r="E6" s="144"/>
+      <c r="F6" s="144"/>
+      <c r="H6" s="165" t="s">
+        <v>187</v>
+      </c>
+      <c r="I6" s="165" t="s">
+        <v>187</v>
+      </c>
+      <c r="J6" s="165" t="s">
+        <v>204</v>
+      </c>
+      <c r="K6" s="166"/>
+    </row>
+    <row r="7" spans="1:12" ht="16">
+      <c r="A7" s="92" t="s">
+        <v>367</v>
+      </c>
+      <c r="B7" s="92"/>
+      <c r="C7" s="163" t="s">
+        <v>312</v>
+      </c>
+      <c r="D7" s="144" t="s">
+        <v>299</v>
+      </c>
+      <c r="E7" s="164"/>
+      <c r="F7" s="164"/>
+      <c r="H7" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="I7" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="J7" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="K7" s="166"/>
+    </row>
+    <row r="8" spans="1:12" ht="16">
+      <c r="A8" s="92" t="s">
+        <v>368</v>
+      </c>
+      <c r="B8" s="92"/>
+      <c r="C8" s="163" t="s">
+        <v>315</v>
+      </c>
+      <c r="D8" s="163" t="s">
+        <v>300</v>
+      </c>
+      <c r="E8" s="164"/>
+      <c r="F8" s="164"/>
+      <c r="H8" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="I8" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="J8" s="45" t="s">
+        <v>215</v>
+      </c>
+      <c r="K8" s="166"/>
+      <c r="L8" s="41"/>
+    </row>
+    <row r="9" spans="1:12" ht="16">
+      <c r="A9" s="92" t="s">
+        <v>369</v>
+      </c>
+      <c r="B9" s="92"/>
+      <c r="C9" s="163" t="s">
+        <v>316</v>
+      </c>
+      <c r="D9" s="163" t="s">
+        <v>300</v>
+      </c>
+      <c r="E9" s="164"/>
+      <c r="F9" s="164"/>
+      <c r="H9" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="K9" s="166"/>
+    </row>
+    <row r="10" spans="1:12" ht="16">
+      <c r="A10" s="92" t="s">
+        <v>370</v>
+      </c>
+      <c r="B10" s="92"/>
+      <c r="C10" s="144" t="s">
+        <v>308</v>
+      </c>
+      <c r="D10" s="144" t="s">
+        <v>298</v>
+      </c>
+      <c r="E10" s="144"/>
+      <c r="F10" s="144"/>
+      <c r="H10" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="I10" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="J10" s="33" t="s">
+        <v>214</v>
+      </c>
+      <c r="K10" s="166"/>
+    </row>
+    <row r="11" spans="1:12" ht="16">
+      <c r="A11" s="92" t="s">
+        <v>309</v>
+      </c>
+      <c r="B11" s="92"/>
+      <c r="C11" s="92" t="s">
+        <v>309</v>
+      </c>
+      <c r="D11" s="144" t="s">
+        <v>298</v>
+      </c>
+      <c r="E11" s="92"/>
+      <c r="F11" s="92"/>
+      <c r="H11" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="I11" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="J11" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="K11" s="166"/>
+    </row>
+    <row r="12" spans="1:12" ht="16">
+      <c r="A12" s="92" t="s">
+        <v>310</v>
+      </c>
+      <c r="B12" s="92"/>
+      <c r="C12" s="92" t="s">
+        <v>310</v>
+      </c>
+      <c r="D12" s="144" t="s">
+        <v>298</v>
+      </c>
+      <c r="E12" s="92"/>
+      <c r="F12" s="92"/>
+      <c r="H12" s="165" t="s">
+        <v>187</v>
+      </c>
+      <c r="I12" s="165" t="s">
+        <v>187</v>
+      </c>
+      <c r="J12" s="165" t="s">
+        <v>204</v>
+      </c>
+      <c r="K12" s="166"/>
+    </row>
+    <row r="13" spans="1:12" ht="16">
+      <c r="A13" s="92" t="s">
+        <v>371</v>
+      </c>
+      <c r="B13" s="92"/>
+      <c r="C13" s="92" t="s">
+        <v>311</v>
+      </c>
+      <c r="D13" s="163" t="s">
+        <v>299</v>
+      </c>
+      <c r="E13" s="92"/>
+      <c r="F13" s="92"/>
+      <c r="H13" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="I13" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="J13" s="33" t="s">
+        <v>214</v>
+      </c>
+      <c r="K13" s="166"/>
+    </row>
+    <row r="14" spans="1:12" ht="16">
+      <c r="A14" s="92" t="s">
+        <v>312</v>
+      </c>
+      <c r="B14" s="92"/>
+      <c r="C14" s="92" t="s">
+        <v>312</v>
+      </c>
+      <c r="D14" s="163" t="s">
+        <v>299</v>
+      </c>
+      <c r="E14" s="92"/>
+      <c r="F14" s="92"/>
+      <c r="H14" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="I14" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="J14" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="K14" s="166"/>
+    </row>
+    <row r="15" spans="1:12" ht="16">
+      <c r="A15" s="92" t="s">
+        <v>313</v>
+      </c>
+      <c r="B15" s="92"/>
+      <c r="C15" s="92" t="s">
+        <v>313</v>
+      </c>
+      <c r="D15" s="163" t="s">
+        <v>299</v>
+      </c>
+      <c r="E15" s="92"/>
+      <c r="F15" s="92"/>
+      <c r="H15" s="165" t="s">
+        <v>187</v>
+      </c>
+      <c r="I15" s="165" t="s">
+        <v>187</v>
+      </c>
+      <c r="J15" s="165" t="s">
+        <v>204</v>
+      </c>
+      <c r="K15" s="166"/>
+    </row>
+    <row r="16" spans="1:12" ht="16">
+      <c r="A16" s="92" t="s">
+        <v>372</v>
+      </c>
+      <c r="B16" s="92"/>
+      <c r="C16" s="92" t="s">
+        <v>314</v>
+      </c>
+      <c r="D16" s="163" t="s">
+        <v>300</v>
+      </c>
+      <c r="E16" s="92"/>
+      <c r="F16" s="92"/>
+      <c r="H16" s="41" t="s">
+        <v>190</v>
+      </c>
+      <c r="I16" s="42" t="s">
+        <v>190</v>
+      </c>
+      <c r="J16" s="42" t="s">
+        <v>213</v>
+      </c>
+      <c r="K16" s="166"/>
+    </row>
+    <row r="17" spans="1:11" ht="16">
+      <c r="A17" s="92" t="s">
+        <v>315</v>
+      </c>
+      <c r="B17" s="92"/>
+      <c r="C17" s="92" t="s">
+        <v>315</v>
+      </c>
+      <c r="D17" s="163" t="s">
+        <v>300</v>
+      </c>
+      <c r="E17" s="92"/>
+      <c r="F17" s="92"/>
+      <c r="H17" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="I17" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="J17" s="45" t="s">
+        <v>215</v>
+      </c>
+      <c r="K17" s="166"/>
+    </row>
+    <row r="18" spans="1:11" ht="16">
+      <c r="A18" s="92" t="s">
+        <v>316</v>
+      </c>
+      <c r="B18" s="92"/>
+      <c r="C18" s="92" t="s">
+        <v>316</v>
+      </c>
+      <c r="D18" s="163" t="s">
+        <v>300</v>
+      </c>
+      <c r="E18" s="92"/>
+      <c r="F18" s="92"/>
+      <c r="H18" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="I18" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="J18" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="K18" s="166"/>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="92" t="s">
+        <v>373</v>
+      </c>
+      <c r="B19" s="92"/>
+      <c r="C19" s="92"/>
+      <c r="D19" s="92"/>
+      <c r="E19" s="92"/>
+      <c r="F19" s="92"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="92" t="s">
+        <v>374</v>
+      </c>
+      <c r="B20" s="92"/>
+      <c r="C20" s="92"/>
+      <c r="D20" s="92"/>
+      <c r="E20" s="92"/>
+      <c r="F20" s="92"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="92" t="s">
+        <v>375</v>
+      </c>
+      <c r="B21" s="92"/>
+      <c r="C21" s="92"/>
+      <c r="D21" s="92"/>
+      <c r="E21" s="92"/>
+      <c r="F21" s="92"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="92" t="s">
+        <v>376</v>
+      </c>
+      <c r="B22" s="92"/>
+      <c r="C22" s="92"/>
+      <c r="D22" s="92"/>
+      <c r="E22" s="92"/>
+      <c r="F22" s="92"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="92" t="s">
+        <v>377</v>
+      </c>
+      <c r="B23" s="92"/>
+      <c r="C23" s="92"/>
+      <c r="D23" s="92"/>
+      <c r="E23" s="92"/>
+      <c r="F23" s="92"/>
+    </row>
+    <row r="24" spans="1:11" ht="16">
+      <c r="A24" s="92" t="s">
+        <v>378</v>
+      </c>
+      <c r="B24" s="92"/>
+      <c r="C24" s="92"/>
+      <c r="D24" s="163"/>
+      <c r="E24" s="92"/>
+      <c r="F24" s="92"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="K24" s="160"/>
+    </row>
+    <row r="25" spans="1:11" ht="16">
+      <c r="A25" s="92" t="s">
+        <v>379</v>
+      </c>
+      <c r="B25" s="92"/>
+      <c r="D25" s="92"/>
+      <c r="E25" s="92"/>
+      <c r="F25" s="92"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="47"/>
+      <c r="J25" s="47"/>
+      <c r="K25" s="48"/>
+    </row>
+    <row r="26" spans="1:11" ht="16">
+      <c r="A26" s="92" t="s">
+        <v>380</v>
+      </c>
+      <c r="B26" s="92"/>
+      <c r="C26" s="92"/>
+      <c r="D26" s="92"/>
+      <c r="E26" s="92"/>
+      <c r="F26" s="92"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="20"/>
+    </row>
+    <row r="27" spans="1:11" ht="16">
+      <c r="A27" s="92" t="s">
+        <v>381</v>
+      </c>
+      <c r="B27" s="92"/>
+      <c r="C27" s="92"/>
+      <c r="D27" s="92"/>
+      <c r="E27" s="92"/>
+      <c r="F27" s="92"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+    </row>
+    <row r="28" spans="1:11" ht="16">
+      <c r="A28" s="92" t="s">
+        <v>382</v>
+      </c>
+      <c r="B28" s="92"/>
+      <c r="C28" s="92"/>
+      <c r="D28" s="92"/>
+      <c r="E28" s="92"/>
+      <c r="F28" s="92"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+    </row>
+    <row r="29" spans="1:11" ht="16">
+      <c r="A29" s="92" t="s">
+        <v>383</v>
+      </c>
+      <c r="B29" s="92"/>
+      <c r="C29" s="92"/>
+      <c r="D29" s="92"/>
+      <c r="E29" s="92"/>
+      <c r="F29" s="92"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+    </row>
+    <row r="30" spans="1:11" ht="16">
+      <c r="A30" s="92" t="s">
+        <v>384</v>
+      </c>
+      <c r="B30" s="92"/>
+      <c r="C30" s="92"/>
+      <c r="D30" s="92"/>
+      <c r="E30" s="92"/>
+      <c r="F30" s="92"/>
+      <c r="H30" s="162"/>
+      <c r="I30" s="161"/>
+      <c r="J30" s="161"/>
+      <c r="K30" s="162"/>
+    </row>
+    <row r="31" spans="1:11" ht="16">
+      <c r="A31" s="92" t="s">
+        <v>385</v>
+      </c>
+      <c r="B31" s="92"/>
+      <c r="C31" s="92"/>
+      <c r="D31" s="92"/>
+      <c r="E31" s="92"/>
+      <c r="F31" s="92"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="47"/>
+      <c r="J31" s="49"/>
+      <c r="K31" s="49"/>
+    </row>
+    <row r="32" spans="1:11" ht="16">
+      <c r="A32" s="92" t="s">
+        <v>386</v>
+      </c>
+      <c r="B32" s="92"/>
+      <c r="C32" s="92"/>
+      <c r="D32" s="92"/>
+      <c r="E32" s="92"/>
+      <c r="F32" s="92"/>
+      <c r="H32" s="46"/>
+      <c r="I32" s="47"/>
+      <c r="J32" s="47"/>
+      <c r="K32" s="48"/>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="92" t="s">
+        <v>387</v>
+      </c>
+      <c r="B33" s="92"/>
+      <c r="C33" s="92"/>
+      <c r="D33" s="92"/>
+      <c r="E33" s="92"/>
+      <c r="F33" s="92"/>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="92" t="s">
+        <v>388</v>
+      </c>
+      <c r="B34" s="92"/>
+      <c r="C34" s="92"/>
+      <c r="D34" s="92"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="92"/>
+    </row>
+    <row r="35" spans="1:10" ht="16">
+      <c r="C35" s="92"/>
+      <c r="D35" s="167"/>
+      <c r="E35" s="92"/>
+      <c r="F35" s="92"/>
+      <c r="H35" s="47"/>
+      <c r="I35" s="47"/>
+      <c r="J35" s="49"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:B69"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="36" customWidth="1"/>
   </cols>
@@ -7999,13 +9886,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:C46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="39.5" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="39.5" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" ht="45.5" customHeight="1" thickBot="1">
       <c r="A1" s="3" t="s">
@@ -8520,13 +10407,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:C21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="33.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.6640625" bestFit="1" customWidth="1"/>
@@ -8689,7 +10576,7 @@
       </c>
       <c r="C20" s="16"/>
     </row>
-    <row r="21" spans="1:3" ht="15" thickBot="1">
+    <row r="21" spans="1:3" ht="16" thickBot="1">
       <c r="A21" s="21" t="s">
         <v>252</v>
       </c>
@@ -8700,116 +10587,4 @@
   <autoFilter ref="A1:A21" xr:uid="{00000000-0001-0000-0600-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41D029F1-3F90-764F-9191-4F62BF9F0215}">
-  <sheetPr>
-    <tabColor theme="9" tint="0.39997558519241921"/>
-  </sheetPr>
-  <dimension ref="A1:A19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
-  <cols>
-    <col min="1" max="1" width="33.5" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" ht="21">
-      <c r="A1" s="6" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="16">
-      <c r="A2" s="4" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="16">
-      <c r="A3" s="4" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="16">
-      <c r="A4" s="4" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="16">
-      <c r="A5" s="4" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="16">
-      <c r="A6" s="4" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" ht="16">
-      <c r="A7" s="4" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" ht="16">
-      <c r="A8" s="4" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" ht="16">
-      <c r="A9" s="4" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" ht="16">
-      <c r="A10" s="4" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" ht="16">
-      <c r="A11" s="4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" ht="16">
-      <c r="A12" s="4" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" ht="16">
-      <c r="A13" s="4" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" ht="16">
-      <c r="A14" s="4" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" ht="16">
-      <c r="A15" s="4" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" ht="16">
-      <c r="A16" s="4" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="16">
-      <c r="A17" s="4" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" ht="16">
-      <c r="A18" s="4" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" ht="16">
-      <c r="A19" s="4" t="s">
-        <v>198</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:A19" xr:uid="{41D029F1-3F90-764F-9191-4F62BF9F0215}"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/atlas_max_plus_to_poly_mapping_template.xlsx
+++ b/atlas_max_plus_to_poly_mapping_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raeltonhonorio/Documents/KDAM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE4C02EC-2C6D-524C-8353-1BF9C391C5B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A6DA5E-71DB-8C44-94C3-AE6B897FB53E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" firstSheet="13" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -1878,7 +1878,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="216">
+  <cellXfs count="202">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2143,19 +2143,7 @@
     <xf numFmtId="0" fontId="4" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="27" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2164,25 +2152,12 @@
     <xf numFmtId="0" fontId="8" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="29" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2192,28 +2167,28 @@
     <xf numFmtId="0" fontId="23" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="30" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="30" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="30" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="30" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="30" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="30" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="30" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2223,6 +2198,13 @@
     <xf numFmtId="0" fontId="4" fillId="30" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="30" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="30" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2390,17 +2372,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="95" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="68.25" customHeight="1">
-      <c r="A1" s="168" t="s">
+      <c r="A1" s="199" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="169"/>
+      <c r="B1" s="200"/>
     </row>
     <row r="2" spans="1:2" ht="45.5" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -2464,7 +2446,7 @@
     <tabColor theme="9" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:A19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="33.5" bestFit="1" customWidth="1"/>
   </cols>
@@ -2576,7 +2558,7 @@
     <tabColor theme="9" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:A19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="33.5" bestFit="1" customWidth="1"/>
   </cols>
@@ -2695,7 +2677,7 @@
     <tabColor theme="9" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:A44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="39.83203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -2932,7 +2914,7 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:A10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="35" bestFit="1" customWidth="1"/>
   </cols>
@@ -2999,7 +2981,7 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:A16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="44" bestFit="1" customWidth="1"/>
   </cols>
@@ -3096,7 +3078,7 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="24.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.6640625" customWidth="1"/>
@@ -3215,7 +3197,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:A34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="35" bestFit="1" customWidth="1"/>
   </cols>
@@ -3401,7 +3383,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:A17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="44" bestFit="1" customWidth="1"/>
   </cols>
@@ -3502,7 +3484,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:A7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="22.5" bestFit="1" customWidth="1"/>
   </cols>
@@ -3553,7 +3535,7 @@
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:A24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="39.5" bestFit="1" customWidth="1"/>
   </cols>
@@ -3690,7 +3672,7 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:L45"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="18.1640625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="18.1640625" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="33.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.1640625" bestFit="1" customWidth="1"/>
@@ -4651,7 +4633,7 @@
       <c r="F43" s="7"/>
       <c r="J43" s="16"/>
     </row>
-    <row r="44" spans="1:10" ht="16" thickBot="1">
+    <row r="44" spans="1:10" ht="15" thickBot="1">
       <c r="A44" s="21"/>
       <c r="B44" s="22"/>
       <c r="C44" s="22"/>
@@ -4677,7 +4659,7 @@
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:A31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="58.83203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -4848,7 +4830,7 @@
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:A34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="56" bestFit="1" customWidth="1"/>
   </cols>
@@ -5034,7 +5016,7 @@
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="18.1640625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="18.1640625" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="33.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.1640625" bestFit="1" customWidth="1"/>
@@ -5048,857 +5030,794 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="16">
-      <c r="A1" s="194" t="s">
+      <c r="A1" s="177" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="195" t="s">
+      <c r="B1" s="178" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="195" t="s">
+      <c r="C1" s="178" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="196" t="s">
+      <c r="D1" s="179" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="197"/>
-      <c r="F1" s="194" t="s">
+      <c r="E1" s="180"/>
+      <c r="F1" s="177" t="s">
         <v>416</v>
       </c>
-      <c r="G1" s="195" t="s">
+      <c r="G1" s="178" t="s">
         <v>417</v>
       </c>
-      <c r="H1" s="195" t="s">
+      <c r="H1" s="178" t="s">
         <v>418</v>
       </c>
-      <c r="I1" s="195" t="s">
+      <c r="I1" s="178" t="s">
         <v>419</v>
       </c>
-      <c r="J1" s="195" t="s">
+      <c r="J1" s="178" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="16">
-      <c r="A2" s="198" t="s">
+      <c r="A2" s="181" t="s">
         <v>181</v>
       </c>
-      <c r="B2" s="199" t="s">
+      <c r="B2" s="182" t="s">
         <v>181</v>
       </c>
-      <c r="C2" s="199" t="s">
+      <c r="C2" s="182" t="s">
         <v>230</v>
       </c>
-      <c r="D2" s="200" t="s">
-        <v>201</v>
-      </c>
-      <c r="E2" s="170"/>
-      <c r="F2" s="176" t="s">
+      <c r="D2" s="183" t="s">
+        <v>201</v>
+      </c>
+      <c r="E2" s="50"/>
+      <c r="F2" s="170" t="s">
         <v>394</v>
       </c>
-      <c r="G2" s="177" t="s">
+      <c r="G2" s="59" t="s">
         <v>394</v>
       </c>
-      <c r="H2" s="178" t="s">
+      <c r="H2" s="75" t="s">
         <v>420</v>
       </c>
-      <c r="I2" s="177" t="s">
+      <c r="I2" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="J2" s="177" t="s">
+      <c r="J2" s="59" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="16">
-      <c r="A3" s="201" t="s">
+      <c r="A3" s="184" t="s">
         <v>182</v>
       </c>
-      <c r="B3" s="202" t="s">
+      <c r="B3" s="185" t="s">
         <v>182</v>
       </c>
-      <c r="C3" s="202" t="s">
+      <c r="C3" s="185" t="s">
         <v>317</v>
       </c>
-      <c r="D3" s="203" t="s">
-        <v>201</v>
-      </c>
-      <c r="E3" s="170"/>
-      <c r="F3" s="179" t="s">
+      <c r="D3" s="186" t="s">
+        <v>201</v>
+      </c>
+      <c r="E3" s="50"/>
+      <c r="F3" s="11" t="s">
         <v>395</v>
       </c>
-      <c r="G3" s="180" t="s">
+      <c r="G3" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="H3" s="180" t="s">
+      <c r="H3" s="15" t="s">
         <v>425</v>
       </c>
-      <c r="I3" s="180" t="s">
+      <c r="I3" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="J3" s="180" t="s">
+      <c r="J3" s="15" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="49" customFormat="1" ht="16">
-      <c r="A4" s="204" t="s">
+      <c r="A4" s="187" t="s">
         <v>184</v>
       </c>
-      <c r="B4" s="205" t="s">
+      <c r="B4" s="188" t="s">
         <v>184</v>
       </c>
-      <c r="C4" s="205" t="s">
+      <c r="C4" s="188" t="s">
         <v>203</v>
       </c>
-      <c r="D4" s="206" t="s">
-        <v>201</v>
-      </c>
-      <c r="E4" s="170"/>
-      <c r="F4" s="181" t="s">
+      <c r="D4" s="189" t="s">
+        <v>201</v>
+      </c>
+      <c r="E4" s="50"/>
+      <c r="F4" s="74" t="s">
         <v>394</v>
       </c>
-      <c r="G4" s="178" t="s">
+      <c r="G4" s="75" t="s">
         <v>394</v>
       </c>
-      <c r="H4" s="178" t="s">
+      <c r="H4" s="75" t="s">
         <v>420</v>
       </c>
-      <c r="I4" s="178" t="s">
+      <c r="I4" s="75" t="s">
         <v>200</v>
       </c>
-      <c r="J4" s="178" t="s">
+      <c r="J4" s="75" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="49" customFormat="1" ht="16">
-      <c r="A5" s="204" t="s">
+      <c r="A5" s="187" t="s">
         <v>183</v>
       </c>
-      <c r="B5" s="205" t="s">
+      <c r="B5" s="188" t="s">
         <v>183</v>
       </c>
-      <c r="C5" s="205" t="s">
+      <c r="C5" s="188" t="s">
         <v>203</v>
       </c>
-      <c r="D5" s="206" t="s">
-        <v>201</v>
-      </c>
-      <c r="E5" s="170"/>
-      <c r="F5" s="181" t="s">
+      <c r="D5" s="189" t="s">
+        <v>201</v>
+      </c>
+      <c r="E5" s="50"/>
+      <c r="F5" s="74" t="s">
         <v>394</v>
       </c>
-      <c r="G5" s="178" t="s">
+      <c r="G5" s="75" t="s">
         <v>394</v>
       </c>
-      <c r="H5" s="178" t="s">
+      <c r="H5" s="75" t="s">
         <v>420</v>
       </c>
-      <c r="I5" s="178" t="s">
+      <c r="I5" s="75" t="s">
         <v>200</v>
       </c>
-      <c r="J5" s="178" t="s">
+      <c r="J5" s="75" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="49" customFormat="1" ht="16">
-      <c r="A6" s="204" t="s">
+      <c r="A6" s="187" t="s">
         <v>185</v>
       </c>
-      <c r="B6" s="205" t="s">
+      <c r="B6" s="188" t="s">
         <v>185</v>
       </c>
-      <c r="C6" s="205" t="s">
+      <c r="C6" s="188" t="s">
         <v>185</v>
       </c>
-      <c r="D6" s="206" t="s">
-        <v>201</v>
-      </c>
-      <c r="E6" s="170"/>
-      <c r="F6" s="182" t="s">
+      <c r="D6" s="189" t="s">
+        <v>201</v>
+      </c>
+      <c r="E6" s="50"/>
+      <c r="F6" s="171" t="s">
         <v>398</v>
       </c>
-      <c r="G6" s="183" t="s">
+      <c r="G6" s="172" t="s">
         <v>398</v>
       </c>
-      <c r="H6" s="183" t="s">
+      <c r="H6" s="172" t="s">
         <v>424</v>
       </c>
-      <c r="I6" s="183" t="s">
+      <c r="I6" s="172" t="s">
         <v>200</v>
       </c>
-      <c r="J6" s="183" t="s">
+      <c r="J6" s="172" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="16">
-      <c r="A7" s="201" t="s">
+      <c r="A7" s="184" t="s">
         <v>186</v>
       </c>
-      <c r="B7" s="202" t="s">
+      <c r="B7" s="185" t="s">
         <v>186</v>
       </c>
-      <c r="C7" s="202" t="s">
+      <c r="C7" s="185" t="s">
         <v>318</v>
       </c>
-      <c r="D7" s="203" t="s">
-        <v>201</v>
-      </c>
-      <c r="E7" s="170"/>
-      <c r="F7" s="179" t="s">
+      <c r="D7" s="186" t="s">
+        <v>201</v>
+      </c>
+      <c r="E7" s="50"/>
+      <c r="F7" s="11" t="s">
         <v>395</v>
       </c>
-      <c r="G7" s="180" t="s">
+      <c r="G7" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="H7" s="180" t="s">
+      <c r="H7" s="15" t="s">
         <v>425</v>
       </c>
-      <c r="I7" s="180" t="s">
+      <c r="I7" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="J7" s="180" t="s">
+      <c r="J7" s="15" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="16">
-      <c r="A8" s="204" t="s">
+      <c r="A8" s="187" t="s">
         <v>188</v>
       </c>
-      <c r="B8" s="205" t="s">
+      <c r="B8" s="188" t="s">
         <v>188</v>
       </c>
-      <c r="C8" s="205" t="s">
+      <c r="C8" s="188" t="s">
         <v>204</v>
       </c>
-      <c r="D8" s="206" t="s">
-        <v>201</v>
-      </c>
-      <c r="E8" s="170"/>
-      <c r="F8" s="182" t="s">
+      <c r="D8" s="189" t="s">
+        <v>201</v>
+      </c>
+      <c r="E8" s="50"/>
+      <c r="F8" s="171" t="s">
         <v>398</v>
       </c>
-      <c r="G8" s="183" t="s">
+      <c r="G8" s="172" t="s">
         <v>398</v>
       </c>
-      <c r="H8" s="183" t="s">
+      <c r="H8" s="172" t="s">
         <v>424</v>
       </c>
-      <c r="I8" s="183" t="s">
+      <c r="I8" s="172" t="s">
         <v>200</v>
       </c>
-      <c r="J8" s="183" t="s">
+      <c r="J8" s="172" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="16">
-      <c r="A9" s="204" t="s">
+      <c r="A9" s="187" t="s">
         <v>187</v>
       </c>
-      <c r="B9" s="205" t="s">
+      <c r="B9" s="188" t="s">
         <v>187</v>
       </c>
-      <c r="C9" s="205" t="s">
+      <c r="C9" s="188" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="206" t="s">
-        <v>201</v>
-      </c>
-      <c r="E9" s="170"/>
-      <c r="F9" s="182" t="s">
+      <c r="D9" s="189" t="s">
+        <v>201</v>
+      </c>
+      <c r="E9" s="50"/>
+      <c r="F9" s="171" t="s">
         <v>398</v>
       </c>
-      <c r="G9" s="183" t="s">
+      <c r="G9" s="172" t="s">
         <v>398</v>
       </c>
-      <c r="H9" s="183" t="s">
+      <c r="H9" s="172" t="s">
         <v>424</v>
       </c>
-      <c r="I9" s="183" t="s">
+      <c r="I9" s="172" t="s">
         <v>200</v>
       </c>
-      <c r="J9" s="183" t="s">
+      <c r="J9" s="172" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="16">
-      <c r="A10" s="201" t="s">
+      <c r="A10" s="184" t="s">
         <v>190</v>
       </c>
-      <c r="B10" s="202" t="s">
+      <c r="B10" s="185" t="s">
         <v>190</v>
       </c>
-      <c r="C10" s="202" t="s">
+      <c r="C10" s="185" t="s">
         <v>213</v>
       </c>
-      <c r="D10" s="203" t="s">
-        <v>201</v>
-      </c>
-      <c r="E10" s="170"/>
-      <c r="F10" s="184" t="s">
+      <c r="D10" s="186" t="s">
+        <v>201</v>
+      </c>
+      <c r="E10" s="50"/>
+      <c r="F10" s="51" t="s">
         <v>401</v>
       </c>
-      <c r="G10" s="185" t="s">
+      <c r="G10" s="60" t="s">
         <v>401</v>
       </c>
-      <c r="H10" s="185" t="s">
+      <c r="H10" s="60" t="s">
         <v>428</v>
       </c>
-      <c r="I10" s="185" t="s">
+      <c r="I10" s="60" t="s">
         <v>200</v>
       </c>
-      <c r="J10" s="185" t="s">
+      <c r="J10" s="60" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="16">
-      <c r="A11" s="204" t="s">
+      <c r="A11" s="187" t="s">
         <v>191</v>
       </c>
-      <c r="B11" s="205" t="s">
+      <c r="B11" s="188" t="s">
         <v>191</v>
       </c>
-      <c r="C11" s="205" t="s">
+      <c r="C11" s="188" t="s">
         <v>319</v>
       </c>
-      <c r="D11" s="206" t="s">
-        <v>201</v>
-      </c>
-      <c r="E11" s="170"/>
-      <c r="F11" s="186" t="s">
+      <c r="D11" s="189" t="s">
+        <v>201</v>
+      </c>
+      <c r="E11" s="50"/>
+      <c r="F11" s="85" t="s">
         <v>399</v>
       </c>
-      <c r="G11" s="187" t="s">
+      <c r="G11" s="86" t="s">
         <v>399</v>
       </c>
-      <c r="H11" s="187" t="s">
+      <c r="H11" s="86" t="s">
         <v>426</v>
       </c>
-      <c r="I11" s="187" t="s">
+      <c r="I11" s="86" t="s">
         <v>200</v>
       </c>
-      <c r="J11" s="187" t="s">
+      <c r="J11" s="86" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="16">
-      <c r="A12" s="201" t="s">
+      <c r="A12" s="184" t="s">
         <v>192</v>
       </c>
-      <c r="B12" s="202" t="s">
+      <c r="B12" s="185" t="s">
         <v>192</v>
       </c>
-      <c r="C12" s="202" t="s">
+      <c r="C12" s="185" t="s">
         <v>207</v>
       </c>
-      <c r="D12" s="203" t="s">
-        <v>201</v>
-      </c>
-      <c r="E12" s="170"/>
-      <c r="F12" s="188" t="s">
+      <c r="D12" s="186" t="s">
+        <v>201</v>
+      </c>
+      <c r="E12" s="50"/>
+      <c r="F12" s="173" t="s">
         <v>400</v>
       </c>
-      <c r="G12" s="189" t="s">
+      <c r="G12" s="130" t="s">
         <v>400</v>
       </c>
-      <c r="H12" s="189" t="s">
+      <c r="H12" s="130" t="s">
         <v>427</v>
       </c>
-      <c r="I12" s="189" t="s">
-        <v>201</v>
-      </c>
-      <c r="J12" s="189" t="s">
+      <c r="I12" s="130" t="s">
+        <v>201</v>
+      </c>
+      <c r="J12" s="130" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="16">
-      <c r="A13" s="207" t="s">
+      <c r="A13" s="190" t="s">
         <v>193</v>
       </c>
-      <c r="B13" s="208" t="s">
+      <c r="B13" s="191" t="s">
         <v>193</v>
       </c>
-      <c r="C13" s="208" t="s">
+      <c r="C13" s="191" t="s">
         <v>208</v>
       </c>
-      <c r="D13" s="209" t="s">
-        <v>201</v>
-      </c>
-      <c r="E13" s="170"/>
-      <c r="F13" s="184" t="s">
+      <c r="D13" s="192" t="s">
+        <v>201</v>
+      </c>
+      <c r="E13" s="50"/>
+      <c r="F13" s="51" t="s">
         <v>401</v>
       </c>
-      <c r="G13" s="185" t="s">
+      <c r="G13" s="60" t="s">
         <v>401</v>
       </c>
-      <c r="H13" s="185" t="s">
+      <c r="H13" s="60" t="s">
         <v>428</v>
       </c>
-      <c r="I13" s="185" t="s">
+      <c r="I13" s="60" t="s">
         <v>200</v>
       </c>
-      <c r="J13" s="185" t="s">
+      <c r="J13" s="60" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="198" t="s">
+    <row r="14" spans="1:10" ht="15">
+      <c r="A14" s="181" t="s">
         <v>194</v>
       </c>
-      <c r="B14" s="210" t="s">
+      <c r="B14" s="193" t="s">
         <v>194</v>
       </c>
-      <c r="C14" s="210" t="s">
+      <c r="C14" s="193" t="s">
         <v>209</v>
       </c>
-      <c r="D14" s="211" t="s">
-        <v>201</v>
-      </c>
-      <c r="E14" s="170"/>
-      <c r="F14" s="190" t="s">
+      <c r="D14" s="194" t="s">
+        <v>201</v>
+      </c>
+      <c r="E14" s="50"/>
+      <c r="F14" s="174" t="s">
         <v>396</v>
       </c>
-      <c r="G14" s="191" t="s">
+      <c r="G14" s="175" t="s">
         <v>396</v>
       </c>
-      <c r="H14" s="191" t="s">
+      <c r="H14" s="175" t="s">
         <v>423</v>
       </c>
-      <c r="I14" s="191" t="s">
-        <v>201</v>
-      </c>
-      <c r="J14" s="191" t="s">
+      <c r="I14" s="175" t="s">
+        <v>201</v>
+      </c>
+      <c r="J14" s="175" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="16">
-      <c r="A15" s="204" t="s">
+      <c r="A15" s="187" t="s">
         <v>195</v>
       </c>
-      <c r="B15" s="205" t="s">
+      <c r="B15" s="188" t="s">
         <v>195</v>
       </c>
-      <c r="C15" s="205" t="s">
+      <c r="C15" s="188" t="s">
         <v>320</v>
       </c>
-      <c r="D15" s="206" t="s">
-        <v>201</v>
-      </c>
-      <c r="E15" s="170"/>
-      <c r="F15" s="192" t="s">
+      <c r="D15" s="189" t="s">
+        <v>201</v>
+      </c>
+      <c r="E15" s="50"/>
+      <c r="F15" s="176" t="s">
         <v>402</v>
       </c>
-      <c r="G15" s="193" t="s">
+      <c r="G15" s="45" t="s">
         <v>402</v>
       </c>
-      <c r="H15" s="193" t="s">
+      <c r="H15" s="45" t="s">
         <v>432</v>
       </c>
-      <c r="I15" s="193" t="s">
+      <c r="I15" s="45" t="s">
         <v>200</v>
       </c>
-      <c r="J15" s="193" t="s">
+      <c r="J15" s="45" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="16">
-      <c r="A16" s="204" t="s">
+      <c r="A16" s="187" t="s">
         <v>196</v>
       </c>
-      <c r="B16" s="205" t="s">
+      <c r="B16" s="188" t="s">
         <v>196</v>
       </c>
-      <c r="C16" s="205" t="s">
+      <c r="C16" s="188" t="s">
         <v>210</v>
       </c>
-      <c r="D16" s="206" t="s">
-        <v>201</v>
-      </c>
-      <c r="E16" s="170"/>
-      <c r="F16" s="192" t="s">
+      <c r="D16" s="189" t="s">
+        <v>201</v>
+      </c>
+      <c r="E16" s="50"/>
+      <c r="F16" s="176" t="s">
         <v>463</v>
       </c>
-      <c r="G16" s="193" t="s">
+      <c r="G16" s="45" t="s">
         <v>463</v>
       </c>
-      <c r="H16" s="193" t="s">
+      <c r="H16" s="45" t="s">
         <v>432</v>
       </c>
-      <c r="I16" s="193" t="s">
+      <c r="I16" s="45" t="s">
         <v>200</v>
       </c>
-      <c r="J16" s="193" t="s">
+      <c r="J16" s="45" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="16">
-      <c r="A17" s="204" t="s">
+      <c r="A17" s="187" t="s">
         <v>197</v>
       </c>
-      <c r="B17" s="205" t="s">
+      <c r="B17" s="188" t="s">
         <v>188</v>
       </c>
-      <c r="C17" s="205" t="s">
+      <c r="C17" s="188" t="s">
         <v>204</v>
       </c>
-      <c r="D17" s="206" t="s">
-        <v>201</v>
-      </c>
-      <c r="E17" s="170"/>
-      <c r="F17" s="182" t="s">
+      <c r="D17" s="189" t="s">
+        <v>201</v>
+      </c>
+      <c r="E17" s="50"/>
+      <c r="F17" s="171" t="s">
         <v>398</v>
       </c>
-      <c r="G17" s="183" t="s">
+      <c r="G17" s="172" t="s">
         <v>398</v>
       </c>
-      <c r="H17" s="183" t="s">
+      <c r="H17" s="172" t="s">
         <v>424</v>
       </c>
-      <c r="I17" s="183" t="s">
+      <c r="I17" s="172" t="s">
         <v>200</v>
       </c>
-      <c r="J17" s="183" t="s">
+      <c r="J17" s="172" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="16">
-      <c r="A18" s="204" t="s">
+      <c r="A18" s="187" t="s">
         <v>198</v>
       </c>
-      <c r="B18" s="205" t="s">
+      <c r="B18" s="188" t="s">
         <v>188</v>
       </c>
-      <c r="C18" s="205" t="s">
+      <c r="C18" s="188" t="s">
         <v>204</v>
       </c>
-      <c r="D18" s="212" t="s">
+      <c r="D18" s="195" t="s">
         <v>200</v>
       </c>
-      <c r="E18" s="170"/>
-      <c r="F18" s="182" t="s">
+      <c r="E18" s="50"/>
+      <c r="F18" s="171" t="s">
         <v>398</v>
       </c>
-      <c r="G18" s="183" t="s">
+      <c r="G18" s="172" t="s">
         <v>398</v>
       </c>
-      <c r="H18" s="183" t="s">
+      <c r="H18" s="172" t="s">
         <v>424</v>
       </c>
-      <c r="I18" s="183" t="s">
+      <c r="I18" s="172" t="s">
         <v>200</v>
       </c>
-      <c r="J18" s="183" t="s">
+      <c r="J18" s="172" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="16">
-      <c r="A19" s="204" t="s">
+      <c r="A19" s="187" t="s">
         <v>184</v>
       </c>
-      <c r="B19" s="205" t="s">
+      <c r="B19" s="188" t="s">
         <v>184</v>
       </c>
-      <c r="C19" s="205" t="s">
+      <c r="C19" s="188" t="s">
         <v>212</v>
       </c>
-      <c r="D19" s="212" t="s">
+      <c r="D19" s="195" t="s">
         <v>200</v>
       </c>
-      <c r="E19" s="170"/>
-      <c r="F19" s="181" t="s">
+      <c r="E19" s="50"/>
+      <c r="F19" s="74" t="s">
         <v>394</v>
       </c>
-      <c r="G19" s="178" t="s">
+      <c r="G19" s="75" t="s">
         <v>394</v>
       </c>
-      <c r="H19" s="178" t="s">
+      <c r="H19" s="75" t="s">
         <v>420</v>
       </c>
-      <c r="I19" s="178" t="s">
+      <c r="I19" s="75" t="s">
         <v>200</v>
       </c>
-      <c r="J19" s="178" t="s">
+      <c r="J19" s="75" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="16">
-      <c r="A20" s="207" t="s">
+      <c r="A20" s="190" t="s">
         <v>193</v>
       </c>
-      <c r="B20" s="208" t="s">
+      <c r="B20" s="191" t="s">
         <v>193</v>
       </c>
-      <c r="C20" s="208" t="s">
+      <c r="C20" s="191" t="s">
         <v>248</v>
       </c>
-      <c r="D20" s="209" t="s">
+      <c r="D20" s="192" t="s">
         <v>200</v>
       </c>
-      <c r="E20" s="170"/>
-      <c r="F20" s="184" t="s">
+      <c r="E20" s="50"/>
+      <c r="F20" s="51" t="s">
         <v>401</v>
       </c>
-      <c r="G20" s="185" t="s">
+      <c r="G20" s="60" t="s">
         <v>401</v>
       </c>
-      <c r="H20" s="185" t="s">
+      <c r="H20" s="60" t="s">
         <v>428</v>
       </c>
-      <c r="I20" s="185" t="s">
+      <c r="I20" s="60" t="s">
         <v>200</v>
       </c>
-      <c r="J20" s="185" t="s">
+      <c r="J20" s="60" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="16">
-      <c r="A21" s="201" t="s">
+      <c r="A21" s="184" t="s">
         <v>182</v>
       </c>
-      <c r="B21" s="202" t="s">
+      <c r="B21" s="185" t="s">
         <v>182</v>
       </c>
-      <c r="C21" s="202" t="s">
+      <c r="C21" s="185" t="s">
         <v>232</v>
       </c>
-      <c r="D21" s="203" t="s">
+      <c r="D21" s="186" t="s">
         <v>200</v>
       </c>
-      <c r="E21" s="172"/>
-      <c r="F21" s="179" t="s">
+      <c r="F21" s="11" t="s">
         <v>395</v>
       </c>
-      <c r="G21" s="180" t="s">
+      <c r="G21" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="H21" s="180" t="s">
+      <c r="H21" s="15" t="s">
         <v>425</v>
       </c>
-      <c r="I21" s="180" t="s">
+      <c r="I21" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="J21" s="180" t="s">
+      <c r="J21" s="15" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="16">
-      <c r="A22" s="201"/>
-      <c r="B22" s="202"/>
-      <c r="C22" s="202"/>
-      <c r="D22" s="203"/>
-      <c r="E22" s="170"/>
+      <c r="A22" s="184"/>
+      <c r="B22" s="185"/>
+      <c r="C22" s="185"/>
+      <c r="D22" s="186"/>
+      <c r="E22" s="50"/>
       <c r="F22" s="7"/>
-      <c r="G22" s="173"/>
-      <c r="H22" s="173"/>
-      <c r="I22" s="173"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="47"/>
       <c r="J22" s="16"/>
     </row>
     <row r="23" spans="1:10" ht="16">
-      <c r="A23" s="201"/>
-      <c r="B23" s="202"/>
-      <c r="C23" s="202"/>
-      <c r="D23" s="203"/>
-      <c r="E23" s="170"/>
+      <c r="A23" s="184"/>
+      <c r="B23" s="185"/>
+      <c r="C23" s="185"/>
+      <c r="D23" s="186"/>
+      <c r="E23" s="50"/>
       <c r="F23" s="7"/>
-      <c r="G23" s="173"/>
-      <c r="H23" s="173"/>
-      <c r="I23" s="173"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="47"/>
+      <c r="I23" s="47"/>
       <c r="J23" s="16"/>
     </row>
     <row r="24" spans="1:10" ht="16">
-      <c r="A24" s="201"/>
-      <c r="B24" s="202"/>
-      <c r="C24" s="202"/>
-      <c r="D24" s="203"/>
-      <c r="E24" s="172"/>
+      <c r="A24" s="184"/>
+      <c r="B24" s="185"/>
+      <c r="C24" s="185"/>
+      <c r="D24" s="186"/>
       <c r="F24" s="7"/>
-      <c r="G24" s="174"/>
-      <c r="H24" s="174"/>
-      <c r="I24" s="174"/>
-      <c r="J24" s="175"/>
+      <c r="G24" s="168"/>
+      <c r="H24" s="168"/>
+      <c r="I24" s="168"/>
+      <c r="J24" s="169"/>
     </row>
     <row r="25" spans="1:10" ht="16">
-      <c r="A25" s="201"/>
-      <c r="B25" s="202"/>
-      <c r="C25" s="202"/>
-      <c r="D25" s="203"/>
-      <c r="E25" s="172"/>
+      <c r="A25" s="184"/>
+      <c r="B25" s="185"/>
+      <c r="C25" s="185"/>
+      <c r="D25" s="186"/>
       <c r="F25" s="7"/>
-      <c r="G25" s="172"/>
-      <c r="H25" s="172"/>
-      <c r="I25" s="172"/>
       <c r="J25" s="16"/>
     </row>
     <row r="26" spans="1:10" ht="16">
-      <c r="A26" s="201"/>
-      <c r="B26" s="202"/>
-      <c r="C26" s="202"/>
-      <c r="D26" s="203"/>
-      <c r="E26" s="172"/>
+      <c r="A26" s="184"/>
+      <c r="B26" s="185"/>
+      <c r="C26" s="185"/>
+      <c r="D26" s="186"/>
       <c r="F26" s="7"/>
-      <c r="G26" s="172"/>
-      <c r="H26" s="172"/>
-      <c r="I26" s="172"/>
       <c r="J26" s="16"/>
     </row>
     <row r="27" spans="1:10" ht="16">
-      <c r="A27" s="201"/>
-      <c r="B27" s="202"/>
-      <c r="C27" s="202"/>
-      <c r="D27" s="203"/>
-      <c r="E27" s="172"/>
+      <c r="A27" s="184"/>
+      <c r="B27" s="185"/>
+      <c r="C27" s="185"/>
+      <c r="D27" s="186"/>
       <c r="F27" s="7"/>
-      <c r="G27" s="172"/>
-      <c r="H27" s="172"/>
-      <c r="I27" s="172"/>
       <c r="J27" s="16"/>
     </row>
     <row r="28" spans="1:10" ht="16">
-      <c r="A28" s="201"/>
-      <c r="B28" s="202"/>
-      <c r="C28" s="202"/>
-      <c r="D28" s="203"/>
-      <c r="E28" s="172"/>
+      <c r="A28" s="184"/>
+      <c r="B28" s="185"/>
+      <c r="C28" s="185"/>
+      <c r="D28" s="186"/>
       <c r="F28" s="7"/>
-      <c r="G28" s="172"/>
-      <c r="H28" s="172"/>
-      <c r="I28" s="172"/>
       <c r="J28" s="16"/>
     </row>
     <row r="29" spans="1:10" ht="16">
-      <c r="A29" s="201"/>
-      <c r="B29" s="202"/>
-      <c r="C29" s="202"/>
-      <c r="D29" s="203"/>
-      <c r="E29" s="172"/>
+      <c r="A29" s="184"/>
+      <c r="B29" s="185"/>
+      <c r="C29" s="185"/>
+      <c r="D29" s="186"/>
       <c r="F29" s="7"/>
-      <c r="G29" s="172"/>
-      <c r="H29" s="172"/>
-      <c r="I29" s="172"/>
       <c r="J29" s="16"/>
     </row>
     <row r="30" spans="1:10" ht="16">
-      <c r="A30" s="201"/>
-      <c r="B30" s="202"/>
-      <c r="C30" s="202"/>
-      <c r="D30" s="203"/>
-      <c r="E30" s="172"/>
+      <c r="A30" s="184"/>
+      <c r="B30" s="185"/>
+      <c r="C30" s="185"/>
+      <c r="D30" s="186"/>
       <c r="F30" s="7"/>
-      <c r="G30" s="172"/>
-      <c r="H30" s="172"/>
-      <c r="I30" s="172"/>
       <c r="J30" s="16"/>
     </row>
     <row r="31" spans="1:10" ht="16">
-      <c r="A31" s="201"/>
-      <c r="B31" s="202"/>
-      <c r="C31" s="202"/>
-      <c r="D31" s="203"/>
-      <c r="E31" s="172"/>
+      <c r="A31" s="184"/>
+      <c r="B31" s="185"/>
+      <c r="C31" s="185"/>
+      <c r="D31" s="186"/>
       <c r="F31" s="7"/>
-      <c r="G31" s="172"/>
-      <c r="H31" s="172"/>
-      <c r="I31" s="172"/>
       <c r="J31" s="16"/>
     </row>
     <row r="32" spans="1:10" ht="16">
-      <c r="A32" s="201"/>
-      <c r="B32" s="202"/>
-      <c r="C32" s="202"/>
-      <c r="D32" s="203"/>
-      <c r="E32" s="172"/>
+      <c r="A32" s="184"/>
+      <c r="B32" s="185"/>
+      <c r="C32" s="185"/>
+      <c r="D32" s="186"/>
       <c r="F32" s="7"/>
-      <c r="G32" s="172"/>
-      <c r="H32" s="172"/>
-      <c r="I32" s="172"/>
       <c r="J32" s="16"/>
     </row>
     <row r="33" spans="1:10" ht="16">
-      <c r="A33" s="201"/>
-      <c r="B33" s="202"/>
-      <c r="C33" s="202"/>
-      <c r="D33" s="203"/>
-      <c r="E33" s="172"/>
+      <c r="A33" s="184"/>
+      <c r="B33" s="185"/>
+      <c r="C33" s="185"/>
+      <c r="D33" s="186"/>
       <c r="F33" s="7"/>
-      <c r="G33" s="172"/>
-      <c r="H33" s="172"/>
-      <c r="I33" s="172"/>
       <c r="J33" s="16"/>
     </row>
     <row r="34" spans="1:10" ht="16">
-      <c r="A34" s="201"/>
-      <c r="B34" s="202"/>
-      <c r="C34" s="202"/>
-      <c r="D34" s="203"/>
-      <c r="E34" s="172"/>
+      <c r="A34" s="184"/>
+      <c r="B34" s="185"/>
+      <c r="C34" s="185"/>
+      <c r="D34" s="186"/>
       <c r="F34" s="7"/>
-      <c r="G34" s="172"/>
-      <c r="H34" s="172"/>
-      <c r="I34" s="172"/>
       <c r="J34" s="16"/>
     </row>
     <row r="35" spans="1:10" ht="16">
-      <c r="A35" s="201"/>
-      <c r="B35" s="202"/>
-      <c r="C35" s="202"/>
-      <c r="D35" s="203"/>
-      <c r="E35" s="172"/>
+      <c r="A35" s="184"/>
+      <c r="B35" s="185"/>
+      <c r="C35" s="185"/>
+      <c r="D35" s="186"/>
       <c r="F35" s="7"/>
-      <c r="G35" s="172"/>
-      <c r="H35" s="172"/>
-      <c r="I35" s="172"/>
       <c r="J35" s="16"/>
     </row>
     <row r="36" spans="1:10" ht="16">
-      <c r="A36" s="201"/>
-      <c r="B36" s="202"/>
-      <c r="C36" s="202"/>
-      <c r="D36" s="203"/>
-      <c r="E36" s="172"/>
+      <c r="A36" s="184"/>
+      <c r="B36" s="185"/>
+      <c r="C36" s="185"/>
+      <c r="D36" s="186"/>
       <c r="F36" s="7"/>
-      <c r="G36" s="172"/>
-      <c r="H36" s="172"/>
-      <c r="I36" s="172"/>
       <c r="J36" s="16"/>
     </row>
     <row r="37" spans="1:10" ht="16">
-      <c r="A37" s="201"/>
-      <c r="B37" s="202"/>
-      <c r="C37" s="202"/>
-      <c r="D37" s="203"/>
-      <c r="E37" s="172"/>
+      <c r="A37" s="184"/>
+      <c r="B37" s="185"/>
+      <c r="C37" s="185"/>
+      <c r="D37" s="186"/>
       <c r="F37" s="7"/>
-      <c r="G37" s="172"/>
-      <c r="H37" s="172"/>
-      <c r="I37" s="172"/>
       <c r="J37" s="16"/>
     </row>
     <row r="38" spans="1:10" ht="16">
-      <c r="A38" s="201"/>
-      <c r="B38" s="202"/>
-      <c r="C38" s="202"/>
-      <c r="D38" s="203"/>
-      <c r="E38" s="172"/>
+      <c r="A38" s="184"/>
+      <c r="B38" s="185"/>
+      <c r="C38" s="185"/>
+      <c r="D38" s="186"/>
       <c r="F38" s="7"/>
-      <c r="G38" s="172"/>
-      <c r="H38" s="172"/>
-      <c r="I38" s="172"/>
       <c r="J38" s="16"/>
     </row>
     <row r="39" spans="1:10" ht="16">
-      <c r="A39" s="201"/>
-      <c r="B39" s="202"/>
-      <c r="C39" s="202"/>
-      <c r="D39" s="203"/>
-      <c r="E39" s="172"/>
+      <c r="A39" s="184"/>
+      <c r="B39" s="185"/>
+      <c r="C39" s="185"/>
+      <c r="D39" s="186"/>
       <c r="F39" s="7"/>
-      <c r="G39" s="172"/>
-      <c r="H39" s="172"/>
-      <c r="I39" s="172"/>
       <c r="J39" s="16"/>
     </row>
     <row r="40" spans="1:10" ht="17" thickBot="1">
-      <c r="A40" s="213"/>
-      <c r="B40" s="214"/>
-      <c r="C40" s="214"/>
-      <c r="D40" s="215"/>
-      <c r="E40" s="172"/>
+      <c r="A40" s="196"/>
+      <c r="B40" s="197"/>
+      <c r="C40" s="197"/>
+      <c r="D40" s="198"/>
       <c r="F40" s="21"/>
       <c r="G40" s="22"/>
       <c r="H40" s="22"/>
@@ -5906,40 +5825,10 @@
       <c r="J40" s="23"/>
     </row>
     <row r="41" spans="1:10" ht="16">
-      <c r="A41" s="171"/>
-      <c r="B41" s="171"/>
-      <c r="C41" s="171"/>
-      <c r="D41" s="171"/>
-      <c r="E41" s="172"/>
-      <c r="F41" s="172"/>
-      <c r="G41" s="172"/>
-      <c r="H41" s="172"/>
-      <c r="I41" s="172"/>
-      <c r="J41" s="172"/>
-    </row>
-    <row r="42" spans="1:10">
-      <c r="A42" s="172"/>
-      <c r="B42" s="172"/>
-      <c r="C42" s="172"/>
-      <c r="D42" s="172"/>
-      <c r="E42" s="172"/>
-      <c r="F42" s="172"/>
-      <c r="G42" s="172"/>
-      <c r="H42" s="172"/>
-      <c r="I42" s="172"/>
-      <c r="J42" s="172"/>
-    </row>
-    <row r="43" spans="1:10">
-      <c r="A43" s="172"/>
-      <c r="B43" s="172"/>
-      <c r="C43" s="172"/>
-      <c r="D43" s="172"/>
-      <c r="E43" s="172"/>
-      <c r="F43" s="172"/>
-      <c r="G43" s="172"/>
-      <c r="H43" s="172"/>
-      <c r="I43" s="172"/>
-      <c r="J43" s="172"/>
+      <c r="A41" s="4"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="7"/>
@@ -5955,7 +5844,7 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:J83"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="38.83203125" style="92" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="39" style="92" bestFit="1" customWidth="1"/>
@@ -7170,7 +7059,7 @@
       <c r="G50" s="93"/>
       <c r="J50" s="88"/>
     </row>
-    <row r="51" spans="1:10" ht="16" thickBot="1">
+    <row r="51" spans="1:10" ht="15" thickBot="1">
       <c r="A51" s="94"/>
       <c r="B51" s="95"/>
       <c r="C51" s="95"/>
@@ -7354,7 +7243,7 @@
     <tabColor theme="1" tint="0.34998626667073579"/>
   </sheetPr>
   <dimension ref="A1:K10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="20" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="20" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="36.6640625" customWidth="1"/>
     <col min="2" max="2" width="31.5" customWidth="1"/>
@@ -7669,7 +7558,7 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:L45"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="37.33203125" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
@@ -8631,7 +8520,7 @@
       <c r="F43" s="7"/>
       <c r="J43" s="16"/>
     </row>
-    <row r="44" spans="1:10" ht="16" thickBot="1">
+    <row r="44" spans="1:10" ht="15" thickBot="1">
       <c r="A44" s="21"/>
       <c r="B44" s="22"/>
       <c r="C44" s="22"/>
@@ -8657,7 +8546,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:L35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="20" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="20" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="36.6640625" customWidth="1"/>
     <col min="3" max="3" width="31.5" customWidth="1"/>
@@ -8714,14 +8603,14 @@
       </c>
       <c r="E2" s="164"/>
       <c r="F2" s="164"/>
-      <c r="H2" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="I2" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="J2" s="24" t="s">
-        <v>238</v>
+      <c r="H2" s="165" t="s">
+        <v>187</v>
+      </c>
+      <c r="I2" s="165" t="s">
+        <v>187</v>
+      </c>
+      <c r="J2" s="165" t="s">
+        <v>204</v>
       </c>
       <c r="K2" s="166"/>
     </row>
@@ -8786,14 +8675,14 @@
       </c>
       <c r="E5" s="164"/>
       <c r="F5" s="164"/>
-      <c r="H5" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="I5" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="J5" s="24" t="s">
-        <v>238</v>
+      <c r="H5" s="165" t="s">
+        <v>187</v>
+      </c>
+      <c r="I5" s="165" t="s">
+        <v>187</v>
+      </c>
+      <c r="J5" s="165" t="s">
+        <v>204</v>
       </c>
       <c r="K5" s="166"/>
     </row>
@@ -8834,14 +8723,14 @@
       </c>
       <c r="E7" s="164"/>
       <c r="F7" s="164"/>
-      <c r="H7" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="I7" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="J7" s="24" t="s">
-        <v>238</v>
+      <c r="H7" s="165" t="s">
+        <v>187</v>
+      </c>
+      <c r="I7" s="165" t="s">
+        <v>187</v>
+      </c>
+      <c r="J7" s="165" t="s">
+        <v>204</v>
       </c>
       <c r="K7" s="166"/>
     </row>
@@ -8931,14 +8820,14 @@
       </c>
       <c r="E11" s="92"/>
       <c r="F11" s="92"/>
-      <c r="H11" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="I11" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="J11" s="24" t="s">
-        <v>238</v>
+      <c r="H11" s="165" t="s">
+        <v>187</v>
+      </c>
+      <c r="I11" s="165" t="s">
+        <v>187</v>
+      </c>
+      <c r="J11" s="165" t="s">
+        <v>204</v>
       </c>
       <c r="K11" s="166"/>
     </row>
@@ -9003,14 +8892,14 @@
       </c>
       <c r="E14" s="92"/>
       <c r="F14" s="92"/>
-      <c r="H14" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="I14" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="J14" s="24" t="s">
-        <v>238</v>
+      <c r="H14" s="165" t="s">
+        <v>187</v>
+      </c>
+      <c r="I14" s="165" t="s">
+        <v>187</v>
+      </c>
+      <c r="J14" s="165" t="s">
+        <v>204</v>
       </c>
       <c r="K14" s="166"/>
     </row>
@@ -9150,7 +9039,7 @@
       <c r="E22" s="92"/>
       <c r="F22" s="92"/>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" ht="16">
       <c r="A23" s="92" t="s">
         <v>377</v>
       </c>
@@ -9159,6 +9048,9 @@
       <c r="D23" s="92"/>
       <c r="E23" s="92"/>
       <c r="F23" s="92"/>
+      <c r="H23" s="201"/>
+      <c r="I23" s="201"/>
+      <c r="J23" s="201"/>
     </row>
     <row r="24" spans="1:11" ht="16">
       <c r="A24" s="92" t="s">
@@ -9322,7 +9214,7 @@
     <tabColor theme="8" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:B69"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="36" customWidth="1"/>
   </cols>
@@ -9892,7 +9784,7 @@
     <tabColor theme="8" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:C46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="39.5" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="39.5" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:3" ht="45.5" customHeight="1" thickBot="1">
       <c r="A1" s="3" t="s">
@@ -10413,7 +10305,7 @@
     <tabColor theme="8" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:C21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="33.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.6640625" bestFit="1" customWidth="1"/>
@@ -10576,7 +10468,7 @@
       </c>
       <c r="C20" s="16"/>
     </row>
-    <row r="21" spans="1:3" ht="16" thickBot="1">
+    <row r="21" spans="1:3" ht="15" thickBot="1">
       <c r="A21" s="21" t="s">
         <v>252</v>
       </c>

--- a/atlas_max_plus_to_poly_mapping_template.xlsx
+++ b/atlas_max_plus_to_poly_mapping_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raeltonhonorio/Documents/KDAM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A6DA5E-71DB-8C44-94C3-AE6B897FB53E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{703945EE-EE2F-8E45-8AC6-7E631739921C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" firstSheet="13" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
     <sheet name="AV100 SETUPS" sheetId="17" r:id="rId16"/>
     <sheet name="AV1000 MEDIA" sheetId="18" r:id="rId17"/>
     <sheet name="AV100_OUTPUT_ICC" sheetId="19" r:id="rId18"/>
-    <sheet name="MATRIX SETUPS" sheetId="21" r:id="rId19"/>
+    <sheet name="MATRIX SETUPS KST" sheetId="21" r:id="rId19"/>
     <sheet name="MATRIX MEDIA" sheetId="22" r:id="rId20"/>
     <sheet name="MATRIX ICC" sheetId="23" r:id="rId21"/>
     <sheet name="PLUS TO MATRIX" sheetId="24" r:id="rId22"/>
@@ -41,7 +41,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'AVHD6 SETUPS'!$A$1:$A$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">AVHD6_OUTPUT_ICC!$A$1:$B$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">AVHD6_TO_PLUS!$A$1:$J$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'MATRIX SETUPS'!$A$1:$A$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'MATRIX ICC'!$A$1:$A$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'MATRIX MEDIA'!$A$1:$A$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'MATRIX SETUPS KST'!$A$1:$A$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">MAX_TO_POLY!$A$1:$J$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Plus Media'!$A$1:$A$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">Plus_Output_ICCs!$A$1:$A$44</definedName>
@@ -70,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1826" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1967" uniqueCount="471">
   <si>
     <t>Atlas Max Plus → Atlas Max Poly Mapping Workbook</t>
   </si>
@@ -1320,18 +1322,6 @@
     <t>Blended Ts STD</t>
   </si>
   <si>
-    <t>MATRIX_BASE_SETUP</t>
-  </si>
-  <si>
-    <t>MATRIX_MEDIA</t>
-  </si>
-  <si>
-    <t>MATRIX_OUTPUT_ICC</t>
-  </si>
-  <si>
-    <t>MATRIX_INPUT_RGB</t>
-  </si>
-  <si>
     <t>Atlas Matrix Cotton Black STD.icm</t>
   </si>
   <si>
@@ -1465,13 +1455,43 @@
   </si>
   <si>
     <t>Super grand pallet</t>
+  </si>
+  <si>
+    <t>TableName</t>
+  </si>
+  <si>
+    <t>MediaName</t>
+  </si>
+  <si>
+    <t>IccInRGBFileName</t>
+  </si>
+  <si>
+    <t>IccInCMYKFileName</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>IccOutFileName</t>
+  </si>
+  <si>
+    <t>RGB Color Space Profile.icm</t>
+  </si>
+  <si>
+    <t>Atlas MATRIX - Standard</t>
+  </si>
+  <si>
+    <t>MATRIX Poly XDi</t>
+  </si>
+  <si>
+    <t>Children pallet small</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1606,8 +1626,19 @@
       <color rgb="FFFFFF00"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="31">
+  <fills count="32">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1775,18 +1806,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1874,11 +1911,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="202">
+  <cellXfs count="221">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2143,20 +2240,7 @@
     <xf numFmtId="0" fontId="4" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="27" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="29" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2170,41 +2254,69 @@
     <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2379,10 +2491,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="68.25" customHeight="1">
-      <c r="A1" s="199" t="s">
+      <c r="A1" s="184" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="200"/>
+      <c r="B1" s="185"/>
     </row>
     <row r="2" spans="1:2" ht="45.5" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -3534,130 +3646,495 @@
   <sheetPr>
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="39.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="42.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="18">
+    <row r="1" spans="1:6" ht="18">
       <c r="A1" s="5" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
+      <c r="B1" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="3" spans="1:1">
+      <c r="B2" t="s">
+        <v>405</v>
+      </c>
+      <c r="C2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D2" t="s">
+        <v>465</v>
+      </c>
+      <c r="E2" t="s">
+        <v>428</v>
+      </c>
+      <c r="F2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="4" spans="1:1">
+      <c r="B3" t="s">
+        <v>394</v>
+      </c>
+      <c r="C3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D3" t="s">
+        <v>265</v>
+      </c>
+      <c r="E3" t="s">
+        <v>416</v>
+      </c>
+      <c r="F3" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="5" spans="1:1">
+      <c r="B4" t="s">
+        <v>395</v>
+      </c>
+      <c r="C4" t="s">
+        <v>200</v>
+      </c>
+      <c r="D4" t="s">
+        <v>265</v>
+      </c>
+      <c r="E4" t="s">
+        <v>421</v>
+      </c>
+      <c r="F4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="6" spans="1:1">
+      <c r="B5" t="s">
+        <v>396</v>
+      </c>
+      <c r="C5" t="s">
+        <v>201</v>
+      </c>
+      <c r="D5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E5" t="s">
+        <v>419</v>
+      </c>
+      <c r="F5" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="7" spans="1:1">
+      <c r="B6" t="s">
+        <v>397</v>
+      </c>
+      <c r="C6" t="s">
+        <v>200</v>
+      </c>
+      <c r="D6" t="s">
+        <v>265</v>
+      </c>
+      <c r="E6" t="s">
+        <v>421</v>
+      </c>
+      <c r="F6" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="8" spans="1:1">
+      <c r="B7" t="s">
+        <v>398</v>
+      </c>
+      <c r="C7" t="s">
+        <v>200</v>
+      </c>
+      <c r="D7" t="s">
+        <v>265</v>
+      </c>
+      <c r="E7" t="s">
+        <v>420</v>
+      </c>
+      <c r="F7" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="9" spans="1:1">
+      <c r="B8" t="s">
+        <v>399</v>
+      </c>
+      <c r="C8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D8" t="s">
+        <v>265</v>
+      </c>
+      <c r="E8" t="s">
+        <v>422</v>
+      </c>
+      <c r="F8" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="10" spans="1:1">
+      <c r="B9" t="s">
+        <v>400</v>
+      </c>
+      <c r="C9" t="s">
+        <v>201</v>
+      </c>
+      <c r="D9" t="s">
+        <v>265</v>
+      </c>
+      <c r="E9" t="s">
+        <v>423</v>
+      </c>
+      <c r="F9" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="11" spans="1:1">
+      <c r="B10" t="s">
+        <v>401</v>
+      </c>
+      <c r="C10" t="s">
+        <v>200</v>
+      </c>
+      <c r="D10" t="s">
+        <v>265</v>
+      </c>
+      <c r="E10" t="s">
+        <v>424</v>
+      </c>
+      <c r="F10" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="12" spans="1:1">
+      <c r="B11" t="s">
+        <v>402</v>
+      </c>
+      <c r="C11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D11" t="s">
+        <v>265</v>
+      </c>
+      <c r="E11" t="s">
+        <v>428</v>
+      </c>
+      <c r="F11" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="13" spans="1:1">
+      <c r="B12" t="s">
+        <v>459</v>
+      </c>
+      <c r="C12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D12" t="s">
+        <v>265</v>
+      </c>
+      <c r="E12" t="s">
+        <v>428</v>
+      </c>
+      <c r="F12" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="14" spans="1:1">
+      <c r="B13" t="s">
+        <v>404</v>
+      </c>
+      <c r="C13" t="s">
+        <v>200</v>
+      </c>
+      <c r="D13" t="s">
+        <v>265</v>
+      </c>
+      <c r="E13" t="s">
+        <v>425</v>
+      </c>
+      <c r="F13" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="15" spans="1:1">
+      <c r="B14" t="s">
+        <v>405</v>
+      </c>
+      <c r="C14" t="s">
+        <v>200</v>
+      </c>
+      <c r="D14" t="s">
+        <v>265</v>
+      </c>
+      <c r="E14" t="s">
+        <v>428</v>
+      </c>
+      <c r="F14" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="16" spans="1:1">
+      <c r="B15" t="s">
+        <v>406</v>
+      </c>
+      <c r="C15" t="s">
+        <v>200</v>
+      </c>
+      <c r="D15" t="s">
+        <v>265</v>
+      </c>
+      <c r="E15" t="s">
+        <v>429</v>
+      </c>
+      <c r="F15" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="17" spans="1:1">
+      <c r="B16" t="s">
+        <v>407</v>
+      </c>
+      <c r="C16" t="s">
+        <v>200</v>
+      </c>
+      <c r="D16" t="s">
+        <v>265</v>
+      </c>
+      <c r="E16" t="s">
+        <v>428</v>
+      </c>
+      <c r="F16" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="18" spans="1:1">
+      <c r="B17" t="s">
+        <v>408</v>
+      </c>
+      <c r="C17" t="s">
+        <v>200</v>
+      </c>
+      <c r="D17" t="s">
+        <v>265</v>
+      </c>
+      <c r="E17" t="s">
+        <v>426</v>
+      </c>
+      <c r="F17" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="19" spans="1:1">
+      <c r="B18" t="s">
+        <v>409</v>
+      </c>
+      <c r="C18" t="s">
+        <v>200</v>
+      </c>
+      <c r="D18" t="s">
+        <v>265</v>
+      </c>
+      <c r="E18" t="s">
+        <v>427</v>
+      </c>
+      <c r="F18" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="20" spans="1:1">
+      <c r="B19" t="s">
+        <v>410</v>
+      </c>
+      <c r="C19" t="s">
+        <v>200</v>
+      </c>
+      <c r="D19" t="s">
+        <v>265</v>
+      </c>
+      <c r="E19" t="s">
+        <v>428</v>
+      </c>
+      <c r="F19" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="21" spans="1:1">
+      <c r="B20" t="s">
+        <v>411</v>
+      </c>
+      <c r="C20" t="s">
+        <v>200</v>
+      </c>
+      <c r="D20" t="s">
+        <v>265</v>
+      </c>
+      <c r="E20" t="s">
+        <v>428</v>
+      </c>
+      <c r="F20" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="22" spans="1:1">
+      <c r="B21" t="s">
+        <v>469</v>
+      </c>
+      <c r="C21" t="s">
+        <v>200</v>
+      </c>
+      <c r="D21" t="s">
+        <v>265</v>
+      </c>
+      <c r="E21" t="s">
+        <v>428</v>
+      </c>
+      <c r="F21" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="23" spans="1:1">
+      <c r="B22" t="s">
+        <v>407</v>
+      </c>
+      <c r="C22" t="s">
+        <v>200</v>
+      </c>
+      <c r="D22" t="s">
+        <v>465</v>
+      </c>
+      <c r="E22" t="s">
+        <v>428</v>
+      </c>
+      <c r="F22" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="24" spans="1:1">
+      <c r="B23" t="s">
+        <v>408</v>
+      </c>
+      <c r="C23" t="s">
+        <v>200</v>
+      </c>
+      <c r="D23" t="s">
+        <v>465</v>
+      </c>
+      <c r="E23" t="s">
+        <v>426</v>
+      </c>
+      <c r="F23" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
         <v>415</v>
+      </c>
+      <c r="B24" t="s">
+        <v>406</v>
+      </c>
+      <c r="C24" t="s">
+        <v>467</v>
+      </c>
+      <c r="D24" t="s">
+        <v>465</v>
+      </c>
+      <c r="E24" t="s">
+        <v>429</v>
+      </c>
+      <c r="F24" t="s">
+        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -4658,168 +5135,181 @@
   <sheetPr>
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="58.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
+    <row r="1" spans="1:1" ht="15">
+      <c r="A1" s="195" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" t="s">
+      <c r="A2" s="196" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="196" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="196" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="196" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="196" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
+    <row r="7" spans="1:1">
+      <c r="A7" s="196" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
+    <row r="8" spans="1:1">
+      <c r="A8" s="196" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
+    <row r="9" spans="1:1">
+      <c r="A9" s="196" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
+    <row r="10" spans="1:1">
+      <c r="A10" s="196" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
+    <row r="11" spans="1:1">
+      <c r="A11" s="196" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
+    <row r="12" spans="1:1">
+      <c r="A12" s="196" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
+    <row r="13" spans="1:1">
+      <c r="A13" s="196" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
+    <row r="14" spans="1:1">
+      <c r="A14" s="196" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
+    <row r="15" spans="1:1">
+      <c r="A15" s="196" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
+    <row r="16" spans="1:1">
+      <c r="A16" s="196" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
+    <row r="17" spans="1:1">
+      <c r="A17" s="196" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
+    <row r="18" spans="1:1">
+      <c r="A18" s="196" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
+    <row r="19" spans="1:1">
+      <c r="A19" s="196" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
+    <row r="20" spans="1:1">
+      <c r="A20" s="196" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
+    <row r="21" spans="1:1">
+      <c r="A21" s="196" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
+    <row r="22" spans="1:1">
+      <c r="A22" s="196" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
+    <row r="23" spans="1:1">
+      <c r="A23" s="196" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
+    <row r="24" spans="1:1">
+      <c r="A24" s="196" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
+    <row r="25" spans="1:1">
+      <c r="A25" s="196" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="196" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="196" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="196" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="196" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
+    <row r="30" spans="1:1">
+      <c r="A30" s="196" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
+    <row r="31" spans="1:1">
+      <c r="A31" s="196" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>462</v>
-      </c>
+    <row r="32" spans="1:1">
+      <c r="A32" s="196"/>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="196"/>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="196"/>
+    </row>
+    <row r="35" spans="1:1" ht="15" thickBot="1">
+      <c r="A35" s="197"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:A31" xr:uid="{8F8736C3-1C58-1646-B830-FED3997DCE44}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4829,183 +5319,202 @@
   <sheetPr>
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="56" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="18">
-      <c r="A1" s="5" t="s">
-        <v>434</v>
+      <c r="A1" s="193" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" t="s">
+      <c r="A2" s="194" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" t="s">
+      <c r="A3" s="194" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" t="s">
+      <c r="A4" s="194" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" t="s">
+      <c r="A5" s="194" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" t="s">
+      <c r="A6" s="194" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" t="s">
+      <c r="A7" s="194" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" t="s">
+      <c r="A8" s="194" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" t="s">
+      <c r="A9" s="194" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" t="s">
+      <c r="A10" s="194" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" t="s">
+      <c r="A11" s="194" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" t="s">
+      <c r="A12" s="194" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" t="s">
+      <c r="A13" s="194" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" t="s">
+      <c r="A14" s="194" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" t="s">
+      <c r="A15" s="194" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="194" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="194" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="194" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="194" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
+    <row r="20" spans="1:1">
+      <c r="A20" s="194" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
+    <row r="21" spans="1:1">
+      <c r="A21" s="194" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
+    <row r="22" spans="1:1">
+      <c r="A22" s="194" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
+    <row r="23" spans="1:1">
+      <c r="A23" s="194" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
+    <row r="24" spans="1:1">
+      <c r="A24" s="194" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
+    <row r="25" spans="1:1">
+      <c r="A25" s="194" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
+    <row r="26" spans="1:1">
+      <c r="A26" s="194" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
+    <row r="27" spans="1:1">
+      <c r="A27" s="194" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
+    <row r="28" spans="1:1">
+      <c r="A28" s="194" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
+    <row r="29" spans="1:1">
+      <c r="A29" s="194" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="194" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="194" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="194" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="194" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
+    <row r="34" spans="1:1">
+      <c r="A34" s="194" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>436</v>
-      </c>
+    <row r="35" spans="1:1">
+      <c r="A35" s="194"/>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="194"/>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="194"/>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="194"/>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="194"/>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="194"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:A34" xr:uid="{4A1D7428-6F4D-D94B-B882-39478008AFA2}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5015,822 +5524,949 @@
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="18.1640625" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="33.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="28.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="1.1640625" customWidth="1"/>
-    <col min="6" max="6" width="36.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="36" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="34.1640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="28.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="42.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16">
-      <c r="A1" s="177" t="s">
+    <row r="1" spans="1:11" ht="18">
+      <c r="A1" s="170" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="178" t="s">
+      <c r="B1" s="171" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="178" t="s">
+      <c r="C1" s="171" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="179" t="s">
+      <c r="D1" s="172" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="180"/>
-      <c r="F1" s="177" t="s">
+      <c r="E1" s="173"/>
+      <c r="F1" s="210" t="s">
+        <v>390</v>
+      </c>
+      <c r="G1" s="211" t="s">
+        <v>462</v>
+      </c>
+      <c r="H1" s="211" t="s">
+        <v>463</v>
+      </c>
+      <c r="I1" s="211" t="s">
+        <v>464</v>
+      </c>
+      <c r="J1" s="211" t="s">
+        <v>466</v>
+      </c>
+      <c r="K1" s="212" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="16">
+      <c r="A2" s="186" t="s">
+        <v>181</v>
+      </c>
+      <c r="B2" s="187" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2" s="187" t="s">
+        <v>230</v>
+      </c>
+      <c r="D2" s="188" t="s">
+        <v>201</v>
+      </c>
+      <c r="E2" s="50"/>
+      <c r="F2" s="74" t="s">
+        <v>394</v>
+      </c>
+      <c r="G2" s="198" t="s">
+        <v>394</v>
+      </c>
+      <c r="H2" s="198" t="s">
+        <v>200</v>
+      </c>
+      <c r="I2" s="198" t="s">
+        <v>265</v>
+      </c>
+      <c r="J2" s="198" t="s">
         <v>416</v>
       </c>
-      <c r="G1" s="178" t="s">
-        <v>417</v>
-      </c>
-      <c r="H1" s="178" t="s">
-        <v>418</v>
-      </c>
-      <c r="I1" s="178" t="s">
-        <v>419</v>
-      </c>
-      <c r="J1" s="178" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="16">
-      <c r="A2" s="181" t="s">
-        <v>181</v>
-      </c>
-      <c r="B2" s="182" t="s">
-        <v>181</v>
-      </c>
-      <c r="C2" s="182" t="s">
-        <v>230</v>
-      </c>
-      <c r="D2" s="183" t="s">
-        <v>201</v>
-      </c>
-      <c r="E2" s="50"/>
-      <c r="F2" s="170" t="s">
-        <v>394</v>
-      </c>
-      <c r="G2" s="59" t="s">
-        <v>394</v>
-      </c>
-      <c r="H2" s="75" t="s">
-        <v>420</v>
-      </c>
-      <c r="I2" s="59" t="s">
-        <v>200</v>
-      </c>
-      <c r="J2" s="59" t="s">
+      <c r="K2" s="77" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="16">
-      <c r="A3" s="184" t="s">
+    <row r="3" spans="1:11" ht="16">
+      <c r="A3" s="177" t="s">
         <v>182</v>
       </c>
-      <c r="B3" s="185" t="s">
+      <c r="B3" s="178" t="s">
         <v>182</v>
       </c>
-      <c r="C3" s="185" t="s">
+      <c r="C3" s="178" t="s">
         <v>317</v>
       </c>
-      <c r="D3" s="186" t="s">
+      <c r="D3" s="180" t="s">
         <v>201</v>
       </c>
       <c r="E3" s="50"/>
       <c r="F3" s="11" t="s">
         <v>395</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="199" t="s">
         <v>395</v>
       </c>
-      <c r="H3" s="15" t="s">
-        <v>425</v>
-      </c>
-      <c r="I3" s="15" t="s">
+      <c r="H3" s="199" t="s">
         <v>200</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="I3" s="199" t="s">
+        <v>265</v>
+      </c>
+      <c r="J3" s="199" t="s">
+        <v>421</v>
+      </c>
+      <c r="K3" s="12" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="49" customFormat="1" ht="16">
-      <c r="A4" s="187" t="s">
+    <row r="4" spans="1:11" s="49" customFormat="1" ht="16">
+      <c r="A4" s="177" t="s">
         <v>184</v>
       </c>
-      <c r="B4" s="188" t="s">
+      <c r="B4" s="178" t="s">
         <v>184</v>
       </c>
-      <c r="C4" s="188" t="s">
+      <c r="C4" s="178" t="s">
         <v>203</v>
       </c>
-      <c r="D4" s="189" t="s">
+      <c r="D4" s="179" t="s">
         <v>201</v>
       </c>
       <c r="E4" s="50"/>
       <c r="F4" s="74" t="s">
         <v>394</v>
       </c>
-      <c r="G4" s="75" t="s">
+      <c r="G4" s="198" t="s">
         <v>394</v>
       </c>
-      <c r="H4" s="75" t="s">
-        <v>420</v>
-      </c>
-      <c r="I4" s="75" t="s">
+      <c r="H4" s="198" t="s">
         <v>200</v>
       </c>
-      <c r="J4" s="75" t="s">
+      <c r="I4" s="198" t="s">
+        <v>265</v>
+      </c>
+      <c r="J4" s="198" t="s">
+        <v>416</v>
+      </c>
+      <c r="K4" s="77" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="49" customFormat="1" ht="16">
-      <c r="A5" s="187" t="s">
+    <row r="5" spans="1:11" s="49" customFormat="1" ht="16">
+      <c r="A5" s="177" t="s">
         <v>183</v>
       </c>
-      <c r="B5" s="188" t="s">
+      <c r="B5" s="178" t="s">
         <v>183</v>
       </c>
-      <c r="C5" s="188" t="s">
+      <c r="C5" s="178" t="s">
         <v>203</v>
       </c>
-      <c r="D5" s="189" t="s">
+      <c r="D5" s="179" t="s">
         <v>201</v>
       </c>
       <c r="E5" s="50"/>
       <c r="F5" s="74" t="s">
         <v>394</v>
       </c>
-      <c r="G5" s="75" t="s">
+      <c r="G5" s="198" t="s">
         <v>394</v>
       </c>
-      <c r="H5" s="75" t="s">
+      <c r="H5" s="198" t="s">
+        <v>200</v>
+      </c>
+      <c r="I5" s="198" t="s">
+        <v>265</v>
+      </c>
+      <c r="J5" s="198" t="s">
+        <v>416</v>
+      </c>
+      <c r="K5" s="77" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" s="49" customFormat="1" ht="16">
+      <c r="A6" s="177" t="s">
+        <v>185</v>
+      </c>
+      <c r="B6" s="178" t="s">
+        <v>185</v>
+      </c>
+      <c r="C6" s="178" t="s">
+        <v>185</v>
+      </c>
+      <c r="D6" s="179" t="s">
+        <v>201</v>
+      </c>
+      <c r="E6" s="50"/>
+      <c r="F6" s="168" t="s">
+        <v>398</v>
+      </c>
+      <c r="G6" s="200" t="s">
+        <v>398</v>
+      </c>
+      <c r="H6" s="200" t="s">
+        <v>200</v>
+      </c>
+      <c r="I6" s="200" t="s">
+        <v>265</v>
+      </c>
+      <c r="J6" s="200" t="s">
         <v>420</v>
       </c>
-      <c r="I5" s="75" t="s">
-        <v>200</v>
-      </c>
-      <c r="J5" s="75" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" s="49" customFormat="1" ht="16">
-      <c r="A6" s="187" t="s">
-        <v>185</v>
-      </c>
-      <c r="B6" s="188" t="s">
-        <v>185</v>
-      </c>
-      <c r="C6" s="188" t="s">
-        <v>185</v>
-      </c>
-      <c r="D6" s="189" t="s">
-        <v>201</v>
-      </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="171" t="s">
-        <v>398</v>
-      </c>
-      <c r="G6" s="172" t="s">
-        <v>398</v>
-      </c>
-      <c r="H6" s="172" t="s">
-        <v>424</v>
-      </c>
-      <c r="I6" s="172" t="s">
-        <v>200</v>
-      </c>
-      <c r="J6" s="172" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="16">
-      <c r="A7" s="184" t="s">
+      <c r="K6" s="213" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="16">
+      <c r="A7" s="177" t="s">
         <v>186</v>
       </c>
-      <c r="B7" s="185" t="s">
+      <c r="B7" s="178" t="s">
         <v>186</v>
       </c>
-      <c r="C7" s="185" t="s">
+      <c r="C7" s="178" t="s">
         <v>318</v>
       </c>
-      <c r="D7" s="186" t="s">
+      <c r="D7" s="180" t="s">
         <v>201</v>
       </c>
       <c r="E7" s="50"/>
       <c r="F7" s="11" t="s">
         <v>395</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="199" t="s">
         <v>395</v>
       </c>
-      <c r="H7" s="15" t="s">
-        <v>425</v>
-      </c>
-      <c r="I7" s="15" t="s">
+      <c r="H7" s="199" t="s">
         <v>200</v>
       </c>
-      <c r="J7" s="15" t="s">
+      <c r="I7" s="199" t="s">
+        <v>265</v>
+      </c>
+      <c r="J7" s="199" t="s">
+        <v>421</v>
+      </c>
+      <c r="K7" s="12" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="16">
-      <c r="A8" s="187" t="s">
+    <row r="8" spans="1:11" ht="16">
+      <c r="A8" s="177" t="s">
         <v>188</v>
       </c>
-      <c r="B8" s="188" t="s">
+      <c r="B8" s="178" t="s">
         <v>188</v>
       </c>
-      <c r="C8" s="188" t="s">
+      <c r="C8" s="178" t="s">
         <v>204</v>
       </c>
-      <c r="D8" s="189" t="s">
+      <c r="D8" s="179" t="s">
         <v>201</v>
       </c>
       <c r="E8" s="50"/>
-      <c r="F8" s="171" t="s">
+      <c r="F8" s="168" t="s">
         <v>398</v>
       </c>
-      <c r="G8" s="172" t="s">
+      <c r="G8" s="200" t="s">
         <v>398</v>
       </c>
-      <c r="H8" s="172" t="s">
-        <v>424</v>
-      </c>
-      <c r="I8" s="172" t="s">
+      <c r="H8" s="200" t="s">
         <v>200</v>
       </c>
-      <c r="J8" s="172" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="16">
-      <c r="A9" s="187" t="s">
+      <c r="I8" s="200" t="s">
+        <v>265</v>
+      </c>
+      <c r="J8" s="200" t="s">
+        <v>420</v>
+      </c>
+      <c r="K8" s="213" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="16">
+      <c r="A9" s="177" t="s">
         <v>187</v>
       </c>
-      <c r="B9" s="188" t="s">
+      <c r="B9" s="178" t="s">
         <v>187</v>
       </c>
-      <c r="C9" s="188" t="s">
+      <c r="C9" s="178" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="189" t="s">
+      <c r="D9" s="179" t="s">
         <v>201</v>
       </c>
       <c r="E9" s="50"/>
-      <c r="F9" s="171" t="s">
+      <c r="F9" s="168" t="s">
         <v>398</v>
       </c>
-      <c r="G9" s="172" t="s">
+      <c r="G9" s="200" t="s">
         <v>398</v>
       </c>
-      <c r="H9" s="172" t="s">
-        <v>424</v>
-      </c>
-      <c r="I9" s="172" t="s">
+      <c r="H9" s="200" t="s">
         <v>200</v>
       </c>
-      <c r="J9" s="172" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="16">
-      <c r="A10" s="184" t="s">
+      <c r="I9" s="200" t="s">
+        <v>265</v>
+      </c>
+      <c r="J9" s="200" t="s">
+        <v>420</v>
+      </c>
+      <c r="K9" s="213" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="16">
+      <c r="A10" s="177" t="s">
         <v>190</v>
       </c>
-      <c r="B10" s="185" t="s">
+      <c r="B10" s="178" t="s">
         <v>190</v>
       </c>
-      <c r="C10" s="185" t="s">
+      <c r="C10" s="178" t="s">
         <v>213</v>
       </c>
-      <c r="D10" s="186" t="s">
+      <c r="D10" s="180" t="s">
         <v>201</v>
       </c>
       <c r="E10" s="50"/>
       <c r="F10" s="51" t="s">
         <v>401</v>
       </c>
-      <c r="G10" s="60" t="s">
+      <c r="G10" s="201" t="s">
         <v>401</v>
       </c>
-      <c r="H10" s="60" t="s">
-        <v>428</v>
-      </c>
-      <c r="I10" s="60" t="s">
+      <c r="H10" s="201" t="s">
         <v>200</v>
       </c>
-      <c r="J10" s="60" t="s">
+      <c r="I10" s="201" t="s">
+        <v>265</v>
+      </c>
+      <c r="J10" s="201" t="s">
+        <v>424</v>
+      </c>
+      <c r="K10" s="52" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="16">
-      <c r="A11" s="187" t="s">
+    <row r="11" spans="1:11" ht="16">
+      <c r="A11" s="177" t="s">
         <v>191</v>
       </c>
-      <c r="B11" s="188" t="s">
+      <c r="B11" s="178" t="s">
         <v>191</v>
       </c>
-      <c r="C11" s="188" t="s">
+      <c r="C11" s="178" t="s">
         <v>319</v>
       </c>
-      <c r="D11" s="189" t="s">
+      <c r="D11" s="179" t="s">
         <v>201</v>
       </c>
       <c r="E11" s="50"/>
-      <c r="F11" s="85" t="s">
+      <c r="F11" s="214" t="s">
         <v>399</v>
       </c>
-      <c r="G11" s="86" t="s">
+      <c r="G11" s="202" t="s">
         <v>399</v>
       </c>
-      <c r="H11" s="86" t="s">
-        <v>426</v>
-      </c>
-      <c r="I11" s="86" t="s">
+      <c r="H11" s="202" t="s">
         <v>200</v>
       </c>
-      <c r="J11" s="86" t="s">
+      <c r="I11" s="202" t="s">
+        <v>265</v>
+      </c>
+      <c r="J11" s="202" t="s">
+        <v>422</v>
+      </c>
+      <c r="K11" s="215" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="16">
-      <c r="A12" s="184" t="s">
+    <row r="12" spans="1:11" ht="16">
+      <c r="A12" s="177" t="s">
         <v>192</v>
       </c>
-      <c r="B12" s="185" t="s">
+      <c r="B12" s="178" t="s">
         <v>192</v>
       </c>
-      <c r="C12" s="185" t="s">
+      <c r="C12" s="178" t="s">
         <v>207</v>
       </c>
-      <c r="D12" s="186" t="s">
+      <c r="D12" s="180" t="s">
         <v>201</v>
       </c>
       <c r="E12" s="50"/>
-      <c r="F12" s="173" t="s">
+      <c r="F12" s="216" t="s">
         <v>400</v>
       </c>
-      <c r="G12" s="130" t="s">
+      <c r="G12" s="203" t="s">
         <v>400</v>
       </c>
-      <c r="H12" s="130" t="s">
-        <v>427</v>
-      </c>
-      <c r="I12" s="130" t="s">
-        <v>201</v>
-      </c>
-      <c r="J12" s="130" t="s">
+      <c r="H12" s="203" t="s">
+        <v>201</v>
+      </c>
+      <c r="I12" s="203" t="s">
+        <v>265</v>
+      </c>
+      <c r="J12" s="203" t="s">
+        <v>423</v>
+      </c>
+      <c r="K12" s="217" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="16">
-      <c r="A13" s="190" t="s">
+    <row r="13" spans="1:11" ht="16">
+      <c r="A13" s="189" t="s">
         <v>193</v>
       </c>
-      <c r="B13" s="191" t="s">
+      <c r="B13" s="190" t="s">
         <v>193</v>
       </c>
-      <c r="C13" s="191" t="s">
+      <c r="C13" s="190" t="s">
         <v>208</v>
       </c>
-      <c r="D13" s="192" t="s">
+      <c r="D13" s="179" t="s">
         <v>201</v>
       </c>
       <c r="E13" s="50"/>
       <c r="F13" s="51" t="s">
         <v>401</v>
       </c>
-      <c r="G13" s="60" t="s">
+      <c r="G13" s="201" t="s">
         <v>401</v>
       </c>
-      <c r="H13" s="60" t="s">
+      <c r="H13" s="201" t="s">
+        <v>200</v>
+      </c>
+      <c r="I13" s="201" t="s">
+        <v>265</v>
+      </c>
+      <c r="J13" s="201" t="s">
+        <v>424</v>
+      </c>
+      <c r="K13" s="52" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="15">
+      <c r="A14" s="186" t="s">
+        <v>194</v>
+      </c>
+      <c r="B14" s="191" t="s">
+        <v>194</v>
+      </c>
+      <c r="C14" s="191" t="s">
+        <v>209</v>
+      </c>
+      <c r="D14" s="192" t="s">
+        <v>201</v>
+      </c>
+      <c r="E14" s="50"/>
+      <c r="F14" s="218" t="s">
+        <v>396</v>
+      </c>
+      <c r="G14" s="204" t="s">
+        <v>396</v>
+      </c>
+      <c r="H14" s="204" t="s">
+        <v>201</v>
+      </c>
+      <c r="I14" s="204" t="s">
+        <v>265</v>
+      </c>
+      <c r="J14" s="204" t="s">
+        <v>419</v>
+      </c>
+      <c r="K14" s="219" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="16">
+      <c r="A15" s="177" t="s">
+        <v>195</v>
+      </c>
+      <c r="B15" s="178" t="s">
+        <v>195</v>
+      </c>
+      <c r="C15" s="178" t="s">
+        <v>320</v>
+      </c>
+      <c r="D15" s="179" t="s">
+        <v>201</v>
+      </c>
+      <c r="E15" s="50"/>
+      <c r="F15" s="169" t="s">
+        <v>402</v>
+      </c>
+      <c r="G15" s="205" t="s">
+        <v>402</v>
+      </c>
+      <c r="H15" s="205" t="s">
+        <v>200</v>
+      </c>
+      <c r="I15" s="205" t="s">
+        <v>265</v>
+      </c>
+      <c r="J15" s="205" t="s">
         <v>428</v>
       </c>
-      <c r="I13" s="60" t="s">
+      <c r="K15" s="132" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="16">
+      <c r="A16" s="177" t="s">
+        <v>196</v>
+      </c>
+      <c r="B16" s="178" t="s">
+        <v>196</v>
+      </c>
+      <c r="C16" s="178" t="s">
+        <v>210</v>
+      </c>
+      <c r="D16" s="179" t="s">
+        <v>201</v>
+      </c>
+      <c r="E16" s="50"/>
+      <c r="F16" s="220" t="s">
+        <v>403</v>
+      </c>
+      <c r="G16" s="206" t="s">
+        <v>459</v>
+      </c>
+      <c r="H16" s="206" t="s">
         <v>200</v>
       </c>
-      <c r="J13" s="60" t="s">
+      <c r="I16" s="206" t="s">
+        <v>265</v>
+      </c>
+      <c r="J16" s="206" t="s">
+        <v>428</v>
+      </c>
+      <c r="K16" s="142" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="15">
-      <c r="A14" s="181" t="s">
-        <v>194</v>
-      </c>
-      <c r="B14" s="193" t="s">
-        <v>194</v>
-      </c>
-      <c r="C14" s="193" t="s">
-        <v>209</v>
-      </c>
-      <c r="D14" s="194" t="s">
-        <v>201</v>
-      </c>
-      <c r="E14" s="50"/>
-      <c r="F14" s="174" t="s">
-        <v>396</v>
-      </c>
-      <c r="G14" s="175" t="s">
-        <v>396</v>
-      </c>
-      <c r="H14" s="175" t="s">
-        <v>423</v>
-      </c>
-      <c r="I14" s="175" t="s">
-        <v>201</v>
-      </c>
-      <c r="J14" s="175" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="16">
-      <c r="A15" s="187" t="s">
-        <v>195</v>
-      </c>
-      <c r="B15" s="188" t="s">
-        <v>195</v>
-      </c>
-      <c r="C15" s="188" t="s">
-        <v>320</v>
-      </c>
-      <c r="D15" s="189" t="s">
-        <v>201</v>
-      </c>
-      <c r="E15" s="50"/>
-      <c r="F15" s="176" t="s">
-        <v>402</v>
-      </c>
-      <c r="G15" s="45" t="s">
-        <v>402</v>
-      </c>
-      <c r="H15" s="45" t="s">
-        <v>432</v>
-      </c>
-      <c r="I15" s="45" t="s">
+    <row r="17" spans="1:11" ht="16">
+      <c r="A17" s="177" t="s">
+        <v>197</v>
+      </c>
+      <c r="B17" s="178" t="s">
+        <v>188</v>
+      </c>
+      <c r="C17" s="178" t="s">
+        <v>204</v>
+      </c>
+      <c r="D17" s="179" t="s">
+        <v>201</v>
+      </c>
+      <c r="E17" s="50"/>
+      <c r="F17" s="168" t="s">
+        <v>398</v>
+      </c>
+      <c r="G17" s="200" t="s">
+        <v>398</v>
+      </c>
+      <c r="H17" s="200" t="s">
         <v>200</v>
       </c>
-      <c r="J15" s="45" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="16">
-      <c r="A16" s="187" t="s">
-        <v>196</v>
-      </c>
-      <c r="B16" s="188" t="s">
-        <v>196</v>
-      </c>
-      <c r="C16" s="188" t="s">
-        <v>210</v>
-      </c>
-      <c r="D16" s="189" t="s">
-        <v>201</v>
-      </c>
-      <c r="E16" s="50"/>
-      <c r="F16" s="176" t="s">
-        <v>463</v>
-      </c>
-      <c r="G16" s="45" t="s">
-        <v>463</v>
-      </c>
-      <c r="H16" s="45" t="s">
-        <v>432</v>
-      </c>
-      <c r="I16" s="45" t="s">
+      <c r="I17" s="200" t="s">
+        <v>265</v>
+      </c>
+      <c r="J17" s="200" t="s">
+        <v>420</v>
+      </c>
+      <c r="K17" s="213" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="16">
+      <c r="A18" s="177" t="s">
+        <v>198</v>
+      </c>
+      <c r="B18" s="178" t="s">
+        <v>188</v>
+      </c>
+      <c r="C18" s="178" t="s">
+        <v>204</v>
+      </c>
+      <c r="D18" s="180" t="s">
         <v>200</v>
       </c>
-      <c r="J16" s="45" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="16">
-      <c r="A17" s="187" t="s">
-        <v>197</v>
-      </c>
-      <c r="B17" s="188" t="s">
-        <v>188</v>
-      </c>
-      <c r="C17" s="188" t="s">
-        <v>204</v>
-      </c>
-      <c r="D17" s="189" t="s">
-        <v>201</v>
-      </c>
-      <c r="E17" s="50"/>
-      <c r="F17" s="171" t="s">
+      <c r="E18" s="50"/>
+      <c r="F18" s="168" t="s">
         <v>398</v>
       </c>
-      <c r="G17" s="172" t="s">
+      <c r="G18" s="200" t="s">
         <v>398</v>
       </c>
-      <c r="H17" s="172" t="s">
-        <v>424</v>
-      </c>
-      <c r="I17" s="172" t="s">
+      <c r="H18" s="200" t="s">
         <v>200</v>
       </c>
-      <c r="J17" s="172" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="16">
-      <c r="A18" s="187" t="s">
-        <v>198</v>
-      </c>
-      <c r="B18" s="188" t="s">
-        <v>188</v>
-      </c>
-      <c r="C18" s="188" t="s">
-        <v>204</v>
-      </c>
-      <c r="D18" s="195" t="s">
-        <v>200</v>
-      </c>
-      <c r="E18" s="50"/>
-      <c r="F18" s="171" t="s">
-        <v>398</v>
-      </c>
-      <c r="G18" s="172" t="s">
-        <v>398</v>
-      </c>
-      <c r="H18" s="172" t="s">
-        <v>424</v>
-      </c>
-      <c r="I18" s="172" t="s">
-        <v>200</v>
-      </c>
-      <c r="J18" s="172" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="16">
-      <c r="A19" s="187" t="s">
+      <c r="I18" s="200" t="s">
+        <v>265</v>
+      </c>
+      <c r="J18" s="200" t="s">
+        <v>420</v>
+      </c>
+      <c r="K18" s="213" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="16">
+      <c r="A19" s="177" t="s">
         <v>184</v>
       </c>
-      <c r="B19" s="188" t="s">
+      <c r="B19" s="178" t="s">
         <v>184</v>
       </c>
-      <c r="C19" s="188" t="s">
+      <c r="C19" s="178" t="s">
         <v>212</v>
       </c>
-      <c r="D19" s="195" t="s">
+      <c r="D19" s="180" t="s">
         <v>200</v>
       </c>
       <c r="E19" s="50"/>
       <c r="F19" s="74" t="s">
         <v>394</v>
       </c>
-      <c r="G19" s="75" t="s">
+      <c r="G19" s="198" t="s">
         <v>394</v>
       </c>
-      <c r="H19" s="75" t="s">
-        <v>420</v>
-      </c>
-      <c r="I19" s="75" t="s">
+      <c r="H19" s="198" t="s">
         <v>200</v>
       </c>
-      <c r="J19" s="75" t="s">
+      <c r="I19" s="198" t="s">
+        <v>265</v>
+      </c>
+      <c r="J19" s="198" t="s">
+        <v>416</v>
+      </c>
+      <c r="K19" s="77" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="16">
-      <c r="A20" s="190" t="s">
+    <row r="20" spans="1:11" ht="16">
+      <c r="A20" s="189" t="s">
         <v>193</v>
       </c>
-      <c r="B20" s="191" t="s">
+      <c r="B20" s="190" t="s">
         <v>193</v>
       </c>
-      <c r="C20" s="191" t="s">
+      <c r="C20" s="190" t="s">
         <v>248</v>
       </c>
-      <c r="D20" s="192" t="s">
+      <c r="D20" s="179" t="s">
         <v>200</v>
       </c>
       <c r="E20" s="50"/>
       <c r="F20" s="51" t="s">
         <v>401</v>
       </c>
-      <c r="G20" s="60" t="s">
+      <c r="G20" s="201" t="s">
         <v>401</v>
       </c>
-      <c r="H20" s="60" t="s">
-        <v>428</v>
-      </c>
-      <c r="I20" s="60" t="s">
+      <c r="H20" s="201" t="s">
         <v>200</v>
       </c>
-      <c r="J20" s="60" t="s">
+      <c r="I20" s="201" t="s">
+        <v>265</v>
+      </c>
+      <c r="J20" s="201" t="s">
+        <v>424</v>
+      </c>
+      <c r="K20" s="52" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="16">
-      <c r="A21" s="184" t="s">
+    <row r="21" spans="1:11" ht="16">
+      <c r="A21" s="177" t="s">
         <v>182</v>
       </c>
-      <c r="B21" s="185" t="s">
+      <c r="B21" s="178" t="s">
         <v>182</v>
       </c>
-      <c r="C21" s="185" t="s">
+      <c r="C21" s="178" t="s">
         <v>232</v>
       </c>
-      <c r="D21" s="186" t="s">
+      <c r="D21" s="180" t="s">
         <v>200</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>395</v>
       </c>
-      <c r="G21" s="15" t="s">
+      <c r="G21" s="199" t="s">
         <v>395</v>
       </c>
-      <c r="H21" s="15" t="s">
-        <v>425</v>
-      </c>
-      <c r="I21" s="15" t="s">
+      <c r="H21" s="199" t="s">
         <v>200</v>
       </c>
-      <c r="J21" s="15" t="s">
+      <c r="I21" s="199" t="s">
+        <v>265</v>
+      </c>
+      <c r="J21" s="199" t="s">
+        <v>421</v>
+      </c>
+      <c r="K21" s="12" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="16">
-      <c r="A22" s="184"/>
-      <c r="B22" s="185"/>
-      <c r="C22" s="185"/>
-      <c r="D22" s="186"/>
+    <row r="22" spans="1:11" ht="16">
+      <c r="A22" s="174"/>
+      <c r="B22" s="175"/>
+      <c r="C22" s="175"/>
+      <c r="D22" s="176"/>
       <c r="E22" s="50"/>
       <c r="F22" s="7"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="47"/>
-      <c r="I22" s="47"/>
-      <c r="J22" s="16"/>
-    </row>
-    <row r="23" spans="1:10" ht="16">
-      <c r="A23" s="184"/>
-      <c r="B23" s="185"/>
-      <c r="C23" s="185"/>
-      <c r="D23" s="186"/>
+      <c r="G22" s="208"/>
+      <c r="H22" s="208"/>
+      <c r="I22" s="208"/>
+      <c r="J22" s="207"/>
+      <c r="K22" s="16"/>
+    </row>
+    <row r="23" spans="1:11" ht="16">
+      <c r="A23" s="174"/>
+      <c r="B23" s="175"/>
+      <c r="C23" s="175"/>
+      <c r="D23" s="176"/>
       <c r="E23" s="50"/>
       <c r="F23" s="7"/>
-      <c r="G23" s="47"/>
-      <c r="H23" s="47"/>
-      <c r="I23" s="47"/>
-      <c r="J23" s="16"/>
-    </row>
-    <row r="24" spans="1:10" ht="16">
-      <c r="A24" s="184"/>
-      <c r="B24" s="185"/>
-      <c r="C24" s="185"/>
-      <c r="D24" s="186"/>
+      <c r="G23" s="208"/>
+      <c r="H23" s="208"/>
+      <c r="I23" s="208"/>
+      <c r="J23" s="207"/>
+      <c r="K23" s="16"/>
+    </row>
+    <row r="24" spans="1:11" ht="16">
+      <c r="A24" s="174"/>
+      <c r="B24" s="175"/>
+      <c r="C24" s="175"/>
+      <c r="D24" s="176"/>
       <c r="F24" s="7"/>
-      <c r="G24" s="168"/>
-      <c r="H24" s="168"/>
-      <c r="I24" s="168"/>
-      <c r="J24" s="169"/>
-    </row>
-    <row r="25" spans="1:10" ht="16">
-      <c r="A25" s="184"/>
-      <c r="B25" s="185"/>
-      <c r="C25" s="185"/>
-      <c r="D25" s="186"/>
+      <c r="G24" s="209"/>
+      <c r="H24" s="209"/>
+      <c r="I24" s="209"/>
+      <c r="J24" s="209"/>
+      <c r="K24" s="16"/>
+    </row>
+    <row r="25" spans="1:11" ht="16">
+      <c r="A25" s="174"/>
+      <c r="B25" s="175"/>
+      <c r="C25" s="175"/>
+      <c r="D25" s="176"/>
       <c r="F25" s="7"/>
-      <c r="J25" s="16"/>
-    </row>
-    <row r="26" spans="1:10" ht="16">
-      <c r="A26" s="184"/>
-      <c r="B26" s="185"/>
-      <c r="C26" s="185"/>
-      <c r="D26" s="186"/>
+      <c r="G25" s="207"/>
+      <c r="H25" s="207"/>
+      <c r="I25" s="207"/>
+      <c r="J25" s="207"/>
+      <c r="K25" s="16"/>
+    </row>
+    <row r="26" spans="1:11" ht="16">
+      <c r="A26" s="174"/>
+      <c r="B26" s="175"/>
+      <c r="C26" s="175"/>
+      <c r="D26" s="176"/>
       <c r="F26" s="7"/>
-      <c r="J26" s="16"/>
-    </row>
-    <row r="27" spans="1:10" ht="16">
-      <c r="A27" s="184"/>
-      <c r="B27" s="185"/>
-      <c r="C27" s="185"/>
-      <c r="D27" s="186"/>
+      <c r="G26" s="207"/>
+      <c r="H26" s="207"/>
+      <c r="I26" s="207"/>
+      <c r="J26" s="207"/>
+      <c r="K26" s="16"/>
+    </row>
+    <row r="27" spans="1:11" ht="16">
+      <c r="A27" s="174"/>
+      <c r="B27" s="175"/>
+      <c r="C27" s="175"/>
+      <c r="D27" s="176"/>
       <c r="F27" s="7"/>
-      <c r="J27" s="16"/>
-    </row>
-    <row r="28" spans="1:10" ht="16">
-      <c r="A28" s="184"/>
-      <c r="B28" s="185"/>
-      <c r="C28" s="185"/>
-      <c r="D28" s="186"/>
+      <c r="G27" s="207"/>
+      <c r="H27" s="207"/>
+      <c r="I27" s="207"/>
+      <c r="J27" s="207"/>
+      <c r="K27" s="16"/>
+    </row>
+    <row r="28" spans="1:11" ht="16">
+      <c r="A28" s="174"/>
+      <c r="B28" s="175"/>
+      <c r="C28" s="175"/>
+      <c r="D28" s="176"/>
       <c r="F28" s="7"/>
-      <c r="J28" s="16"/>
-    </row>
-    <row r="29" spans="1:10" ht="16">
-      <c r="A29" s="184"/>
-      <c r="B29" s="185"/>
-      <c r="C29" s="185"/>
-      <c r="D29" s="186"/>
+      <c r="G28" s="207"/>
+      <c r="H28" s="207"/>
+      <c r="I28" s="207"/>
+      <c r="J28" s="207"/>
+      <c r="K28" s="16"/>
+    </row>
+    <row r="29" spans="1:11" ht="16">
+      <c r="A29" s="174"/>
+      <c r="B29" s="175"/>
+      <c r="C29" s="175"/>
+      <c r="D29" s="176"/>
       <c r="F29" s="7"/>
-      <c r="J29" s="16"/>
-    </row>
-    <row r="30" spans="1:10" ht="16">
-      <c r="A30" s="184"/>
-      <c r="B30" s="185"/>
-      <c r="C30" s="185"/>
-      <c r="D30" s="186"/>
+      <c r="G29" s="207"/>
+      <c r="H29" s="207"/>
+      <c r="I29" s="207"/>
+      <c r="J29" s="207"/>
+      <c r="K29" s="16"/>
+    </row>
+    <row r="30" spans="1:11" ht="16">
+      <c r="A30" s="174"/>
+      <c r="B30" s="175"/>
+      <c r="C30" s="175"/>
+      <c r="D30" s="176"/>
       <c r="F30" s="7"/>
-      <c r="J30" s="16"/>
-    </row>
-    <row r="31" spans="1:10" ht="16">
-      <c r="A31" s="184"/>
-      <c r="B31" s="185"/>
-      <c r="C31" s="185"/>
-      <c r="D31" s="186"/>
+      <c r="G30" s="207"/>
+      <c r="H30" s="207"/>
+      <c r="I30" s="207"/>
+      <c r="J30" s="207"/>
+      <c r="K30" s="16"/>
+    </row>
+    <row r="31" spans="1:11" ht="16">
+      <c r="A31" s="174"/>
+      <c r="B31" s="175"/>
+      <c r="C31" s="175"/>
+      <c r="D31" s="176"/>
       <c r="F31" s="7"/>
-      <c r="J31" s="16"/>
-    </row>
-    <row r="32" spans="1:10" ht="16">
-      <c r="A32" s="184"/>
-      <c r="B32" s="185"/>
-      <c r="C32" s="185"/>
-      <c r="D32" s="186"/>
+      <c r="G31" s="207"/>
+      <c r="H31" s="207"/>
+      <c r="I31" s="207"/>
+      <c r="J31" s="207"/>
+      <c r="K31" s="16"/>
+    </row>
+    <row r="32" spans="1:11" ht="16">
+      <c r="A32" s="174"/>
+      <c r="B32" s="175"/>
+      <c r="C32" s="175"/>
+      <c r="D32" s="176"/>
       <c r="F32" s="7"/>
-      <c r="J32" s="16"/>
-    </row>
-    <row r="33" spans="1:10" ht="16">
-      <c r="A33" s="184"/>
-      <c r="B33" s="185"/>
-      <c r="C33" s="185"/>
-      <c r="D33" s="186"/>
+      <c r="G32" s="207"/>
+      <c r="H32" s="207"/>
+      <c r="I32" s="207"/>
+      <c r="J32" s="207"/>
+      <c r="K32" s="16"/>
+    </row>
+    <row r="33" spans="1:11" ht="16">
+      <c r="A33" s="174"/>
+      <c r="B33" s="175"/>
+      <c r="C33" s="175"/>
+      <c r="D33" s="176"/>
       <c r="F33" s="7"/>
-      <c r="J33" s="16"/>
-    </row>
-    <row r="34" spans="1:10" ht="16">
-      <c r="A34" s="184"/>
-      <c r="B34" s="185"/>
-      <c r="C34" s="185"/>
-      <c r="D34" s="186"/>
+      <c r="G33" s="207"/>
+      <c r="H33" s="207"/>
+      <c r="I33" s="207"/>
+      <c r="J33" s="207"/>
+      <c r="K33" s="16"/>
+    </row>
+    <row r="34" spans="1:11" ht="16">
+      <c r="A34" s="174"/>
+      <c r="B34" s="175"/>
+      <c r="C34" s="175"/>
+      <c r="D34" s="176"/>
       <c r="F34" s="7"/>
-      <c r="J34" s="16"/>
-    </row>
-    <row r="35" spans="1:10" ht="16">
-      <c r="A35" s="184"/>
-      <c r="B35" s="185"/>
-      <c r="C35" s="185"/>
-      <c r="D35" s="186"/>
+      <c r="G34" s="207"/>
+      <c r="H34" s="207"/>
+      <c r="I34" s="207"/>
+      <c r="J34" s="207"/>
+      <c r="K34" s="16"/>
+    </row>
+    <row r="35" spans="1:11" ht="16">
+      <c r="A35" s="174"/>
+      <c r="B35" s="175"/>
+      <c r="C35" s="175"/>
+      <c r="D35" s="176"/>
       <c r="F35" s="7"/>
-      <c r="J35" s="16"/>
-    </row>
-    <row r="36" spans="1:10" ht="16">
-      <c r="A36" s="184"/>
-      <c r="B36" s="185"/>
-      <c r="C36" s="185"/>
-      <c r="D36" s="186"/>
+      <c r="G35" s="207"/>
+      <c r="H35" s="207"/>
+      <c r="I35" s="207"/>
+      <c r="J35" s="207"/>
+      <c r="K35" s="16"/>
+    </row>
+    <row r="36" spans="1:11" ht="16">
+      <c r="A36" s="174"/>
+      <c r="B36" s="175"/>
+      <c r="C36" s="175"/>
+      <c r="D36" s="176"/>
       <c r="F36" s="7"/>
-      <c r="J36" s="16"/>
-    </row>
-    <row r="37" spans="1:10" ht="16">
-      <c r="A37" s="184"/>
-      <c r="B37" s="185"/>
-      <c r="C37" s="185"/>
-      <c r="D37" s="186"/>
+      <c r="G36" s="207"/>
+      <c r="H36" s="207"/>
+      <c r="I36" s="207"/>
+      <c r="J36" s="207"/>
+      <c r="K36" s="16"/>
+    </row>
+    <row r="37" spans="1:11" ht="16">
+      <c r="A37" s="174"/>
+      <c r="B37" s="175"/>
+      <c r="C37" s="175"/>
+      <c r="D37" s="176"/>
       <c r="F37" s="7"/>
-      <c r="J37" s="16"/>
-    </row>
-    <row r="38" spans="1:10" ht="16">
-      <c r="A38" s="184"/>
-      <c r="B38" s="185"/>
-      <c r="C38" s="185"/>
-      <c r="D38" s="186"/>
+      <c r="G37" s="207"/>
+      <c r="H37" s="207"/>
+      <c r="I37" s="207"/>
+      <c r="J37" s="207"/>
+      <c r="K37" s="16"/>
+    </row>
+    <row r="38" spans="1:11" ht="16">
+      <c r="A38" s="174"/>
+      <c r="B38" s="175"/>
+      <c r="C38" s="175"/>
+      <c r="D38" s="176"/>
       <c r="F38" s="7"/>
-      <c r="J38" s="16"/>
-    </row>
-    <row r="39" spans="1:10" ht="16">
-      <c r="A39" s="184"/>
-      <c r="B39" s="185"/>
-      <c r="C39" s="185"/>
-      <c r="D39" s="186"/>
+      <c r="G38" s="207"/>
+      <c r="H38" s="207"/>
+      <c r="I38" s="207"/>
+      <c r="J38" s="207"/>
+      <c r="K38" s="16"/>
+    </row>
+    <row r="39" spans="1:11" ht="16">
+      <c r="A39" s="174"/>
+      <c r="B39" s="175"/>
+      <c r="C39" s="175"/>
+      <c r="D39" s="176"/>
       <c r="F39" s="7"/>
-      <c r="J39" s="16"/>
-    </row>
-    <row r="40" spans="1:10" ht="17" thickBot="1">
-      <c r="A40" s="196"/>
-      <c r="B40" s="197"/>
-      <c r="C40" s="197"/>
-      <c r="D40" s="198"/>
+      <c r="G39" s="207"/>
+      <c r="H39" s="207"/>
+      <c r="I39" s="207"/>
+      <c r="J39" s="207"/>
+      <c r="K39" s="16"/>
+    </row>
+    <row r="40" spans="1:11" ht="17" thickBot="1">
+      <c r="A40" s="181"/>
+      <c r="B40" s="182"/>
+      <c r="C40" s="182"/>
+      <c r="D40" s="183"/>
       <c r="F40" s="21"/>
       <c r="G40" s="22"/>
       <c r="H40" s="22"/>
       <c r="I40" s="22"/>
-      <c r="J40" s="23"/>
-    </row>
-    <row r="41" spans="1:10" ht="16">
+      <c r="J40" s="22"/>
+      <c r="K40" s="23"/>
+    </row>
+    <row r="41" spans="1:11" ht="16">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:11">
       <c r="A44" s="7"/>
     </row>
   </sheetData>
@@ -9048,9 +9684,9 @@
       <c r="D23" s="92"/>
       <c r="E23" s="92"/>
       <c r="F23" s="92"/>
-      <c r="H23" s="201"/>
-      <c r="I23" s="201"/>
-      <c r="J23" s="201"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
     </row>
     <row r="24" spans="1:11" ht="16">
       <c r="A24" s="92" t="s">
